--- a/data/catalogo_jusp.xlsx
+++ b/data/catalogo_jusp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\JUSP\jusp-app2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19EA6043-9FA2-4F6F-9D58-33943BC3F3E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCB5F206-7097-4A7E-AA7E-A1A312B757DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{9D76B832-63ED-42EE-808B-55D551049E26}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="33">
   <si>
     <t>product_slug</t>
   </si>
@@ -123,6 +123,18 @@
   </si>
   <si>
     <t>Nike Pants Purple</t>
+  </si>
+  <si>
+    <t>nike-dri-fit-quick-dry-running-compression-training-sports-tank-top-women</t>
+  </si>
+  <si>
+    <t>Nike sujetador</t>
+  </si>
+  <si>
+    <t>nike-dunk-low-retro</t>
+  </si>
+  <si>
+    <t>Nike low</t>
   </si>
 </sst>
 </file>
@@ -508,7 +520,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CD597CA-4AEE-4C4B-81F6-85992B5AE07D}">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="12.25" bestFit="1" customWidth="1"/>
@@ -749,6 +761,58 @@
         <v>23</v>
       </c>
     </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10">
+        <v>99990</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10" t="s">
+        <v>23</v>
+      </c>
+      <c r="H10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11">
+        <v>7</v>
+      </c>
+      <c r="E11">
+        <v>99990</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11" t="s">
+        <v>24</v>
+      </c>
+      <c r="H11" t="s">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/catalogo_jusp.xlsx
+++ b/data/catalogo_jusp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\JUSP\jusp-app2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCB5F206-7097-4A7E-AA7E-A1A312B757DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39C669E8-B688-4924-8082-42E655CFA9A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{9D76B832-63ED-42EE-808B-55D551049E26}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="41">
   <si>
     <t>product_slug</t>
   </si>
@@ -135,6 +135,30 @@
   </si>
   <si>
     <t>Nike low</t>
+  </si>
+  <si>
+    <t>pickup_today</t>
+  </si>
+  <si>
+    <t>express_delivery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">color </t>
+  </si>
+  <si>
+    <t>purple</t>
+  </si>
+  <si>
+    <t>black</t>
+  </si>
+  <si>
+    <t>white</t>
+  </si>
+  <si>
+    <t>pink</t>
+  </si>
+  <si>
+    <t>beige</t>
   </si>
 </sst>
 </file>
@@ -520,14 +544,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CD597CA-4AEE-4C4B-81F6-85992B5AE07D}">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.5" customWidth="1"/>
     <col min="2" max="2" width="27.08203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.58203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="14.5">
+    <row r="1" spans="1:11" ht="14.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -552,8 +578,17 @@
       <c r="H1" s="1" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -578,8 +613,17 @@
       <c r="H2" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -604,8 +648,17 @@
       <c r="H3" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -630,8 +683,17 @@
       <c r="H4" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -656,8 +718,17 @@
       <c r="H5" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -682,8 +753,17 @@
       <c r="H6" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -708,8 +788,17 @@
       <c r="H7" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -734,8 +823,17 @@
       <c r="H8" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
       <c r="A9" t="s">
         <v>27</v>
       </c>
@@ -760,8 +858,17 @@
       <c r="H9" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="10" spans="1:8">
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -786,8 +893,17 @@
       <c r="H10" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="11" spans="1:8">
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
       <c r="A11" t="s">
         <v>31</v>
       </c>
@@ -811,6 +927,15 @@
       </c>
       <c r="H11" t="s">
         <v>24</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/data/catalogo_jusp.xlsx
+++ b/data/catalogo_jusp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\JUSP\jusp-app2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39C669E8-B688-4924-8082-42E655CFA9A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27E2F9CC-CC6A-49A6-AA13-B8AADDCA687B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{9D76B832-63ED-42EE-808B-55D551049E26}"/>
   </bookViews>
@@ -122,9 +122,6 @@
     <t>nike-sports-pants-womens-purple</t>
   </si>
   <si>
-    <t>Nike Pants Purple</t>
-  </si>
-  <si>
     <t>nike-dri-fit-quick-dry-running-compression-training-sports-tank-top-women</t>
   </si>
   <si>
@@ -146,19 +143,22 @@
     <t xml:space="preserve">color </t>
   </si>
   <si>
+    <t>beige</t>
+  </si>
+  <si>
+    <t>Black</t>
+  </si>
+  <si>
+    <t>Pink</t>
+  </si>
+  <si>
+    <t>White</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nike Pants </t>
+  </si>
+  <si>
     <t>purple</t>
-  </si>
-  <si>
-    <t>black</t>
-  </si>
-  <si>
-    <t>white</t>
-  </si>
-  <si>
-    <t>pink</t>
-  </si>
-  <si>
-    <t>beige</t>
   </si>
 </sst>
 </file>
@@ -579,13 +579,13 @@
         <v>25</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -620,7 +620,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -655,7 +655,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -690,7 +690,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -725,7 +725,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -760,7 +760,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -795,7 +795,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -830,7 +830,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -838,7 +838,7 @@
         <v>27</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C9" t="s">
         <v>8</v>
@@ -865,15 +865,15 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" t="s">
         <v>29</v>
-      </c>
-      <c r="B10" t="s">
-        <v>30</v>
       </c>
       <c r="C10" t="s">
         <v>8</v>
@@ -905,10 +905,10 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" t="s">
         <v>31</v>
-      </c>
-      <c r="B11" t="s">
-        <v>32</v>
       </c>
       <c r="C11" t="s">
         <v>8</v>
@@ -935,7 +935,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/data/catalogo_jusp.xlsx
+++ b/data/catalogo_jusp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\JUSP\jusp-app2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27E2F9CC-CC6A-49A6-AA13-B8AADDCA687B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{082C9E38-E4A8-441A-857A-5F66069755A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{9D76B832-63ED-42EE-808B-55D551049E26}"/>
   </bookViews>
@@ -125,9 +125,6 @@
     <t>nike-dri-fit-quick-dry-running-compression-training-sports-tank-top-women</t>
   </si>
   <si>
-    <t>Nike sujetador</t>
-  </si>
-  <si>
     <t>nike-dunk-low-retro</t>
   </si>
   <si>
@@ -159,6 +156,9 @@
   </si>
   <si>
     <t>purple</t>
+  </si>
+  <si>
+    <t>Nike sujetador tops</t>
   </si>
 </sst>
 </file>
@@ -579,13 +579,13 @@
         <v>25</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -620,7 +620,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -655,7 +655,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -690,7 +690,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -725,7 +725,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -760,7 +760,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -795,7 +795,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -830,7 +830,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -838,7 +838,7 @@
         <v>27</v>
       </c>
       <c r="B9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C9" t="s">
         <v>8</v>
@@ -865,7 +865,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -873,7 +873,7 @@
         <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="C10" t="s">
         <v>8</v>
@@ -900,15 +900,15 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" t="s">
         <v>30</v>
-      </c>
-      <c r="B11" t="s">
-        <v>31</v>
       </c>
       <c r="C11" t="s">
         <v>8</v>
@@ -935,7 +935,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/data/catalogo_jusp.xlsx
+++ b/data/catalogo_jusp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\JUSP\jusp-app2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{082C9E38-E4A8-441A-857A-5F66069755A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCDBBC29-FC7F-4145-B33A-90D89533FC8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{9D76B832-63ED-42EE-808B-55D551049E26}"/>
   </bookViews>
@@ -672,7 +672,7 @@
         <v>13</v>
       </c>
       <c r="E4">
-        <v>69990</v>
+        <v>0</v>
       </c>
       <c r="F4">
         <v>1</v>

--- a/data/catalogo_jusp.xlsx
+++ b/data/catalogo_jusp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\JUSP\jusp-app2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCDBBC29-FC7F-4145-B33A-90D89533FC8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D664C317-9EFA-4171-931D-0A9089C77888}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{9D76B832-63ED-42EE-808B-55D551049E26}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="41">
   <si>
     <t>product_slug</t>
   </si>
@@ -672,7 +672,7 @@
         <v>13</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -707,7 +707,7 @@
         <v>14</v>
       </c>
       <c r="E5">
-        <v>79990</v>
+        <v>1</v>
       </c>
       <c r="F5">
         <v>1</v>

--- a/data/catalogo_jusp.xlsx
+++ b/data/catalogo_jusp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\JUSP\jusp-app2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D664C317-9EFA-4171-931D-0A9089C77888}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{078D7852-D18D-46F9-9085-BE8482DBAAFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{9D76B832-63ED-42EE-808B-55D551049E26}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="41">
   <si>
     <t>product_slug</t>
   </si>
@@ -672,7 +672,7 @@
         <v>13</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>89990</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -707,7 +707,7 @@
         <v>14</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>89990</v>
       </c>
       <c r="F5">
         <v>1</v>

--- a/data/catalogo_jusp.xlsx
+++ b/data/catalogo_jusp.xlsx
@@ -1,42 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
-  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\JUSP\jusp-app2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{078D7852-D18D-46F9-9085-BE8482DBAAFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{9D76B832-63ED-42EE-808B-55D551049E26}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500"/>
   </bookViews>
   <sheets>
     <sheet name="productos" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <si>
     <t>product_slug</t>
   </si>
@@ -56,6 +38,21 @@
     <t>stock</t>
   </si>
   <si>
+    <t>gender</t>
+  </si>
+  <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t>pickup_today</t>
+  </si>
+  <si>
+    <t>express_delivery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">color </t>
+  </si>
+  <si>
     <t>short-nike-kids</t>
   </si>
   <si>
@@ -68,6 +65,15 @@
     <t>XS (135)</t>
   </si>
   <si>
+    <t>kids</t>
+  </si>
+  <si>
+    <t>kisd</t>
+  </si>
+  <si>
+    <t>Black</t>
+  </si>
+  <si>
     <t>S (140)</t>
   </si>
   <si>
@@ -80,6 +86,12 @@
     <t>S</t>
   </si>
   <si>
+    <t>women</t>
+  </si>
+  <si>
+    <t>Pink</t>
+  </si>
+  <si>
     <t>M</t>
   </si>
   <si>
@@ -95,76 +107,46 @@
     <t>S/M</t>
   </si>
   <si>
+    <t>men</t>
+  </si>
+  <si>
+    <t>beige</t>
+  </si>
+  <si>
     <t>M/L</t>
   </si>
   <si>
     <t>L/XL</t>
   </si>
   <si>
-    <t>gender</t>
-  </si>
-  <si>
-    <t>kids</t>
-  </si>
-  <si>
-    <t>women</t>
-  </si>
-  <si>
-    <t>men</t>
-  </si>
-  <si>
-    <t>category</t>
-  </si>
-  <si>
-    <t>kisd</t>
-  </si>
-  <si>
     <t>nike-sports-pants-womens-purple</t>
   </si>
   <si>
+    <t xml:space="preserve">Nike Pants </t>
+  </si>
+  <si>
+    <t>purple</t>
+  </si>
+  <si>
     <t>nike-dri-fit-quick-dry-running-compression-training-sports-tank-top-women</t>
   </si>
   <si>
+    <t>Nike sujetador tops</t>
+  </si>
+  <si>
+    <t>White</t>
+  </si>
+  <si>
     <t>nike-dunk-low-retro</t>
   </si>
   <si>
     <t>Nike low</t>
-  </si>
-  <si>
-    <t>pickup_today</t>
-  </si>
-  <si>
-    <t>express_delivery</t>
-  </si>
-  <si>
-    <t xml:space="preserve">color </t>
-  </si>
-  <si>
-    <t>beige</t>
-  </si>
-  <si>
-    <t>Black</t>
-  </si>
-  <si>
-    <t>Pink</t>
-  </si>
-  <si>
-    <t>White</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nike Pants </t>
-  </si>
-  <si>
-    <t>purple</t>
-  </si>
-  <si>
-    <t>Nike sujetador tops</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -194,13 +176,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -216,14 +192,6 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -232,10 +200,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="0E2841"/>
@@ -404,6 +372,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -430,24 +399,25 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="19050" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -508,52 +478,25 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CD597CA-4AEE-4C4B-81F6-85992B5AE07D}">
-  <dimension ref="A1:K11"/>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="30.5" customWidth="1"/>
-    <col min="2" max="2" width="27.08203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.58203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.08203" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.16406" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.58203" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="14.5">
+    <row r="1" ht="14.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -573,33 +516,33 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E2">
         <v>88990</v>
@@ -608,10 +551,10 @@
         <v>1</v>
       </c>
       <c r="G2" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H2" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -620,21 +563,21 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E3">
         <v>88990</v>
@@ -643,10 +586,10 @@
         <v>1</v>
       </c>
       <c r="G3" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H3" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -655,21 +598,21 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E4">
         <v>89990</v>
@@ -678,33 +621,33 @@
         <v>1</v>
       </c>
       <c r="G4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4" t="s">
         <v>23</v>
       </c>
-      <c r="H4" t="s">
-        <v>23</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+    </row>
+    <row r="5">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E5">
         <v>89990</v>
@@ -713,45 +656,45 @@
         <v>1</v>
       </c>
       <c r="G5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5" t="s">
         <v>23</v>
       </c>
-      <c r="H5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+    </row>
+    <row r="6">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="E6">
         <v>75990</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="H6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -760,33 +703,33 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="D7" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="E7">
         <v>79990</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="H7" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -795,56 +738,56 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="D8" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="E8">
         <v>78990</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H8" t="s">
+        <v>29</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" t="s">
         <v>24</v>
-      </c>
-      <c r="H8" t="s">
-        <v>24</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="A9" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" t="s">
-        <v>14</v>
       </c>
       <c r="E9">
         <v>69990</v>
@@ -853,10 +796,10 @@
         <v>1</v>
       </c>
       <c r="G9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -865,21 +808,21 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B10" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C10" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D10" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E10">
         <v>99990</v>
@@ -888,10 +831,10 @@
         <v>1</v>
       </c>
       <c r="G10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -900,18 +843,18 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C11" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D11">
         <v>7</v>
@@ -923,10 +866,10 @@
         <v>1</v>
       </c>
       <c r="G11" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="H11" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -935,10 +878,9 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/catalogo_jusp.xlsx
+++ b/data/catalogo_jusp.xlsx
@@ -758,7 +758,7 @@
         <v>78990</v>
       </c>
       <c r="F8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G8" t="s">
         <v>29</v>

--- a/data/catalogo_jusp.xlsx
+++ b/data/catalogo_jusp.xlsx
@@ -141,6 +141,63 @@
   </si>
   <si>
     <t>Nike low</t>
+  </si>
+  <si>
+    <t>nike-sport-high</t>
+  </si>
+  <si>
+    <t>Nike Sport BH High Compression Bra Swoosh Sujetador</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>nike-unisex-dri-fit-fly-unstrukturierte-swoosh-cap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NIKE Unisex Dri-fit Fly Unstrukturierte Swoosh-Cap </t>
+  </si>
+  <si>
+    <t>Platinum violet</t>
+  </si>
+  <si>
+    <t>nike-sportswear</t>
+  </si>
+  <si>
+    <t>Nike Sportswear Women's Ribbed Tank Top</t>
+  </si>
+  <si>
+    <t>XS</t>
+  </si>
+  <si>
+    <t>XL</t>
+  </si>
+  <si>
+    <t>nike-dri-fit-pro-cropped-printed-women</t>
+  </si>
+  <si>
+    <t>NIKE Dri-FIT Pro Cropped Printed Women's Training Tank</t>
+  </si>
+  <si>
+    <t>grey</t>
+  </si>
+  <si>
+    <t>puma-622575-01</t>
+  </si>
+  <si>
+    <t>Puma Camiseta Deportiva sin Mangas Ajustada con Estampado de Letras para Mujer Negro</t>
+  </si>
+  <si>
+    <t>Puma</t>
+  </si>
+  <si>
+    <t>jordan-cw2427-360</t>
+  </si>
+  <si>
+    <t>Jordan Jumpman logo treeningjooksusport aluspesu naiste aluspesu roheline</t>
+  </si>
+  <si>
+    <t>phosphorescent green</t>
   </si>
 </sst>
 </file>
@@ -181,11 +238,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -881,6 +939,566 @@
         <v>30</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" t="s">
+        <v>43</v>
+      </c>
+      <c r="E12" s="2">
+        <v>119990</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12" t="s">
+        <v>22</v>
+      </c>
+      <c r="H12" t="s">
+        <v>22</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13">
+        <v>65990</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13" t="s">
+        <v>29</v>
+      </c>
+      <c r="H13" t="s">
+        <v>29</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14">
+        <v>75990</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14" t="s">
+        <v>29</v>
+      </c>
+      <c r="H14" t="s">
+        <v>29</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" t="s">
+        <v>32</v>
+      </c>
+      <c r="E15">
+        <v>85990</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15" t="s">
+        <v>29</v>
+      </c>
+      <c r="H15" t="s">
+        <v>29</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" t="s">
+        <v>49</v>
+      </c>
+      <c r="E16">
+        <v>79990</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H16" t="s">
+        <v>22</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" t="s">
+        <v>21</v>
+      </c>
+      <c r="E17">
+        <v>79990</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H17" t="s">
+        <v>22</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E18">
+        <v>79990</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18" t="s">
+        <v>22</v>
+      </c>
+      <c r="H18" t="s">
+        <v>22</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>47</v>
+      </c>
+      <c r="B19" t="s">
+        <v>48</v>
+      </c>
+      <c r="C19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19" t="s">
+        <v>43</v>
+      </c>
+      <c r="E19">
+        <v>79990</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19" t="s">
+        <v>22</v>
+      </c>
+      <c r="H19" t="s">
+        <v>22</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" t="s">
+        <v>48</v>
+      </c>
+      <c r="C20" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" t="s">
+        <v>50</v>
+      </c>
+      <c r="E20">
+        <v>79990</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+      <c r="G20" t="s">
+        <v>22</v>
+      </c>
+      <c r="H20" t="s">
+        <v>22</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>51</v>
+      </c>
+      <c r="B21" t="s">
+        <v>52</v>
+      </c>
+      <c r="C21" t="s">
+        <v>13</v>
+      </c>
+      <c r="D21" t="s">
+        <v>21</v>
+      </c>
+      <c r="E21">
+        <v>155990</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+      <c r="G21" t="s">
+        <v>22</v>
+      </c>
+      <c r="H21" t="s">
+        <v>22</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>51</v>
+      </c>
+      <c r="B22" t="s">
+        <v>52</v>
+      </c>
+      <c r="C22" t="s">
+        <v>13</v>
+      </c>
+      <c r="D22" t="s">
+        <v>24</v>
+      </c>
+      <c r="E22">
+        <v>155990</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22" t="s">
+        <v>22</v>
+      </c>
+      <c r="H22" t="s">
+        <v>22</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>51</v>
+      </c>
+      <c r="B23" t="s">
+        <v>52</v>
+      </c>
+      <c r="C23" t="s">
+        <v>13</v>
+      </c>
+      <c r="D23" t="s">
+        <v>43</v>
+      </c>
+      <c r="E23">
+        <v>155990</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23" t="s">
+        <v>22</v>
+      </c>
+      <c r="H23" t="s">
+        <v>22</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>51</v>
+      </c>
+      <c r="B24" t="s">
+        <v>52</v>
+      </c>
+      <c r="C24" t="s">
+        <v>13</v>
+      </c>
+      <c r="D24" t="s">
+        <v>50</v>
+      </c>
+      <c r="E24">
+        <v>155990</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="G24" t="s">
+        <v>22</v>
+      </c>
+      <c r="H24" t="s">
+        <v>22</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>54</v>
+      </c>
+      <c r="B25" t="s">
+        <v>55</v>
+      </c>
+      <c r="C25" t="s">
+        <v>56</v>
+      </c>
+      <c r="D25" t="s">
+        <v>21</v>
+      </c>
+      <c r="E25">
+        <v>49990</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+      <c r="G25" t="s">
+        <v>22</v>
+      </c>
+      <c r="H25" t="s">
+        <v>22</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>54</v>
+      </c>
+      <c r="B26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C26" t="s">
+        <v>56</v>
+      </c>
+      <c r="D26" t="s">
+        <v>24</v>
+      </c>
+      <c r="E26">
+        <v>49990</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+      <c r="G26" t="s">
+        <v>22</v>
+      </c>
+      <c r="H26" t="s">
+        <v>22</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>57</v>
+      </c>
+      <c r="B27" t="s">
+        <v>58</v>
+      </c>
+      <c r="C27" t="s">
+        <v>27</v>
+      </c>
+      <c r="D27" t="s">
+        <v>24</v>
+      </c>
+      <c r="E27">
+        <v>125990</v>
+      </c>
+      <c r="F27">
+        <v>1</v>
+      </c>
+      <c r="G27" t="s">
+        <v>22</v>
+      </c>
+      <c r="H27" t="s">
+        <v>22</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27" t="s">
+        <v>59</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/data/catalogo_jusp.xlsx
+++ b/data/catalogo_jusp.xlsx
@@ -198,6 +198,15 @@
   </si>
   <si>
     <t>phosphorescent green</t>
+  </si>
+  <si>
+    <t>nike-hq5684-345</t>
+  </si>
+  <si>
+    <t>NIKE Dri-FIT Pro Cropped Printed Women</t>
+  </si>
+  <si>
+    <t>Blue</t>
   </si>
 </sst>
 </file>
@@ -1499,6 +1508,111 @@
         <v>59</v>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>60</v>
+      </c>
+      <c r="B28" t="s">
+        <v>61</v>
+      </c>
+      <c r="C28" t="s">
+        <v>13</v>
+      </c>
+      <c r="D28" t="s">
+        <v>21</v>
+      </c>
+      <c r="E28">
+        <v>155990</v>
+      </c>
+      <c r="F28">
+        <v>1</v>
+      </c>
+      <c r="G28" t="s">
+        <v>22</v>
+      </c>
+      <c r="H28" t="s">
+        <v>22</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>60</v>
+      </c>
+      <c r="B29" t="s">
+        <v>61</v>
+      </c>
+      <c r="C29" t="s">
+        <v>13</v>
+      </c>
+      <c r="D29" t="s">
+        <v>43</v>
+      </c>
+      <c r="E29">
+        <v>155990</v>
+      </c>
+      <c r="F29">
+        <v>1</v>
+      </c>
+      <c r="G29" t="s">
+        <v>22</v>
+      </c>
+      <c r="H29" t="s">
+        <v>22</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>60</v>
+      </c>
+      <c r="B30" t="s">
+        <v>61</v>
+      </c>
+      <c r="C30" t="s">
+        <v>13</v>
+      </c>
+      <c r="D30" t="s">
+        <v>50</v>
+      </c>
+      <c r="E30">
+        <v>155990</v>
+      </c>
+      <c r="F30">
+        <v>1</v>
+      </c>
+      <c r="G30" t="s">
+        <v>22</v>
+      </c>
+      <c r="H30" t="s">
+        <v>22</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30" t="s">
+        <v>62</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/data/catalogo_jusp.xlsx
+++ b/data/catalogo_jusp.xlsx
@@ -207,6 +207,15 @@
   </si>
   <si>
     <t>Blue</t>
+  </si>
+  <si>
+    <t>nike-im9607-010</t>
+  </si>
+  <si>
+    <t>Gorra de golf sin estructura</t>
+  </si>
+  <si>
+    <t>unisex</t>
   </si>
 </sst>
 </file>
@@ -1613,6 +1622,76 @@
         <v>62</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>63</v>
+      </c>
+      <c r="B31" t="s">
+        <v>64</v>
+      </c>
+      <c r="C31" t="s">
+        <v>13</v>
+      </c>
+      <c r="D31" t="s">
+        <v>31</v>
+      </c>
+      <c r="E31">
+        <v>129990</v>
+      </c>
+      <c r="F31">
+        <v>1</v>
+      </c>
+      <c r="G31" t="s">
+        <v>65</v>
+      </c>
+      <c r="H31" t="s">
+        <v>65</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>63</v>
+      </c>
+      <c r="B32" t="s">
+        <v>64</v>
+      </c>
+      <c r="C32" t="s">
+        <v>13</v>
+      </c>
+      <c r="D32" t="s">
+        <v>32</v>
+      </c>
+      <c r="E32">
+        <v>129990</v>
+      </c>
+      <c r="F32">
+        <v>1</v>
+      </c>
+      <c r="G32" t="s">
+        <v>65</v>
+      </c>
+      <c r="H32" t="s">
+        <v>65</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32" t="s">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/data/catalogo_jusp.xlsx
+++ b/data/catalogo_jusp.xlsx
@@ -158,7 +158,7 @@
     <t xml:space="preserve">NIKE Unisex Dri-fit Fly Unstrukturierte Swoosh-Cap </t>
   </si>
   <si>
-    <t>Platinum violet</t>
+    <t>violet</t>
   </si>
   <si>
     <t>nike-sportswear</t>
@@ -197,7 +197,7 @@
     <t>Jordan Jumpman logo treeningjooksusport aluspesu naiste aluspesu roheline</t>
   </si>
   <si>
-    <t>phosphorescent green</t>
+    <t>green</t>
   </si>
   <si>
     <t>nike-hq5684-345</t>

--- a/data/catalogo_jusp.xlsx
+++ b/data/catalogo_jusp.xlsx
@@ -216,6 +216,18 @@
   </si>
   <si>
     <t>unisex</t>
+  </si>
+  <si>
+    <t>lacoste-rk5398</t>
+  </si>
+  <si>
+    <t>Unisex Microfiber Sport Cap</t>
+  </si>
+  <si>
+    <t>Lacoste</t>
+  </si>
+  <si>
+    <t>Ajustable</t>
   </si>
 </sst>
 </file>
@@ -1692,6 +1704,41 @@
         <v>17</v>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>66</v>
+      </c>
+      <c r="B33" t="s">
+        <v>67</v>
+      </c>
+      <c r="C33" t="s">
+        <v>68</v>
+      </c>
+      <c r="D33" t="s">
+        <v>69</v>
+      </c>
+      <c r="E33">
+        <v>175990</v>
+      </c>
+      <c r="F33">
+        <v>1</v>
+      </c>
+      <c r="G33" t="s">
+        <v>65</v>
+      </c>
+      <c r="H33" t="s">
+        <v>65</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33" t="s">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/data/catalogo_jusp.xlsx
+++ b/data/catalogo_jusp.xlsx
@@ -194,7 +194,7 @@
     <t>jordan-cw2427-360</t>
   </si>
   <si>
-    <t>Jordan Jumpman logo treeningjooksusport aluspesu naiste aluspesu roheline</t>
+    <t xml:space="preserve">Jordan Jumpman </t>
   </si>
   <si>
     <t>green</t>
@@ -1718,7 +1718,7 @@
         <v>69</v>
       </c>
       <c r="E33">
-        <v>175990</v>
+        <v>179990</v>
       </c>
       <c r="F33">
         <v>1</v>

--- a/data/catalogo_jusp.xlsx
+++ b/data/catalogo_jusp.xlsx
@@ -228,6 +228,12 @@
   </si>
   <si>
     <t>Ajustable</t>
+  </si>
+  <si>
+    <t>nike-iq4185-010</t>
+  </si>
+  <si>
+    <t>Nike Fly Unstructured Cap</t>
   </si>
 </sst>
 </file>
@@ -1739,6 +1745,42 @@
         <v>17</v>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>70</v>
+      </c>
+      <c r="B34" t="s">
+        <v>71</v>
+      </c>
+      <c r="C34" t="s">
+        <v>13</v>
+      </c>
+      <c r="D34" t="s">
+        <v>69</v>
+      </c>
+      <c r="E34">
+        <v>159990</v>
+      </c>
+      <c r="F34">
+        <v>1</v>
+      </c>
+      <c r="G34" t="s">
+        <v>65</v>
+      </c>
+      <c r="H34" t="s">
+        <v>65</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34" t="s">
+        <v>17</v>
+      </c>
+      <c r="L34"/>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/data/catalogo_jusp.xlsx
+++ b/data/catalogo_jusp.xlsx
@@ -234,6 +234,12 @@
   </si>
   <si>
     <t>Nike Fly Unstructured Cap</t>
+  </si>
+  <si>
+    <t>nike-ih9258-010</t>
+  </si>
+  <si>
+    <t>Nike Club Cap</t>
   </si>
 </sst>
 </file>
@@ -1781,6 +1787,111 @@
       </c>
       <c r="L34"/>
     </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>72</v>
+      </c>
+      <c r="B35" t="s">
+        <v>73</v>
+      </c>
+      <c r="C35" t="s">
+        <v>13</v>
+      </c>
+      <c r="D35" t="s">
+        <v>28</v>
+      </c>
+      <c r="E35">
+        <v>134990</v>
+      </c>
+      <c r="F35">
+        <v>1</v>
+      </c>
+      <c r="G35" t="s">
+        <v>65</v>
+      </c>
+      <c r="H35" t="s">
+        <v>65</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>72</v>
+      </c>
+      <c r="B36" t="s">
+        <v>73</v>
+      </c>
+      <c r="C36" t="s">
+        <v>13</v>
+      </c>
+      <c r="D36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E36">
+        <v>134990</v>
+      </c>
+      <c r="F36">
+        <v>1</v>
+      </c>
+      <c r="G36" t="s">
+        <v>65</v>
+      </c>
+      <c r="H36" t="s">
+        <v>65</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>72</v>
+      </c>
+      <c r="B37" t="s">
+        <v>73</v>
+      </c>
+      <c r="C37" t="s">
+        <v>13</v>
+      </c>
+      <c r="D37" t="s">
+        <v>32</v>
+      </c>
+      <c r="E37">
+        <v>134990</v>
+      </c>
+      <c r="F37">
+        <v>1</v>
+      </c>
+      <c r="G37" t="s">
+        <v>65</v>
+      </c>
+      <c r="H37" t="s">
+        <v>65</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37" t="s">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/data/catalogo_jusp.xlsx
+++ b/data/catalogo_jusp.xlsx
@@ -240,6 +240,24 @@
   </si>
   <si>
     <t>Nike Club Cap</t>
+  </si>
+  <si>
+    <t>nike-if1805-010</t>
+  </si>
+  <si>
+    <t>Nike Dri-FIT Ace Kids' Swoosh Visor</t>
+  </si>
+  <si>
+    <t>Unica</t>
+  </si>
+  <si>
+    <t>Kisd</t>
+  </si>
+  <si>
+    <t>NIKE AIR JORDAN OVERSIZED T</t>
+  </si>
+  <si>
+    <t>XXL</t>
   </si>
 </sst>
 </file>
@@ -1892,6 +1910,216 @@
         <v>17</v>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>74</v>
+      </c>
+      <c r="B38" t="s">
+        <v>75</v>
+      </c>
+      <c r="C38" t="s">
+        <v>13</v>
+      </c>
+      <c r="D38" t="s">
+        <v>76</v>
+      </c>
+      <c r="E38">
+        <v>79990</v>
+      </c>
+      <c r="F38">
+        <v>1</v>
+      </c>
+      <c r="G38" t="s">
+        <v>77</v>
+      </c>
+      <c r="H38" t="s">
+        <v>77</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>74</v>
+      </c>
+      <c r="B39" t="s">
+        <v>78</v>
+      </c>
+      <c r="C39" t="s">
+        <v>13</v>
+      </c>
+      <c r="D39" t="s">
+        <v>21</v>
+      </c>
+      <c r="E39">
+        <v>134990</v>
+      </c>
+      <c r="F39">
+        <v>1</v>
+      </c>
+      <c r="G39" t="s">
+        <v>29</v>
+      </c>
+      <c r="H39" t="s">
+        <v>29</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>74</v>
+      </c>
+      <c r="B40" t="s">
+        <v>78</v>
+      </c>
+      <c r="C40" t="s">
+        <v>27</v>
+      </c>
+      <c r="D40" t="s">
+        <v>24</v>
+      </c>
+      <c r="E40">
+        <v>134990</v>
+      </c>
+      <c r="F40">
+        <v>1</v>
+      </c>
+      <c r="G40" t="s">
+        <v>29</v>
+      </c>
+      <c r="H40" t="s">
+        <v>29</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>74</v>
+      </c>
+      <c r="B41" t="s">
+        <v>78</v>
+      </c>
+      <c r="C41" t="s">
+        <v>27</v>
+      </c>
+      <c r="D41" t="s">
+        <v>43</v>
+      </c>
+      <c r="E41">
+        <v>134990</v>
+      </c>
+      <c r="F41">
+        <v>1</v>
+      </c>
+      <c r="G41" t="s">
+        <v>29</v>
+      </c>
+      <c r="H41" t="s">
+        <v>29</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>74</v>
+      </c>
+      <c r="B42" t="s">
+        <v>78</v>
+      </c>
+      <c r="C42" t="s">
+        <v>27</v>
+      </c>
+      <c r="D42" t="s">
+        <v>50</v>
+      </c>
+      <c r="E42">
+        <v>134990</v>
+      </c>
+      <c r="F42">
+        <v>1</v>
+      </c>
+      <c r="G42" t="s">
+        <v>29</v>
+      </c>
+      <c r="H42" t="s">
+        <v>29</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>74</v>
+      </c>
+      <c r="B43" t="s">
+        <v>78</v>
+      </c>
+      <c r="C43" t="s">
+        <v>27</v>
+      </c>
+      <c r="D43" t="s">
+        <v>79</v>
+      </c>
+      <c r="E43">
+        <v>134990</v>
+      </c>
+      <c r="F43">
+        <v>1</v>
+      </c>
+      <c r="G43" t="s">
+        <v>29</v>
+      </c>
+      <c r="H43" t="s">
+        <v>29</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43" t="s">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/data/catalogo_jusp.xlsx
+++ b/data/catalogo_jusp.xlsx
@@ -242,16 +242,19 @@
     <t>Nike Club Cap</t>
   </si>
   <si>
+    <t>nike-fb5061-010</t>
+  </si>
+  <si>
+    <t>Nike Dri-FIT Ace Kids' Swoosh Visor</t>
+  </si>
+  <si>
+    <t>Unica</t>
+  </si>
+  <si>
+    <t>Kisd</t>
+  </si>
+  <si>
     <t>nike-if1805-010</t>
-  </si>
-  <si>
-    <t>Nike Dri-FIT Ace Kids' Swoosh Visor</t>
-  </si>
-  <si>
-    <t>Unica</t>
-  </si>
-  <si>
-    <t>Kisd</t>
   </si>
   <si>
     <t>NIKE AIR JORDAN OVERSIZED T</t>
@@ -1947,10 +1950,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B39" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C39" t="s">
         <v>13</v>
@@ -1982,10 +1985,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B40" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C40" t="s">
         <v>27</v>
@@ -2017,10 +2020,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B41" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C41" t="s">
         <v>27</v>
@@ -2052,10 +2055,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B42" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C42" t="s">
         <v>27</v>
@@ -2087,16 +2090,16 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B43" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C43" t="s">
         <v>27</v>
       </c>
       <c r="D43" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E43">
         <v>134990</v>

--- a/data/catalogo_jusp.xlsx
+++ b/data/catalogo_jusp.xlsx
@@ -261,6 +261,21 @@
   </si>
   <si>
     <t>XXL</t>
+  </si>
+  <si>
+    <t>jordan-jd2413048AD-001</t>
+  </si>
+  <si>
+    <t>Bóxer Nike Jordan Flight</t>
+  </si>
+  <si>
+    <t>jordan-jd2413048AD-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bóxer Nike Jordan </t>
+  </si>
+  <si>
+    <t>white</t>
   </si>
 </sst>
 </file>
@@ -1806,7 +1821,6 @@
       <c r="K34" t="s">
         <v>17</v>
       </c>
-      <c r="L34"/>
     </row>
     <row r="35">
       <c r="A35" t="s">
@@ -2123,6 +2137,181 @@
         <v>17</v>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>81</v>
+      </c>
+      <c r="B44" t="s">
+        <v>82</v>
+      </c>
+      <c r="C44" t="s">
+        <v>27</v>
+      </c>
+      <c r="D44" t="s">
+        <v>21</v>
+      </c>
+      <c r="E44">
+        <v>119990</v>
+      </c>
+      <c r="F44">
+        <v>1</v>
+      </c>
+      <c r="G44" t="s">
+        <v>29</v>
+      </c>
+      <c r="H44" t="s">
+        <v>29</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>81</v>
+      </c>
+      <c r="B45" t="s">
+        <v>82</v>
+      </c>
+      <c r="C45" t="s">
+        <v>27</v>
+      </c>
+      <c r="D45" t="s">
+        <v>24</v>
+      </c>
+      <c r="E45">
+        <v>119990</v>
+      </c>
+      <c r="F45">
+        <v>1</v>
+      </c>
+      <c r="G45" t="s">
+        <v>29</v>
+      </c>
+      <c r="H45" t="s">
+        <v>29</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>81</v>
+      </c>
+      <c r="B46" t="s">
+        <v>82</v>
+      </c>
+      <c r="C46" t="s">
+        <v>27</v>
+      </c>
+      <c r="D46" t="s">
+        <v>43</v>
+      </c>
+      <c r="E46">
+        <v>119990</v>
+      </c>
+      <c r="F46">
+        <v>1</v>
+      </c>
+      <c r="G46" t="s">
+        <v>29</v>
+      </c>
+      <c r="H46" t="s">
+        <v>29</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>83</v>
+      </c>
+      <c r="B47" t="s">
+        <v>84</v>
+      </c>
+      <c r="C47" t="s">
+        <v>27</v>
+      </c>
+      <c r="D47" t="s">
+        <v>24</v>
+      </c>
+      <c r="E47">
+        <v>119990</v>
+      </c>
+      <c r="F47">
+        <v>1</v>
+      </c>
+      <c r="G47" t="s">
+        <v>29</v>
+      </c>
+      <c r="H47" t="s">
+        <v>29</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>83</v>
+      </c>
+      <c r="B48" t="s">
+        <v>84</v>
+      </c>
+      <c r="C48" t="s">
+        <v>27</v>
+      </c>
+      <c r="D48" t="s">
+        <v>43</v>
+      </c>
+      <c r="E48">
+        <v>119990</v>
+      </c>
+      <c r="F48">
+        <v>1</v>
+      </c>
+      <c r="G48" t="s">
+        <v>29</v>
+      </c>
+      <c r="H48" t="s">
+        <v>29</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48" t="s">
+        <v>85</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/data/catalogo_jusp.xlsx
+++ b/data/catalogo_jusp.xlsx
@@ -267,6 +267,9 @@
   </si>
   <si>
     <t>Bóxer Nike Jordan Flight</t>
+  </si>
+  <si>
+    <t>accessories</t>
   </si>
   <si>
     <t>jordan-jd2413048AD-002</t>
@@ -2160,7 +2163,7 @@
         <v>29</v>
       </c>
       <c r="H44" t="s">
-        <v>29</v>
+        <v>83</v>
       </c>
       <c r="I44">
         <v>0</v>
@@ -2195,7 +2198,7 @@
         <v>29</v>
       </c>
       <c r="H45" t="s">
-        <v>29</v>
+        <v>83</v>
       </c>
       <c r="I45">
         <v>0</v>
@@ -2230,7 +2233,7 @@
         <v>29</v>
       </c>
       <c r="H46" t="s">
-        <v>29</v>
+        <v>83</v>
       </c>
       <c r="I46">
         <v>0</v>
@@ -2244,10 +2247,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B47" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C47" t="s">
         <v>27</v>
@@ -2265,7 +2268,7 @@
         <v>29</v>
       </c>
       <c r="H47" t="s">
-        <v>29</v>
+        <v>83</v>
       </c>
       <c r="I47">
         <v>0</v>
@@ -2274,15 +2277,15 @@
         <v>0</v>
       </c>
       <c r="K47" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B48" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C48" t="s">
         <v>27</v>
@@ -2300,7 +2303,7 @@
         <v>29</v>
       </c>
       <c r="H48" t="s">
-        <v>29</v>
+        <v>83</v>
       </c>
       <c r="I48">
         <v>0</v>
@@ -2309,7 +2312,7 @@
         <v>0</v>
       </c>
       <c r="K48" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/data/catalogo_jusp.xlsx
+++ b/data/catalogo_jusp.xlsx
@@ -276,6 +276,9 @@
   </si>
   <si>
     <t xml:space="preserve">Bóxer Nike Jordan </t>
+  </si>
+  <si>
+    <t>Boxers</t>
   </si>
   <si>
     <t>white</t>
@@ -2268,7 +2271,7 @@
         <v>29</v>
       </c>
       <c r="H47" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="I47">
         <v>0</v>
@@ -2277,7 +2280,7 @@
         <v>0</v>
       </c>
       <c r="K47" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="48">
@@ -2303,7 +2306,7 @@
         <v>29</v>
       </c>
       <c r="H48" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="I48">
         <v>0</v>
@@ -2312,7 +2315,7 @@
         <v>0</v>
       </c>
       <c r="K48" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>

--- a/data/catalogo_jusp.xlsx
+++ b/data/catalogo_jusp.xlsx
@@ -276,9 +276,6 @@
   </si>
   <si>
     <t xml:space="preserve">Bóxer Nike Jordan </t>
-  </si>
-  <si>
-    <t>Boxers</t>
   </si>
   <si>
     <t>white</t>
@@ -2271,16 +2268,16 @@
         <v>29</v>
       </c>
       <c r="H47" t="s">
+        <v>83</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47" t="s">
         <v>86</v>
-      </c>
-      <c r="I47">
-        <v>0</v>
-      </c>
-      <c r="J47">
-        <v>0</v>
-      </c>
-      <c r="K47" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="48">
@@ -2306,16 +2303,16 @@
         <v>29</v>
       </c>
       <c r="H48" t="s">
+        <v>83</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48" t="s">
         <v>86</v>
-      </c>
-      <c r="I48">
-        <v>0</v>
-      </c>
-      <c r="J48">
-        <v>0</v>
-      </c>
-      <c r="K48" t="s">
-        <v>87</v>
       </c>
     </row>
   </sheetData>

--- a/data/catalogo_jusp.xlsx
+++ b/data/catalogo_jusp.xlsx
@@ -279,6 +279,18 @@
   </si>
   <si>
     <t>white</t>
+  </si>
+  <si>
+    <t>jordan-ac4142-010</t>
+  </si>
+  <si>
+    <t>Jordan Mangas de baloncesto UV</t>
+  </si>
+  <si>
+    <t>jordan-ac4142-010 W</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jordan Mangas de baloncesto </t>
   </si>
 </sst>
 </file>
@@ -2315,6 +2327,111 @@
         <v>86</v>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>87</v>
+      </c>
+      <c r="B49" t="s">
+        <v>88</v>
+      </c>
+      <c r="C49" t="s">
+        <v>27</v>
+      </c>
+      <c r="D49" t="s">
+        <v>28</v>
+      </c>
+      <c r="E49">
+        <v>39990</v>
+      </c>
+      <c r="F49">
+        <v>1</v>
+      </c>
+      <c r="G49" t="s">
+        <v>29</v>
+      </c>
+      <c r="H49" t="s">
+        <v>83</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>87</v>
+      </c>
+      <c r="B50" t="s">
+        <v>88</v>
+      </c>
+      <c r="C50" t="s">
+        <v>27</v>
+      </c>
+      <c r="D50" t="s">
+        <v>32</v>
+      </c>
+      <c r="E50">
+        <v>39990</v>
+      </c>
+      <c r="F50">
+        <v>1</v>
+      </c>
+      <c r="G50" t="s">
+        <v>29</v>
+      </c>
+      <c r="H50" t="s">
+        <v>83</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>89</v>
+      </c>
+      <c r="B51" t="s">
+        <v>90</v>
+      </c>
+      <c r="C51" t="s">
+        <v>27</v>
+      </c>
+      <c r="D51" t="s">
+        <v>32</v>
+      </c>
+      <c r="E51">
+        <v>39990</v>
+      </c>
+      <c r="F51">
+        <v>1</v>
+      </c>
+      <c r="G51" t="s">
+        <v>29</v>
+      </c>
+      <c r="H51" t="s">
+        <v>83</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="K51" t="s">
+        <v>86</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/data/catalogo_jusp.xlsx
+++ b/data/catalogo_jusp.xlsx
@@ -1014,7 +1014,7 @@
         <v>99990</v>
       </c>
       <c r="F11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" t="s">
         <v>29</v>

--- a/data/catalogo_jusp.xlsx
+++ b/data/catalogo_jusp.xlsx
@@ -291,6 +291,18 @@
   </si>
   <si>
     <t xml:space="preserve">Jordan Mangas de baloncesto </t>
+  </si>
+  <si>
+    <t>lacoste-rk0527</t>
+  </si>
+  <si>
+    <t>Gorra de béisbol unisex Lacoste de otoño con visera plana</t>
+  </si>
+  <si>
+    <t>M(56-58cm)</t>
+  </si>
+  <si>
+    <t>L(58-60cm)</t>
   </si>
 </sst>
 </file>
@@ -2432,6 +2444,76 @@
         <v>86</v>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>91</v>
+      </c>
+      <c r="B52" t="s">
+        <v>92</v>
+      </c>
+      <c r="C52" t="s">
+        <v>68</v>
+      </c>
+      <c r="D52" t="s">
+        <v>93</v>
+      </c>
+      <c r="E52">
+        <v>140990</v>
+      </c>
+      <c r="F52">
+        <v>1</v>
+      </c>
+      <c r="G52" t="s">
+        <v>65</v>
+      </c>
+      <c r="H52" t="s">
+        <v>83</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>0</v>
+      </c>
+      <c r="K52" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>91</v>
+      </c>
+      <c r="B53" t="s">
+        <v>92</v>
+      </c>
+      <c r="C53" t="s">
+        <v>68</v>
+      </c>
+      <c r="D53" t="s">
+        <v>94</v>
+      </c>
+      <c r="E53">
+        <v>145990</v>
+      </c>
+      <c r="F53">
+        <v>1</v>
+      </c>
+      <c r="G53" t="s">
+        <v>65</v>
+      </c>
+      <c r="H53" t="s">
+        <v>83</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>0</v>
+      </c>
+      <c r="K53" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/data/catalogo_jusp.xlsx
+++ b/data/catalogo_jusp.xlsx
@@ -303,6 +303,45 @@
   </si>
   <si>
     <t>L(58-60cm)</t>
+  </si>
+  <si>
+    <t>nike-ii0682-121</t>
+  </si>
+  <si>
+    <t>Nike Sportswear Polera para hombre</t>
+  </si>
+  <si>
+    <t>nike-if0787-010</t>
+  </si>
+  <si>
+    <t>NIKE AS M J NC GOAT SS CREW</t>
+  </si>
+  <si>
+    <t>nike-hv0885-133</t>
+  </si>
+  <si>
+    <t>Nike Life Men's Heavyweight Polo</t>
+  </si>
+  <si>
+    <t>Khaki</t>
+  </si>
+  <si>
+    <t>nike-if5172-100</t>
+  </si>
+  <si>
+    <t>Nike Kobe Dri-Fit T-Shirt 'All-Star</t>
+  </si>
+  <si>
+    <t>jordan-fn5841-010</t>
+  </si>
+  <si>
+    <t>Nike As M J Df Sprt Woven Pant</t>
+  </si>
+  <si>
+    <t>nike-dx6822-494</t>
+  </si>
+  <si>
+    <t>Nike Swoosh Medium Support Women's Padded Sports Bra</t>
   </si>
 </sst>
 </file>
@@ -2514,6 +2553,811 @@
         <v>30</v>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>95</v>
+      </c>
+      <c r="B54" t="s">
+        <v>96</v>
+      </c>
+      <c r="C54" t="s">
+        <v>13</v>
+      </c>
+      <c r="D54" t="s">
+        <v>21</v>
+      </c>
+      <c r="E54" s="2">
+        <v>199990</v>
+      </c>
+      <c r="F54">
+        <v>1</v>
+      </c>
+      <c r="G54" t="s">
+        <v>29</v>
+      </c>
+      <c r="H54" t="s">
+        <v>29</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>0</v>
+      </c>
+      <c r="K54" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>95</v>
+      </c>
+      <c r="B55" t="s">
+        <v>96</v>
+      </c>
+      <c r="C55" t="s">
+        <v>13</v>
+      </c>
+      <c r="D55" t="s">
+        <v>24</v>
+      </c>
+      <c r="E55" s="2">
+        <v>199990</v>
+      </c>
+      <c r="F55">
+        <v>1</v>
+      </c>
+      <c r="G55" t="s">
+        <v>29</v>
+      </c>
+      <c r="H55" t="s">
+        <v>29</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>0</v>
+      </c>
+      <c r="K55" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>95</v>
+      </c>
+      <c r="B56" t="s">
+        <v>96</v>
+      </c>
+      <c r="C56" t="s">
+        <v>13</v>
+      </c>
+      <c r="D56" t="s">
+        <v>43</v>
+      </c>
+      <c r="E56" s="2">
+        <v>199990</v>
+      </c>
+      <c r="F56">
+        <v>1</v>
+      </c>
+      <c r="G56" t="s">
+        <v>29</v>
+      </c>
+      <c r="H56" t="s">
+        <v>29</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>0</v>
+      </c>
+      <c r="K56" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>95</v>
+      </c>
+      <c r="B57" t="s">
+        <v>96</v>
+      </c>
+      <c r="C57" t="s">
+        <v>13</v>
+      </c>
+      <c r="D57" t="s">
+        <v>50</v>
+      </c>
+      <c r="E57" s="2">
+        <v>199990</v>
+      </c>
+      <c r="F57">
+        <v>1</v>
+      </c>
+      <c r="G57" t="s">
+        <v>29</v>
+      </c>
+      <c r="H57" t="s">
+        <v>29</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>0</v>
+      </c>
+      <c r="K57" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>95</v>
+      </c>
+      <c r="B58" t="s">
+        <v>96</v>
+      </c>
+      <c r="C58" t="s">
+        <v>13</v>
+      </c>
+      <c r="D58" t="s">
+        <v>80</v>
+      </c>
+      <c r="E58" s="2">
+        <v>199990</v>
+      </c>
+      <c r="F58">
+        <v>1</v>
+      </c>
+      <c r="G58" t="s">
+        <v>29</v>
+      </c>
+      <c r="H58" t="s">
+        <v>29</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>0</v>
+      </c>
+      <c r="K58" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>97</v>
+      </c>
+      <c r="B59" t="s">
+        <v>98</v>
+      </c>
+      <c r="C59" t="s">
+        <v>27</v>
+      </c>
+      <c r="D59" t="s">
+        <v>21</v>
+      </c>
+      <c r="E59">
+        <v>155990</v>
+      </c>
+      <c r="F59">
+        <v>1</v>
+      </c>
+      <c r="G59" t="s">
+        <v>29</v>
+      </c>
+      <c r="H59" t="s">
+        <v>29</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>0</v>
+      </c>
+      <c r="K59" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>97</v>
+      </c>
+      <c r="B60" t="s">
+        <v>98</v>
+      </c>
+      <c r="C60" t="s">
+        <v>27</v>
+      </c>
+      <c r="D60" t="s">
+        <v>24</v>
+      </c>
+      <c r="E60">
+        <v>155990</v>
+      </c>
+      <c r="F60">
+        <v>1</v>
+      </c>
+      <c r="G60" t="s">
+        <v>29</v>
+      </c>
+      <c r="H60" t="s">
+        <v>29</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>0</v>
+      </c>
+      <c r="K60" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>97</v>
+      </c>
+      <c r="B61" t="s">
+        <v>98</v>
+      </c>
+      <c r="C61" t="s">
+        <v>27</v>
+      </c>
+      <c r="D61" t="s">
+        <v>43</v>
+      </c>
+      <c r="E61">
+        <v>155990</v>
+      </c>
+      <c r="F61">
+        <v>1</v>
+      </c>
+      <c r="G61" t="s">
+        <v>29</v>
+      </c>
+      <c r="H61" t="s">
+        <v>29</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>0</v>
+      </c>
+      <c r="K61" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>97</v>
+      </c>
+      <c r="B62" t="s">
+        <v>98</v>
+      </c>
+      <c r="C62" t="s">
+        <v>27</v>
+      </c>
+      <c r="D62" t="s">
+        <v>50</v>
+      </c>
+      <c r="E62">
+        <v>155990</v>
+      </c>
+      <c r="F62">
+        <v>1</v>
+      </c>
+      <c r="G62" t="s">
+        <v>29</v>
+      </c>
+      <c r="H62" t="s">
+        <v>29</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>0</v>
+      </c>
+      <c r="K62" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>99</v>
+      </c>
+      <c r="B63" t="s">
+        <v>100</v>
+      </c>
+      <c r="C63" t="s">
+        <v>13</v>
+      </c>
+      <c r="D63" t="s">
+        <v>21</v>
+      </c>
+      <c r="E63">
+        <v>269990</v>
+      </c>
+      <c r="F63">
+        <v>1</v>
+      </c>
+      <c r="G63" t="s">
+        <v>29</v>
+      </c>
+      <c r="H63" t="s">
+        <v>29</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>0</v>
+      </c>
+      <c r="K63" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>99</v>
+      </c>
+      <c r="B64" t="s">
+        <v>100</v>
+      </c>
+      <c r="C64" t="s">
+        <v>13</v>
+      </c>
+      <c r="D64" t="s">
+        <v>24</v>
+      </c>
+      <c r="E64">
+        <v>269990</v>
+      </c>
+      <c r="F64">
+        <v>1</v>
+      </c>
+      <c r="G64" t="s">
+        <v>29</v>
+      </c>
+      <c r="H64" t="s">
+        <v>29</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>0</v>
+      </c>
+      <c r="K64" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>99</v>
+      </c>
+      <c r="B65" t="s">
+        <v>100</v>
+      </c>
+      <c r="C65" t="s">
+        <v>13</v>
+      </c>
+      <c r="D65" t="s">
+        <v>43</v>
+      </c>
+      <c r="E65">
+        <v>269990</v>
+      </c>
+      <c r="F65">
+        <v>1</v>
+      </c>
+      <c r="G65" t="s">
+        <v>29</v>
+      </c>
+      <c r="H65" t="s">
+        <v>29</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>0</v>
+      </c>
+      <c r="K65" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>99</v>
+      </c>
+      <c r="B66" t="s">
+        <v>100</v>
+      </c>
+      <c r="C66" t="s">
+        <v>13</v>
+      </c>
+      <c r="D66" t="s">
+        <v>50</v>
+      </c>
+      <c r="E66">
+        <v>269990</v>
+      </c>
+      <c r="F66">
+        <v>1</v>
+      </c>
+      <c r="G66" t="s">
+        <v>29</v>
+      </c>
+      <c r="H66" t="s">
+        <v>29</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>0</v>
+      </c>
+      <c r="K66" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>99</v>
+      </c>
+      <c r="B67" t="s">
+        <v>100</v>
+      </c>
+      <c r="C67" t="s">
+        <v>13</v>
+      </c>
+      <c r="D67" t="s">
+        <v>80</v>
+      </c>
+      <c r="E67">
+        <v>269990</v>
+      </c>
+      <c r="F67">
+        <v>1</v>
+      </c>
+      <c r="G67" t="s">
+        <v>29</v>
+      </c>
+      <c r="H67" t="s">
+        <v>29</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>0</v>
+      </c>
+      <c r="K67" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>102</v>
+      </c>
+      <c r="B68" t="s">
+        <v>103</v>
+      </c>
+      <c r="C68" t="s">
+        <v>13</v>
+      </c>
+      <c r="D68" t="s">
+        <v>24</v>
+      </c>
+      <c r="E68">
+        <v>199990</v>
+      </c>
+      <c r="F68">
+        <v>1</v>
+      </c>
+      <c r="G68" t="s">
+        <v>29</v>
+      </c>
+      <c r="H68" t="s">
+        <v>29</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>0</v>
+      </c>
+      <c r="K68" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>102</v>
+      </c>
+      <c r="B69" t="s">
+        <v>103</v>
+      </c>
+      <c r="C69" t="s">
+        <v>13</v>
+      </c>
+      <c r="D69" t="s">
+        <v>43</v>
+      </c>
+      <c r="E69">
+        <v>199990</v>
+      </c>
+      <c r="F69">
+        <v>1</v>
+      </c>
+      <c r="G69" t="s">
+        <v>29</v>
+      </c>
+      <c r="H69" t="s">
+        <v>29</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>0</v>
+      </c>
+      <c r="K69" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>102</v>
+      </c>
+      <c r="B70" t="s">
+        <v>103</v>
+      </c>
+      <c r="C70" t="s">
+        <v>13</v>
+      </c>
+      <c r="D70" t="s">
+        <v>50</v>
+      </c>
+      <c r="E70">
+        <v>199990</v>
+      </c>
+      <c r="F70">
+        <v>1</v>
+      </c>
+      <c r="G70" t="s">
+        <v>29</v>
+      </c>
+      <c r="H70" t="s">
+        <v>29</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>0</v>
+      </c>
+      <c r="K70" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>102</v>
+      </c>
+      <c r="B71" t="s">
+        <v>103</v>
+      </c>
+      <c r="C71" t="s">
+        <v>13</v>
+      </c>
+      <c r="D71" t="s">
+        <v>80</v>
+      </c>
+      <c r="E71">
+        <v>199990</v>
+      </c>
+      <c r="F71">
+        <v>1</v>
+      </c>
+      <c r="G71" t="s">
+        <v>29</v>
+      </c>
+      <c r="H71" t="s">
+        <v>29</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>0</v>
+      </c>
+      <c r="K71" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>104</v>
+      </c>
+      <c r="B72" t="s">
+        <v>105</v>
+      </c>
+      <c r="C72" t="s">
+        <v>27</v>
+      </c>
+      <c r="D72" t="s">
+        <v>21</v>
+      </c>
+      <c r="E72">
+        <v>194990</v>
+      </c>
+      <c r="F72">
+        <v>1</v>
+      </c>
+      <c r="G72" t="s">
+        <v>29</v>
+      </c>
+      <c r="H72" t="s">
+        <v>29</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>0</v>
+      </c>
+      <c r="K72" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>104</v>
+      </c>
+      <c r="B73" t="s">
+        <v>105</v>
+      </c>
+      <c r="C73" t="s">
+        <v>27</v>
+      </c>
+      <c r="D73" t="s">
+        <v>24</v>
+      </c>
+      <c r="E73">
+        <v>194990</v>
+      </c>
+      <c r="F73">
+        <v>1</v>
+      </c>
+      <c r="G73" t="s">
+        <v>29</v>
+      </c>
+      <c r="H73" t="s">
+        <v>29</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>0</v>
+      </c>
+      <c r="K73" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>104</v>
+      </c>
+      <c r="B74" t="s">
+        <v>105</v>
+      </c>
+      <c r="C74" t="s">
+        <v>27</v>
+      </c>
+      <c r="D74" t="s">
+        <v>43</v>
+      </c>
+      <c r="E74">
+        <v>194990</v>
+      </c>
+      <c r="F74">
+        <v>1</v>
+      </c>
+      <c r="G74" t="s">
+        <v>29</v>
+      </c>
+      <c r="H74" t="s">
+        <v>29</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>0</v>
+      </c>
+      <c r="K74" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>104</v>
+      </c>
+      <c r="B75" t="s">
+        <v>105</v>
+      </c>
+      <c r="C75" t="s">
+        <v>27</v>
+      </c>
+      <c r="D75" t="s">
+        <v>50</v>
+      </c>
+      <c r="E75">
+        <v>194990</v>
+      </c>
+      <c r="F75">
+        <v>1</v>
+      </c>
+      <c r="G75" t="s">
+        <v>29</v>
+      </c>
+      <c r="H75" t="s">
+        <v>29</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>0</v>
+      </c>
+      <c r="K75" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>106</v>
+      </c>
+      <c r="B76" t="s">
+        <v>107</v>
+      </c>
+      <c r="C76" t="s">
+        <v>13</v>
+      </c>
+      <c r="D76" t="s">
+        <v>21</v>
+      </c>
+      <c r="E76">
+        <v>202990</v>
+      </c>
+      <c r="F76">
+        <v>1</v>
+      </c>
+      <c r="G76" t="s">
+        <v>29</v>
+      </c>
+      <c r="H76" t="s">
+        <v>29</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>0</v>
+      </c>
+      <c r="K76" t="s">
+        <v>62</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/data/catalogo_jusp.xlsx
+++ b/data/catalogo_jusp.xlsx
@@ -3343,10 +3343,10 @@
         <v>1</v>
       </c>
       <c r="G76" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="H76" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="I76">
         <v>0</v>

--- a/data/catalogo_jusp.xlsx
+++ b/data/catalogo_jusp.xlsx
@@ -759,10 +759,10 @@
         <v>16</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="s">
         <v>17</v>
@@ -794,10 +794,10 @@
         <v>16</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="s">
         <v>17</v>

--- a/data/catalogo_jusp.xlsx
+++ b/data/catalogo_jusp.xlsx
@@ -51,6 +51,9 @@
   </si>
   <si>
     <t xml:space="preserve">color </t>
+  </si>
+  <si>
+    <t>descuento</t>
   </si>
   <si>
     <t>short-nike-kids</t>
@@ -732,19 +735,23 @@
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1"/>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E2">
         <v>88990</v>
@@ -753,10 +760,10 @@
         <v>1</v>
       </c>
       <c r="G2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I2">
         <v>1</v>
@@ -765,21 +772,24 @@
         <v>1</v>
       </c>
       <c r="K2" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="L2">
+        <v>5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E3">
         <v>88990</v>
@@ -788,10 +798,10 @@
         <v>1</v>
       </c>
       <c r="G3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -800,21 +810,24 @@
         <v>1</v>
       </c>
       <c r="K3" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="L3">
+        <v>5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E4">
         <v>89990</v>
@@ -823,10 +836,10 @@
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -835,21 +848,21 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E5">
         <v>89990</v>
@@ -858,10 +871,10 @@
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -870,21 +883,21 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E6">
         <v>75990</v>
@@ -893,10 +906,10 @@
         <v>2</v>
       </c>
       <c r="G6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -905,21 +918,21 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E7">
         <v>79990</v>
@@ -928,10 +941,10 @@
         <v>2</v>
       </c>
       <c r="G7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -940,21 +953,21 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E8">
         <v>78990</v>
@@ -963,10 +976,10 @@
         <v>1</v>
       </c>
       <c r="G8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -975,21 +988,21 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E9">
         <v>69990</v>
@@ -998,10 +1011,10 @@
         <v>1</v>
       </c>
       <c r="G9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -1010,21 +1023,21 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E10">
         <v>99990</v>
@@ -1033,10 +1046,10 @@
         <v>1</v>
       </c>
       <c r="G10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -1045,18 +1058,18 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D11">
         <v>7</v>
@@ -1068,10 +1081,10 @@
         <v>0</v>
       </c>
       <c r="G11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -1080,21 +1093,21 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E12" s="2">
         <v>119990</v>
@@ -1103,10 +1116,10 @@
         <v>1</v>
       </c>
       <c r="G12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -1115,21 +1128,21 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E13">
         <v>65990</v>
@@ -1138,10 +1151,10 @@
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -1150,21 +1163,21 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E14">
         <v>75990</v>
@@ -1173,10 +1186,10 @@
         <v>1</v>
       </c>
       <c r="G14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -1185,21 +1198,21 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E15">
         <v>85990</v>
@@ -1208,10 +1221,10 @@
         <v>1</v>
       </c>
       <c r="G15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -1220,21 +1233,21 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C16" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E16">
         <v>79990</v>
@@ -1243,10 +1256,10 @@
         <v>1</v>
       </c>
       <c r="G16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -1255,21 +1268,21 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B17" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C17" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E17">
         <v>79990</v>
@@ -1278,10 +1291,10 @@
         <v>1</v>
       </c>
       <c r="G17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -1290,21 +1303,21 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B18" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C18" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D18" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E18">
         <v>79990</v>
@@ -1313,10 +1326,10 @@
         <v>1</v>
       </c>
       <c r="G18" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H18" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -1325,21 +1338,21 @@
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B19" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C19" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D19" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E19">
         <v>79990</v>
@@ -1348,10 +1361,10 @@
         <v>1</v>
       </c>
       <c r="G19" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H19" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -1360,21 +1373,21 @@
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B20" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C20" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D20" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E20">
         <v>79990</v>
@@ -1383,10 +1396,10 @@
         <v>1</v>
       </c>
       <c r="G20" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H20" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -1395,21 +1408,21 @@
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B21" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C21" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D21" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E21">
         <v>155990</v>
@@ -1418,10 +1431,10 @@
         <v>1</v>
       </c>
       <c r="G21" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H21" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -1430,21 +1443,21 @@
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B22" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C22" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D22" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E22">
         <v>155990</v>
@@ -1453,10 +1466,10 @@
         <v>1</v>
       </c>
       <c r="G22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -1465,21 +1478,21 @@
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B23" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C23" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D23" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E23">
         <v>155990</v>
@@ -1488,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="G23" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H23" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -1500,21 +1513,21 @@
         <v>0</v>
       </c>
       <c r="K23" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
+        <v>52</v>
+      </c>
+      <c r="B24" t="s">
+        <v>53</v>
+      </c>
+      <c r="C24" t="s">
+        <v>14</v>
+      </c>
+      <c r="D24" t="s">
         <v>51</v>
-      </c>
-      <c r="B24" t="s">
-        <v>52</v>
-      </c>
-      <c r="C24" t="s">
-        <v>13</v>
-      </c>
-      <c r="D24" t="s">
-        <v>50</v>
       </c>
       <c r="E24">
         <v>155990</v>
@@ -1523,10 +1536,10 @@
         <v>1</v>
       </c>
       <c r="G24" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H24" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I24">
         <v>0</v>
@@ -1535,21 +1548,21 @@
         <v>0</v>
       </c>
       <c r="K24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B25" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C25" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D25" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E25">
         <v>49990</v>
@@ -1558,10 +1571,10 @@
         <v>1</v>
       </c>
       <c r="G25" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H25" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -1570,21 +1583,21 @@
         <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B26" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C26" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D26" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E26">
         <v>49990</v>
@@ -1593,10 +1606,10 @@
         <v>1</v>
       </c>
       <c r="G26" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H26" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -1605,21 +1618,21 @@
         <v>0</v>
       </c>
       <c r="K26" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B27" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D27" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E27">
         <v>125990</v>
@@ -1628,10 +1641,10 @@
         <v>1</v>
       </c>
       <c r="G27" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H27" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -1640,21 +1653,21 @@
         <v>0</v>
       </c>
       <c r="K27" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B28" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C28" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D28" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E28">
         <v>155990</v>
@@ -1663,10 +1676,10 @@
         <v>1</v>
       </c>
       <c r="G28" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H28" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -1675,21 +1688,21 @@
         <v>0</v>
       </c>
       <c r="K28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C29" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D29" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E29">
         <v>155990</v>
@@ -1698,10 +1711,10 @@
         <v>1</v>
       </c>
       <c r="G29" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H29" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -1710,21 +1723,21 @@
         <v>0</v>
       </c>
       <c r="K29" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B30" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C30" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D30" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E30">
         <v>155990</v>
@@ -1733,10 +1746,10 @@
         <v>1</v>
       </c>
       <c r="G30" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H30" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -1745,21 +1758,21 @@
         <v>0</v>
       </c>
       <c r="K30" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B31" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C31" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D31" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E31">
         <v>129990</v>
@@ -1768,10 +1781,10 @@
         <v>1</v>
       </c>
       <c r="G31" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H31" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -1780,21 +1793,21 @@
         <v>0</v>
       </c>
       <c r="K31" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B32" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C32" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D32" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E32">
         <v>129990</v>
@@ -1803,10 +1816,10 @@
         <v>1</v>
       </c>
       <c r="G32" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H32" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -1815,21 +1828,21 @@
         <v>0</v>
       </c>
       <c r="K32" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B33" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C33" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D33" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E33">
         <v>179990</v>
@@ -1838,10 +1851,10 @@
         <v>1</v>
       </c>
       <c r="G33" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H33" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -1850,21 +1863,21 @@
         <v>0</v>
       </c>
       <c r="K33" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
+        <v>71</v>
+      </c>
+      <c r="B34" t="s">
+        <v>72</v>
+      </c>
+      <c r="C34" t="s">
+        <v>14</v>
+      </c>
+      <c r="D34" t="s">
         <v>70</v>
-      </c>
-      <c r="B34" t="s">
-        <v>71</v>
-      </c>
-      <c r="C34" t="s">
-        <v>13</v>
-      </c>
-      <c r="D34" t="s">
-        <v>69</v>
       </c>
       <c r="E34">
         <v>159990</v>
@@ -1873,10 +1886,10 @@
         <v>1</v>
       </c>
       <c r="G34" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H34" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -1885,21 +1898,21 @@
         <v>0</v>
       </c>
       <c r="K34" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B35" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C35" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D35" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E35">
         <v>134990</v>
@@ -1908,10 +1921,10 @@
         <v>1</v>
       </c>
       <c r="G35" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H35" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -1920,21 +1933,21 @@
         <v>0</v>
       </c>
       <c r="K35" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B36" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C36" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D36" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E36">
         <v>134990</v>
@@ -1943,10 +1956,10 @@
         <v>1</v>
       </c>
       <c r="G36" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H36" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -1955,21 +1968,21 @@
         <v>0</v>
       </c>
       <c r="K36" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B37" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C37" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D37" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E37">
         <v>134990</v>
@@ -1978,10 +1991,10 @@
         <v>1</v>
       </c>
       <c r="G37" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H37" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -1990,21 +2003,21 @@
         <v>0</v>
       </c>
       <c r="K37" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B38" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C38" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D38" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E38">
         <v>79990</v>
@@ -2013,10 +2026,10 @@
         <v>1</v>
       </c>
       <c r="G38" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H38" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -2025,21 +2038,21 @@
         <v>0</v>
       </c>
       <c r="K38" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B39" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C39" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D39" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E39">
         <v>134990</v>
@@ -2048,10 +2061,10 @@
         <v>1</v>
       </c>
       <c r="G39" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H39" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I39">
         <v>0</v>
@@ -2060,21 +2073,21 @@
         <v>0</v>
       </c>
       <c r="K39" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B40" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C40" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D40" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E40">
         <v>134990</v>
@@ -2083,10 +2096,10 @@
         <v>1</v>
       </c>
       <c r="G40" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H40" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I40">
         <v>0</v>
@@ -2095,21 +2108,21 @@
         <v>0</v>
       </c>
       <c r="K40" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B41" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C41" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D41" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E41">
         <v>134990</v>
@@ -2118,10 +2131,10 @@
         <v>1</v>
       </c>
       <c r="G41" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H41" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I41">
         <v>0</v>
@@ -2130,21 +2143,21 @@
         <v>0</v>
       </c>
       <c r="K41" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B42" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C42" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D42" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E42">
         <v>134990</v>
@@ -2153,10 +2166,10 @@
         <v>1</v>
       </c>
       <c r="G42" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H42" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -2165,21 +2178,21 @@
         <v>0</v>
       </c>
       <c r="K42" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B43" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C43" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D43" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E43">
         <v>134990</v>
@@ -2188,10 +2201,10 @@
         <v>1</v>
       </c>
       <c r="G43" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H43" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I43">
         <v>0</v>
@@ -2200,21 +2213,21 @@
         <v>0</v>
       </c>
       <c r="K43" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B44" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C44" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D44" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E44">
         <v>119990</v>
@@ -2223,10 +2236,10 @@
         <v>1</v>
       </c>
       <c r="G44" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H44" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I44">
         <v>0</v>
@@ -2235,21 +2248,21 @@
         <v>0</v>
       </c>
       <c r="K44" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B45" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C45" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D45" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E45">
         <v>119990</v>
@@ -2258,10 +2271,10 @@
         <v>1</v>
       </c>
       <c r="G45" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H45" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I45">
         <v>0</v>
@@ -2270,21 +2283,21 @@
         <v>0</v>
       </c>
       <c r="K45" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B46" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C46" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D46" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E46">
         <v>119990</v>
@@ -2293,10 +2306,10 @@
         <v>1</v>
       </c>
       <c r="G46" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H46" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I46">
         <v>0</v>
@@ -2305,21 +2318,21 @@
         <v>0</v>
       </c>
       <c r="K46" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B47" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C47" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D47" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E47">
         <v>119990</v>
@@ -2328,10 +2341,10 @@
         <v>1</v>
       </c>
       <c r="G47" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H47" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I47">
         <v>0</v>
@@ -2340,21 +2353,21 @@
         <v>0</v>
       </c>
       <c r="K47" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B48" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C48" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D48" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E48">
         <v>119990</v>
@@ -2363,10 +2376,10 @@
         <v>1</v>
       </c>
       <c r="G48" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H48" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I48">
         <v>0</v>
@@ -2375,21 +2388,21 @@
         <v>0</v>
       </c>
       <c r="K48" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B49" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C49" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D49" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E49">
         <v>39990</v>
@@ -2398,10 +2411,10 @@
         <v>1</v>
       </c>
       <c r="G49" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H49" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I49">
         <v>0</v>
@@ -2410,21 +2423,21 @@
         <v>0</v>
       </c>
       <c r="K49" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B50" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C50" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D50" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E50">
         <v>39990</v>
@@ -2433,10 +2446,10 @@
         <v>1</v>
       </c>
       <c r="G50" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H50" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I50">
         <v>0</v>
@@ -2445,21 +2458,21 @@
         <v>0</v>
       </c>
       <c r="K50" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C51" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D51" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E51">
         <v>39990</v>
@@ -2468,10 +2481,10 @@
         <v>1</v>
       </c>
       <c r="G51" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H51" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I51">
         <v>0</v>
@@ -2480,21 +2493,21 @@
         <v>0</v>
       </c>
       <c r="K51" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B52" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C52" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D52" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E52">
         <v>140990</v>
@@ -2503,10 +2516,10 @@
         <v>1</v>
       </c>
       <c r="G52" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H52" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I52">
         <v>0</v>
@@ -2515,21 +2528,21 @@
         <v>0</v>
       </c>
       <c r="K52" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B53" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C53" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D53" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E53">
         <v>145990</v>
@@ -2538,10 +2551,10 @@
         <v>1</v>
       </c>
       <c r="G53" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H53" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I53">
         <v>0</v>
@@ -2550,21 +2563,21 @@
         <v>0</v>
       </c>
       <c r="K53" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B54" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C54" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D54" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E54" s="2">
         <v>199990</v>
@@ -2573,10 +2586,10 @@
         <v>1</v>
       </c>
       <c r="G54" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H54" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I54">
         <v>0</v>
@@ -2585,21 +2598,21 @@
         <v>0</v>
       </c>
       <c r="K54" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B55" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C55" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D55" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E55" s="2">
         <v>199990</v>
@@ -2608,10 +2621,10 @@
         <v>1</v>
       </c>
       <c r="G55" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H55" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I55">
         <v>0</v>
@@ -2620,21 +2633,21 @@
         <v>0</v>
       </c>
       <c r="K55" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B56" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C56" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D56" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E56" s="2">
         <v>199990</v>
@@ -2643,10 +2656,10 @@
         <v>1</v>
       </c>
       <c r="G56" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H56" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I56">
         <v>0</v>
@@ -2655,21 +2668,21 @@
         <v>0</v>
       </c>
       <c r="K56" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B57" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C57" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D57" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E57" s="2">
         <v>199990</v>
@@ -2678,10 +2691,10 @@
         <v>1</v>
       </c>
       <c r="G57" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H57" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I57">
         <v>0</v>
@@ -2690,21 +2703,21 @@
         <v>0</v>
       </c>
       <c r="K57" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B58" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C58" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D58" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E58" s="2">
         <v>199990</v>
@@ -2713,10 +2726,10 @@
         <v>1</v>
       </c>
       <c r="G58" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H58" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I58">
         <v>0</v>
@@ -2725,21 +2738,21 @@
         <v>0</v>
       </c>
       <c r="K58" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B59" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C59" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D59" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E59">
         <v>155990</v>
@@ -2748,10 +2761,10 @@
         <v>1</v>
       </c>
       <c r="G59" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H59" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I59">
         <v>0</v>
@@ -2760,21 +2773,21 @@
         <v>0</v>
       </c>
       <c r="K59" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B60" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C60" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D60" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E60">
         <v>155990</v>
@@ -2783,10 +2796,10 @@
         <v>1</v>
       </c>
       <c r="G60" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H60" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I60">
         <v>0</v>
@@ -2795,21 +2808,21 @@
         <v>0</v>
       </c>
       <c r="K60" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B61" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C61" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D61" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E61">
         <v>155990</v>
@@ -2818,10 +2831,10 @@
         <v>1</v>
       </c>
       <c r="G61" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H61" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I61">
         <v>0</v>
@@ -2830,21 +2843,21 @@
         <v>0</v>
       </c>
       <c r="K61" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B62" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C62" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D62" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E62">
         <v>155990</v>
@@ -2853,10 +2866,10 @@
         <v>1</v>
       </c>
       <c r="G62" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H62" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I62">
         <v>0</v>
@@ -2865,21 +2878,21 @@
         <v>0</v>
       </c>
       <c r="K62" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B63" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C63" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D63" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E63">
         <v>269990</v>
@@ -2888,10 +2901,10 @@
         <v>1</v>
       </c>
       <c r="G63" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H63" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I63">
         <v>0</v>
@@ -2900,21 +2913,21 @@
         <v>0</v>
       </c>
       <c r="K63" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B64" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C64" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D64" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E64">
         <v>269990</v>
@@ -2923,10 +2936,10 @@
         <v>1</v>
       </c>
       <c r="G64" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H64" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I64">
         <v>0</v>
@@ -2935,21 +2948,21 @@
         <v>0</v>
       </c>
       <c r="K64" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B65" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C65" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D65" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E65">
         <v>269990</v>
@@ -2958,10 +2971,10 @@
         <v>1</v>
       </c>
       <c r="G65" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H65" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I65">
         <v>0</v>
@@ -2970,21 +2983,21 @@
         <v>0</v>
       </c>
       <c r="K65" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B66" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C66" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D66" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E66">
         <v>269990</v>
@@ -2993,10 +3006,10 @@
         <v>1</v>
       </c>
       <c r="G66" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H66" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I66">
         <v>0</v>
@@ -3005,21 +3018,21 @@
         <v>0</v>
       </c>
       <c r="K66" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B67" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C67" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D67" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E67">
         <v>269990</v>
@@ -3028,10 +3041,10 @@
         <v>1</v>
       </c>
       <c r="G67" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H67" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I67">
         <v>0</v>
@@ -3040,21 +3053,21 @@
         <v>0</v>
       </c>
       <c r="K67" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B68" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C68" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D68" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E68">
         <v>199990</v>
@@ -3063,10 +3076,10 @@
         <v>1</v>
       </c>
       <c r="G68" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H68" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I68">
         <v>0</v>
@@ -3075,21 +3088,21 @@
         <v>0</v>
       </c>
       <c r="K68" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B69" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C69" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D69" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E69">
         <v>199990</v>
@@ -3098,10 +3111,10 @@
         <v>1</v>
       </c>
       <c r="G69" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H69" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I69">
         <v>0</v>
@@ -3110,21 +3123,21 @@
         <v>0</v>
       </c>
       <c r="K69" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B70" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C70" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D70" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E70">
         <v>199990</v>
@@ -3133,10 +3146,10 @@
         <v>1</v>
       </c>
       <c r="G70" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H70" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I70">
         <v>0</v>
@@ -3145,21 +3158,21 @@
         <v>0</v>
       </c>
       <c r="K70" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B71" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C71" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D71" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E71">
         <v>199990</v>
@@ -3168,10 +3181,10 @@
         <v>1</v>
       </c>
       <c r="G71" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H71" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I71">
         <v>0</v>
@@ -3180,21 +3193,21 @@
         <v>0</v>
       </c>
       <c r="K71" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B72" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C72" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D72" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E72">
         <v>194990</v>
@@ -3203,10 +3216,10 @@
         <v>1</v>
       </c>
       <c r="G72" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H72" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I72">
         <v>0</v>
@@ -3215,21 +3228,21 @@
         <v>0</v>
       </c>
       <c r="K72" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B73" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C73" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D73" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E73">
         <v>194990</v>
@@ -3238,10 +3251,10 @@
         <v>1</v>
       </c>
       <c r="G73" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H73" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I73">
         <v>0</v>
@@ -3250,21 +3263,21 @@
         <v>0</v>
       </c>
       <c r="K73" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B74" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C74" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D74" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E74">
         <v>194990</v>
@@ -3273,10 +3286,10 @@
         <v>1</v>
       </c>
       <c r="G74" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H74" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I74">
         <v>0</v>
@@ -3285,21 +3298,21 @@
         <v>0</v>
       </c>
       <c r="K74" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B75" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C75" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D75" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E75">
         <v>194990</v>
@@ -3308,10 +3321,10 @@
         <v>1</v>
       </c>
       <c r="G75" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H75" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I75">
         <v>0</v>
@@ -3320,21 +3333,21 @@
         <v>0</v>
       </c>
       <c r="K75" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B76" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C76" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D76" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E76">
         <v>202990</v>
@@ -3343,10 +3356,10 @@
         <v>1</v>
       </c>
       <c r="G76" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H76" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I76">
         <v>0</v>
@@ -3355,7 +3368,7 @@
         <v>0</v>
       </c>
       <c r="K76" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>

--- a/data/catalogo_jusp.xlsx
+++ b/data/catalogo_jusp.xlsx
@@ -738,7 +738,6 @@
       <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1"/>
     </row>
     <row r="2">
       <c r="A2" t="s">
@@ -903,7 +902,7 @@
         <v>75990</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" t="s">
         <v>30</v>
@@ -938,7 +937,7 @@
         <v>79990</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7" t="s">
         <v>30</v>

--- a/data/catalogo_jusp.xlsx
+++ b/data/catalogo_jusp.xlsx
@@ -56,15 +56,30 @@
     <t>descuento</t>
   </si>
   <si>
+    <t>nike-hf5407-010</t>
+  </si>
+  <si>
+    <t>Women's Medium-Support Padded Sports Bra Tank Top</t>
+  </si>
+  <si>
+    <t>Nike</t>
+  </si>
+  <si>
+    <t>XL</t>
+  </si>
+  <si>
+    <t>women</t>
+  </si>
+  <si>
+    <t>Black</t>
+  </si>
+  <si>
     <t>short-nike-kids</t>
   </si>
   <si>
     <t>Pantalones cortos Nike niños</t>
   </si>
   <si>
-    <t>Nike</t>
-  </si>
-  <si>
     <t>XS (135)</t>
   </si>
   <si>
@@ -74,9 +89,6 @@
     <t>kisd</t>
   </si>
   <si>
-    <t>Black</t>
-  </si>
-  <si>
     <t>S (140)</t>
   </si>
   <si>
@@ -89,9 +101,6 @@
     <t>S</t>
   </si>
   <si>
-    <t>women</t>
-  </si>
-  <si>
     <t>Pink</t>
   </si>
   <si>
@@ -171,9 +180,6 @@
   </si>
   <si>
     <t>XS</t>
-  </si>
-  <si>
-    <t>XL</t>
   </si>
   <si>
     <t>nike-dri-fit-pro-cropped-printed-women</t>
@@ -753,7 +759,7 @@
         <v>15</v>
       </c>
       <c r="E2">
-        <v>88990</v>
+        <v>135990</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -762,33 +768,30 @@
         <v>16</v>
       </c>
       <c r="H2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2" t="s">
         <v>17</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2" t="s">
-        <v>18</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
         <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E3">
         <v>88990</v>
@@ -797,19 +800,19 @@
         <v>1</v>
       </c>
       <c r="G3" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3" t="s">
         <v>17</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3" t="s">
-        <v>18</v>
       </c>
       <c r="L3">
         <v>5</v>
@@ -817,51 +820,54 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4">
+        <v>88990</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4" t="s">
         <v>21</v>
       </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="H4" t="s">
         <v>22</v>
       </c>
-      <c r="E4">
-        <v>89990</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4" t="s">
-        <v>23</v>
-      </c>
-      <c r="H4" t="s">
-        <v>23</v>
-      </c>
       <c r="I4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="s">
-        <v>24</v>
+        <v>17</v>
+      </c>
+      <c r="L4">
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
         <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E5">
         <v>89990</v>
@@ -870,10 +876,10 @@
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="H5" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -882,68 +888,68 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6">
+        <v>89990</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6" t="s">
         <v>27</v>
-      </c>
-      <c r="C6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E6">
-        <v>75990</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6" t="s">
-        <v>30</v>
-      </c>
-      <c r="H6" t="s">
-        <v>30</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D7" t="s">
         <v>32</v>
       </c>
       <c r="E7">
-        <v>79990</v>
+        <v>75990</v>
       </c>
       <c r="F7">
         <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H7" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -952,33 +958,33 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E8">
-        <v>78990</v>
+        <v>79990</v>
       </c>
       <c r="F8">
         <v>1</v>
       </c>
       <c r="G8" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H8" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -987,42 +993,42 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9">
+        <v>78990</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H9" t="s">
+        <v>33</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9" t="s">
         <v>34</v>
-      </c>
-      <c r="B9" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9">
-        <v>69990</v>
-      </c>
-      <c r="F9">
-        <v>1</v>
-      </c>
-      <c r="G9" t="s">
-        <v>23</v>
-      </c>
-      <c r="H9" t="s">
-        <v>23</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="10">
@@ -1036,19 +1042,19 @@
         <v>14</v>
       </c>
       <c r="D10" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E10">
-        <v>99990</v>
+        <v>69990</v>
       </c>
       <c r="F10">
         <v>1</v>
       </c>
       <c r="G10" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="H10" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -1070,20 +1076,20 @@
       <c r="C11" t="s">
         <v>14</v>
       </c>
-      <c r="D11">
-        <v>7</v>
+      <c r="D11" t="s">
+        <v>28</v>
       </c>
       <c r="E11">
         <v>99990</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="H11" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -1092,33 +1098,33 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C12" t="s">
         <v>14</v>
       </c>
-      <c r="D12" t="s">
-        <v>44</v>
-      </c>
-      <c r="E12" s="2">
-        <v>119990</v>
+      <c r="D12">
+        <v>7</v>
+      </c>
+      <c r="E12">
+        <v>99990</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="H12" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -1127,7 +1133,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13">
@@ -1141,19 +1147,19 @@
         <v>14</v>
       </c>
       <c r="D13" t="s">
-        <v>29</v>
-      </c>
-      <c r="E13">
-        <v>65990</v>
+        <v>47</v>
+      </c>
+      <c r="E13" s="2">
+        <v>119990</v>
       </c>
       <c r="F13">
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="H13" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -1162,15 +1168,15 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B14" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C14" t="s">
         <v>14</v>
@@ -1179,16 +1185,16 @@
         <v>32</v>
       </c>
       <c r="E14">
-        <v>75990</v>
+        <v>65990</v>
       </c>
       <c r="F14">
         <v>1</v>
       </c>
       <c r="G14" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H14" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -1197,33 +1203,33 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B15" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C15" t="s">
         <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E15">
-        <v>85990</v>
+        <v>75990</v>
       </c>
       <c r="F15">
         <v>1</v>
       </c>
       <c r="G15" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H15" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -1232,7 +1238,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1246,42 +1252,42 @@
         <v>14</v>
       </c>
       <c r="D16" t="s">
+        <v>36</v>
+      </c>
+      <c r="E16">
+        <v>85990</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16" t="s">
+        <v>33</v>
+      </c>
+      <c r="H16" t="s">
+        <v>33</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16" t="s">
         <v>50</v>
-      </c>
-      <c r="E16">
-        <v>79990</v>
-      </c>
-      <c r="F16">
-        <v>1</v>
-      </c>
-      <c r="G16" t="s">
-        <v>23</v>
-      </c>
-      <c r="H16" t="s">
-        <v>23</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B17" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C17" t="s">
         <v>14</v>
       </c>
       <c r="D17" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="E17">
         <v>79990</v>
@@ -1290,10 +1296,10 @@
         <v>1</v>
       </c>
       <c r="G17" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="H17" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -1302,21 +1308,21 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B18" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C18" t="s">
         <v>14</v>
       </c>
       <c r="D18" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E18">
         <v>79990</v>
@@ -1325,10 +1331,10 @@
         <v>1</v>
       </c>
       <c r="G18" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="H18" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -1337,21 +1343,21 @@
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B19" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C19" t="s">
         <v>14</v>
       </c>
       <c r="D19" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="E19">
         <v>79990</v>
@@ -1360,10 +1366,10 @@
         <v>1</v>
       </c>
       <c r="G19" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="H19" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -1372,21 +1378,21 @@
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B20" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C20" t="s">
         <v>14</v>
       </c>
       <c r="D20" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E20">
         <v>79990</v>
@@ -1395,10 +1401,10 @@
         <v>1</v>
       </c>
       <c r="G20" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="H20" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -1407,33 +1413,33 @@
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
+        <v>51</v>
+      </c>
+      <c r="B21" t="s">
         <v>52</v>
       </c>
-      <c r="B21" t="s">
-        <v>53</v>
-      </c>
       <c r="C21" t="s">
         <v>14</v>
       </c>
       <c r="D21" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E21">
-        <v>155990</v>
+        <v>79990</v>
       </c>
       <c r="F21">
         <v>1</v>
       </c>
       <c r="G21" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="H21" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -1442,21 +1448,21 @@
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B22" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C22" t="s">
         <v>14</v>
       </c>
       <c r="D22" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E22">
         <v>155990</v>
@@ -1465,10 +1471,10 @@
         <v>1</v>
       </c>
       <c r="G22" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="H22" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -1477,21 +1483,21 @@
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B23" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C23" t="s">
         <v>14</v>
       </c>
       <c r="D23" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="E23">
         <v>155990</v>
@@ -1500,10 +1506,10 @@
         <v>1</v>
       </c>
       <c r="G23" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="H23" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -1512,21 +1518,21 @@
         <v>0</v>
       </c>
       <c r="K23" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B24" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C24" t="s">
         <v>14</v>
       </c>
       <c r="D24" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E24">
         <v>155990</v>
@@ -1535,10 +1541,10 @@
         <v>1</v>
       </c>
       <c r="G24" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="H24" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I24">
         <v>0</v>
@@ -1547,56 +1553,56 @@
         <v>0</v>
       </c>
       <c r="K24" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
+        <v>54</v>
+      </c>
+      <c r="B25" t="s">
         <v>55</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
+        <v>14</v>
+      </c>
+      <c r="D25" t="s">
+        <v>15</v>
+      </c>
+      <c r="E25">
+        <v>155990</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+      <c r="G25" t="s">
+        <v>16</v>
+      </c>
+      <c r="H25" t="s">
+        <v>16</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25" t="s">
         <v>56</v>
-      </c>
-      <c r="C25" t="s">
-        <v>57</v>
-      </c>
-      <c r="D25" t="s">
-        <v>22</v>
-      </c>
-      <c r="E25">
-        <v>49990</v>
-      </c>
-      <c r="F25">
-        <v>1</v>
-      </c>
-      <c r="G25" t="s">
-        <v>23</v>
-      </c>
-      <c r="H25" t="s">
-        <v>23</v>
-      </c>
-      <c r="I25">
-        <v>0</v>
-      </c>
-      <c r="J25">
-        <v>0</v>
-      </c>
-      <c r="K25" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B26" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C26" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D26" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E26">
         <v>49990</v>
@@ -1605,10 +1611,10 @@
         <v>1</v>
       </c>
       <c r="G26" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="H26" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -1617,33 +1623,33 @@
         <v>0</v>
       </c>
       <c r="K26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
+        <v>57</v>
+      </c>
+      <c r="B27" t="s">
         <v>58</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
         <v>59</v>
       </c>
-      <c r="C27" t="s">
+      <c r="D27" t="s">
         <v>28</v>
       </c>
-      <c r="D27" t="s">
-        <v>25</v>
-      </c>
       <c r="E27">
-        <v>125990</v>
+        <v>49990</v>
       </c>
       <c r="F27">
         <v>1</v>
       </c>
       <c r="G27" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="H27" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -1652,56 +1658,56 @@
         <v>0</v>
       </c>
       <c r="K27" t="s">
-        <v>60</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
+        <v>60</v>
+      </c>
+      <c r="B28" t="s">
         <v>61</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
+        <v>31</v>
+      </c>
+      <c r="D28" t="s">
+        <v>28</v>
+      </c>
+      <c r="E28">
+        <v>125990</v>
+      </c>
+      <c r="F28">
+        <v>1</v>
+      </c>
+      <c r="G28" t="s">
+        <v>16</v>
+      </c>
+      <c r="H28" t="s">
+        <v>16</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28" t="s">
         <v>62</v>
-      </c>
-      <c r="C28" t="s">
-        <v>14</v>
-      </c>
-      <c r="D28" t="s">
-        <v>22</v>
-      </c>
-      <c r="E28">
-        <v>155990</v>
-      </c>
-      <c r="F28">
-        <v>1</v>
-      </c>
-      <c r="G28" t="s">
-        <v>23</v>
-      </c>
-      <c r="H28" t="s">
-        <v>23</v>
-      </c>
-      <c r="I28">
-        <v>0</v>
-      </c>
-      <c r="J28">
-        <v>0</v>
-      </c>
-      <c r="K28" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B29" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C29" t="s">
         <v>14</v>
       </c>
       <c r="D29" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="E29">
         <v>155990</v>
@@ -1710,10 +1716,10 @@
         <v>1</v>
       </c>
       <c r="G29" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="H29" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -1722,21 +1728,21 @@
         <v>0</v>
       </c>
       <c r="K29" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B30" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C30" t="s">
         <v>14</v>
       </c>
       <c r="D30" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E30">
         <v>155990</v>
@@ -1745,10 +1751,10 @@
         <v>1</v>
       </c>
       <c r="G30" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="H30" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -1757,56 +1763,56 @@
         <v>0</v>
       </c>
       <c r="K30" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
+        <v>63</v>
+      </c>
+      <c r="B31" t="s">
         <v>64</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" t="s">
+        <v>14</v>
+      </c>
+      <c r="D31" t="s">
+        <v>15</v>
+      </c>
+      <c r="E31">
+        <v>155990</v>
+      </c>
+      <c r="F31">
+        <v>1</v>
+      </c>
+      <c r="G31" t="s">
+        <v>16</v>
+      </c>
+      <c r="H31" t="s">
+        <v>16</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31" t="s">
         <v>65</v>
-      </c>
-      <c r="C31" t="s">
-        <v>14</v>
-      </c>
-      <c r="D31" t="s">
-        <v>32</v>
-      </c>
-      <c r="E31">
-        <v>129990</v>
-      </c>
-      <c r="F31">
-        <v>1</v>
-      </c>
-      <c r="G31" t="s">
-        <v>66</v>
-      </c>
-      <c r="H31" t="s">
-        <v>66</v>
-      </c>
-      <c r="I31">
-        <v>0</v>
-      </c>
-      <c r="J31">
-        <v>0</v>
-      </c>
-      <c r="K31" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B32" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C32" t="s">
         <v>14</v>
       </c>
       <c r="D32" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E32">
         <v>129990</v>
@@ -1815,10 +1821,10 @@
         <v>1</v>
       </c>
       <c r="G32" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H32" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -1827,33 +1833,33 @@
         <v>0</v>
       </c>
       <c r="K32" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
+        <v>66</v>
+      </c>
+      <c r="B33" t="s">
         <v>67</v>
       </c>
-      <c r="B33" t="s">
+      <c r="C33" t="s">
+        <v>14</v>
+      </c>
+      <c r="D33" t="s">
+        <v>36</v>
+      </c>
+      <c r="E33">
+        <v>129990</v>
+      </c>
+      <c r="F33">
+        <v>1</v>
+      </c>
+      <c r="G33" t="s">
         <v>68</v>
       </c>
-      <c r="C33" t="s">
-        <v>69</v>
-      </c>
-      <c r="D33" t="s">
-        <v>70</v>
-      </c>
-      <c r="E33">
-        <v>179990</v>
-      </c>
-      <c r="F33">
-        <v>1</v>
-      </c>
-      <c r="G33" t="s">
-        <v>66</v>
-      </c>
       <c r="H33" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -1862,33 +1868,33 @@
         <v>0</v>
       </c>
       <c r="K33" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
+        <v>69</v>
+      </c>
+      <c r="B34" t="s">
+        <v>70</v>
+      </c>
+      <c r="C34" t="s">
         <v>71</v>
       </c>
-      <c r="B34" t="s">
+      <c r="D34" t="s">
         <v>72</v>
       </c>
-      <c r="C34" t="s">
-        <v>14</v>
-      </c>
-      <c r="D34" t="s">
-        <v>70</v>
-      </c>
       <c r="E34">
-        <v>159990</v>
+        <v>179990</v>
       </c>
       <c r="F34">
         <v>1</v>
       </c>
       <c r="G34" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H34" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -1897,7 +1903,7 @@
         <v>0</v>
       </c>
       <c r="K34" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="35">
@@ -1911,19 +1917,19 @@
         <v>14</v>
       </c>
       <c r="D35" t="s">
-        <v>29</v>
+        <v>72</v>
       </c>
       <c r="E35">
-        <v>134990</v>
+        <v>159990</v>
       </c>
       <c r="F35">
         <v>1</v>
       </c>
       <c r="G35" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H35" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -1932,15 +1938,15 @@
         <v>0</v>
       </c>
       <c r="K35" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B36" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C36" t="s">
         <v>14</v>
@@ -1955,10 +1961,10 @@
         <v>1</v>
       </c>
       <c r="G36" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H36" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -1967,21 +1973,21 @@
         <v>0</v>
       </c>
       <c r="K36" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B37" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C37" t="s">
         <v>14</v>
       </c>
       <c r="D37" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E37">
         <v>134990</v>
@@ -1990,10 +1996,10 @@
         <v>1</v>
       </c>
       <c r="G37" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H37" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -2002,7 +2008,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="38">
@@ -2016,19 +2022,19 @@
         <v>14</v>
       </c>
       <c r="D38" t="s">
-        <v>77</v>
+        <v>36</v>
       </c>
       <c r="E38">
-        <v>79990</v>
+        <v>134990</v>
       </c>
       <c r="F38">
         <v>1</v>
       </c>
       <c r="G38" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="H38" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -2037,33 +2043,33 @@
         <v>0</v>
       </c>
       <c r="K38" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
+        <v>77</v>
+      </c>
+      <c r="B39" t="s">
+        <v>78</v>
+      </c>
+      <c r="C39" t="s">
+        <v>14</v>
+      </c>
+      <c r="D39" t="s">
         <v>79</v>
       </c>
-      <c r="B39" t="s">
+      <c r="E39">
+        <v>79990</v>
+      </c>
+      <c r="F39">
+        <v>1</v>
+      </c>
+      <c r="G39" t="s">
         <v>80</v>
       </c>
-      <c r="C39" t="s">
-        <v>14</v>
-      </c>
-      <c r="D39" t="s">
-        <v>22</v>
-      </c>
-      <c r="E39">
-        <v>134990</v>
-      </c>
-      <c r="F39">
-        <v>1</v>
-      </c>
-      <c r="G39" t="s">
-        <v>30</v>
-      </c>
       <c r="H39" t="s">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="I39">
         <v>0</v>
@@ -2072,21 +2078,21 @@
         <v>0</v>
       </c>
       <c r="K39" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B40" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C40" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="D40" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E40">
         <v>134990</v>
@@ -2095,10 +2101,10 @@
         <v>1</v>
       </c>
       <c r="G40" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H40" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I40">
         <v>0</v>
@@ -2107,21 +2113,21 @@
         <v>0</v>
       </c>
       <c r="K40" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B41" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C41" t="s">
+        <v>31</v>
+      </c>
+      <c r="D41" t="s">
         <v>28</v>
-      </c>
-      <c r="D41" t="s">
-        <v>44</v>
       </c>
       <c r="E41">
         <v>134990</v>
@@ -2130,10 +2136,10 @@
         <v>1</v>
       </c>
       <c r="G41" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H41" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I41">
         <v>0</v>
@@ -2142,21 +2148,21 @@
         <v>0</v>
       </c>
       <c r="K41" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B42" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C42" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D42" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E42">
         <v>134990</v>
@@ -2165,10 +2171,10 @@
         <v>1</v>
       </c>
       <c r="G42" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H42" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -2177,21 +2183,21 @@
         <v>0</v>
       </c>
       <c r="K42" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B43" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C43" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D43" t="s">
-        <v>81</v>
+        <v>15</v>
       </c>
       <c r="E43">
         <v>134990</v>
@@ -2200,10 +2206,10 @@
         <v>1</v>
       </c>
       <c r="G43" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H43" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I43">
         <v>0</v>
@@ -2212,33 +2218,33 @@
         <v>0</v>
       </c>
       <c r="K43" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
+        <v>81</v>
+      </c>
+      <c r="B44" t="s">
         <v>82</v>
       </c>
-      <c r="B44" t="s">
+      <c r="C44" t="s">
+        <v>31</v>
+      </c>
+      <c r="D44" t="s">
         <v>83</v>
       </c>
-      <c r="C44" t="s">
-        <v>28</v>
-      </c>
-      <c r="D44" t="s">
-        <v>22</v>
-      </c>
       <c r="E44">
-        <v>119990</v>
+        <v>134990</v>
       </c>
       <c r="F44">
         <v>1</v>
       </c>
       <c r="G44" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H44" t="s">
-        <v>84</v>
+        <v>33</v>
       </c>
       <c r="I44">
         <v>0</v>
@@ -2247,21 +2253,21 @@
         <v>0</v>
       </c>
       <c r="K44" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B45" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C45" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D45" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E45">
         <v>119990</v>
@@ -2270,10 +2276,10 @@
         <v>1</v>
       </c>
       <c r="G45" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H45" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I45">
         <v>0</v>
@@ -2282,21 +2288,21 @@
         <v>0</v>
       </c>
       <c r="K45" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B46" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C46" t="s">
+        <v>31</v>
+      </c>
+      <c r="D46" t="s">
         <v>28</v>
-      </c>
-      <c r="D46" t="s">
-        <v>44</v>
       </c>
       <c r="E46">
         <v>119990</v>
@@ -2305,10 +2311,10 @@
         <v>1</v>
       </c>
       <c r="G46" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H46" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I46">
         <v>0</v>
@@ -2317,21 +2323,21 @@
         <v>0</v>
       </c>
       <c r="K46" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
+        <v>84</v>
+      </c>
+      <c r="B47" t="s">
         <v>85</v>
       </c>
-      <c r="B47" t="s">
-        <v>86</v>
-      </c>
       <c r="C47" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D47" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="E47">
         <v>119990</v>
@@ -2340,10 +2346,10 @@
         <v>1</v>
       </c>
       <c r="G47" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H47" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I47">
         <v>0</v>
@@ -2352,21 +2358,21 @@
         <v>0</v>
       </c>
       <c r="K47" t="s">
-        <v>87</v>
+        <v>17</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B48" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C48" t="s">
+        <v>31</v>
+      </c>
+      <c r="D48" t="s">
         <v>28</v>
-      </c>
-      <c r="D48" t="s">
-        <v>44</v>
       </c>
       <c r="E48">
         <v>119990</v>
@@ -2375,10 +2381,10 @@
         <v>1</v>
       </c>
       <c r="G48" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H48" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I48">
         <v>0</v>
@@ -2387,56 +2393,56 @@
         <v>0</v>
       </c>
       <c r="K48" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
+        <v>87</v>
+      </c>
+      <c r="B49" t="s">
         <v>88</v>
       </c>
-      <c r="B49" t="s">
+      <c r="C49" t="s">
+        <v>31</v>
+      </c>
+      <c r="D49" t="s">
+        <v>47</v>
+      </c>
+      <c r="E49">
+        <v>119990</v>
+      </c>
+      <c r="F49">
+        <v>1</v>
+      </c>
+      <c r="G49" t="s">
+        <v>33</v>
+      </c>
+      <c r="H49" t="s">
+        <v>86</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49" t="s">
         <v>89</v>
-      </c>
-      <c r="C49" t="s">
-        <v>28</v>
-      </c>
-      <c r="D49" t="s">
-        <v>29</v>
-      </c>
-      <c r="E49">
-        <v>39990</v>
-      </c>
-      <c r="F49">
-        <v>1</v>
-      </c>
-      <c r="G49" t="s">
-        <v>30</v>
-      </c>
-      <c r="H49" t="s">
-        <v>84</v>
-      </c>
-      <c r="I49">
-        <v>0</v>
-      </c>
-      <c r="J49">
-        <v>0</v>
-      </c>
-      <c r="K49" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B50" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C50" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D50" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E50">
         <v>39990</v>
@@ -2445,10 +2451,10 @@
         <v>1</v>
       </c>
       <c r="G50" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H50" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I50">
         <v>0</v>
@@ -2457,7 +2463,7 @@
         <v>0</v>
       </c>
       <c r="K50" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="51">
@@ -2468,10 +2474,10 @@
         <v>91</v>
       </c>
       <c r="C51" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D51" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E51">
         <v>39990</v>
@@ -2480,10 +2486,10 @@
         <v>1</v>
       </c>
       <c r="G51" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H51" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I51">
         <v>0</v>
@@ -2492,7 +2498,7 @@
         <v>0</v>
       </c>
       <c r="K51" t="s">
-        <v>87</v>
+        <v>17</v>
       </c>
     </row>
     <row r="52">
@@ -2503,22 +2509,22 @@
         <v>93</v>
       </c>
       <c r="C52" t="s">
-        <v>69</v>
+        <v>31</v>
       </c>
       <c r="D52" t="s">
-        <v>94</v>
+        <v>36</v>
       </c>
       <c r="E52">
-        <v>140990</v>
+        <v>39990</v>
       </c>
       <c r="F52">
         <v>1</v>
       </c>
       <c r="G52" t="s">
-        <v>66</v>
+        <v>33</v>
       </c>
       <c r="H52" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I52">
         <v>0</v>
@@ -2527,33 +2533,33 @@
         <v>0</v>
       </c>
       <c r="K52" t="s">
-        <v>31</v>
+        <v>89</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B53" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C53" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D53" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E53">
-        <v>145990</v>
+        <v>140990</v>
       </c>
       <c r="F53">
         <v>1</v>
       </c>
       <c r="G53" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H53" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I53">
         <v>0</v>
@@ -2562,33 +2568,33 @@
         <v>0</v>
       </c>
       <c r="K53" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B54" t="s">
+        <v>95</v>
+      </c>
+      <c r="C54" t="s">
+        <v>71</v>
+      </c>
+      <c r="D54" t="s">
         <v>97</v>
       </c>
-      <c r="C54" t="s">
-        <v>14</v>
-      </c>
-      <c r="D54" t="s">
-        <v>22</v>
-      </c>
-      <c r="E54" s="2">
-        <v>199990</v>
+      <c r="E54">
+        <v>145990</v>
       </c>
       <c r="F54">
         <v>1</v>
       </c>
       <c r="G54" t="s">
-        <v>30</v>
+        <v>68</v>
       </c>
       <c r="H54" t="s">
-        <v>30</v>
+        <v>86</v>
       </c>
       <c r="I54">
         <v>0</v>
@@ -2597,21 +2603,21 @@
         <v>0</v>
       </c>
       <c r="K54" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B55" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C55" t="s">
         <v>14</v>
       </c>
       <c r="D55" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E55" s="2">
         <v>199990</v>
@@ -2620,10 +2626,10 @@
         <v>1</v>
       </c>
       <c r="G55" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H55" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I55">
         <v>0</v>
@@ -2632,21 +2638,21 @@
         <v>0</v>
       </c>
       <c r="K55" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B56" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C56" t="s">
         <v>14</v>
       </c>
       <c r="D56" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="E56" s="2">
         <v>199990</v>
@@ -2655,10 +2661,10 @@
         <v>1</v>
       </c>
       <c r="G56" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H56" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I56">
         <v>0</v>
@@ -2667,21 +2673,21 @@
         <v>0</v>
       </c>
       <c r="K56" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B57" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C57" t="s">
         <v>14</v>
       </c>
       <c r="D57" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E57" s="2">
         <v>199990</v>
@@ -2690,10 +2696,10 @@
         <v>1</v>
       </c>
       <c r="G57" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H57" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I57">
         <v>0</v>
@@ -2702,21 +2708,21 @@
         <v>0</v>
       </c>
       <c r="K57" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B58" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C58" t="s">
         <v>14</v>
       </c>
       <c r="D58" t="s">
-        <v>81</v>
+        <v>15</v>
       </c>
       <c r="E58" s="2">
         <v>199990</v>
@@ -2725,10 +2731,10 @@
         <v>1</v>
       </c>
       <c r="G58" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H58" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I58">
         <v>0</v>
@@ -2737,7 +2743,7 @@
         <v>0</v>
       </c>
       <c r="K58" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="59">
@@ -2748,22 +2754,22 @@
         <v>99</v>
       </c>
       <c r="C59" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="D59" t="s">
-        <v>22</v>
-      </c>
-      <c r="E59">
-        <v>155990</v>
+        <v>83</v>
+      </c>
+      <c r="E59" s="2">
+        <v>199990</v>
       </c>
       <c r="F59">
         <v>1</v>
       </c>
       <c r="G59" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H59" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I59">
         <v>0</v>
@@ -2772,21 +2778,21 @@
         <v>0</v>
       </c>
       <c r="K59" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B60" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C60" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D60" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E60">
         <v>155990</v>
@@ -2795,10 +2801,10 @@
         <v>1</v>
       </c>
       <c r="G60" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H60" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I60">
         <v>0</v>
@@ -2807,21 +2813,21 @@
         <v>0</v>
       </c>
       <c r="K60" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B61" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C61" t="s">
+        <v>31</v>
+      </c>
+      <c r="D61" t="s">
         <v>28</v>
-      </c>
-      <c r="D61" t="s">
-        <v>44</v>
       </c>
       <c r="E61">
         <v>155990</v>
@@ -2830,10 +2836,10 @@
         <v>1</v>
       </c>
       <c r="G61" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H61" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I61">
         <v>0</v>
@@ -2842,21 +2848,21 @@
         <v>0</v>
       </c>
       <c r="K61" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B62" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C62" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D62" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E62">
         <v>155990</v>
@@ -2865,10 +2871,10 @@
         <v>1</v>
       </c>
       <c r="G62" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H62" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I62">
         <v>0</v>
@@ -2877,7 +2883,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="63">
@@ -2888,22 +2894,22 @@
         <v>101</v>
       </c>
       <c r="C63" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D63" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E63">
-        <v>269990</v>
+        <v>155990</v>
       </c>
       <c r="F63">
         <v>1</v>
       </c>
       <c r="G63" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H63" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I63">
         <v>0</v>
@@ -2912,21 +2918,21 @@
         <v>0</v>
       </c>
       <c r="K63" t="s">
-        <v>102</v>
+        <v>17</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B64" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C64" t="s">
         <v>14</v>
       </c>
       <c r="D64" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E64">
         <v>269990</v>
@@ -2935,10 +2941,10 @@
         <v>1</v>
       </c>
       <c r="G64" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H64" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I64">
         <v>0</v>
@@ -2947,21 +2953,21 @@
         <v>0</v>
       </c>
       <c r="K64" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B65" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C65" t="s">
         <v>14</v>
       </c>
       <c r="D65" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="E65">
         <v>269990</v>
@@ -2970,10 +2976,10 @@
         <v>1</v>
       </c>
       <c r="G65" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H65" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I65">
         <v>0</v>
@@ -2982,21 +2988,21 @@
         <v>0</v>
       </c>
       <c r="K65" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B66" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C66" t="s">
         <v>14</v>
       </c>
       <c r="D66" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E66">
         <v>269990</v>
@@ -3005,10 +3011,10 @@
         <v>1</v>
       </c>
       <c r="G66" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H66" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I66">
         <v>0</v>
@@ -3017,21 +3023,21 @@
         <v>0</v>
       </c>
       <c r="K66" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B67" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C67" t="s">
         <v>14</v>
       </c>
       <c r="D67" t="s">
-        <v>81</v>
+        <v>15</v>
       </c>
       <c r="E67">
         <v>269990</v>
@@ -3040,10 +3046,10 @@
         <v>1</v>
       </c>
       <c r="G67" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H67" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I67">
         <v>0</v>
@@ -3052,56 +3058,56 @@
         <v>0</v>
       </c>
       <c r="K67" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
+        <v>102</v>
+      </c>
+      <c r="B68" t="s">
         <v>103</v>
       </c>
-      <c r="B68" t="s">
+      <c r="C68" t="s">
+        <v>14</v>
+      </c>
+      <c r="D68" t="s">
+        <v>83</v>
+      </c>
+      <c r="E68">
+        <v>269990</v>
+      </c>
+      <c r="F68">
+        <v>1</v>
+      </c>
+      <c r="G68" t="s">
+        <v>33</v>
+      </c>
+      <c r="H68" t="s">
+        <v>33</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>0</v>
+      </c>
+      <c r="K68" t="s">
         <v>104</v>
-      </c>
-      <c r="C68" t="s">
-        <v>14</v>
-      </c>
-      <c r="D68" t="s">
-        <v>25</v>
-      </c>
-      <c r="E68">
-        <v>199990</v>
-      </c>
-      <c r="F68">
-        <v>1</v>
-      </c>
-      <c r="G68" t="s">
-        <v>30</v>
-      </c>
-      <c r="H68" t="s">
-        <v>30</v>
-      </c>
-      <c r="I68">
-        <v>0</v>
-      </c>
-      <c r="J68">
-        <v>0</v>
-      </c>
-      <c r="K68" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B69" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C69" t="s">
         <v>14</v>
       </c>
       <c r="D69" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="E69">
         <v>199990</v>
@@ -3110,10 +3116,10 @@
         <v>1</v>
       </c>
       <c r="G69" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H69" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I69">
         <v>0</v>
@@ -3122,21 +3128,21 @@
         <v>0</v>
       </c>
       <c r="K69" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B70" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C70" t="s">
         <v>14</v>
       </c>
       <c r="D70" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E70">
         <v>199990</v>
@@ -3145,10 +3151,10 @@
         <v>1</v>
       </c>
       <c r="G70" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H70" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I70">
         <v>0</v>
@@ -3157,21 +3163,21 @@
         <v>0</v>
       </c>
       <c r="K70" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B71" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C71" t="s">
         <v>14</v>
       </c>
       <c r="D71" t="s">
-        <v>81</v>
+        <v>15</v>
       </c>
       <c r="E71">
         <v>199990</v>
@@ -3180,10 +3186,10 @@
         <v>1</v>
       </c>
       <c r="G71" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H71" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I71">
         <v>0</v>
@@ -3192,7 +3198,7 @@
         <v>0</v>
       </c>
       <c r="K71" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="72">
@@ -3203,22 +3209,22 @@
         <v>106</v>
       </c>
       <c r="C72" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="D72" t="s">
-        <v>22</v>
+        <v>83</v>
       </c>
       <c r="E72">
-        <v>194990</v>
+        <v>199990</v>
       </c>
       <c r="F72">
         <v>1</v>
       </c>
       <c r="G72" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H72" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I72">
         <v>0</v>
@@ -3227,21 +3233,21 @@
         <v>0</v>
       </c>
       <c r="K72" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B73" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C73" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D73" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E73">
         <v>194990</v>
@@ -3250,10 +3256,10 @@
         <v>1</v>
       </c>
       <c r="G73" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H73" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I73">
         <v>0</v>
@@ -3262,21 +3268,21 @@
         <v>0</v>
       </c>
       <c r="K73" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B74" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C74" t="s">
+        <v>31</v>
+      </c>
+      <c r="D74" t="s">
         <v>28</v>
-      </c>
-      <c r="D74" t="s">
-        <v>44</v>
       </c>
       <c r="E74">
         <v>194990</v>
@@ -3285,10 +3291,10 @@
         <v>1</v>
       </c>
       <c r="G74" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H74" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I74">
         <v>0</v>
@@ -3297,21 +3303,21 @@
         <v>0</v>
       </c>
       <c r="K74" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B75" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C75" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D75" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E75">
         <v>194990</v>
@@ -3320,10 +3326,10 @@
         <v>1</v>
       </c>
       <c r="G75" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H75" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I75">
         <v>0</v>
@@ -3332,7 +3338,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="76">
@@ -3343,31 +3349,66 @@
         <v>108</v>
       </c>
       <c r="C76" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D76" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E76">
+        <v>194990</v>
+      </c>
+      <c r="F76">
+        <v>1</v>
+      </c>
+      <c r="G76" t="s">
+        <v>33</v>
+      </c>
+      <c r="H76" t="s">
+        <v>33</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>0</v>
+      </c>
+      <c r="K76" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>109</v>
+      </c>
+      <c r="B77" t="s">
+        <v>110</v>
+      </c>
+      <c r="C77" t="s">
+        <v>14</v>
+      </c>
+      <c r="D77" t="s">
+        <v>26</v>
+      </c>
+      <c r="E77">
         <v>202990</v>
       </c>
-      <c r="F76">
-        <v>1</v>
-      </c>
-      <c r="G76" t="s">
-        <v>23</v>
-      </c>
-      <c r="H76" t="s">
-        <v>23</v>
-      </c>
-      <c r="I76">
-        <v>0</v>
-      </c>
-      <c r="J76">
-        <v>0</v>
-      </c>
-      <c r="K76" t="s">
-        <v>63</v>
+      <c r="F77">
+        <v>1</v>
+      </c>
+      <c r="G77" t="s">
+        <v>16</v>
+      </c>
+      <c r="H77" t="s">
+        <v>16</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>0</v>
+      </c>
+      <c r="K77" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/data/catalogo_jusp.xlsx
+++ b/data/catalogo_jusp.xlsx
@@ -56,6 +56,18 @@
     <t>descuento</t>
   </si>
   <si>
+    <t>is_flash_24h</t>
+  </si>
+  <si>
+    <t>flash_starts_at</t>
+  </si>
+  <si>
+    <t>flash_expires_at</t>
+  </si>
+  <si>
+    <t>is_active</t>
+  </si>
+  <si>
     <t>nike-hf5407-010</t>
   </si>
   <si>
@@ -74,6 +86,141 @@
     <t>Black</t>
   </si>
   <si>
+    <t>TRUE</t>
+  </si>
+  <si>
+    <t>nike-cn5263-010</t>
+  </si>
+  <si>
+    <t>Sujetador deportivo de entrenamiento NIKE CLASSIC SWOOSH</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>jordan-cw2427-010</t>
+  </si>
+  <si>
+    <t>AS WJ JUMPMAN BRA</t>
+  </si>
+  <si>
+    <t>Jordan</t>
+  </si>
+  <si>
+    <t>nike-dm0672-100</t>
+  </si>
+  <si>
+    <t>Nike Low Impact Support Padded Letter Sports Bra Women Underwear White</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L </t>
+  </si>
+  <si>
+    <t>White</t>
+  </si>
+  <si>
+    <t>nike-fb4125-100</t>
+  </si>
+  <si>
+    <t>Sujetador deportivo de entrenamiento NIKE DRY BRA</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>nike-fb4081-675</t>
+  </si>
+  <si>
+    <t>Sujetador deportivo Nike Swoosh</t>
+  </si>
+  <si>
+    <t>bright pink</t>
+  </si>
+  <si>
+    <t>nike-fb4081-100</t>
+  </si>
+  <si>
+    <t>Nike Nk Swsh Med Spt Futura Br</t>
+  </si>
+  <si>
+    <t>jordan-fb6873-633</t>
+  </si>
+  <si>
+    <t>JORDAN BRAND AS W J SPT JUMPMAN BRA PICANTE RED</t>
+  </si>
+  <si>
+    <t>Red</t>
+  </si>
+  <si>
+    <t>nike-dd1459-010</t>
+  </si>
+  <si>
+    <t>Nike women's sports bra, intensity</t>
+  </si>
+  <si>
+    <t>nike-cz4457-100</t>
+  </si>
+  <si>
+    <t>Nike DIR-FIT Training Sports Bra</t>
+  </si>
+  <si>
+    <t>nike-dq5135-539</t>
+  </si>
+  <si>
+    <t>NIKE AS W NK DF SWSH</t>
+  </si>
+  <si>
+    <t>light periwinkle blue</t>
+  </si>
+  <si>
+    <t>nike-dq5135-043</t>
+  </si>
+  <si>
+    <t>light grey</t>
+  </si>
+  <si>
+    <t>jordan-cw2427-386</t>
+  </si>
+  <si>
+    <t>JORDAN BRAND AS W J JUMPMAN</t>
+  </si>
+  <si>
+    <t>olive green</t>
+  </si>
+  <si>
+    <t>nike-bv3637-010</t>
+  </si>
+  <si>
+    <t>Women's Medium-Support 1-Piece Pad Sports Bra</t>
+  </si>
+  <si>
+    <t>Blanck</t>
+  </si>
+  <si>
+    <t>nike-fz2856-010</t>
+  </si>
+  <si>
+    <t>NIKE AS W NSW SS TEE OC VARZITY BLACK</t>
+  </si>
+  <si>
+    <t>puma-521598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sujetador Puma MID IMPACT STRONG SPORT-BH  W</t>
+  </si>
+  <si>
+    <t>Puma</t>
+  </si>
+  <si>
+    <t>slate blue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">puma-526429 </t>
+  </si>
+  <si>
+    <t>Puma breathable sports bra</t>
+  </si>
+  <si>
     <t>short-nike-kids</t>
   </si>
   <si>
@@ -104,18 +251,12 @@
     <t>Pink</t>
   </si>
   <si>
-    <t>M</t>
-  </si>
-  <si>
     <t>jordan-club-cap</t>
   </si>
   <si>
     <t>Jordan Club Cap</t>
   </si>
   <si>
-    <t>Jordan</t>
-  </si>
-  <si>
     <t>S/M</t>
   </si>
   <si>
@@ -146,9 +287,6 @@
     <t>Nike sujetador tops</t>
   </si>
   <si>
-    <t>White</t>
-  </si>
-  <si>
     <t>nike-dunk-low-retro</t>
   </si>
   <si>
@@ -161,9 +299,6 @@
     <t>Nike Sport BH High Compression Bra Swoosh Sujetador</t>
   </si>
   <si>
-    <t>L</t>
-  </si>
-  <si>
     <t>nike-unisex-dri-fit-fly-unstrukturierte-swoosh-cap</t>
   </si>
   <si>
@@ -195,9 +330,6 @@
   </si>
   <si>
     <t>Puma Camiseta Deportiva sin Mangas Ajustada con Estampado de Letras para Mujer Negro</t>
-  </si>
-  <si>
-    <t>Puma</t>
   </si>
   <si>
     <t>jordan-cw2427-360</t>
@@ -357,7 +489,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -366,9 +498,15 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -381,7 +519,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF111111"/>
+        <fgColor rgb="FF9ACCFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -391,11 +529,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -705,58 +845,73 @@
     <col min="2" max="2" width="27.08203" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11.16406" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.58203" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.5">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+    <row r="1" s="1" customFormat="1" ht="14.5">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E2">
         <v>135990</v>
@@ -765,10 +920,10 @@
         <v>1</v>
       </c>
       <c r="G2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -777,249 +932,285 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>17</v>
+        <v>21</v>
+      </c>
+      <c r="M2" t="s">
+        <v>22</v>
+      </c>
+      <c r="N2" s="3">
+        <v>46130.833333333328</v>
+      </c>
+      <c r="O2" s="3">
+        <v>46130.957638888889</v>
+      </c>
+      <c r="P2" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E3">
-        <v>88990</v>
+        <v>99990</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3" t="s">
         <v>21</v>
       </c>
-      <c r="H3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3" t="s">
-        <v>17</v>
-      </c>
       <c r="L3">
-        <v>5</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E4">
-        <v>88990</v>
+        <v>119990</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4" t="s">
         <v>21</v>
       </c>
-      <c r="H4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4" t="s">
-        <v>17</v>
-      </c>
       <c r="L4">
-        <v>5</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="N4" s="3"/>
+      <c r="O4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E5">
-        <v>89990</v>
+        <v>95990</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>27</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="L5">
+        <v>45</v>
+      </c>
+      <c r="N5" s="3"/>
+      <c r="O5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" t="s">
         <v>25</v>
       </c>
-      <c r="C6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" t="s">
-        <v>28</v>
-      </c>
       <c r="E6">
-        <v>89990</v>
+        <v>95990</v>
       </c>
       <c r="F6">
         <v>1</v>
       </c>
       <c r="G6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="s">
-        <v>27</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="L6">
+        <v>45</v>
+      </c>
+      <c r="N6" s="3"/>
+      <c r="O6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="D7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7">
+        <v>110990</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7" t="s">
         <v>32</v>
       </c>
-      <c r="E7">
-        <v>75990</v>
-      </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-      <c r="G7" t="s">
-        <v>33</v>
-      </c>
-      <c r="H7" t="s">
-        <v>33</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7" t="s">
-        <v>34</v>
-      </c>
+      <c r="L7">
+        <v>20</v>
+      </c>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C8" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="D8" t="s">
         <v>35</v>
       </c>
       <c r="E8">
-        <v>79990</v>
+        <v>110990</v>
       </c>
       <c r="F8">
         <v>1</v>
       </c>
       <c r="G8" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="H8" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="s">
-        <v>34</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="L8">
+        <v>20</v>
+      </c>
+      <c r="N8" s="3"/>
+      <c r="O8" s="3"/>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="C9" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="D9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E9">
-        <v>78990</v>
+        <v>195990</v>
       </c>
       <c r="F9">
         <v>1</v>
       </c>
       <c r="G9" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="H9" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -1028,183 +1219,207 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>34</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="N9" s="3"/>
+      <c r="O9" s="3"/>
     </row>
     <row r="10">
       <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
         <v>37</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10">
+        <v>205990</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H10" t="s">
+        <v>20</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10" t="s">
         <v>38</v>
       </c>
-      <c r="C10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D10" t="s">
-        <v>28</v>
-      </c>
-      <c r="E10">
-        <v>69990</v>
-      </c>
-      <c r="F10">
-        <v>1</v>
-      </c>
-      <c r="G10" t="s">
-        <v>16</v>
-      </c>
-      <c r="H10" t="s">
-        <v>16</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10" t="s">
-        <v>39</v>
-      </c>
+      <c r="N10" s="3"/>
+      <c r="O10" s="3"/>
     </row>
     <row r="11">
       <c r="A11" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" t="s">
         <v>40</v>
       </c>
-      <c r="B11" t="s">
-        <v>41</v>
-      </c>
       <c r="C11" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D11" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="E11">
-        <v>99990</v>
+        <v>139990</v>
       </c>
       <c r="F11">
         <v>1</v>
       </c>
       <c r="G11" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H11" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="s">
-        <v>42</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="L11">
+        <v>20</v>
+      </c>
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
     </row>
     <row r="12">
       <c r="A12" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12">
+        <v>125990</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12" t="s">
+        <v>20</v>
+      </c>
+      <c r="H12" t="s">
+        <v>20</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="K12" t="s">
         <v>43</v>
       </c>
-      <c r="B12" t="s">
-        <v>44</v>
-      </c>
-      <c r="C12" t="s">
-        <v>14</v>
-      </c>
-      <c r="D12">
-        <v>7</v>
-      </c>
-      <c r="E12">
-        <v>99990</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12" t="s">
-        <v>33</v>
-      </c>
-      <c r="H12" t="s">
-        <v>33</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12" t="s">
-        <v>34</v>
-      </c>
+      <c r="L12">
+        <v>35</v>
+      </c>
+      <c r="N12" s="3"/>
+      <c r="O12" s="3"/>
     </row>
     <row r="13">
       <c r="A13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" t="s">
         <v>45</v>
       </c>
-      <c r="B13" t="s">
-        <v>46</v>
-      </c>
       <c r="C13" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D13" t="s">
-        <v>47</v>
-      </c>
-      <c r="E13" s="2">
-        <v>119990</v>
+        <v>35</v>
+      </c>
+      <c r="E13">
+        <v>99990</v>
       </c>
       <c r="F13">
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H13" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="s">
-        <v>42</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="L13">
+        <v>25</v>
+      </c>
+      <c r="N13" s="3"/>
+      <c r="O13" s="3"/>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B14" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C14" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D14" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14">
+        <v>95990</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" t="s">
+        <v>20</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+      <c r="K14" t="s">
         <v>32</v>
       </c>
-      <c r="E14">
-        <v>65990</v>
-      </c>
-      <c r="F14">
-        <v>1</v>
-      </c>
-      <c r="G14" t="s">
-        <v>33</v>
-      </c>
-      <c r="H14" t="s">
-        <v>33</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14" t="s">
-        <v>50</v>
-      </c>
+      <c r="L14">
+        <v>30</v>
+      </c>
+      <c r="N14" s="3"/>
+      <c r="O14" s="3"/>
     </row>
     <row r="15">
       <c r="A15" t="s">
@@ -1214,337 +1429,382 @@
         <v>49</v>
       </c>
       <c r="C15" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D15" t="s">
         <v>35</v>
       </c>
       <c r="E15">
-        <v>75990</v>
+        <v>119990</v>
       </c>
       <c r="F15">
         <v>1</v>
       </c>
       <c r="G15" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="H15" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="s">
         <v>50</v>
       </c>
+      <c r="L15">
+        <v>30</v>
+      </c>
+      <c r="N15" s="3"/>
+      <c r="O15" s="3"/>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B16" t="s">
         <v>49</v>
       </c>
       <c r="C16" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E16">
-        <v>85990</v>
+        <v>119990</v>
       </c>
       <c r="F16">
         <v>1</v>
       </c>
       <c r="G16" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="H16" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="s">
-        <v>50</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="L16">
+        <v>30</v>
+      </c>
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B17" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C17" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="D17" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="E17">
-        <v>79990</v>
+        <v>119990</v>
       </c>
       <c r="F17">
         <v>1</v>
       </c>
       <c r="G17" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H17" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="s">
-        <v>34</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="L17">
+        <v>35</v>
+      </c>
+      <c r="N17" s="3"/>
+      <c r="O17" s="3"/>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B18" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C18" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E18">
-        <v>79990</v>
+        <v>99990</v>
       </c>
       <c r="F18">
         <v>1</v>
       </c>
       <c r="G18" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H18" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="s">
-        <v>34</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="L18">
+        <v>25</v>
+      </c>
+      <c r="N18" s="3"/>
+      <c r="O18" s="3"/>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="B19" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="C19" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D19" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E19">
-        <v>79990</v>
+        <v>86990</v>
       </c>
       <c r="F19">
         <v>1</v>
       </c>
       <c r="G19" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H19" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="s">
-        <v>34</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="L19">
+        <v>30</v>
+      </c>
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="B20" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="C20" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D20" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="E20">
-        <v>79990</v>
+        <v>86990</v>
       </c>
       <c r="F20">
         <v>1</v>
       </c>
       <c r="G20" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H20" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="s">
-        <v>34</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="L20">
+        <v>30</v>
+      </c>
+      <c r="N20" s="3"/>
+      <c r="O20" s="3"/>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="B21" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="C21" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D21" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E21">
-        <v>79990</v>
+        <v>86990</v>
       </c>
       <c r="F21">
         <v>1</v>
       </c>
       <c r="G21" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H21" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="s">
-        <v>34</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="L21">
+        <v>30</v>
+      </c>
+      <c r="N21" s="3"/>
+      <c r="O21" s="3"/>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="B22" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="C22" t="s">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="D22" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="E22">
-        <v>155990</v>
+        <v>96990</v>
       </c>
       <c r="F22">
         <v>1</v>
       </c>
       <c r="G22" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H22" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="s">
-        <v>56</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="L22">
+        <v>25</v>
+      </c>
+      <c r="N22" s="3"/>
+      <c r="O22" s="3"/>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="B23" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C23" t="s">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="D23" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="E23">
-        <v>155990</v>
+        <v>95990</v>
       </c>
       <c r="F23">
         <v>1</v>
       </c>
       <c r="G23" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H23" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="s">
-        <v>56</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="L23">
+        <v>25</v>
+      </c>
+      <c r="N23" s="3"/>
+      <c r="O23" s="3"/>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="B24" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="C24" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D24" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="E24">
-        <v>155990</v>
+        <v>88990</v>
       </c>
       <c r="F24">
         <v>1</v>
       </c>
       <c r="G24" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="H24" t="s">
-        <v>16</v>
+        <v>71</v>
       </c>
       <c r="I24">
         <v>0</v>
@@ -1553,33 +1813,36 @@
         <v>0</v>
       </c>
       <c r="K24" t="s">
-        <v>56</v>
+        <v>21</v>
+      </c>
+      <c r="L24">
+        <v>5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="B25" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="C25" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D25" t="s">
-        <v>15</v>
+        <v>72</v>
       </c>
       <c r="E25">
-        <v>155990</v>
+        <v>88990</v>
       </c>
       <c r="F25">
         <v>1</v>
       </c>
       <c r="G25" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="H25" t="s">
-        <v>16</v>
+        <v>71</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -1588,33 +1851,36 @@
         <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>56</v>
+        <v>21</v>
+      </c>
+      <c r="L25">
+        <v>5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="B26" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="C26" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="D26" t="s">
-        <v>26</v>
+        <v>75</v>
       </c>
       <c r="E26">
-        <v>49990</v>
+        <v>89990</v>
       </c>
       <c r="F26">
         <v>1</v>
       </c>
       <c r="G26" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H26" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -1623,33 +1889,33 @@
         <v>0</v>
       </c>
       <c r="K26" t="s">
-        <v>17</v>
+        <v>76</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="B27" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="C27" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="D27" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E27">
-        <v>49990</v>
+        <v>89990</v>
       </c>
       <c r="F27">
         <v>1</v>
       </c>
       <c r="G27" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H27" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -1658,33 +1924,33 @@
         <v>0</v>
       </c>
       <c r="K27" t="s">
-        <v>17</v>
+        <v>76</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="B28" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="C28" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D28" t="s">
-        <v>28</v>
+        <v>79</v>
       </c>
       <c r="E28">
-        <v>125990</v>
+        <v>75990</v>
       </c>
       <c r="F28">
         <v>1</v>
       </c>
       <c r="G28" t="s">
-        <v>16</v>
+        <v>80</v>
       </c>
       <c r="H28" t="s">
-        <v>16</v>
+        <v>80</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -1693,33 +1959,33 @@
         <v>0</v>
       </c>
       <c r="K28" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="B29" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="C29" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="D29" t="s">
-        <v>26</v>
+        <v>82</v>
       </c>
       <c r="E29">
-        <v>155990</v>
+        <v>79990</v>
       </c>
       <c r="F29">
         <v>1</v>
       </c>
       <c r="G29" t="s">
-        <v>16</v>
+        <v>80</v>
       </c>
       <c r="H29" t="s">
-        <v>16</v>
+        <v>80</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -1728,33 +1994,33 @@
         <v>0</v>
       </c>
       <c r="K29" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="B30" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="C30" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="D30" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="E30">
-        <v>155990</v>
+        <v>78990</v>
       </c>
       <c r="F30">
         <v>1</v>
       </c>
       <c r="G30" t="s">
-        <v>16</v>
+        <v>80</v>
       </c>
       <c r="H30" t="s">
-        <v>16</v>
+        <v>80</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -1763,33 +2029,33 @@
         <v>0</v>
       </c>
       <c r="K30" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="B31" t="s">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="C31" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D31" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E31">
-        <v>155990</v>
+        <v>69990</v>
       </c>
       <c r="F31">
         <v>1</v>
       </c>
       <c r="G31" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H31" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -1798,33 +2064,33 @@
         <v>0</v>
       </c>
       <c r="K31" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="B32" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="C32" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D32" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E32">
-        <v>129990</v>
+        <v>99990</v>
       </c>
       <c r="F32">
         <v>1</v>
       </c>
       <c r="G32" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="H32" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -1833,33 +2099,33 @@
         <v>0</v>
       </c>
       <c r="K32" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="B33" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="C33" t="s">
-        <v>14</v>
-      </c>
-      <c r="D33" t="s">
-        <v>36</v>
+        <v>18</v>
+      </c>
+      <c r="D33">
+        <v>7</v>
       </c>
       <c r="E33">
-        <v>129990</v>
+        <v>99990</v>
       </c>
       <c r="F33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G33" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="H33" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -1868,33 +2134,33 @@
         <v>0</v>
       </c>
       <c r="K33" t="s">
-        <v>17</v>
+        <v>81</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="B34" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="C34" t="s">
-        <v>71</v>
+        <v>18</v>
       </c>
       <c r="D34" t="s">
-        <v>72</v>
-      </c>
-      <c r="E34">
-        <v>179990</v>
+        <v>35</v>
+      </c>
+      <c r="E34" s="4">
+        <v>119990</v>
       </c>
       <c r="F34">
         <v>1</v>
       </c>
       <c r="G34" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="H34" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -1903,33 +2169,33 @@
         <v>0</v>
       </c>
       <c r="K34" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="B35" t="s">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="C35" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D35" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="E35">
-        <v>159990</v>
+        <v>65990</v>
       </c>
       <c r="F35">
         <v>1</v>
       </c>
       <c r="G35" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="H35" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -1938,33 +2204,33 @@
         <v>0</v>
       </c>
       <c r="K35" t="s">
-        <v>17</v>
+        <v>95</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="B36" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="C36" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D36" t="s">
-        <v>32</v>
+        <v>82</v>
       </c>
       <c r="E36">
-        <v>134990</v>
+        <v>75990</v>
       </c>
       <c r="F36">
         <v>1</v>
       </c>
       <c r="G36" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="H36" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -1973,33 +2239,33 @@
         <v>0</v>
       </c>
       <c r="K36" t="s">
-        <v>17</v>
+        <v>95</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="B37" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="C37" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D37" t="s">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="E37">
-        <v>134990</v>
+        <v>85990</v>
       </c>
       <c r="F37">
         <v>1</v>
       </c>
       <c r="G37" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="H37" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -2008,33 +2274,33 @@
         <v>0</v>
       </c>
       <c r="K37" t="s">
-        <v>17</v>
+        <v>95</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="B38" t="s">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="C38" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D38" t="s">
-        <v>36</v>
+        <v>98</v>
       </c>
       <c r="E38">
-        <v>134990</v>
+        <v>79990</v>
       </c>
       <c r="F38">
         <v>1</v>
       </c>
       <c r="G38" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="H38" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -2043,21 +2309,21 @@
         <v>0</v>
       </c>
       <c r="K38" t="s">
-        <v>17</v>
+        <v>81</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="B39" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="C39" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D39" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E39">
         <v>79990</v>
@@ -2066,10 +2332,10 @@
         <v>1</v>
       </c>
       <c r="G39" t="s">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="H39" t="s">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="I39">
         <v>0</v>
@@ -2078,138 +2344,138 @@
         <v>0</v>
       </c>
       <c r="K39" t="s">
-        <v>17</v>
+        <v>81</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
+        <v>96</v>
+      </c>
+      <c r="B40" t="s">
+        <v>97</v>
+      </c>
+      <c r="C40" t="s">
+        <v>18</v>
+      </c>
+      <c r="D40" t="s">
+        <v>25</v>
+      </c>
+      <c r="E40">
+        <v>79990</v>
+      </c>
+      <c r="F40">
+        <v>1</v>
+      </c>
+      <c r="G40" t="s">
+        <v>20</v>
+      </c>
+      <c r="H40" t="s">
+        <v>20</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40" t="s">
         <v>81</v>
-      </c>
-      <c r="B40" t="s">
-        <v>82</v>
-      </c>
-      <c r="C40" t="s">
-        <v>14</v>
-      </c>
-      <c r="D40" t="s">
-        <v>26</v>
-      </c>
-      <c r="E40">
-        <v>134990</v>
-      </c>
-      <c r="F40">
-        <v>1</v>
-      </c>
-      <c r="G40" t="s">
-        <v>33</v>
-      </c>
-      <c r="H40" t="s">
-        <v>33</v>
-      </c>
-      <c r="I40">
-        <v>0</v>
-      </c>
-      <c r="J40">
-        <v>0</v>
-      </c>
-      <c r="K40" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
+        <v>96</v>
+      </c>
+      <c r="B41" t="s">
+        <v>97</v>
+      </c>
+      <c r="C41" t="s">
+        <v>18</v>
+      </c>
+      <c r="D41" t="s">
+        <v>35</v>
+      </c>
+      <c r="E41">
+        <v>79990</v>
+      </c>
+      <c r="F41">
+        <v>1</v>
+      </c>
+      <c r="G41" t="s">
+        <v>20</v>
+      </c>
+      <c r="H41" t="s">
+        <v>20</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41" t="s">
         <v>81</v>
-      </c>
-      <c r="B41" t="s">
-        <v>82</v>
-      </c>
-      <c r="C41" t="s">
-        <v>31</v>
-      </c>
-      <c r="D41" t="s">
-        <v>28</v>
-      </c>
-      <c r="E41">
-        <v>134990</v>
-      </c>
-      <c r="F41">
-        <v>1</v>
-      </c>
-      <c r="G41" t="s">
-        <v>33</v>
-      </c>
-      <c r="H41" t="s">
-        <v>33</v>
-      </c>
-      <c r="I41">
-        <v>0</v>
-      </c>
-      <c r="J41">
-        <v>0</v>
-      </c>
-      <c r="K41" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
+        <v>96</v>
+      </c>
+      <c r="B42" t="s">
+        <v>97</v>
+      </c>
+      <c r="C42" t="s">
+        <v>18</v>
+      </c>
+      <c r="D42" t="s">
+        <v>19</v>
+      </c>
+      <c r="E42">
+        <v>79990</v>
+      </c>
+      <c r="F42">
+        <v>1</v>
+      </c>
+      <c r="G42" t="s">
+        <v>20</v>
+      </c>
+      <c r="H42" t="s">
+        <v>20</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42" t="s">
         <v>81</v>
-      </c>
-      <c r="B42" t="s">
-        <v>82</v>
-      </c>
-      <c r="C42" t="s">
-        <v>31</v>
-      </c>
-      <c r="D42" t="s">
-        <v>47</v>
-      </c>
-      <c r="E42">
-        <v>134990</v>
-      </c>
-      <c r="F42">
-        <v>1</v>
-      </c>
-      <c r="G42" t="s">
-        <v>33</v>
-      </c>
-      <c r="H42" t="s">
-        <v>33</v>
-      </c>
-      <c r="I42">
-        <v>0</v>
-      </c>
-      <c r="J42">
-        <v>0</v>
-      </c>
-      <c r="K42" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="B43" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="C43" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="D43" t="s">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="E43">
-        <v>134990</v>
+        <v>155990</v>
       </c>
       <c r="F43">
         <v>1</v>
       </c>
       <c r="G43" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="H43" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="I43">
         <v>0</v>
@@ -2218,33 +2484,33 @@
         <v>0</v>
       </c>
       <c r="K43" t="s">
-        <v>17</v>
+        <v>101</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="B44" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="C44" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="D44" t="s">
-        <v>83</v>
+        <v>25</v>
       </c>
       <c r="E44">
-        <v>134990</v>
+        <v>155990</v>
       </c>
       <c r="F44">
         <v>1</v>
       </c>
       <c r="G44" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="H44" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="I44">
         <v>0</v>
@@ -2253,33 +2519,33 @@
         <v>0</v>
       </c>
       <c r="K44" t="s">
-        <v>17</v>
+        <v>101</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="B45" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="C45" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="D45" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="E45">
-        <v>119990</v>
+        <v>155990</v>
       </c>
       <c r="F45">
         <v>1</v>
       </c>
       <c r="G45" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="H45" t="s">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="I45">
         <v>0</v>
@@ -2288,33 +2554,33 @@
         <v>0</v>
       </c>
       <c r="K45" t="s">
-        <v>17</v>
+        <v>101</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="B46" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="C46" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="D46" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="E46">
-        <v>119990</v>
+        <v>155990</v>
       </c>
       <c r="F46">
         <v>1</v>
       </c>
       <c r="G46" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="H46" t="s">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="I46">
         <v>0</v>
@@ -2323,33 +2589,33 @@
         <v>0</v>
       </c>
       <c r="K46" t="s">
-        <v>17</v>
+        <v>101</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="B47" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="C47" t="s">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="D47" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="E47">
-        <v>119990</v>
+        <v>49990</v>
       </c>
       <c r="F47">
         <v>1</v>
       </c>
       <c r="G47" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="H47" t="s">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="I47">
         <v>0</v>
@@ -2358,33 +2624,33 @@
         <v>0</v>
       </c>
       <c r="K47" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="B48" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="C48" t="s">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="D48" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E48">
-        <v>119990</v>
+        <v>49990</v>
       </c>
       <c r="F48">
         <v>1</v>
       </c>
       <c r="G48" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="H48" t="s">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="I48">
         <v>0</v>
@@ -2393,33 +2659,33 @@
         <v>0</v>
       </c>
       <c r="K48" t="s">
-        <v>89</v>
+        <v>21</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="B49" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="C49" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D49" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="E49">
-        <v>119990</v>
+        <v>135990</v>
       </c>
       <c r="F49">
         <v>1</v>
       </c>
       <c r="G49" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="H49" t="s">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="I49">
         <v>0</v>
@@ -2428,33 +2694,33 @@
         <v>0</v>
       </c>
       <c r="K49" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="B50" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="C50" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="D50" t="s">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="E50">
-        <v>39990</v>
+        <v>155990</v>
       </c>
       <c r="F50">
         <v>1</v>
       </c>
       <c r="G50" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="H50" t="s">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="I50">
         <v>0</v>
@@ -2463,33 +2729,33 @@
         <v>0</v>
       </c>
       <c r="K50" t="s">
-        <v>17</v>
+        <v>109</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="B51" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="C51" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="D51" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E51">
-        <v>39990</v>
+        <v>155990</v>
       </c>
       <c r="F51">
         <v>1</v>
       </c>
       <c r="G51" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="H51" t="s">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="I51">
         <v>0</v>
@@ -2498,33 +2764,33 @@
         <v>0</v>
       </c>
       <c r="K51" t="s">
-        <v>17</v>
+        <v>109</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="B52" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="C52" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="D52" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="E52">
-        <v>39990</v>
+        <v>155990</v>
       </c>
       <c r="F52">
         <v>1</v>
       </c>
       <c r="G52" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="H52" t="s">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="I52">
         <v>0</v>
@@ -2533,33 +2799,33 @@
         <v>0</v>
       </c>
       <c r="K52" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="B53" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="C53" t="s">
-        <v>71</v>
+        <v>18</v>
       </c>
       <c r="D53" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="E53">
-        <v>140990</v>
+        <v>129990</v>
       </c>
       <c r="F53">
         <v>1</v>
       </c>
       <c r="G53" t="s">
-        <v>68</v>
+        <v>112</v>
       </c>
       <c r="H53" t="s">
-        <v>86</v>
+        <v>112</v>
       </c>
       <c r="I53">
         <v>0</v>
@@ -2568,33 +2834,33 @@
         <v>0</v>
       </c>
       <c r="K53" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="B54" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="C54" t="s">
-        <v>71</v>
+        <v>18</v>
       </c>
       <c r="D54" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="E54">
-        <v>145990</v>
+        <v>129990</v>
       </c>
       <c r="F54">
         <v>1</v>
       </c>
       <c r="G54" t="s">
-        <v>68</v>
+        <v>112</v>
       </c>
       <c r="H54" t="s">
-        <v>86</v>
+        <v>112</v>
       </c>
       <c r="I54">
         <v>0</v>
@@ -2603,33 +2869,33 @@
         <v>0</v>
       </c>
       <c r="K54" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="B55" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="C55" t="s">
-        <v>14</v>
+        <v>115</v>
       </c>
       <c r="D55" t="s">
-        <v>26</v>
-      </c>
-      <c r="E55" s="2">
-        <v>199990</v>
+        <v>116</v>
+      </c>
+      <c r="E55">
+        <v>179990</v>
       </c>
       <c r="F55">
         <v>1</v>
       </c>
       <c r="G55" t="s">
-        <v>33</v>
+        <v>112</v>
       </c>
       <c r="H55" t="s">
-        <v>33</v>
+        <v>112</v>
       </c>
       <c r="I55">
         <v>0</v>
@@ -2638,33 +2904,33 @@
         <v>0</v>
       </c>
       <c r="K55" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>98</v>
+        <v>117</v>
       </c>
       <c r="B56" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="C56" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D56" t="s">
-        <v>28</v>
-      </c>
-      <c r="E56" s="2">
-        <v>199990</v>
+        <v>116</v>
+      </c>
+      <c r="E56">
+        <v>159990</v>
       </c>
       <c r="F56">
         <v>1</v>
       </c>
       <c r="G56" t="s">
-        <v>33</v>
+        <v>112</v>
       </c>
       <c r="H56" t="s">
-        <v>33</v>
+        <v>112</v>
       </c>
       <c r="I56">
         <v>0</v>
@@ -2673,33 +2939,33 @@
         <v>0</v>
       </c>
       <c r="K56" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="B57" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="C57" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D57" t="s">
-        <v>47</v>
-      </c>
-      <c r="E57" s="2">
-        <v>199990</v>
+        <v>79</v>
+      </c>
+      <c r="E57">
+        <v>134990</v>
       </c>
       <c r="F57">
         <v>1</v>
       </c>
       <c r="G57" t="s">
-        <v>33</v>
+        <v>112</v>
       </c>
       <c r="H57" t="s">
-        <v>33</v>
+        <v>112</v>
       </c>
       <c r="I57">
         <v>0</v>
@@ -2708,33 +2974,33 @@
         <v>0</v>
       </c>
       <c r="K57" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="B58" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="C58" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D58" t="s">
-        <v>15</v>
-      </c>
-      <c r="E58" s="2">
-        <v>199990</v>
+        <v>82</v>
+      </c>
+      <c r="E58">
+        <v>134990</v>
       </c>
       <c r="F58">
         <v>1</v>
       </c>
       <c r="G58" t="s">
-        <v>33</v>
+        <v>112</v>
       </c>
       <c r="H58" t="s">
-        <v>33</v>
+        <v>112</v>
       </c>
       <c r="I58">
         <v>0</v>
@@ -2743,33 +3009,33 @@
         <v>0</v>
       </c>
       <c r="K58" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="B59" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="C59" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D59" t="s">
         <v>83</v>
       </c>
-      <c r="E59" s="2">
-        <v>199990</v>
+      <c r="E59">
+        <v>134990</v>
       </c>
       <c r="F59">
         <v>1</v>
       </c>
       <c r="G59" t="s">
-        <v>33</v>
+        <v>112</v>
       </c>
       <c r="H59" t="s">
-        <v>33</v>
+        <v>112</v>
       </c>
       <c r="I59">
         <v>0</v>
@@ -2778,33 +3044,33 @@
         <v>0</v>
       </c>
       <c r="K59" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="B60" t="s">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="C60" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="D60" t="s">
-        <v>26</v>
+        <v>123</v>
       </c>
       <c r="E60">
-        <v>155990</v>
+        <v>79990</v>
       </c>
       <c r="F60">
         <v>1</v>
       </c>
       <c r="G60" t="s">
-        <v>33</v>
+        <v>124</v>
       </c>
       <c r="H60" t="s">
-        <v>33</v>
+        <v>124</v>
       </c>
       <c r="I60">
         <v>0</v>
@@ -2813,33 +3079,33 @@
         <v>0</v>
       </c>
       <c r="K60" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="B61" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="C61" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="D61" t="s">
-        <v>28</v>
+        <v>75</v>
       </c>
       <c r="E61">
-        <v>155990</v>
+        <v>134990</v>
       </c>
       <c r="F61">
         <v>1</v>
       </c>
       <c r="G61" t="s">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="H61" t="s">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="I61">
         <v>0</v>
@@ -2848,33 +3114,33 @@
         <v>0</v>
       </c>
       <c r="K61" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="B62" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="C62" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D62" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="E62">
-        <v>155990</v>
+        <v>134990</v>
       </c>
       <c r="F62">
         <v>1</v>
       </c>
       <c r="G62" t="s">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="H62" t="s">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="I62">
         <v>0</v>
@@ -2883,33 +3149,33 @@
         <v>0</v>
       </c>
       <c r="K62" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="B63" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="C63" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D63" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="E63">
-        <v>155990</v>
+        <v>134990</v>
       </c>
       <c r="F63">
         <v>1</v>
       </c>
       <c r="G63" t="s">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="H63" t="s">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="I63">
         <v>0</v>
@@ -2918,33 +3184,33 @@
         <v>0</v>
       </c>
       <c r="K63" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>102</v>
+        <v>125</v>
       </c>
       <c r="B64" t="s">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="C64" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="D64" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="E64">
-        <v>269990</v>
+        <v>134990</v>
       </c>
       <c r="F64">
         <v>1</v>
       </c>
       <c r="G64" t="s">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="H64" t="s">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="I64">
         <v>0</v>
@@ -2953,33 +3219,33 @@
         <v>0</v>
       </c>
       <c r="K64" t="s">
-        <v>104</v>
+        <v>21</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>102</v>
+        <v>125</v>
       </c>
       <c r="B65" t="s">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="C65" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="D65" t="s">
-        <v>28</v>
+        <v>127</v>
       </c>
       <c r="E65">
-        <v>269990</v>
+        <v>134990</v>
       </c>
       <c r="F65">
         <v>1</v>
       </c>
       <c r="G65" t="s">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="H65" t="s">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="I65">
         <v>0</v>
@@ -2988,33 +3254,33 @@
         <v>0</v>
       </c>
       <c r="K65" t="s">
-        <v>104</v>
+        <v>21</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="B66" t="s">
-        <v>103</v>
+        <v>129</v>
       </c>
       <c r="C66" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="D66" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="E66">
-        <v>269990</v>
+        <v>119990</v>
       </c>
       <c r="F66">
         <v>1</v>
       </c>
       <c r="G66" t="s">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="H66" t="s">
-        <v>33</v>
+        <v>130</v>
       </c>
       <c r="I66">
         <v>0</v>
@@ -3023,33 +3289,33 @@
         <v>0</v>
       </c>
       <c r="K66" t="s">
-        <v>104</v>
+        <v>21</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="B67" t="s">
-        <v>103</v>
+        <v>129</v>
       </c>
       <c r="C67" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="D67" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E67">
-        <v>269990</v>
+        <v>119990</v>
       </c>
       <c r="F67">
         <v>1</v>
       </c>
       <c r="G67" t="s">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="H67" t="s">
-        <v>33</v>
+        <v>130</v>
       </c>
       <c r="I67">
         <v>0</v>
@@ -3058,33 +3324,33 @@
         <v>0</v>
       </c>
       <c r="K67" t="s">
-        <v>104</v>
+        <v>21</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="B68" t="s">
-        <v>103</v>
+        <v>129</v>
       </c>
       <c r="C68" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="D68" t="s">
-        <v>83</v>
+        <v>35</v>
       </c>
       <c r="E68">
-        <v>269990</v>
+        <v>119990</v>
       </c>
       <c r="F68">
         <v>1</v>
       </c>
       <c r="G68" t="s">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="H68" t="s">
-        <v>33</v>
+        <v>130</v>
       </c>
       <c r="I68">
         <v>0</v>
@@ -3093,33 +3359,33 @@
         <v>0</v>
       </c>
       <c r="K68" t="s">
-        <v>104</v>
+        <v>21</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>105</v>
+        <v>131</v>
       </c>
       <c r="B69" t="s">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="C69" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="D69" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E69">
-        <v>199990</v>
+        <v>119990</v>
       </c>
       <c r="F69">
         <v>1</v>
       </c>
       <c r="G69" t="s">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="H69" t="s">
-        <v>33</v>
+        <v>130</v>
       </c>
       <c r="I69">
         <v>0</v>
@@ -3128,33 +3394,33 @@
         <v>0</v>
       </c>
       <c r="K69" t="s">
-        <v>42</v>
+        <v>133</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>105</v>
+        <v>131</v>
       </c>
       <c r="B70" t="s">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="C70" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="D70" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="E70">
-        <v>199990</v>
+        <v>119990</v>
       </c>
       <c r="F70">
         <v>1</v>
       </c>
       <c r="G70" t="s">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="H70" t="s">
-        <v>33</v>
+        <v>130</v>
       </c>
       <c r="I70">
         <v>0</v>
@@ -3163,33 +3429,33 @@
         <v>0</v>
       </c>
       <c r="K70" t="s">
-        <v>42</v>
+        <v>133</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>105</v>
+        <v>134</v>
       </c>
       <c r="B71" t="s">
-        <v>106</v>
+        <v>135</v>
       </c>
       <c r="C71" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="D71" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="E71">
-        <v>199990</v>
+        <v>39990</v>
       </c>
       <c r="F71">
         <v>1</v>
       </c>
       <c r="G71" t="s">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="H71" t="s">
-        <v>33</v>
+        <v>130</v>
       </c>
       <c r="I71">
         <v>0</v>
@@ -3198,33 +3464,33 @@
         <v>0</v>
       </c>
       <c r="K71" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>105</v>
+        <v>134</v>
       </c>
       <c r="B72" t="s">
-        <v>106</v>
+        <v>135</v>
       </c>
       <c r="C72" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="D72" t="s">
         <v>83</v>
       </c>
       <c r="E72">
-        <v>199990</v>
+        <v>39990</v>
       </c>
       <c r="F72">
         <v>1</v>
       </c>
       <c r="G72" t="s">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="H72" t="s">
-        <v>33</v>
+        <v>130</v>
       </c>
       <c r="I72">
         <v>0</v>
@@ -3233,33 +3499,33 @@
         <v>0</v>
       </c>
       <c r="K72" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="B73" t="s">
-        <v>108</v>
+        <v>137</v>
       </c>
       <c r="C73" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D73" t="s">
-        <v>26</v>
+        <v>83</v>
       </c>
       <c r="E73">
-        <v>194990</v>
+        <v>39990</v>
       </c>
       <c r="F73">
         <v>1</v>
       </c>
       <c r="G73" t="s">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="H73" t="s">
-        <v>33</v>
+        <v>130</v>
       </c>
       <c r="I73">
         <v>0</v>
@@ -3268,33 +3534,33 @@
         <v>0</v>
       </c>
       <c r="K73" t="s">
-        <v>17</v>
+        <v>133</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>107</v>
+        <v>138</v>
       </c>
       <c r="B74" t="s">
-        <v>108</v>
+        <v>139</v>
       </c>
       <c r="C74" t="s">
-        <v>31</v>
+        <v>115</v>
       </c>
       <c r="D74" t="s">
-        <v>28</v>
+        <v>140</v>
       </c>
       <c r="E74">
-        <v>194990</v>
+        <v>140990</v>
       </c>
       <c r="F74">
         <v>1</v>
       </c>
       <c r="G74" t="s">
-        <v>33</v>
+        <v>112</v>
       </c>
       <c r="H74" t="s">
-        <v>33</v>
+        <v>130</v>
       </c>
       <c r="I74">
         <v>0</v>
@@ -3303,33 +3569,33 @@
         <v>0</v>
       </c>
       <c r="K74" t="s">
-        <v>17</v>
+        <v>81</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>107</v>
+        <v>138</v>
       </c>
       <c r="B75" t="s">
-        <v>108</v>
+        <v>139</v>
       </c>
       <c r="C75" t="s">
-        <v>31</v>
+        <v>115</v>
       </c>
       <c r="D75" t="s">
-        <v>47</v>
+        <v>141</v>
       </c>
       <c r="E75">
-        <v>194990</v>
+        <v>145990</v>
       </c>
       <c r="F75">
         <v>1</v>
       </c>
       <c r="G75" t="s">
-        <v>33</v>
+        <v>112</v>
       </c>
       <c r="H75" t="s">
-        <v>33</v>
+        <v>130</v>
       </c>
       <c r="I75">
         <v>0</v>
@@ -3338,33 +3604,33 @@
         <v>0</v>
       </c>
       <c r="K75" t="s">
-        <v>17</v>
+        <v>81</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>107</v>
+        <v>142</v>
       </c>
       <c r="B76" t="s">
-        <v>108</v>
+        <v>143</v>
       </c>
       <c r="C76" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="D76" t="s">
-        <v>15</v>
-      </c>
-      <c r="E76">
-        <v>194990</v>
+        <v>75</v>
+      </c>
+      <c r="E76" s="4">
+        <v>199990</v>
       </c>
       <c r="F76">
         <v>1</v>
       </c>
       <c r="G76" t="s">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="H76" t="s">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="I76">
         <v>0</v>
@@ -3373,42 +3639,777 @@
         <v>0</v>
       </c>
       <c r="K76" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
+        <v>142</v>
+      </c>
+      <c r="B77" t="s">
+        <v>143</v>
+      </c>
+      <c r="C77" t="s">
+        <v>18</v>
+      </c>
+      <c r="D77" t="s">
+        <v>25</v>
+      </c>
+      <c r="E77" s="4">
+        <v>199990</v>
+      </c>
+      <c r="F77">
+        <v>1</v>
+      </c>
+      <c r="G77" t="s">
+        <v>80</v>
+      </c>
+      <c r="H77" t="s">
+        <v>80</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>0</v>
+      </c>
+      <c r="K77" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>142</v>
+      </c>
+      <c r="B78" t="s">
+        <v>143</v>
+      </c>
+      <c r="C78" t="s">
+        <v>18</v>
+      </c>
+      <c r="D78" t="s">
+        <v>35</v>
+      </c>
+      <c r="E78" s="4">
+        <v>199990</v>
+      </c>
+      <c r="F78">
+        <v>1</v>
+      </c>
+      <c r="G78" t="s">
+        <v>80</v>
+      </c>
+      <c r="H78" t="s">
+        <v>80</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>0</v>
+      </c>
+      <c r="K78" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>142</v>
+      </c>
+      <c r="B79" t="s">
+        <v>143</v>
+      </c>
+      <c r="C79" t="s">
+        <v>18</v>
+      </c>
+      <c r="D79" t="s">
+        <v>19</v>
+      </c>
+      <c r="E79" s="4">
+        <v>199990</v>
+      </c>
+      <c r="F79">
+        <v>1</v>
+      </c>
+      <c r="G79" t="s">
+        <v>80</v>
+      </c>
+      <c r="H79" t="s">
+        <v>80</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>0</v>
+      </c>
+      <c r="K79" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>142</v>
+      </c>
+      <c r="B80" t="s">
+        <v>143</v>
+      </c>
+      <c r="C80" t="s">
+        <v>18</v>
+      </c>
+      <c r="D80" t="s">
+        <v>127</v>
+      </c>
+      <c r="E80" s="4">
+        <v>199990</v>
+      </c>
+      <c r="F80">
+        <v>1</v>
+      </c>
+      <c r="G80" t="s">
+        <v>80</v>
+      </c>
+      <c r="H80" t="s">
+        <v>80</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>0</v>
+      </c>
+      <c r="K80" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>144</v>
+      </c>
+      <c r="B81" t="s">
+        <v>145</v>
+      </c>
+      <c r="C81" t="s">
+        <v>28</v>
+      </c>
+      <c r="D81" t="s">
+        <v>75</v>
+      </c>
+      <c r="E81">
+        <v>155990</v>
+      </c>
+      <c r="F81">
+        <v>1</v>
+      </c>
+      <c r="G81" t="s">
+        <v>80</v>
+      </c>
+      <c r="H81" t="s">
+        <v>80</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>0</v>
+      </c>
+      <c r="K81" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>144</v>
+      </c>
+      <c r="B82" t="s">
+        <v>145</v>
+      </c>
+      <c r="C82" t="s">
+        <v>28</v>
+      </c>
+      <c r="D82" t="s">
+        <v>25</v>
+      </c>
+      <c r="E82">
+        <v>155990</v>
+      </c>
+      <c r="F82">
+        <v>1</v>
+      </c>
+      <c r="G82" t="s">
+        <v>80</v>
+      </c>
+      <c r="H82" t="s">
+        <v>80</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>0</v>
+      </c>
+      <c r="K82" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>144</v>
+      </c>
+      <c r="B83" t="s">
+        <v>145</v>
+      </c>
+      <c r="C83" t="s">
+        <v>28</v>
+      </c>
+      <c r="D83" t="s">
+        <v>35</v>
+      </c>
+      <c r="E83">
+        <v>155990</v>
+      </c>
+      <c r="F83">
+        <v>1</v>
+      </c>
+      <c r="G83" t="s">
+        <v>80</v>
+      </c>
+      <c r="H83" t="s">
+        <v>80</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>0</v>
+      </c>
+      <c r="K83" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>144</v>
+      </c>
+      <c r="B84" t="s">
+        <v>145</v>
+      </c>
+      <c r="C84" t="s">
+        <v>28</v>
+      </c>
+      <c r="D84" t="s">
+        <v>19</v>
+      </c>
+      <c r="E84">
+        <v>155990</v>
+      </c>
+      <c r="F84">
+        <v>1</v>
+      </c>
+      <c r="G84" t="s">
+        <v>80</v>
+      </c>
+      <c r="H84" t="s">
+        <v>80</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>0</v>
+      </c>
+      <c r="K84" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>146</v>
+      </c>
+      <c r="B85" t="s">
+        <v>147</v>
+      </c>
+      <c r="C85" t="s">
+        <v>18</v>
+      </c>
+      <c r="D85" t="s">
+        <v>75</v>
+      </c>
+      <c r="E85">
+        <v>269990</v>
+      </c>
+      <c r="F85">
+        <v>1</v>
+      </c>
+      <c r="G85" t="s">
+        <v>80</v>
+      </c>
+      <c r="H85" t="s">
+        <v>80</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>0</v>
+      </c>
+      <c r="K85" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>146</v>
+      </c>
+      <c r="B86" t="s">
+        <v>147</v>
+      </c>
+      <c r="C86" t="s">
+        <v>18</v>
+      </c>
+      <c r="D86" t="s">
+        <v>25</v>
+      </c>
+      <c r="E86">
+        <v>269990</v>
+      </c>
+      <c r="F86">
+        <v>1</v>
+      </c>
+      <c r="G86" t="s">
+        <v>80</v>
+      </c>
+      <c r="H86" t="s">
+        <v>80</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>0</v>
+      </c>
+      <c r="K86" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>146</v>
+      </c>
+      <c r="B87" t="s">
+        <v>147</v>
+      </c>
+      <c r="C87" t="s">
+        <v>18</v>
+      </c>
+      <c r="D87" t="s">
+        <v>35</v>
+      </c>
+      <c r="E87">
+        <v>269990</v>
+      </c>
+      <c r="F87">
+        <v>1</v>
+      </c>
+      <c r="G87" t="s">
+        <v>80</v>
+      </c>
+      <c r="H87" t="s">
+        <v>80</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>0</v>
+      </c>
+      <c r="K87" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>146</v>
+      </c>
+      <c r="B88" t="s">
+        <v>147</v>
+      </c>
+      <c r="C88" t="s">
+        <v>18</v>
+      </c>
+      <c r="D88" t="s">
+        <v>19</v>
+      </c>
+      <c r="E88">
+        <v>269990</v>
+      </c>
+      <c r="F88">
+        <v>1</v>
+      </c>
+      <c r="G88" t="s">
+        <v>80</v>
+      </c>
+      <c r="H88" t="s">
+        <v>80</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>0</v>
+      </c>
+      <c r="K88" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>146</v>
+      </c>
+      <c r="B89" t="s">
+        <v>147</v>
+      </c>
+      <c r="C89" t="s">
+        <v>18</v>
+      </c>
+      <c r="D89" t="s">
+        <v>127</v>
+      </c>
+      <c r="E89">
+        <v>269990</v>
+      </c>
+      <c r="F89">
+        <v>1</v>
+      </c>
+      <c r="G89" t="s">
+        <v>80</v>
+      </c>
+      <c r="H89" t="s">
+        <v>80</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>0</v>
+      </c>
+      <c r="K89" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>149</v>
+      </c>
+      <c r="B90" t="s">
+        <v>150</v>
+      </c>
+      <c r="C90" t="s">
+        <v>18</v>
+      </c>
+      <c r="D90" t="s">
+        <v>25</v>
+      </c>
+      <c r="E90">
+        <v>199990</v>
+      </c>
+      <c r="F90">
+        <v>1</v>
+      </c>
+      <c r="G90" t="s">
+        <v>80</v>
+      </c>
+      <c r="H90" t="s">
+        <v>80</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>0</v>
+      </c>
+      <c r="K90" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>149</v>
+      </c>
+      <c r="B91" t="s">
+        <v>150</v>
+      </c>
+      <c r="C91" t="s">
+        <v>18</v>
+      </c>
+      <c r="D91" t="s">
+        <v>35</v>
+      </c>
+      <c r="E91">
+        <v>199990</v>
+      </c>
+      <c r="F91">
+        <v>1</v>
+      </c>
+      <c r="G91" t="s">
+        <v>80</v>
+      </c>
+      <c r="H91" t="s">
+        <v>80</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>0</v>
+      </c>
+      <c r="K91" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>149</v>
+      </c>
+      <c r="B92" t="s">
+        <v>150</v>
+      </c>
+      <c r="C92" t="s">
+        <v>18</v>
+      </c>
+      <c r="D92" t="s">
+        <v>19</v>
+      </c>
+      <c r="E92">
+        <v>199990</v>
+      </c>
+      <c r="F92">
+        <v>1</v>
+      </c>
+      <c r="G92" t="s">
+        <v>80</v>
+      </c>
+      <c r="H92" t="s">
+        <v>80</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>0</v>
+      </c>
+      <c r="K92" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>149</v>
+      </c>
+      <c r="B93" t="s">
+        <v>150</v>
+      </c>
+      <c r="C93" t="s">
+        <v>18</v>
+      </c>
+      <c r="D93" t="s">
+        <v>127</v>
+      </c>
+      <c r="E93">
+        <v>199990</v>
+      </c>
+      <c r="F93">
+        <v>1</v>
+      </c>
+      <c r="G93" t="s">
+        <v>80</v>
+      </c>
+      <c r="H93" t="s">
+        <v>80</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>0</v>
+      </c>
+      <c r="K93" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>151</v>
+      </c>
+      <c r="B94" t="s">
+        <v>152</v>
+      </c>
+      <c r="C94" t="s">
+        <v>28</v>
+      </c>
+      <c r="D94" t="s">
+        <v>75</v>
+      </c>
+      <c r="E94">
+        <v>194990</v>
+      </c>
+      <c r="F94">
+        <v>1</v>
+      </c>
+      <c r="G94" t="s">
+        <v>80</v>
+      </c>
+      <c r="H94" t="s">
+        <v>80</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>0</v>
+      </c>
+      <c r="K94" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>151</v>
+      </c>
+      <c r="B95" t="s">
+        <v>152</v>
+      </c>
+      <c r="C95" t="s">
+        <v>28</v>
+      </c>
+      <c r="D95" t="s">
+        <v>25</v>
+      </c>
+      <c r="E95">
+        <v>194990</v>
+      </c>
+      <c r="F95">
+        <v>1</v>
+      </c>
+      <c r="G95" t="s">
+        <v>80</v>
+      </c>
+      <c r="H95" t="s">
+        <v>80</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>0</v>
+      </c>
+      <c r="K95" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>151</v>
+      </c>
+      <c r="B96" t="s">
+        <v>152</v>
+      </c>
+      <c r="C96" t="s">
+        <v>28</v>
+      </c>
+      <c r="D96" t="s">
+        <v>35</v>
+      </c>
+      <c r="E96">
+        <v>194990</v>
+      </c>
+      <c r="F96">
+        <v>1</v>
+      </c>
+      <c r="G96" t="s">
+        <v>80</v>
+      </c>
+      <c r="H96" t="s">
+        <v>80</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>0</v>
+      </c>
+      <c r="K96" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>151</v>
+      </c>
+      <c r="B97" t="s">
+        <v>152</v>
+      </c>
+      <c r="C97" t="s">
+        <v>28</v>
+      </c>
+      <c r="D97" t="s">
+        <v>19</v>
+      </c>
+      <c r="E97">
+        <v>194990</v>
+      </c>
+      <c r="F97">
+        <v>1</v>
+      </c>
+      <c r="G97" t="s">
+        <v>80</v>
+      </c>
+      <c r="H97" t="s">
+        <v>80</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>0</v>
+      </c>
+      <c r="K97" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>153</v>
+      </c>
+      <c r="B98" t="s">
+        <v>154</v>
+      </c>
+      <c r="C98" t="s">
+        <v>18</v>
+      </c>
+      <c r="D98" t="s">
+        <v>75</v>
+      </c>
+      <c r="E98">
+        <v>202990</v>
+      </c>
+      <c r="F98">
+        <v>1</v>
+      </c>
+      <c r="G98" t="s">
+        <v>20</v>
+      </c>
+      <c r="H98" t="s">
+        <v>20</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>0</v>
+      </c>
+      <c r="K98" t="s">
         <v>109</v>
-      </c>
-      <c r="B77" t="s">
-        <v>110</v>
-      </c>
-      <c r="C77" t="s">
-        <v>14</v>
-      </c>
-      <c r="D77" t="s">
-        <v>26</v>
-      </c>
-      <c r="E77">
-        <v>202990</v>
-      </c>
-      <c r="F77">
-        <v>1</v>
-      </c>
-      <c r="G77" t="s">
-        <v>16</v>
-      </c>
-      <c r="H77" t="s">
-        <v>16</v>
-      </c>
-      <c r="I77">
-        <v>0</v>
-      </c>
-      <c r="J77">
-        <v>0</v>
-      </c>
-      <c r="K77" t="s">
-        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/data/catalogo_jusp.xlsx
+++ b/data/catalogo_jusp.xlsx
@@ -221,6 +221,21 @@
     <t>Puma breathable sports bra</t>
   </si>
   <si>
+    <t>jordan-JD2213006GS-001</t>
+  </si>
+  <si>
+    <t>Nike Jordan shoulder bag</t>
+  </si>
+  <si>
+    <t>Unica</t>
+  </si>
+  <si>
+    <t>Unisex</t>
+  </si>
+  <si>
+    <t>accessories</t>
+  </si>
+  <si>
     <t>short-nike-kids</t>
   </si>
   <si>
@@ -389,9 +404,6 @@
     <t>Nike Dri-FIT Ace Kids' Swoosh Visor</t>
   </si>
   <si>
-    <t>Unica</t>
-  </si>
-  <si>
     <t>Kisd</t>
   </si>
   <si>
@@ -408,9 +420,6 @@
   </si>
   <si>
     <t>Bóxer Nike Jordan Flight</t>
-  </si>
-  <si>
-    <t>accessories</t>
   </si>
   <si>
     <t>jordan-jd2413048AD-002</t>
@@ -1795,7 +1804,7 @@
         <v>69</v>
       </c>
       <c r="E24">
-        <v>88990</v>
+        <v>129990</v>
       </c>
       <c r="F24">
         <v>1</v>
@@ -1815,22 +1824,22 @@
       <c r="K24" t="s">
         <v>21</v>
       </c>
-      <c r="L24">
-        <v>5</v>
-      </c>
+      <c r="L24"/>
+      <c r="N24" s="3"/>
+      <c r="O24" s="3"/>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B25" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C25" t="s">
         <v>18</v>
       </c>
       <c r="D25" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E25">
         <v>88990</v>
@@ -1839,10 +1848,10 @@
         <v>1</v>
       </c>
       <c r="G25" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H25" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -1859,28 +1868,28 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
+        <v>72</v>
+      </c>
+      <c r="B26" t="s">
         <v>73</v>
       </c>
-      <c r="B26" t="s">
-        <v>74</v>
-      </c>
       <c r="C26" t="s">
         <v>18</v>
       </c>
       <c r="D26" t="s">
+        <v>77</v>
+      </c>
+      <c r="E26">
+        <v>88990</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+      <c r="G26" t="s">
         <v>75</v>
       </c>
-      <c r="E26">
-        <v>89990</v>
-      </c>
-      <c r="F26">
-        <v>1</v>
-      </c>
-      <c r="G26" t="s">
-        <v>20</v>
-      </c>
       <c r="H26" t="s">
-        <v>20</v>
+        <v>76</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -1889,21 +1898,24 @@
         <v>0</v>
       </c>
       <c r="K26" t="s">
-        <v>76</v>
+        <v>21</v>
+      </c>
+      <c r="L26">
+        <v>5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="B27" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C27" t="s">
         <v>18</v>
       </c>
       <c r="D27" t="s">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="E27">
         <v>89990</v>
@@ -1924,33 +1936,33 @@
         <v>0</v>
       </c>
       <c r="K27" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B28" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C28" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D28" t="s">
-        <v>79</v>
+        <v>25</v>
       </c>
       <c r="E28">
-        <v>75990</v>
+        <v>89990</v>
       </c>
       <c r="F28">
         <v>1</v>
       </c>
       <c r="G28" t="s">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="H28" t="s">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -1964,28 +1976,28 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B29" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C29" t="s">
         <v>28</v>
       </c>
       <c r="D29" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E29">
-        <v>79990</v>
+        <v>75990</v>
       </c>
       <c r="F29">
         <v>1</v>
       </c>
       <c r="G29" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="H29" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -1994,33 +2006,33 @@
         <v>0</v>
       </c>
       <c r="K29" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B30" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C30" t="s">
         <v>28</v>
       </c>
       <c r="D30" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E30">
-        <v>78990</v>
+        <v>79990</v>
       </c>
       <c r="F30">
         <v>1</v>
       </c>
       <c r="G30" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="H30" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -2029,33 +2041,33 @@
         <v>0</v>
       </c>
       <c r="K30" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B31" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C31" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="D31" t="s">
-        <v>25</v>
+        <v>88</v>
       </c>
       <c r="E31">
-        <v>69990</v>
+        <v>78990</v>
       </c>
       <c r="F31">
         <v>1</v>
       </c>
       <c r="G31" t="s">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="H31" t="s">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -2069,10 +2081,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B32" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C32" t="s">
         <v>18</v>
@@ -2081,7 +2093,7 @@
         <v>25</v>
       </c>
       <c r="E32">
-        <v>99990</v>
+        <v>69990</v>
       </c>
       <c r="F32">
         <v>1</v>
@@ -2099,33 +2111,33 @@
         <v>0</v>
       </c>
       <c r="K32" t="s">
-        <v>32</v>
+        <v>91</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B33" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C33" t="s">
         <v>18</v>
       </c>
-      <c r="D33">
-        <v>7</v>
+      <c r="D33" t="s">
+        <v>25</v>
       </c>
       <c r="E33">
         <v>99990</v>
       </c>
       <c r="F33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G33" t="s">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="H33" t="s">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -2134,33 +2146,33 @@
         <v>0</v>
       </c>
       <c r="K33" t="s">
-        <v>81</v>
+        <v>32</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B34" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C34" t="s">
         <v>18</v>
       </c>
-      <c r="D34" t="s">
-        <v>35</v>
-      </c>
-      <c r="E34" s="4">
-        <v>119990</v>
+      <c r="D34">
+        <v>7</v>
+      </c>
+      <c r="E34">
+        <v>99990</v>
       </c>
       <c r="F34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G34" t="s">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="H34" t="s">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -2169,33 +2181,33 @@
         <v>0</v>
       </c>
       <c r="K34" t="s">
-        <v>32</v>
+        <v>86</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B35" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C35" t="s">
         <v>18</v>
       </c>
       <c r="D35" t="s">
-        <v>79</v>
-      </c>
-      <c r="E35">
-        <v>65990</v>
+        <v>35</v>
+      </c>
+      <c r="E35" s="4">
+        <v>119990</v>
       </c>
       <c r="F35">
         <v>1</v>
       </c>
       <c r="G35" t="s">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="H35" t="s">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -2204,33 +2216,33 @@
         <v>0</v>
       </c>
       <c r="K35" t="s">
-        <v>95</v>
+        <v>32</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B36" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="C36" t="s">
         <v>18</v>
       </c>
       <c r="D36" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E36">
-        <v>75990</v>
+        <v>65990</v>
       </c>
       <c r="F36">
         <v>1</v>
       </c>
       <c r="G36" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="H36" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -2239,33 +2251,33 @@
         <v>0</v>
       </c>
       <c r="K36" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B37" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="C37" t="s">
         <v>18</v>
       </c>
       <c r="D37" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E37">
-        <v>85990</v>
+        <v>75990</v>
       </c>
       <c r="F37">
         <v>1</v>
       </c>
       <c r="G37" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="H37" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -2274,33 +2286,33 @@
         <v>0</v>
       </c>
       <c r="K37" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B38" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C38" t="s">
         <v>18</v>
       </c>
       <c r="D38" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="E38">
-        <v>79990</v>
+        <v>85990</v>
       </c>
       <c r="F38">
         <v>1</v>
       </c>
       <c r="G38" t="s">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="H38" t="s">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -2309,21 +2321,21 @@
         <v>0</v>
       </c>
       <c r="K38" t="s">
-        <v>81</v>
+        <v>100</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B39" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="C39" t="s">
         <v>18</v>
       </c>
       <c r="D39" t="s">
-        <v>75</v>
+        <v>103</v>
       </c>
       <c r="E39">
         <v>79990</v>
@@ -2344,21 +2356,21 @@
         <v>0</v>
       </c>
       <c r="K39" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B40" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="C40" t="s">
         <v>18</v>
       </c>
       <c r="D40" t="s">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="E40">
         <v>79990</v>
@@ -2379,21 +2391,21 @@
         <v>0</v>
       </c>
       <c r="K40" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B41" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="C41" t="s">
         <v>18</v>
       </c>
       <c r="D41" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E41">
         <v>79990</v>
@@ -2414,21 +2426,21 @@
         <v>0</v>
       </c>
       <c r="K41" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B42" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="C42" t="s">
         <v>18</v>
       </c>
       <c r="D42" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="E42">
         <v>79990</v>
@@ -2449,24 +2461,24 @@
         <v>0</v>
       </c>
       <c r="K42" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B43" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C43" t="s">
         <v>18</v>
       </c>
       <c r="D43" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="E43">
-        <v>155990</v>
+        <v>79990</v>
       </c>
       <c r="F43">
         <v>1</v>
@@ -2484,21 +2496,21 @@
         <v>0</v>
       </c>
       <c r="K43" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="B44" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C44" t="s">
         <v>18</v>
       </c>
       <c r="D44" t="s">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="E44">
         <v>155990</v>
@@ -2519,21 +2531,21 @@
         <v>0</v>
       </c>
       <c r="K44" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="B45" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C45" t="s">
         <v>18</v>
       </c>
       <c r="D45" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E45">
         <v>155990</v>
@@ -2554,21 +2566,21 @@
         <v>0</v>
       </c>
       <c r="K45" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="B46" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C46" t="s">
         <v>18</v>
       </c>
       <c r="D46" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="E46">
         <v>155990</v>
@@ -2589,24 +2601,24 @@
         <v>0</v>
       </c>
       <c r="K46" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B47" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C47" t="s">
-        <v>63</v>
+        <v>18</v>
       </c>
       <c r="D47" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="E47">
-        <v>49990</v>
+        <v>155990</v>
       </c>
       <c r="F47">
         <v>1</v>
@@ -2624,21 +2636,21 @@
         <v>0</v>
       </c>
       <c r="K47" t="s">
-        <v>21</v>
+        <v>106</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="B48" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C48" t="s">
         <v>63</v>
       </c>
       <c r="D48" t="s">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="E48">
         <v>49990</v>
@@ -2664,19 +2676,19 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B49" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C49" t="s">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="D49" t="s">
         <v>25</v>
       </c>
       <c r="E49">
-        <v>135990</v>
+        <v>49990</v>
       </c>
       <c r="F49">
         <v>1</v>
@@ -2694,24 +2706,24 @@
         <v>0</v>
       </c>
       <c r="K49" t="s">
-        <v>106</v>
+        <v>21</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B50" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C50" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="D50" t="s">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="E50">
-        <v>155990</v>
+        <v>135990</v>
       </c>
       <c r="F50">
         <v>1</v>
@@ -2729,21 +2741,21 @@
         <v>0</v>
       </c>
       <c r="K50" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="B51" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="C51" t="s">
         <v>18</v>
       </c>
       <c r="D51" t="s">
-        <v>35</v>
+        <v>80</v>
       </c>
       <c r="E51">
         <v>155990</v>
@@ -2764,21 +2776,21 @@
         <v>0</v>
       </c>
       <c r="K51" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="B52" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="C52" t="s">
         <v>18</v>
       </c>
       <c r="D52" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="E52">
         <v>155990</v>
@@ -2799,33 +2811,33 @@
         <v>0</v>
       </c>
       <c r="K52" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B53" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C53" t="s">
         <v>18</v>
       </c>
       <c r="D53" t="s">
-        <v>82</v>
+        <v>19</v>
       </c>
       <c r="E53">
-        <v>129990</v>
+        <v>155990</v>
       </c>
       <c r="F53">
         <v>1</v>
       </c>
       <c r="G53" t="s">
-        <v>112</v>
+        <v>20</v>
       </c>
       <c r="H53" t="s">
-        <v>112</v>
+        <v>20</v>
       </c>
       <c r="I53">
         <v>0</v>
@@ -2834,21 +2846,21 @@
         <v>0</v>
       </c>
       <c r="K53" t="s">
-        <v>21</v>
+        <v>114</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B54" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C54" t="s">
         <v>18</v>
       </c>
       <c r="D54" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E54">
         <v>129990</v>
@@ -2857,10 +2869,10 @@
         <v>1</v>
       </c>
       <c r="G54" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="H54" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="I54">
         <v>0</v>
@@ -2874,28 +2886,28 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B55" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C55" t="s">
-        <v>115</v>
+        <v>18</v>
       </c>
       <c r="D55" t="s">
-        <v>116</v>
+        <v>88</v>
       </c>
       <c r="E55">
-        <v>179990</v>
+        <v>129990</v>
       </c>
       <c r="F55">
         <v>1</v>
       </c>
       <c r="G55" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="H55" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="I55">
         <v>0</v>
@@ -2909,28 +2921,28 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
+        <v>118</v>
+      </c>
+      <c r="B56" t="s">
+        <v>119</v>
+      </c>
+      <c r="C56" t="s">
+        <v>120</v>
+      </c>
+      <c r="D56" t="s">
+        <v>121</v>
+      </c>
+      <c r="E56">
+        <v>179990</v>
+      </c>
+      <c r="F56">
+        <v>1</v>
+      </c>
+      <c r="G56" t="s">
         <v>117</v>
       </c>
-      <c r="B56" t="s">
-        <v>118</v>
-      </c>
-      <c r="C56" t="s">
-        <v>18</v>
-      </c>
-      <c r="D56" t="s">
-        <v>116</v>
-      </c>
-      <c r="E56">
-        <v>159990</v>
-      </c>
-      <c r="F56">
-        <v>1</v>
-      </c>
-      <c r="G56" t="s">
-        <v>112</v>
-      </c>
       <c r="H56" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="I56">
         <v>0</v>
@@ -2944,28 +2956,28 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B57" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C57" t="s">
         <v>18</v>
       </c>
       <c r="D57" t="s">
-        <v>79</v>
+        <v>121</v>
       </c>
       <c r="E57">
-        <v>134990</v>
+        <v>159990</v>
       </c>
       <c r="F57">
         <v>1</v>
       </c>
       <c r="G57" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="H57" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="I57">
         <v>0</v>
@@ -2979,16 +2991,16 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="B58" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C58" t="s">
         <v>18</v>
       </c>
       <c r="D58" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E58">
         <v>134990</v>
@@ -2997,10 +3009,10 @@
         <v>1</v>
       </c>
       <c r="G58" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="H58" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="I58">
         <v>0</v>
@@ -3014,16 +3026,16 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="B59" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C59" t="s">
         <v>18</v>
       </c>
       <c r="D59" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E59">
         <v>134990</v>
@@ -3032,10 +3044,10 @@
         <v>1</v>
       </c>
       <c r="G59" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="H59" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="I59">
         <v>0</v>
@@ -3049,28 +3061,28 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B60" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C60" t="s">
         <v>18</v>
       </c>
       <c r="D60" t="s">
-        <v>123</v>
+        <v>88</v>
       </c>
       <c r="E60">
-        <v>79990</v>
+        <v>134990</v>
       </c>
       <c r="F60">
         <v>1</v>
       </c>
       <c r="G60" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="H60" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="I60">
         <v>0</v>
@@ -3084,28 +3096,28 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B61" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C61" t="s">
         <v>18</v>
       </c>
       <c r="D61" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="E61">
-        <v>134990</v>
+        <v>79990</v>
       </c>
       <c r="F61">
         <v>1</v>
       </c>
       <c r="G61" t="s">
-        <v>80</v>
+        <v>128</v>
       </c>
       <c r="H61" t="s">
-        <v>80</v>
+        <v>128</v>
       </c>
       <c r="I61">
         <v>0</v>
@@ -3119,16 +3131,16 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B62" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C62" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D62" t="s">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="E62">
         <v>134990</v>
@@ -3137,10 +3149,10 @@
         <v>1</v>
       </c>
       <c r="G62" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="H62" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I62">
         <v>0</v>
@@ -3154,16 +3166,16 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B63" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C63" t="s">
         <v>28</v>
       </c>
       <c r="D63" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E63">
         <v>134990</v>
@@ -3172,10 +3184,10 @@
         <v>1</v>
       </c>
       <c r="G63" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="H63" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I63">
         <v>0</v>
@@ -3189,16 +3201,16 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B64" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C64" t="s">
         <v>28</v>
       </c>
       <c r="D64" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="E64">
         <v>134990</v>
@@ -3207,10 +3219,10 @@
         <v>1</v>
       </c>
       <c r="G64" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="H64" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I64">
         <v>0</v>
@@ -3224,16 +3236,16 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B65" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C65" t="s">
         <v>28</v>
       </c>
       <c r="D65" t="s">
-        <v>127</v>
+        <v>19</v>
       </c>
       <c r="E65">
         <v>134990</v>
@@ -3242,10 +3254,10 @@
         <v>1</v>
       </c>
       <c r="G65" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="H65" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I65">
         <v>0</v>
@@ -3259,28 +3271,28 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B66" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C66" t="s">
         <v>28</v>
       </c>
       <c r="D66" t="s">
-        <v>75</v>
+        <v>131</v>
       </c>
       <c r="E66">
-        <v>119990</v>
+        <v>134990</v>
       </c>
       <c r="F66">
         <v>1</v>
       </c>
       <c r="G66" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="H66" t="s">
-        <v>130</v>
+        <v>85</v>
       </c>
       <c r="I66">
         <v>0</v>
@@ -3294,16 +3306,16 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B67" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C67" t="s">
         <v>28</v>
       </c>
       <c r="D67" t="s">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="E67">
         <v>119990</v>
@@ -3312,10 +3324,10 @@
         <v>1</v>
       </c>
       <c r="G67" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="H67" t="s">
-        <v>130</v>
+        <v>71</v>
       </c>
       <c r="I67">
         <v>0</v>
@@ -3329,16 +3341,16 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B68" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C68" t="s">
         <v>28</v>
       </c>
       <c r="D68" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E68">
         <v>119990</v>
@@ -3347,10 +3359,10 @@
         <v>1</v>
       </c>
       <c r="G68" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="H68" t="s">
-        <v>130</v>
+        <v>71</v>
       </c>
       <c r="I68">
         <v>0</v>
@@ -3364,16 +3376,16 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B69" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C69" t="s">
         <v>28</v>
       </c>
       <c r="D69" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="E69">
         <v>119990</v>
@@ -3382,10 +3394,10 @@
         <v>1</v>
       </c>
       <c r="G69" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="H69" t="s">
-        <v>130</v>
+        <v>71</v>
       </c>
       <c r="I69">
         <v>0</v>
@@ -3394,21 +3406,21 @@
         <v>0</v>
       </c>
       <c r="K69" t="s">
-        <v>133</v>
+        <v>21</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B70" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C70" t="s">
         <v>28</v>
       </c>
       <c r="D70" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E70">
         <v>119990</v>
@@ -3417,10 +3429,10 @@
         <v>1</v>
       </c>
       <c r="G70" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="H70" t="s">
-        <v>130</v>
+        <v>71</v>
       </c>
       <c r="I70">
         <v>0</v>
@@ -3429,7 +3441,7 @@
         <v>0</v>
       </c>
       <c r="K70" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="71">
@@ -3443,19 +3455,19 @@
         <v>28</v>
       </c>
       <c r="D71" t="s">
-        <v>79</v>
+        <v>35</v>
       </c>
       <c r="E71">
-        <v>39990</v>
+        <v>119990</v>
       </c>
       <c r="F71">
         <v>1</v>
       </c>
       <c r="G71" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="H71" t="s">
-        <v>130</v>
+        <v>71</v>
       </c>
       <c r="I71">
         <v>0</v>
@@ -3464,21 +3476,21 @@
         <v>0</v>
       </c>
       <c r="K71" t="s">
-        <v>21</v>
+        <v>136</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B72" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C72" t="s">
         <v>28</v>
       </c>
       <c r="D72" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E72">
         <v>39990</v>
@@ -3487,10 +3499,10 @@
         <v>1</v>
       </c>
       <c r="G72" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="H72" t="s">
-        <v>130</v>
+        <v>71</v>
       </c>
       <c r="I72">
         <v>0</v>
@@ -3504,16 +3516,16 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B73" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C73" t="s">
         <v>28</v>
       </c>
       <c r="D73" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="E73">
         <v>39990</v>
@@ -3522,10 +3534,10 @@
         <v>1</v>
       </c>
       <c r="G73" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="H73" t="s">
-        <v>130</v>
+        <v>71</v>
       </c>
       <c r="I73">
         <v>0</v>
@@ -3534,33 +3546,33 @@
         <v>0</v>
       </c>
       <c r="K73" t="s">
-        <v>133</v>
+        <v>21</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B74" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C74" t="s">
-        <v>115</v>
+        <v>28</v>
       </c>
       <c r="D74" t="s">
-        <v>140</v>
+        <v>88</v>
       </c>
       <c r="E74">
-        <v>140990</v>
+        <v>39990</v>
       </c>
       <c r="F74">
         <v>1</v>
       </c>
       <c r="G74" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="H74" t="s">
-        <v>130</v>
+        <v>71</v>
       </c>
       <c r="I74">
         <v>0</v>
@@ -3569,33 +3581,33 @@
         <v>0</v>
       </c>
       <c r="K74" t="s">
-        <v>81</v>
+        <v>136</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B75" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C75" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D75" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E75">
-        <v>145990</v>
+        <v>140990</v>
       </c>
       <c r="F75">
         <v>1</v>
       </c>
       <c r="G75" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="H75" t="s">
-        <v>130</v>
+        <v>71</v>
       </c>
       <c r="I75">
         <v>0</v>
@@ -3604,33 +3616,33 @@
         <v>0</v>
       </c>
       <c r="K75" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
+        <v>141</v>
+      </c>
+      <c r="B76" t="s">
         <v>142</v>
       </c>
-      <c r="B76" t="s">
-        <v>143</v>
-      </c>
       <c r="C76" t="s">
-        <v>18</v>
+        <v>120</v>
       </c>
       <c r="D76" t="s">
-        <v>75</v>
-      </c>
-      <c r="E76" s="4">
-        <v>199990</v>
+        <v>144</v>
+      </c>
+      <c r="E76">
+        <v>145990</v>
       </c>
       <c r="F76">
         <v>1</v>
       </c>
       <c r="G76" t="s">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="H76" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="I76">
         <v>0</v>
@@ -3639,21 +3651,21 @@
         <v>0</v>
       </c>
       <c r="K76" t="s">
-        <v>32</v>
+        <v>86</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B77" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C77" t="s">
         <v>18</v>
       </c>
       <c r="D77" t="s">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="E77" s="4">
         <v>199990</v>
@@ -3662,10 +3674,10 @@
         <v>1</v>
       </c>
       <c r="G77" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="H77" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I77">
         <v>0</v>
@@ -3679,16 +3691,16 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B78" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C78" t="s">
         <v>18</v>
       </c>
       <c r="D78" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E78" s="4">
         <v>199990</v>
@@ -3697,10 +3709,10 @@
         <v>1</v>
       </c>
       <c r="G78" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="H78" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I78">
         <v>0</v>
@@ -3714,16 +3726,16 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B79" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C79" t="s">
         <v>18</v>
       </c>
       <c r="D79" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="E79" s="4">
         <v>199990</v>
@@ -3732,10 +3744,10 @@
         <v>1</v>
       </c>
       <c r="G79" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="H79" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I79">
         <v>0</v>
@@ -3749,16 +3761,16 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B80" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C80" t="s">
         <v>18</v>
       </c>
       <c r="D80" t="s">
-        <v>127</v>
+        <v>19</v>
       </c>
       <c r="E80" s="4">
         <v>199990</v>
@@ -3767,10 +3779,10 @@
         <v>1</v>
       </c>
       <c r="G80" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="H80" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I80">
         <v>0</v>
@@ -3784,28 +3796,28 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B81" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C81" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D81" t="s">
-        <v>75</v>
-      </c>
-      <c r="E81">
-        <v>155990</v>
+        <v>131</v>
+      </c>
+      <c r="E81" s="4">
+        <v>199990</v>
       </c>
       <c r="F81">
         <v>1</v>
       </c>
       <c r="G81" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="H81" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I81">
         <v>0</v>
@@ -3814,21 +3826,21 @@
         <v>0</v>
       </c>
       <c r="K81" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B82" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C82" t="s">
         <v>28</v>
       </c>
       <c r="D82" t="s">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="E82">
         <v>155990</v>
@@ -3837,10 +3849,10 @@
         <v>1</v>
       </c>
       <c r="G82" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="H82" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I82">
         <v>0</v>
@@ -3854,16 +3866,16 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B83" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C83" t="s">
         <v>28</v>
       </c>
       <c r="D83" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E83">
         <v>155990</v>
@@ -3872,10 +3884,10 @@
         <v>1</v>
       </c>
       <c r="G83" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="H83" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I83">
         <v>0</v>
@@ -3889,16 +3901,16 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B84" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C84" t="s">
         <v>28</v>
       </c>
       <c r="D84" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="E84">
         <v>155990</v>
@@ -3907,10 +3919,10 @@
         <v>1</v>
       </c>
       <c r="G84" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="H84" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I84">
         <v>0</v>
@@ -3924,28 +3936,28 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B85" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C85" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="D85" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="E85">
-        <v>269990</v>
+        <v>155990</v>
       </c>
       <c r="F85">
         <v>1</v>
       </c>
       <c r="G85" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="H85" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I85">
         <v>0</v>
@@ -3954,21 +3966,21 @@
         <v>0</v>
       </c>
       <c r="K85" t="s">
-        <v>148</v>
+        <v>21</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B86" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C86" t="s">
         <v>18</v>
       </c>
       <c r="D86" t="s">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="E86">
         <v>269990</v>
@@ -3977,10 +3989,10 @@
         <v>1</v>
       </c>
       <c r="G86" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="H86" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I86">
         <v>0</v>
@@ -3989,21 +4001,21 @@
         <v>0</v>
       </c>
       <c r="K86" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B87" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C87" t="s">
         <v>18</v>
       </c>
       <c r="D87" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E87">
         <v>269990</v>
@@ -4012,10 +4024,10 @@
         <v>1</v>
       </c>
       <c r="G87" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="H87" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I87">
         <v>0</v>
@@ -4024,21 +4036,21 @@
         <v>0</v>
       </c>
       <c r="K87" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B88" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C88" t="s">
         <v>18</v>
       </c>
       <c r="D88" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="E88">
         <v>269990</v>
@@ -4047,10 +4059,10 @@
         <v>1</v>
       </c>
       <c r="G88" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="H88" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I88">
         <v>0</v>
@@ -4059,21 +4071,21 @@
         <v>0</v>
       </c>
       <c r="K88" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B89" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C89" t="s">
         <v>18</v>
       </c>
       <c r="D89" t="s">
-        <v>127</v>
+        <v>19</v>
       </c>
       <c r="E89">
         <v>269990</v>
@@ -4082,10 +4094,10 @@
         <v>1</v>
       </c>
       <c r="G89" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="H89" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I89">
         <v>0</v>
@@ -4094,7 +4106,7 @@
         <v>0</v>
       </c>
       <c r="K89" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="90">
@@ -4108,19 +4120,19 @@
         <v>18</v>
       </c>
       <c r="D90" t="s">
-        <v>25</v>
+        <v>131</v>
       </c>
       <c r="E90">
-        <v>199990</v>
+        <v>269990</v>
       </c>
       <c r="F90">
         <v>1</v>
       </c>
       <c r="G90" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="H90" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I90">
         <v>0</v>
@@ -4129,21 +4141,21 @@
         <v>0</v>
       </c>
       <c r="K90" t="s">
-        <v>32</v>
+        <v>151</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B91" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C91" t="s">
         <v>18</v>
       </c>
       <c r="D91" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E91">
         <v>199990</v>
@@ -4152,10 +4164,10 @@
         <v>1</v>
       </c>
       <c r="G91" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="H91" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I91">
         <v>0</v>
@@ -4169,16 +4181,16 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B92" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C92" t="s">
         <v>18</v>
       </c>
       <c r="D92" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="E92">
         <v>199990</v>
@@ -4187,10 +4199,10 @@
         <v>1</v>
       </c>
       <c r="G92" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="H92" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I92">
         <v>0</v>
@@ -4204,16 +4216,16 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B93" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C93" t="s">
         <v>18</v>
       </c>
       <c r="D93" t="s">
-        <v>127</v>
+        <v>19</v>
       </c>
       <c r="E93">
         <v>199990</v>
@@ -4222,10 +4234,10 @@
         <v>1</v>
       </c>
       <c r="G93" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="H93" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I93">
         <v>0</v>
@@ -4239,28 +4251,28 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B94" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C94" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D94" t="s">
-        <v>75</v>
+        <v>131</v>
       </c>
       <c r="E94">
-        <v>194990</v>
+        <v>199990</v>
       </c>
       <c r="F94">
         <v>1</v>
       </c>
       <c r="G94" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="H94" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I94">
         <v>0</v>
@@ -4269,21 +4281,21 @@
         <v>0</v>
       </c>
       <c r="K94" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B95" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C95" t="s">
         <v>28</v>
       </c>
       <c r="D95" t="s">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="E95">
         <v>194990</v>
@@ -4292,10 +4304,10 @@
         <v>1</v>
       </c>
       <c r="G95" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="H95" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I95">
         <v>0</v>
@@ -4309,16 +4321,16 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B96" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C96" t="s">
         <v>28</v>
       </c>
       <c r="D96" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E96">
         <v>194990</v>
@@ -4327,10 +4339,10 @@
         <v>1</v>
       </c>
       <c r="G96" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="H96" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I96">
         <v>0</v>
@@ -4344,16 +4356,16 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B97" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C97" t="s">
         <v>28</v>
       </c>
       <c r="D97" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="E97">
         <v>194990</v>
@@ -4362,10 +4374,10 @@
         <v>1</v>
       </c>
       <c r="G97" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="H97" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I97">
         <v>0</v>
@@ -4379,37 +4391,72 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B98" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C98" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="D98" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="E98">
+        <v>194990</v>
+      </c>
+      <c r="F98">
+        <v>1</v>
+      </c>
+      <c r="G98" t="s">
+        <v>85</v>
+      </c>
+      <c r="H98" t="s">
+        <v>85</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>0</v>
+      </c>
+      <c r="K98" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>156</v>
+      </c>
+      <c r="B99" t="s">
+        <v>157</v>
+      </c>
+      <c r="C99" t="s">
+        <v>18</v>
+      </c>
+      <c r="D99" t="s">
+        <v>80</v>
+      </c>
+      <c r="E99">
         <v>202990</v>
       </c>
-      <c r="F98">
-        <v>1</v>
-      </c>
-      <c r="G98" t="s">
-        <v>20</v>
-      </c>
-      <c r="H98" t="s">
-        <v>20</v>
-      </c>
-      <c r="I98">
-        <v>0</v>
-      </c>
-      <c r="J98">
-        <v>0</v>
-      </c>
-      <c r="K98" t="s">
-        <v>109</v>
+      <c r="F99">
+        <v>1</v>
+      </c>
+      <c r="G99" t="s">
+        <v>20</v>
+      </c>
+      <c r="H99" t="s">
+        <v>20</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>0</v>
+      </c>
+      <c r="K99" t="s">
+        <v>114</v>
       </c>
     </row>
   </sheetData>

--- a/data/catalogo_jusp.xlsx
+++ b/data/catalogo_jusp.xlsx
@@ -95,18 +95,21 @@
     <t>Sujetador deportivo de entrenamiento NIKE CLASSIC SWOOSH</t>
   </si>
   <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>jordan-cw2427-010</t>
+  </si>
+  <si>
+    <t>AS WJ JUMPMAN BRA</t>
+  </si>
+  <si>
+    <t>Jordan</t>
+  </si>
+  <si>
     <t>M</t>
   </si>
   <si>
-    <t>jordan-cw2427-010</t>
-  </si>
-  <si>
-    <t>AS WJ JUMPMAN BRA</t>
-  </si>
-  <si>
-    <t>Jordan</t>
-  </si>
-  <si>
     <t>nike-dm0672-100</t>
   </si>
   <si>
@@ -125,9 +128,6 @@
     <t>Sujetador deportivo de entrenamiento NIKE DRY BRA</t>
   </si>
   <si>
-    <t>L</t>
-  </si>
-  <si>
     <t>nike-fb4081-675</t>
   </si>
   <si>
@@ -164,7 +164,10 @@
     <t>Nike DIR-FIT Training Sports Bra</t>
   </si>
   <si>
-    <t>nike-dq5135-539</t>
+    <t>S</t>
+  </si>
+  <si>
+    <t>nike-dq5135-569</t>
   </si>
   <si>
     <t>NIKE AS W NK DF SWSH</t>
@@ -258,9 +261,6 @@
   </si>
   <si>
     <t>Sujetador deportivo Nike Dri-FIT</t>
-  </si>
-  <si>
-    <t>S</t>
   </si>
   <si>
     <t>Pink</t>
@@ -1007,7 +1007,7 @@
         <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E4">
         <v>119990</v>
@@ -1038,16 +1038,16 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C5" t="s">
         <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E5">
         <v>95990</v>
@@ -1068,7 +1068,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L5">
         <v>45</v>
@@ -1078,19 +1078,19 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C6" t="s">
         <v>18</v>
       </c>
       <c r="D6" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E6">
-        <v>95990</v>
+        <v>110990</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -1108,29 +1108,29 @@
         <v>1</v>
       </c>
       <c r="K6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L6">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="N6" s="3"/>
       <c r="O6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B7" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C7" t="s">
         <v>18</v>
       </c>
       <c r="D7" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E7">
-        <v>110990</v>
+        <v>195990</v>
       </c>
       <c r="F7">
         <v>1</v>
@@ -1142,35 +1142,32 @@
         <v>20</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>32</v>
-      </c>
-      <c r="L7">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="N7" s="3"/>
       <c r="O7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C8" t="s">
         <v>18</v>
       </c>
       <c r="D8" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E8">
-        <v>110990</v>
+        <v>205990</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -1182,35 +1179,32 @@
         <v>20</v>
       </c>
       <c r="I8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>32</v>
-      </c>
-      <c r="L8">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C9" t="s">
         <v>18</v>
       </c>
       <c r="D9" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E9">
-        <v>195990</v>
+        <v>139990</v>
       </c>
       <c r="F9">
         <v>1</v>
@@ -1222,32 +1216,35 @@
         <v>20</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="s">
-        <v>38</v>
+        <v>33</v>
+      </c>
+      <c r="L9">
+        <v>20</v>
       </c>
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B10" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C10" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="D10" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="E10">
-        <v>205990</v>
+        <v>125990</v>
       </c>
       <c r="F10">
         <v>1</v>
@@ -1259,32 +1256,35 @@
         <v>20</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="s">
-        <v>38</v>
+        <v>43</v>
+      </c>
+      <c r="L10">
+        <v>35</v>
       </c>
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B11" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C11" t="s">
         <v>18</v>
       </c>
       <c r="D11" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="E11">
-        <v>139990</v>
+        <v>99990</v>
       </c>
       <c r="F11">
         <v>1</v>
@@ -1302,29 +1302,29 @@
         <v>1</v>
       </c>
       <c r="K11" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="L11">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B12" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C12" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D12" t="s">
         <v>25</v>
       </c>
       <c r="E12">
-        <v>125990</v>
+        <v>99990</v>
       </c>
       <c r="F12">
         <v>1</v>
@@ -1342,29 +1342,29 @@
         <v>1</v>
       </c>
       <c r="K12" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="L12">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B13" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C13" t="s">
         <v>18</v>
       </c>
       <c r="D13" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E13">
-        <v>99990</v>
+        <v>109990</v>
       </c>
       <c r="F13">
         <v>1</v>
@@ -1376,35 +1376,35 @@
         <v>20</v>
       </c>
       <c r="I13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="L13">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N13" s="3"/>
       <c r="O13" s="3"/>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B14" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C14" t="s">
         <v>18</v>
       </c>
       <c r="D14" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E14">
-        <v>95990</v>
+        <v>119990</v>
       </c>
       <c r="F14">
         <v>1</v>
@@ -1416,13 +1416,13 @@
         <v>20</v>
       </c>
       <c r="I14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="L14">
         <v>30</v>
@@ -1432,16 +1432,16 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B15" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C15" t="s">
         <v>18</v>
       </c>
       <c r="D15" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E15">
         <v>119990</v>
@@ -1456,13 +1456,13 @@
         <v>20</v>
       </c>
       <c r="I15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L15">
         <v>30</v>
@@ -1472,16 +1472,16 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C16" t="s">
         <v>18</v>
       </c>
       <c r="D16" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E16">
         <v>119990</v>
@@ -1502,7 +1502,7 @@
         <v>1</v>
       </c>
       <c r="K16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="L16">
         <v>30</v>
@@ -1512,16 +1512,16 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B17" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C17" t="s">
         <v>28</v>
       </c>
       <c r="D17" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E17">
         <v>119990</v>
@@ -1542,7 +1542,7 @@
         <v>1</v>
       </c>
       <c r="K17" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L17">
         <v>35</v>
@@ -1552,16 +1552,16 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B18" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C18" t="s">
         <v>18</v>
       </c>
       <c r="D18" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E18">
         <v>99990</v>
@@ -1582,7 +1582,7 @@
         <v>1</v>
       </c>
       <c r="K18" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L18">
         <v>25</v>
@@ -1592,10 +1592,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B19" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C19" t="s">
         <v>18</v>
@@ -1622,7 +1622,7 @@
         <v>1</v>
       </c>
       <c r="K19" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L19">
         <v>30</v>
@@ -1632,16 +1632,16 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B20" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C20" t="s">
         <v>18</v>
       </c>
       <c r="D20" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E20">
         <v>86990</v>
@@ -1662,7 +1662,7 @@
         <v>1</v>
       </c>
       <c r="K20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L20">
         <v>30</v>
@@ -1672,19 +1672,19 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B21" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C21" t="s">
-        <v>18</v>
+        <v>64</v>
       </c>
       <c r="D21" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E21">
-        <v>86990</v>
+        <v>96990</v>
       </c>
       <c r="F21">
         <v>1</v>
@@ -1702,29 +1702,29 @@
         <v>1</v>
       </c>
       <c r="K21" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="L21">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N21" s="3"/>
       <c r="O21" s="3"/>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B22" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C22" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D22" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E22">
-        <v>96990</v>
+        <v>95990</v>
       </c>
       <c r="F22">
         <v>1</v>
@@ -1742,7 +1742,7 @@
         <v>1</v>
       </c>
       <c r="K22" t="s">
-        <v>64</v>
+        <v>21</v>
       </c>
       <c r="L22">
         <v>25</v>
@@ -1752,68 +1752,65 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B23" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C23" t="s">
-        <v>63</v>
+        <v>18</v>
       </c>
       <c r="D23" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="E23">
-        <v>95990</v>
+        <v>129990</v>
       </c>
       <c r="F23">
         <v>1</v>
       </c>
       <c r="G23" t="s">
-        <v>20</v>
+        <v>71</v>
       </c>
       <c r="H23" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="I23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="s">
         <v>21</v>
       </c>
-      <c r="L23">
-        <v>25</v>
-      </c>
       <c r="N23" s="3"/>
       <c r="O23" s="3"/>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="B24" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C24" t="s">
         <v>18</v>
       </c>
       <c r="D24" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="E24">
-        <v>129990</v>
+        <v>88990</v>
       </c>
       <c r="F24">
         <v>1</v>
       </c>
       <c r="G24" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="H24" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="I24">
         <v>0</v>
@@ -1824,22 +1821,22 @@
       <c r="K24" t="s">
         <v>21</v>
       </c>
-      <c r="L24"/>
-      <c r="N24" s="3"/>
-      <c r="O24" s="3"/>
+      <c r="L24">
+        <v>5</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B25" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C25" t="s">
         <v>18</v>
       </c>
       <c r="D25" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E25">
         <v>88990</v>
@@ -1848,10 +1845,10 @@
         <v>1</v>
       </c>
       <c r="G25" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H25" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -1868,28 +1865,28 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="B26" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="C26" t="s">
         <v>18</v>
       </c>
       <c r="D26" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="E26">
-        <v>88990</v>
+        <v>89990</v>
       </c>
       <c r="F26">
         <v>1</v>
       </c>
       <c r="G26" t="s">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="H26" t="s">
-        <v>76</v>
+        <v>20</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -1898,24 +1895,21 @@
         <v>0</v>
       </c>
       <c r="K26" t="s">
-        <v>21</v>
-      </c>
-      <c r="L26">
-        <v>5</v>
+        <v>81</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B27" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C27" t="s">
         <v>18</v>
       </c>
       <c r="D27" t="s">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="E27">
         <v>89990</v>
@@ -1941,28 +1935,28 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B28" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C28" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="D28" t="s">
-        <v>25</v>
+        <v>84</v>
       </c>
       <c r="E28">
-        <v>89990</v>
+        <v>75990</v>
       </c>
       <c r="F28">
         <v>1</v>
       </c>
       <c r="G28" t="s">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="H28" t="s">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -1971,7 +1965,7 @@
         <v>0</v>
       </c>
       <c r="K28" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
     <row r="29">
@@ -1985,10 +1979,10 @@
         <v>28</v>
       </c>
       <c r="D29" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E29">
-        <v>75990</v>
+        <v>79990</v>
       </c>
       <c r="F29">
         <v>1</v>
@@ -2020,10 +2014,10 @@
         <v>28</v>
       </c>
       <c r="D30" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E30">
-        <v>79990</v>
+        <v>78990</v>
       </c>
       <c r="F30">
         <v>1</v>
@@ -2046,28 +2040,28 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="B31" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="C31" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D31" t="s">
-        <v>88</v>
+        <v>29</v>
       </c>
       <c r="E31">
-        <v>78990</v>
+        <v>69990</v>
       </c>
       <c r="F31">
         <v>1</v>
       </c>
       <c r="G31" t="s">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="H31" t="s">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -2076,24 +2070,24 @@
         <v>0</v>
       </c>
       <c r="K31" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B32" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C32" t="s">
         <v>18</v>
       </c>
       <c r="D32" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E32">
-        <v>69990</v>
+        <v>99990</v>
       </c>
       <c r="F32">
         <v>1</v>
@@ -2111,33 +2105,33 @@
         <v>0</v>
       </c>
       <c r="K32" t="s">
-        <v>91</v>
+        <v>33</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B33" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C33" t="s">
         <v>18</v>
       </c>
-      <c r="D33" t="s">
-        <v>25</v>
+      <c r="D33">
+        <v>7</v>
       </c>
       <c r="E33">
         <v>99990</v>
       </c>
       <c r="F33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G33" t="s">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="H33" t="s">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -2146,33 +2140,33 @@
         <v>0</v>
       </c>
       <c r="K33" t="s">
-        <v>32</v>
+        <v>86</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B34" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C34" t="s">
         <v>18</v>
       </c>
-      <c r="D34">
-        <v>7</v>
-      </c>
-      <c r="E34">
-        <v>99990</v>
+      <c r="D34" t="s">
+        <v>25</v>
+      </c>
+      <c r="E34" s="4">
+        <v>119990</v>
       </c>
       <c r="F34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G34" t="s">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="H34" t="s">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -2181,33 +2175,33 @@
         <v>0</v>
       </c>
       <c r="K34" t="s">
-        <v>86</v>
+        <v>33</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B35" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C35" t="s">
         <v>18</v>
       </c>
       <c r="D35" t="s">
-        <v>35</v>
-      </c>
-      <c r="E35" s="4">
-        <v>119990</v>
+        <v>84</v>
+      </c>
+      <c r="E35">
+        <v>65990</v>
       </c>
       <c r="F35">
         <v>1</v>
       </c>
       <c r="G35" t="s">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="H35" t="s">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -2216,7 +2210,7 @@
         <v>0</v>
       </c>
       <c r="K35" t="s">
-        <v>32</v>
+        <v>100</v>
       </c>
     </row>
     <row r="36">
@@ -2230,10 +2224,10 @@
         <v>18</v>
       </c>
       <c r="D36" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E36">
-        <v>65990</v>
+        <v>75990</v>
       </c>
       <c r="F36">
         <v>1</v>
@@ -2265,10 +2259,10 @@
         <v>18</v>
       </c>
       <c r="D37" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E37">
-        <v>75990</v>
+        <v>85990</v>
       </c>
       <c r="F37">
         <v>1</v>
@@ -2291,28 +2285,28 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B38" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C38" t="s">
         <v>18</v>
       </c>
       <c r="D38" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="E38">
-        <v>85990</v>
+        <v>79990</v>
       </c>
       <c r="F38">
         <v>1</v>
       </c>
       <c r="G38" t="s">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="H38" t="s">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -2321,7 +2315,7 @@
         <v>0</v>
       </c>
       <c r="K38" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
     </row>
     <row r="39">
@@ -2335,7 +2329,7 @@
         <v>18</v>
       </c>
       <c r="D39" t="s">
-        <v>103</v>
+        <v>48</v>
       </c>
       <c r="E39">
         <v>79990</v>
@@ -2370,7 +2364,7 @@
         <v>18</v>
       </c>
       <c r="D40" t="s">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="E40">
         <v>79990</v>
@@ -2440,7 +2434,7 @@
         <v>18</v>
       </c>
       <c r="D42" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E42">
         <v>79990</v>
@@ -2466,19 +2460,19 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B43" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C43" t="s">
         <v>18</v>
       </c>
       <c r="D43" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="E43">
-        <v>79990</v>
+        <v>155990</v>
       </c>
       <c r="F43">
         <v>1</v>
@@ -2496,7 +2490,7 @@
         <v>0</v>
       </c>
       <c r="K43" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
     </row>
     <row r="44">
@@ -2510,7 +2504,7 @@
         <v>18</v>
       </c>
       <c r="D44" t="s">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="E44">
         <v>155990</v>
@@ -2580,7 +2574,7 @@
         <v>18</v>
       </c>
       <c r="D46" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E46">
         <v>155990</v>
@@ -2606,19 +2600,19 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B47" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C47" t="s">
-        <v>18</v>
+        <v>64</v>
       </c>
       <c r="D47" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="E47">
-        <v>155990</v>
+        <v>49990</v>
       </c>
       <c r="F47">
         <v>1</v>
@@ -2636,7 +2630,7 @@
         <v>0</v>
       </c>
       <c r="K47" t="s">
-        <v>106</v>
+        <v>21</v>
       </c>
     </row>
     <row r="48">
@@ -2647,10 +2641,10 @@
         <v>108</v>
       </c>
       <c r="C48" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D48" t="s">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="E48">
         <v>49990</v>
@@ -2676,19 +2670,19 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B49" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C49" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="D49" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E49">
-        <v>49990</v>
+        <v>135990</v>
       </c>
       <c r="F49">
         <v>1</v>
@@ -2706,24 +2700,24 @@
         <v>0</v>
       </c>
       <c r="K49" t="s">
-        <v>21</v>
+        <v>111</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B50" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C50" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D50" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="E50">
-        <v>135990</v>
+        <v>155990</v>
       </c>
       <c r="F50">
         <v>1</v>
@@ -2741,7 +2735,7 @@
         <v>0</v>
       </c>
       <c r="K50" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="51">
@@ -2755,7 +2749,7 @@
         <v>18</v>
       </c>
       <c r="D51" t="s">
-        <v>80</v>
+        <v>25</v>
       </c>
       <c r="E51">
         <v>155990</v>
@@ -2790,7 +2784,7 @@
         <v>18</v>
       </c>
       <c r="D52" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E52">
         <v>155990</v>
@@ -2816,28 +2810,28 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B53" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C53" t="s">
         <v>18</v>
       </c>
       <c r="D53" t="s">
-        <v>19</v>
+        <v>87</v>
       </c>
       <c r="E53">
-        <v>155990</v>
+        <v>129990</v>
       </c>
       <c r="F53">
         <v>1</v>
       </c>
       <c r="G53" t="s">
-        <v>20</v>
+        <v>117</v>
       </c>
       <c r="H53" t="s">
-        <v>20</v>
+        <v>117</v>
       </c>
       <c r="I53">
         <v>0</v>
@@ -2846,7 +2840,7 @@
         <v>0</v>
       </c>
       <c r="K53" t="s">
-        <v>114</v>
+        <v>21</v>
       </c>
     </row>
     <row r="54">
@@ -2860,7 +2854,7 @@
         <v>18</v>
       </c>
       <c r="D54" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E54">
         <v>129990</v>
@@ -2886,19 +2880,19 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B55" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C55" t="s">
-        <v>18</v>
+        <v>120</v>
       </c>
       <c r="D55" t="s">
-        <v>88</v>
+        <v>121</v>
       </c>
       <c r="E55">
-        <v>129990</v>
+        <v>179990</v>
       </c>
       <c r="F55">
         <v>1</v>
@@ -2921,19 +2915,19 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B56" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C56" t="s">
-        <v>120</v>
+        <v>18</v>
       </c>
       <c r="D56" t="s">
         <v>121</v>
       </c>
       <c r="E56">
-        <v>179990</v>
+        <v>159990</v>
       </c>
       <c r="F56">
         <v>1</v>
@@ -2956,19 +2950,19 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B57" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C57" t="s">
         <v>18</v>
       </c>
       <c r="D57" t="s">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="E57">
-        <v>159990</v>
+        <v>134990</v>
       </c>
       <c r="F57">
         <v>1</v>
@@ -3000,7 +2994,7 @@
         <v>18</v>
       </c>
       <c r="D58" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E58">
         <v>134990</v>
@@ -3035,7 +3029,7 @@
         <v>18</v>
       </c>
       <c r="D59" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E59">
         <v>134990</v>
@@ -3061,28 +3055,28 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B60" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C60" t="s">
         <v>18</v>
       </c>
       <c r="D60" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="E60">
-        <v>134990</v>
+        <v>79990</v>
       </c>
       <c r="F60">
         <v>1</v>
       </c>
       <c r="G60" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="H60" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="I60">
         <v>0</v>
@@ -3096,28 +3090,28 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B61" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C61" t="s">
         <v>18</v>
       </c>
       <c r="D61" t="s">
-        <v>69</v>
+        <v>48</v>
       </c>
       <c r="E61">
-        <v>79990</v>
+        <v>134990</v>
       </c>
       <c r="F61">
         <v>1</v>
       </c>
       <c r="G61" t="s">
-        <v>128</v>
+        <v>85</v>
       </c>
       <c r="H61" t="s">
-        <v>128</v>
+        <v>85</v>
       </c>
       <c r="I61">
         <v>0</v>
@@ -3137,10 +3131,10 @@
         <v>130</v>
       </c>
       <c r="C62" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="D62" t="s">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="E62">
         <v>134990</v>
@@ -3210,7 +3204,7 @@
         <v>28</v>
       </c>
       <c r="D64" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E64">
         <v>134990</v>
@@ -3245,7 +3239,7 @@
         <v>28</v>
       </c>
       <c r="D65" t="s">
-        <v>19</v>
+        <v>131</v>
       </c>
       <c r="E65">
         <v>134990</v>
@@ -3271,19 +3265,19 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B66" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C66" t="s">
         <v>28</v>
       </c>
       <c r="D66" t="s">
-        <v>131</v>
+        <v>48</v>
       </c>
       <c r="E66">
-        <v>134990</v>
+        <v>119990</v>
       </c>
       <c r="F66">
         <v>1</v>
@@ -3292,7 +3286,7 @@
         <v>85</v>
       </c>
       <c r="H66" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="I66">
         <v>0</v>
@@ -3315,7 +3309,7 @@
         <v>28</v>
       </c>
       <c r="D67" t="s">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="E67">
         <v>119990</v>
@@ -3327,7 +3321,7 @@
         <v>85</v>
       </c>
       <c r="H67" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I67">
         <v>0</v>
@@ -3362,7 +3356,7 @@
         <v>85</v>
       </c>
       <c r="H68" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I68">
         <v>0</v>
@@ -3376,16 +3370,16 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B69" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C69" t="s">
         <v>28</v>
       </c>
       <c r="D69" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="E69">
         <v>119990</v>
@@ -3397,7 +3391,7 @@
         <v>85</v>
       </c>
       <c r="H69" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I69">
         <v>0</v>
@@ -3406,7 +3400,7 @@
         <v>0</v>
       </c>
       <c r="K69" t="s">
-        <v>21</v>
+        <v>136</v>
       </c>
     </row>
     <row r="70">
@@ -3432,7 +3426,7 @@
         <v>85</v>
       </c>
       <c r="H70" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I70">
         <v>0</v>
@@ -3446,19 +3440,19 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B71" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C71" t="s">
         <v>28</v>
       </c>
       <c r="D71" t="s">
-        <v>35</v>
+        <v>84</v>
       </c>
       <c r="E71">
-        <v>119990</v>
+        <v>39990</v>
       </c>
       <c r="F71">
         <v>1</v>
@@ -3467,7 +3461,7 @@
         <v>85</v>
       </c>
       <c r="H71" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I71">
         <v>0</v>
@@ -3476,7 +3470,7 @@
         <v>0</v>
       </c>
       <c r="K71" t="s">
-        <v>136</v>
+        <v>21</v>
       </c>
     </row>
     <row r="72">
@@ -3490,7 +3484,7 @@
         <v>28</v>
       </c>
       <c r="D72" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E72">
         <v>39990</v>
@@ -3502,7 +3496,7 @@
         <v>85</v>
       </c>
       <c r="H72" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I72">
         <v>0</v>
@@ -3516,10 +3510,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B73" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C73" t="s">
         <v>28</v>
@@ -3537,7 +3531,7 @@
         <v>85</v>
       </c>
       <c r="H73" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I73">
         <v>0</v>
@@ -3546,33 +3540,33 @@
         <v>0</v>
       </c>
       <c r="K73" t="s">
-        <v>21</v>
+        <v>136</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B74" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C74" t="s">
-        <v>28</v>
+        <v>120</v>
       </c>
       <c r="D74" t="s">
-        <v>88</v>
+        <v>143</v>
       </c>
       <c r="E74">
-        <v>39990</v>
+        <v>140990</v>
       </c>
       <c r="F74">
         <v>1</v>
       </c>
       <c r="G74" t="s">
-        <v>85</v>
+        <v>117</v>
       </c>
       <c r="H74" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I74">
         <v>0</v>
@@ -3581,7 +3575,7 @@
         <v>0</v>
       </c>
       <c r="K74" t="s">
-        <v>136</v>
+        <v>86</v>
       </c>
     </row>
     <row r="75">
@@ -3595,10 +3589,10 @@
         <v>120</v>
       </c>
       <c r="D75" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E75">
-        <v>140990</v>
+        <v>145990</v>
       </c>
       <c r="F75">
         <v>1</v>
@@ -3607,7 +3601,7 @@
         <v>117</v>
       </c>
       <c r="H75" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I75">
         <v>0</v>
@@ -3621,28 +3615,28 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B76" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="C76" t="s">
-        <v>120</v>
+        <v>18</v>
       </c>
       <c r="D76" t="s">
-        <v>144</v>
-      </c>
-      <c r="E76">
-        <v>145990</v>
+        <v>48</v>
+      </c>
+      <c r="E76" s="4">
+        <v>199990</v>
       </c>
       <c r="F76">
         <v>1</v>
       </c>
       <c r="G76" t="s">
-        <v>117</v>
+        <v>85</v>
       </c>
       <c r="H76" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="I76">
         <v>0</v>
@@ -3651,7 +3645,7 @@
         <v>0</v>
       </c>
       <c r="K76" t="s">
-        <v>86</v>
+        <v>33</v>
       </c>
     </row>
     <row r="77">
@@ -3665,7 +3659,7 @@
         <v>18</v>
       </c>
       <c r="D77" t="s">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="E77" s="4">
         <v>199990</v>
@@ -3686,7 +3680,7 @@
         <v>0</v>
       </c>
       <c r="K77" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="78">
@@ -3721,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="K78" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="79">
@@ -3735,7 +3729,7 @@
         <v>18</v>
       </c>
       <c r="D79" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E79" s="4">
         <v>199990</v>
@@ -3756,7 +3750,7 @@
         <v>0</v>
       </c>
       <c r="K79" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="80">
@@ -3770,7 +3764,7 @@
         <v>18</v>
       </c>
       <c r="D80" t="s">
-        <v>19</v>
+        <v>131</v>
       </c>
       <c r="E80" s="4">
         <v>199990</v>
@@ -3791,24 +3785,24 @@
         <v>0</v>
       </c>
       <c r="K80" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B81" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C81" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="D81" t="s">
-        <v>131</v>
-      </c>
-      <c r="E81" s="4">
-        <v>199990</v>
+        <v>48</v>
+      </c>
+      <c r="E81">
+        <v>155990</v>
       </c>
       <c r="F81">
         <v>1</v>
@@ -3826,7 +3820,7 @@
         <v>0</v>
       </c>
       <c r="K81" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
     </row>
     <row r="82">
@@ -3840,7 +3834,7 @@
         <v>28</v>
       </c>
       <c r="D82" t="s">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="E82">
         <v>155990</v>
@@ -3910,7 +3904,7 @@
         <v>28</v>
       </c>
       <c r="D84" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E84">
         <v>155990</v>
@@ -3936,19 +3930,19 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B85" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C85" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D85" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="E85">
-        <v>155990</v>
+        <v>269990</v>
       </c>
       <c r="F85">
         <v>1</v>
@@ -3966,7 +3960,7 @@
         <v>0</v>
       </c>
       <c r="K85" t="s">
-        <v>21</v>
+        <v>151</v>
       </c>
     </row>
     <row r="86">
@@ -3980,7 +3974,7 @@
         <v>18</v>
       </c>
       <c r="D86" t="s">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="E86">
         <v>269990</v>
@@ -4050,7 +4044,7 @@
         <v>18</v>
       </c>
       <c r="D88" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E88">
         <v>269990</v>
@@ -4085,7 +4079,7 @@
         <v>18</v>
       </c>
       <c r="D89" t="s">
-        <v>19</v>
+        <v>131</v>
       </c>
       <c r="E89">
         <v>269990</v>
@@ -4111,19 +4105,19 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B90" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C90" t="s">
         <v>18</v>
       </c>
       <c r="D90" t="s">
-        <v>131</v>
+        <v>29</v>
       </c>
       <c r="E90">
-        <v>269990</v>
+        <v>199990</v>
       </c>
       <c r="F90">
         <v>1</v>
@@ -4141,7 +4135,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="s">
-        <v>151</v>
+        <v>33</v>
       </c>
     </row>
     <row r="91">
@@ -4176,7 +4170,7 @@
         <v>0</v>
       </c>
       <c r="K91" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="92">
@@ -4190,7 +4184,7 @@
         <v>18</v>
       </c>
       <c r="D92" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E92">
         <v>199990</v>
@@ -4211,7 +4205,7 @@
         <v>0</v>
       </c>
       <c r="K92" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="93">
@@ -4225,7 +4219,7 @@
         <v>18</v>
       </c>
       <c r="D93" t="s">
-        <v>19</v>
+        <v>131</v>
       </c>
       <c r="E93">
         <v>199990</v>
@@ -4246,24 +4240,24 @@
         <v>0</v>
       </c>
       <c r="K93" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B94" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C94" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="D94" t="s">
-        <v>131</v>
+        <v>48</v>
       </c>
       <c r="E94">
-        <v>199990</v>
+        <v>194990</v>
       </c>
       <c r="F94">
         <v>1</v>
@@ -4281,7 +4275,7 @@
         <v>0</v>
       </c>
       <c r="K94" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
     </row>
     <row r="95">
@@ -4295,7 +4289,7 @@
         <v>28</v>
       </c>
       <c r="D95" t="s">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="E95">
         <v>194990</v>
@@ -4365,7 +4359,7 @@
         <v>28</v>
       </c>
       <c r="D97" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E97">
         <v>194990</v>
@@ -4391,28 +4385,28 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B98" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C98" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D98" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="E98">
-        <v>194990</v>
+        <v>202990</v>
       </c>
       <c r="F98">
         <v>1</v>
       </c>
       <c r="G98" t="s">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="H98" t="s">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="I98">
         <v>0</v>
@@ -4421,41 +4415,6 @@
         <v>0</v>
       </c>
       <c r="K98" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="s">
-        <v>156</v>
-      </c>
-      <c r="B99" t="s">
-        <v>157</v>
-      </c>
-      <c r="C99" t="s">
-        <v>18</v>
-      </c>
-      <c r="D99" t="s">
-        <v>80</v>
-      </c>
-      <c r="E99">
-        <v>202990</v>
-      </c>
-      <c r="F99">
-        <v>1</v>
-      </c>
-      <c r="G99" t="s">
-        <v>20</v>
-      </c>
-      <c r="H99" t="s">
-        <v>20</v>
-      </c>
-      <c r="I99">
-        <v>0</v>
-      </c>
-      <c r="J99">
-        <v>0</v>
-      </c>
-      <c r="K99" t="s">
         <v>114</v>
       </c>
     </row>

--- a/data/catalogo_jusp.xlsx
+++ b/data/catalogo_jusp.xlsx
@@ -2084,10 +2084,10 @@
         <v>18</v>
       </c>
       <c r="D32" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E32">
-        <v>99990</v>
+        <v>139990</v>
       </c>
       <c r="F32">
         <v>1</v>

--- a/data/catalogo_jusp.xlsx
+++ b/data/catalogo_jusp.xlsx
@@ -950,7 +950,7 @@
         <v>46130.833333333328</v>
       </c>
       <c r="O2" s="3">
-        <v>46130.957638888889</v>
+        <v>46133.957638888889</v>
       </c>
       <c r="P2" t="s">
         <v>22</v>

--- a/data/catalogo_jusp.xlsx
+++ b/data/catalogo_jusp.xlsx
@@ -195,9 +195,6 @@
   </si>
   <si>
     <t>Women's Medium-Support 1-Piece Pad Sports Bra</t>
-  </si>
-  <si>
-    <t>Blanck</t>
   </si>
   <si>
     <t>nike-fz2856-010</t>
@@ -1582,7 +1579,7 @@
         <v>1</v>
       </c>
       <c r="K18" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
       <c r="L18">
         <v>25</v>
@@ -1592,10 +1589,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
+        <v>59</v>
+      </c>
+      <c r="B19" t="s">
         <v>60</v>
-      </c>
-      <c r="B19" t="s">
-        <v>61</v>
       </c>
       <c r="C19" t="s">
         <v>18</v>
@@ -1622,7 +1619,7 @@
         <v>1</v>
       </c>
       <c r="K19" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
       <c r="L19">
         <v>30</v>
@@ -1632,10 +1629,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" t="s">
         <v>60</v>
-      </c>
-      <c r="B20" t="s">
-        <v>61</v>
       </c>
       <c r="C20" t="s">
         <v>18</v>
@@ -1662,7 +1659,7 @@
         <v>1</v>
       </c>
       <c r="K20" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
       <c r="L20">
         <v>30</v>
@@ -1672,13 +1669,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
+        <v>61</v>
+      </c>
+      <c r="B21" t="s">
         <v>62</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>63</v>
-      </c>
-      <c r="C21" t="s">
-        <v>64</v>
       </c>
       <c r="D21" t="s">
         <v>25</v>
@@ -1702,7 +1699,7 @@
         <v>1</v>
       </c>
       <c r="K21" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="L21">
         <v>25</v>
@@ -1712,13 +1709,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
+        <v>65</v>
+      </c>
+      <c r="B22" t="s">
         <v>66</v>
       </c>
-      <c r="B22" t="s">
-        <v>67</v>
-      </c>
       <c r="C22" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D22" t="s">
         <v>25</v>
@@ -1752,16 +1749,16 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
+        <v>67</v>
+      </c>
+      <c r="B23" t="s">
         <v>68</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
+        <v>18</v>
+      </c>
+      <c r="D23" t="s">
         <v>69</v>
-      </c>
-      <c r="C23" t="s">
-        <v>18</v>
-      </c>
-      <c r="D23" t="s">
-        <v>70</v>
       </c>
       <c r="E23">
         <v>129990</v>
@@ -1770,10 +1767,10 @@
         <v>1</v>
       </c>
       <c r="G23" t="s">
+        <v>70</v>
+      </c>
+      <c r="H23" t="s">
         <v>71</v>
-      </c>
-      <c r="H23" t="s">
-        <v>72</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -1789,16 +1786,16 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
+        <v>72</v>
+      </c>
+      <c r="B24" t="s">
         <v>73</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
+        <v>18</v>
+      </c>
+      <c r="D24" t="s">
         <v>74</v>
-      </c>
-      <c r="C24" t="s">
-        <v>18</v>
-      </c>
-      <c r="D24" t="s">
-        <v>75</v>
       </c>
       <c r="E24">
         <v>88990</v>
@@ -1807,10 +1804,10 @@
         <v>1</v>
       </c>
       <c r="G24" t="s">
+        <v>75</v>
+      </c>
+      <c r="H24" t="s">
         <v>76</v>
-      </c>
-      <c r="H24" t="s">
-        <v>77</v>
       </c>
       <c r="I24">
         <v>0</v>
@@ -1827,16 +1824,16 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
+        <v>72</v>
+      </c>
+      <c r="B25" t="s">
         <v>73</v>
       </c>
-      <c r="B25" t="s">
-        <v>74</v>
-      </c>
       <c r="C25" t="s">
         <v>18</v>
       </c>
       <c r="D25" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E25">
         <v>88990</v>
@@ -1845,10 +1842,10 @@
         <v>1</v>
       </c>
       <c r="G25" t="s">
+        <v>75</v>
+      </c>
+      <c r="H25" t="s">
         <v>76</v>
-      </c>
-      <c r="H25" t="s">
-        <v>77</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -1865,10 +1862,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
+        <v>78</v>
+      </c>
+      <c r="B26" t="s">
         <v>79</v>
-      </c>
-      <c r="B26" t="s">
-        <v>80</v>
       </c>
       <c r="C26" t="s">
         <v>18</v>
@@ -1895,15 +1892,15 @@
         <v>0</v>
       </c>
       <c r="K26" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
+        <v>78</v>
+      </c>
+      <c r="B27" t="s">
         <v>79</v>
-      </c>
-      <c r="B27" t="s">
-        <v>80</v>
       </c>
       <c r="C27" t="s">
         <v>18</v>
@@ -1930,21 +1927,21 @@
         <v>0</v>
       </c>
       <c r="K27" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
+        <v>81</v>
+      </c>
+      <c r="B28" t="s">
         <v>82</v>
-      </c>
-      <c r="B28" t="s">
-        <v>83</v>
       </c>
       <c r="C28" t="s">
         <v>28</v>
       </c>
       <c r="D28" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E28">
         <v>75990</v>
@@ -1953,33 +1950,33 @@
         <v>1</v>
       </c>
       <c r="G28" t="s">
+        <v>84</v>
+      </c>
+      <c r="H28" t="s">
+        <v>84</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28" t="s">
         <v>85</v>
-      </c>
-      <c r="H28" t="s">
-        <v>85</v>
-      </c>
-      <c r="I28">
-        <v>0</v>
-      </c>
-      <c r="J28">
-        <v>0</v>
-      </c>
-      <c r="K28" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
+        <v>81</v>
+      </c>
+      <c r="B29" t="s">
         <v>82</v>
-      </c>
-      <c r="B29" t="s">
-        <v>83</v>
       </c>
       <c r="C29" t="s">
         <v>28</v>
       </c>
       <c r="D29" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E29">
         <v>79990</v>
@@ -1988,33 +1985,33 @@
         <v>1</v>
       </c>
       <c r="G29" t="s">
+        <v>84</v>
+      </c>
+      <c r="H29" t="s">
+        <v>84</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29" t="s">
         <v>85</v>
-      </c>
-      <c r="H29" t="s">
-        <v>85</v>
-      </c>
-      <c r="I29">
-        <v>0</v>
-      </c>
-      <c r="J29">
-        <v>0</v>
-      </c>
-      <c r="K29" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
+        <v>81</v>
+      </c>
+      <c r="B30" t="s">
         <v>82</v>
-      </c>
-      <c r="B30" t="s">
-        <v>83</v>
       </c>
       <c r="C30" t="s">
         <v>28</v>
       </c>
       <c r="D30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E30">
         <v>78990</v>
@@ -2023,27 +2020,27 @@
         <v>1</v>
       </c>
       <c r="G30" t="s">
+        <v>84</v>
+      </c>
+      <c r="H30" t="s">
+        <v>84</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30" t="s">
         <v>85</v>
-      </c>
-      <c r="H30" t="s">
-        <v>85</v>
-      </c>
-      <c r="I30">
-        <v>0</v>
-      </c>
-      <c r="J30">
-        <v>0</v>
-      </c>
-      <c r="K30" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
+        <v>88</v>
+      </c>
+      <c r="B31" t="s">
         <v>89</v>
-      </c>
-      <c r="B31" t="s">
-        <v>90</v>
       </c>
       <c r="C31" t="s">
         <v>18</v>
@@ -2070,15 +2067,15 @@
         <v>0</v>
       </c>
       <c r="K31" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
+        <v>91</v>
+      </c>
+      <c r="B32" t="s">
         <v>92</v>
-      </c>
-      <c r="B32" t="s">
-        <v>93</v>
       </c>
       <c r="C32" t="s">
         <v>18</v>
@@ -2110,10 +2107,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
+        <v>93</v>
+      </c>
+      <c r="B33" t="s">
         <v>94</v>
-      </c>
-      <c r="B33" t="s">
-        <v>95</v>
       </c>
       <c r="C33" t="s">
         <v>18</v>
@@ -2128,27 +2125,27 @@
         <v>0</v>
       </c>
       <c r="G33" t="s">
+        <v>84</v>
+      </c>
+      <c r="H33" t="s">
+        <v>84</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33" t="s">
         <v>85</v>
-      </c>
-      <c r="H33" t="s">
-        <v>85</v>
-      </c>
-      <c r="I33">
-        <v>0</v>
-      </c>
-      <c r="J33">
-        <v>0</v>
-      </c>
-      <c r="K33" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
+        <v>95</v>
+      </c>
+      <c r="B34" t="s">
         <v>96</v>
-      </c>
-      <c r="B34" t="s">
-        <v>97</v>
       </c>
       <c r="C34" t="s">
         <v>18</v>
@@ -2180,16 +2177,16 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
+        <v>97</v>
+      </c>
+      <c r="B35" t="s">
         <v>98</v>
       </c>
-      <c r="B35" t="s">
-        <v>99</v>
-      </c>
       <c r="C35" t="s">
         <v>18</v>
       </c>
       <c r="D35" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E35">
         <v>65990</v>
@@ -2198,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="G35" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H35" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -2210,21 +2207,21 @@
         <v>0</v>
       </c>
       <c r="K35" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
+        <v>97</v>
+      </c>
+      <c r="B36" t="s">
         <v>98</v>
       </c>
-      <c r="B36" t="s">
-        <v>99</v>
-      </c>
       <c r="C36" t="s">
         <v>18</v>
       </c>
       <c r="D36" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E36">
         <v>75990</v>
@@ -2233,10 +2230,10 @@
         <v>1</v>
       </c>
       <c r="G36" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H36" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -2245,21 +2242,21 @@
         <v>0</v>
       </c>
       <c r="K36" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
+        <v>97</v>
+      </c>
+      <c r="B37" t="s">
         <v>98</v>
       </c>
-      <c r="B37" t="s">
-        <v>99</v>
-      </c>
       <c r="C37" t="s">
         <v>18</v>
       </c>
       <c r="D37" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E37">
         <v>85990</v>
@@ -2268,10 +2265,10 @@
         <v>1</v>
       </c>
       <c r="G37" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H37" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -2280,21 +2277,21 @@
         <v>0</v>
       </c>
       <c r="K37" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
+        <v>100</v>
+      </c>
+      <c r="B38" t="s">
         <v>101</v>
       </c>
-      <c r="B38" t="s">
+      <c r="C38" t="s">
+        <v>18</v>
+      </c>
+      <c r="D38" t="s">
         <v>102</v>
-      </c>
-      <c r="C38" t="s">
-        <v>18</v>
-      </c>
-      <c r="D38" t="s">
-        <v>103</v>
       </c>
       <c r="E38">
         <v>79990</v>
@@ -2315,15 +2312,15 @@
         <v>0</v>
       </c>
       <c r="K38" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
+        <v>100</v>
+      </c>
+      <c r="B39" t="s">
         <v>101</v>
-      </c>
-      <c r="B39" t="s">
-        <v>102</v>
       </c>
       <c r="C39" t="s">
         <v>18</v>
@@ -2350,15 +2347,15 @@
         <v>0</v>
       </c>
       <c r="K39" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
+        <v>100</v>
+      </c>
+      <c r="B40" t="s">
         <v>101</v>
-      </c>
-      <c r="B40" t="s">
-        <v>102</v>
       </c>
       <c r="C40" t="s">
         <v>18</v>
@@ -2385,15 +2382,15 @@
         <v>0</v>
       </c>
       <c r="K40" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
+        <v>100</v>
+      </c>
+      <c r="B41" t="s">
         <v>101</v>
-      </c>
-      <c r="B41" t="s">
-        <v>102</v>
       </c>
       <c r="C41" t="s">
         <v>18</v>
@@ -2420,15 +2417,15 @@
         <v>0</v>
       </c>
       <c r="K41" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
+        <v>100</v>
+      </c>
+      <c r="B42" t="s">
         <v>101</v>
-      </c>
-      <c r="B42" t="s">
-        <v>102</v>
       </c>
       <c r="C42" t="s">
         <v>18</v>
@@ -2455,15 +2452,15 @@
         <v>0</v>
       </c>
       <c r="K42" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
+        <v>103</v>
+      </c>
+      <c r="B43" t="s">
         <v>104</v>
-      </c>
-      <c r="B43" t="s">
-        <v>105</v>
       </c>
       <c r="C43" t="s">
         <v>18</v>
@@ -2490,15 +2487,15 @@
         <v>0</v>
       </c>
       <c r="K43" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
+        <v>103</v>
+      </c>
+      <c r="B44" t="s">
         <v>104</v>
-      </c>
-      <c r="B44" t="s">
-        <v>105</v>
       </c>
       <c r="C44" t="s">
         <v>18</v>
@@ -2525,15 +2522,15 @@
         <v>0</v>
       </c>
       <c r="K44" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
+        <v>103</v>
+      </c>
+      <c r="B45" t="s">
         <v>104</v>
-      </c>
-      <c r="B45" t="s">
-        <v>105</v>
       </c>
       <c r="C45" t="s">
         <v>18</v>
@@ -2560,15 +2557,15 @@
         <v>0</v>
       </c>
       <c r="K45" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
+        <v>103</v>
+      </c>
+      <c r="B46" t="s">
         <v>104</v>
-      </c>
-      <c r="B46" t="s">
-        <v>105</v>
       </c>
       <c r="C46" t="s">
         <v>18</v>
@@ -2595,18 +2592,18 @@
         <v>0</v>
       </c>
       <c r="K46" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
+        <v>106</v>
+      </c>
+      <c r="B47" t="s">
         <v>107</v>
       </c>
-      <c r="B47" t="s">
-        <v>108</v>
-      </c>
       <c r="C47" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D47" t="s">
         <v>48</v>
@@ -2635,13 +2632,13 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
+        <v>106</v>
+      </c>
+      <c r="B48" t="s">
         <v>107</v>
       </c>
-      <c r="B48" t="s">
-        <v>108</v>
-      </c>
       <c r="C48" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D48" t="s">
         <v>29</v>
@@ -2670,10 +2667,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
+        <v>108</v>
+      </c>
+      <c r="B49" t="s">
         <v>109</v>
-      </c>
-      <c r="B49" t="s">
-        <v>110</v>
       </c>
       <c r="C49" t="s">
         <v>28</v>
@@ -2700,15 +2697,15 @@
         <v>0</v>
       </c>
       <c r="K49" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
+        <v>111</v>
+      </c>
+      <c r="B50" t="s">
         <v>112</v>
-      </c>
-      <c r="B50" t="s">
-        <v>113</v>
       </c>
       <c r="C50" t="s">
         <v>18</v>
@@ -2735,15 +2732,15 @@
         <v>0</v>
       </c>
       <c r="K50" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
+        <v>111</v>
+      </c>
+      <c r="B51" t="s">
         <v>112</v>
-      </c>
-      <c r="B51" t="s">
-        <v>113</v>
       </c>
       <c r="C51" t="s">
         <v>18</v>
@@ -2770,15 +2767,15 @@
         <v>0</v>
       </c>
       <c r="K51" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
+        <v>111</v>
+      </c>
+      <c r="B52" t="s">
         <v>112</v>
-      </c>
-      <c r="B52" t="s">
-        <v>113</v>
       </c>
       <c r="C52" t="s">
         <v>18</v>
@@ -2805,21 +2802,21 @@
         <v>0</v>
       </c>
       <c r="K52" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
+        <v>114</v>
+      </c>
+      <c r="B53" t="s">
         <v>115</v>
       </c>
-      <c r="B53" t="s">
-        <v>116</v>
-      </c>
       <c r="C53" t="s">
         <v>18</v>
       </c>
       <c r="D53" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E53">
         <v>129990</v>
@@ -2828,10 +2825,10 @@
         <v>1</v>
       </c>
       <c r="G53" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H53" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I53">
         <v>0</v>
@@ -2845,16 +2842,16 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
+        <v>114</v>
+      </c>
+      <c r="B54" t="s">
         <v>115</v>
       </c>
-      <c r="B54" t="s">
-        <v>116</v>
-      </c>
       <c r="C54" t="s">
         <v>18</v>
       </c>
       <c r="D54" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E54">
         <v>129990</v>
@@ -2863,10 +2860,10 @@
         <v>1</v>
       </c>
       <c r="G54" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H54" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I54">
         <v>0</v>
@@ -2880,16 +2877,16 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
+        <v>117</v>
+      </c>
+      <c r="B55" t="s">
         <v>118</v>
       </c>
-      <c r="B55" t="s">
+      <c r="C55" t="s">
         <v>119</v>
       </c>
-      <c r="C55" t="s">
+      <c r="D55" t="s">
         <v>120</v>
-      </c>
-      <c r="D55" t="s">
-        <v>121</v>
       </c>
       <c r="E55">
         <v>179990</v>
@@ -2898,10 +2895,10 @@
         <v>1</v>
       </c>
       <c r="G55" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H55" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I55">
         <v>0</v>
@@ -2915,16 +2912,16 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
+        <v>121</v>
+      </c>
+      <c r="B56" t="s">
         <v>122</v>
       </c>
-      <c r="B56" t="s">
-        <v>123</v>
-      </c>
       <c r="C56" t="s">
         <v>18</v>
       </c>
       <c r="D56" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E56">
         <v>159990</v>
@@ -2933,10 +2930,10 @@
         <v>1</v>
       </c>
       <c r="G56" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H56" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I56">
         <v>0</v>
@@ -2950,16 +2947,16 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
+        <v>123</v>
+      </c>
+      <c r="B57" t="s">
         <v>124</v>
       </c>
-      <c r="B57" t="s">
-        <v>125</v>
-      </c>
       <c r="C57" t="s">
         <v>18</v>
       </c>
       <c r="D57" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E57">
         <v>134990</v>
@@ -2968,10 +2965,10 @@
         <v>1</v>
       </c>
       <c r="G57" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H57" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I57">
         <v>0</v>
@@ -2985,16 +2982,16 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
+        <v>123</v>
+      </c>
+      <c r="B58" t="s">
         <v>124</v>
       </c>
-      <c r="B58" t="s">
-        <v>125</v>
-      </c>
       <c r="C58" t="s">
         <v>18</v>
       </c>
       <c r="D58" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E58">
         <v>134990</v>
@@ -3003,10 +3000,10 @@
         <v>1</v>
       </c>
       <c r="G58" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H58" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I58">
         <v>0</v>
@@ -3020,16 +3017,16 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
+        <v>123</v>
+      </c>
+      <c r="B59" t="s">
         <v>124</v>
       </c>
-      <c r="B59" t="s">
-        <v>125</v>
-      </c>
       <c r="C59" t="s">
         <v>18</v>
       </c>
       <c r="D59" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E59">
         <v>134990</v>
@@ -3038,10 +3035,10 @@
         <v>1</v>
       </c>
       <c r="G59" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H59" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I59">
         <v>0</v>
@@ -3055,16 +3052,16 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
+        <v>125</v>
+      </c>
+      <c r="B60" t="s">
         <v>126</v>
       </c>
-      <c r="B60" t="s">
-        <v>127</v>
-      </c>
       <c r="C60" t="s">
         <v>18</v>
       </c>
       <c r="D60" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E60">
         <v>79990</v>
@@ -3073,10 +3070,10 @@
         <v>1</v>
       </c>
       <c r="G60" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H60" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I60">
         <v>0</v>
@@ -3090,10 +3087,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
+        <v>128</v>
+      </c>
+      <c r="B61" t="s">
         <v>129</v>
-      </c>
-      <c r="B61" t="s">
-        <v>130</v>
       </c>
       <c r="C61" t="s">
         <v>18</v>
@@ -3108,10 +3105,10 @@
         <v>1</v>
       </c>
       <c r="G61" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H61" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I61">
         <v>0</v>
@@ -3125,10 +3122,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
+        <v>128</v>
+      </c>
+      <c r="B62" t="s">
         <v>129</v>
-      </c>
-      <c r="B62" t="s">
-        <v>130</v>
       </c>
       <c r="C62" t="s">
         <v>28</v>
@@ -3143,10 +3140,10 @@
         <v>1</v>
       </c>
       <c r="G62" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H62" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I62">
         <v>0</v>
@@ -3160,10 +3157,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
+        <v>128</v>
+      </c>
+      <c r="B63" t="s">
         <v>129</v>
-      </c>
-      <c r="B63" t="s">
-        <v>130</v>
       </c>
       <c r="C63" t="s">
         <v>28</v>
@@ -3178,10 +3175,10 @@
         <v>1</v>
       </c>
       <c r="G63" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H63" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I63">
         <v>0</v>
@@ -3195,10 +3192,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
+        <v>128</v>
+      </c>
+      <c r="B64" t="s">
         <v>129</v>
-      </c>
-      <c r="B64" t="s">
-        <v>130</v>
       </c>
       <c r="C64" t="s">
         <v>28</v>
@@ -3213,10 +3210,10 @@
         <v>1</v>
       </c>
       <c r="G64" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H64" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I64">
         <v>0</v>
@@ -3230,16 +3227,16 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
+        <v>128</v>
+      </c>
+      <c r="B65" t="s">
         <v>129</v>
-      </c>
-      <c r="B65" t="s">
-        <v>130</v>
       </c>
       <c r="C65" t="s">
         <v>28</v>
       </c>
       <c r="D65" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E65">
         <v>134990</v>
@@ -3248,10 +3245,10 @@
         <v>1</v>
       </c>
       <c r="G65" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H65" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I65">
         <v>0</v>
@@ -3265,10 +3262,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
+        <v>131</v>
+      </c>
+      <c r="B66" t="s">
         <v>132</v>
-      </c>
-      <c r="B66" t="s">
-        <v>133</v>
       </c>
       <c r="C66" t="s">
         <v>28</v>
@@ -3283,10 +3280,10 @@
         <v>1</v>
       </c>
       <c r="G66" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H66" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I66">
         <v>0</v>
@@ -3300,10 +3297,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
+        <v>131</v>
+      </c>
+      <c r="B67" t="s">
         <v>132</v>
-      </c>
-      <c r="B67" t="s">
-        <v>133</v>
       </c>
       <c r="C67" t="s">
         <v>28</v>
@@ -3318,10 +3315,10 @@
         <v>1</v>
       </c>
       <c r="G67" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H67" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I67">
         <v>0</v>
@@ -3335,10 +3332,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
+        <v>131</v>
+      </c>
+      <c r="B68" t="s">
         <v>132</v>
-      </c>
-      <c r="B68" t="s">
-        <v>133</v>
       </c>
       <c r="C68" t="s">
         <v>28</v>
@@ -3353,10 +3350,10 @@
         <v>1</v>
       </c>
       <c r="G68" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H68" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I68">
         <v>0</v>
@@ -3370,10 +3367,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
+        <v>133</v>
+      </c>
+      <c r="B69" t="s">
         <v>134</v>
-      </c>
-      <c r="B69" t="s">
-        <v>135</v>
       </c>
       <c r="C69" t="s">
         <v>28</v>
@@ -3388,10 +3385,10 @@
         <v>1</v>
       </c>
       <c r="G69" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H69" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I69">
         <v>0</v>
@@ -3400,15 +3397,15 @@
         <v>0</v>
       </c>
       <c r="K69" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
+        <v>133</v>
+      </c>
+      <c r="B70" t="s">
         <v>134</v>
-      </c>
-      <c r="B70" t="s">
-        <v>135</v>
       </c>
       <c r="C70" t="s">
         <v>28</v>
@@ -3423,10 +3420,10 @@
         <v>1</v>
       </c>
       <c r="G70" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H70" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I70">
         <v>0</v>
@@ -3435,21 +3432,21 @@
         <v>0</v>
       </c>
       <c r="K70" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
+        <v>136</v>
+      </c>
+      <c r="B71" t="s">
         <v>137</v>
-      </c>
-      <c r="B71" t="s">
-        <v>138</v>
       </c>
       <c r="C71" t="s">
         <v>28</v>
       </c>
       <c r="D71" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E71">
         <v>39990</v>
@@ -3458,10 +3455,10 @@
         <v>1</v>
       </c>
       <c r="G71" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H71" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I71">
         <v>0</v>
@@ -3475,16 +3472,16 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
+        <v>136</v>
+      </c>
+      <c r="B72" t="s">
         <v>137</v>
-      </c>
-      <c r="B72" t="s">
-        <v>138</v>
       </c>
       <c r="C72" t="s">
         <v>28</v>
       </c>
       <c r="D72" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E72">
         <v>39990</v>
@@ -3493,10 +3490,10 @@
         <v>1</v>
       </c>
       <c r="G72" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H72" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I72">
         <v>0</v>
@@ -3510,16 +3507,16 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
+        <v>138</v>
+      </c>
+      <c r="B73" t="s">
         <v>139</v>
-      </c>
-      <c r="B73" t="s">
-        <v>140</v>
       </c>
       <c r="C73" t="s">
         <v>28</v>
       </c>
       <c r="D73" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E73">
         <v>39990</v>
@@ -3528,10 +3525,10 @@
         <v>1</v>
       </c>
       <c r="G73" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H73" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I73">
         <v>0</v>
@@ -3540,21 +3537,21 @@
         <v>0</v>
       </c>
       <c r="K73" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
+        <v>140</v>
+      </c>
+      <c r="B74" t="s">
         <v>141</v>
       </c>
-      <c r="B74" t="s">
+      <c r="C74" t="s">
+        <v>119</v>
+      </c>
+      <c r="D74" t="s">
         <v>142</v>
-      </c>
-      <c r="C74" t="s">
-        <v>120</v>
-      </c>
-      <c r="D74" t="s">
-        <v>143</v>
       </c>
       <c r="E74">
         <v>140990</v>
@@ -3563,10 +3560,10 @@
         <v>1</v>
       </c>
       <c r="G74" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H74" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I74">
         <v>0</v>
@@ -3575,21 +3572,21 @@
         <v>0</v>
       </c>
       <c r="K74" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
+        <v>140</v>
+      </c>
+      <c r="B75" t="s">
         <v>141</v>
       </c>
-      <c r="B75" t="s">
-        <v>142</v>
-      </c>
       <c r="C75" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D75" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E75">
         <v>145990</v>
@@ -3598,10 +3595,10 @@
         <v>1</v>
       </c>
       <c r="G75" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H75" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I75">
         <v>0</v>
@@ -3610,15 +3607,15 @@
         <v>0</v>
       </c>
       <c r="K75" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
+        <v>144</v>
+      </c>
+      <c r="B76" t="s">
         <v>145</v>
-      </c>
-      <c r="B76" t="s">
-        <v>146</v>
       </c>
       <c r="C76" t="s">
         <v>18</v>
@@ -3633,10 +3630,10 @@
         <v>1</v>
       </c>
       <c r="G76" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H76" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I76">
         <v>0</v>
@@ -3650,10 +3647,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
+        <v>144</v>
+      </c>
+      <c r="B77" t="s">
         <v>145</v>
-      </c>
-      <c r="B77" t="s">
-        <v>146</v>
       </c>
       <c r="C77" t="s">
         <v>18</v>
@@ -3668,10 +3665,10 @@
         <v>1</v>
       </c>
       <c r="G77" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H77" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I77">
         <v>0</v>
@@ -3685,10 +3682,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
+        <v>144</v>
+      </c>
+      <c r="B78" t="s">
         <v>145</v>
-      </c>
-      <c r="B78" t="s">
-        <v>146</v>
       </c>
       <c r="C78" t="s">
         <v>18</v>
@@ -3703,10 +3700,10 @@
         <v>1</v>
       </c>
       <c r="G78" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H78" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I78">
         <v>0</v>
@@ -3720,10 +3717,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
+        <v>144</v>
+      </c>
+      <c r="B79" t="s">
         <v>145</v>
-      </c>
-      <c r="B79" t="s">
-        <v>146</v>
       </c>
       <c r="C79" t="s">
         <v>18</v>
@@ -3738,10 +3735,10 @@
         <v>1</v>
       </c>
       <c r="G79" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H79" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I79">
         <v>0</v>
@@ -3755,16 +3752,16 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
+        <v>144</v>
+      </c>
+      <c r="B80" t="s">
         <v>145</v>
       </c>
-      <c r="B80" t="s">
-        <v>146</v>
-      </c>
       <c r="C80" t="s">
         <v>18</v>
       </c>
       <c r="D80" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E80" s="4">
         <v>199990</v>
@@ -3773,10 +3770,10 @@
         <v>1</v>
       </c>
       <c r="G80" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H80" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I80">
         <v>0</v>
@@ -3790,10 +3787,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
+        <v>146</v>
+      </c>
+      <c r="B81" t="s">
         <v>147</v>
-      </c>
-      <c r="B81" t="s">
-        <v>148</v>
       </c>
       <c r="C81" t="s">
         <v>28</v>
@@ -3808,10 +3805,10 @@
         <v>1</v>
       </c>
       <c r="G81" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H81" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I81">
         <v>0</v>
@@ -3825,10 +3822,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
+        <v>146</v>
+      </c>
+      <c r="B82" t="s">
         <v>147</v>
-      </c>
-      <c r="B82" t="s">
-        <v>148</v>
       </c>
       <c r="C82" t="s">
         <v>28</v>
@@ -3843,10 +3840,10 @@
         <v>1</v>
       </c>
       <c r="G82" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H82" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I82">
         <v>0</v>
@@ -3860,10 +3857,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
+        <v>146</v>
+      </c>
+      <c r="B83" t="s">
         <v>147</v>
-      </c>
-      <c r="B83" t="s">
-        <v>148</v>
       </c>
       <c r="C83" t="s">
         <v>28</v>
@@ -3878,10 +3875,10 @@
         <v>1</v>
       </c>
       <c r="G83" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H83" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I83">
         <v>0</v>
@@ -3895,10 +3892,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
+        <v>146</v>
+      </c>
+      <c r="B84" t="s">
         <v>147</v>
-      </c>
-      <c r="B84" t="s">
-        <v>148</v>
       </c>
       <c r="C84" t="s">
         <v>28</v>
@@ -3913,10 +3910,10 @@
         <v>1</v>
       </c>
       <c r="G84" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H84" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I84">
         <v>0</v>
@@ -3930,10 +3927,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
+        <v>148</v>
+      </c>
+      <c r="B85" t="s">
         <v>149</v>
-      </c>
-      <c r="B85" t="s">
-        <v>150</v>
       </c>
       <c r="C85" t="s">
         <v>18</v>
@@ -3948,10 +3945,10 @@
         <v>1</v>
       </c>
       <c r="G85" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H85" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I85">
         <v>0</v>
@@ -3960,15 +3957,15 @@
         <v>0</v>
       </c>
       <c r="K85" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
+        <v>148</v>
+      </c>
+      <c r="B86" t="s">
         <v>149</v>
-      </c>
-      <c r="B86" t="s">
-        <v>150</v>
       </c>
       <c r="C86" t="s">
         <v>18</v>
@@ -3983,10 +3980,10 @@
         <v>1</v>
       </c>
       <c r="G86" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H86" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I86">
         <v>0</v>
@@ -3995,15 +3992,15 @@
         <v>0</v>
       </c>
       <c r="K86" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
+        <v>148</v>
+      </c>
+      <c r="B87" t="s">
         <v>149</v>
-      </c>
-      <c r="B87" t="s">
-        <v>150</v>
       </c>
       <c r="C87" t="s">
         <v>18</v>
@@ -4018,10 +4015,10 @@
         <v>1</v>
       </c>
       <c r="G87" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H87" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I87">
         <v>0</v>
@@ -4030,15 +4027,15 @@
         <v>0</v>
       </c>
       <c r="K87" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
+        <v>148</v>
+      </c>
+      <c r="B88" t="s">
         <v>149</v>
-      </c>
-      <c r="B88" t="s">
-        <v>150</v>
       </c>
       <c r="C88" t="s">
         <v>18</v>
@@ -4053,10 +4050,10 @@
         <v>1</v>
       </c>
       <c r="G88" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H88" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I88">
         <v>0</v>
@@ -4065,21 +4062,21 @@
         <v>0</v>
       </c>
       <c r="K88" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
+        <v>148</v>
+      </c>
+      <c r="B89" t="s">
         <v>149</v>
       </c>
-      <c r="B89" t="s">
-        <v>150</v>
-      </c>
       <c r="C89" t="s">
         <v>18</v>
       </c>
       <c r="D89" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E89">
         <v>269990</v>
@@ -4088,10 +4085,10 @@
         <v>1</v>
       </c>
       <c r="G89" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H89" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I89">
         <v>0</v>
@@ -4100,15 +4097,15 @@
         <v>0</v>
       </c>
       <c r="K89" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
+        <v>151</v>
+      </c>
+      <c r="B90" t="s">
         <v>152</v>
-      </c>
-      <c r="B90" t="s">
-        <v>153</v>
       </c>
       <c r="C90" t="s">
         <v>18</v>
@@ -4123,10 +4120,10 @@
         <v>1</v>
       </c>
       <c r="G90" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H90" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I90">
         <v>0</v>
@@ -4140,10 +4137,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
+        <v>151</v>
+      </c>
+      <c r="B91" t="s">
         <v>152</v>
-      </c>
-      <c r="B91" t="s">
-        <v>153</v>
       </c>
       <c r="C91" t="s">
         <v>18</v>
@@ -4158,10 +4155,10 @@
         <v>1</v>
       </c>
       <c r="G91" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H91" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I91">
         <v>0</v>
@@ -4175,10 +4172,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
+        <v>151</v>
+      </c>
+      <c r="B92" t="s">
         <v>152</v>
-      </c>
-      <c r="B92" t="s">
-        <v>153</v>
       </c>
       <c r="C92" t="s">
         <v>18</v>
@@ -4193,10 +4190,10 @@
         <v>1</v>
       </c>
       <c r="G92" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H92" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I92">
         <v>0</v>
@@ -4210,16 +4207,16 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
+        <v>151</v>
+      </c>
+      <c r="B93" t="s">
         <v>152</v>
       </c>
-      <c r="B93" t="s">
-        <v>153</v>
-      </c>
       <c r="C93" t="s">
         <v>18</v>
       </c>
       <c r="D93" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E93">
         <v>199990</v>
@@ -4228,10 +4225,10 @@
         <v>1</v>
       </c>
       <c r="G93" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H93" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I93">
         <v>0</v>
@@ -4245,10 +4242,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
+        <v>153</v>
+      </c>
+      <c r="B94" t="s">
         <v>154</v>
-      </c>
-      <c r="B94" t="s">
-        <v>155</v>
       </c>
       <c r="C94" t="s">
         <v>28</v>
@@ -4263,10 +4260,10 @@
         <v>1</v>
       </c>
       <c r="G94" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H94" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I94">
         <v>0</v>
@@ -4280,10 +4277,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
+        <v>153</v>
+      </c>
+      <c r="B95" t="s">
         <v>154</v>
-      </c>
-      <c r="B95" t="s">
-        <v>155</v>
       </c>
       <c r="C95" t="s">
         <v>28</v>
@@ -4298,10 +4295,10 @@
         <v>1</v>
       </c>
       <c r="G95" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H95" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I95">
         <v>0</v>
@@ -4315,10 +4312,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
+        <v>153</v>
+      </c>
+      <c r="B96" t="s">
         <v>154</v>
-      </c>
-      <c r="B96" t="s">
-        <v>155</v>
       </c>
       <c r="C96" t="s">
         <v>28</v>
@@ -4333,10 +4330,10 @@
         <v>1</v>
       </c>
       <c r="G96" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H96" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I96">
         <v>0</v>
@@ -4350,10 +4347,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
+        <v>153</v>
+      </c>
+      <c r="B97" t="s">
         <v>154</v>
-      </c>
-      <c r="B97" t="s">
-        <v>155</v>
       </c>
       <c r="C97" t="s">
         <v>28</v>
@@ -4368,10 +4365,10 @@
         <v>1</v>
       </c>
       <c r="G97" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H97" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I97">
         <v>0</v>
@@ -4385,10 +4382,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
+        <v>155</v>
+      </c>
+      <c r="B98" t="s">
         <v>156</v>
-      </c>
-      <c r="B98" t="s">
-        <v>157</v>
       </c>
       <c r="C98" t="s">
         <v>18</v>
@@ -4415,7 +4412,7 @@
         <v>0</v>
       </c>
       <c r="K98" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/data/catalogo_jusp.xlsx
+++ b/data/catalogo_jusp.xlsx
@@ -944,10 +944,10 @@
         <v>22</v>
       </c>
       <c r="N2" s="3">
-        <v>46130.833333333328</v>
+        <v>46134</v>
       </c>
       <c r="O2" s="3">
-        <v>46133.957638888889</v>
+        <v>46135</v>
       </c>
       <c r="P2" t="s">
         <v>22</v>

--- a/data/catalogo_jusp.xlsx
+++ b/data/catalogo_jusp.xlsx
@@ -947,7 +947,7 @@
         <v>46134</v>
       </c>
       <c r="O2" s="3">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="P2" t="s">
         <v>22</v>

--- a/data/catalogo_jusp.xlsx
+++ b/data/catalogo_jusp.xlsx
@@ -489,6 +489,45 @@
   </si>
   <si>
     <t>Nike Swoosh Medium Support Women's Padded Sports Bra</t>
+  </si>
+  <si>
+    <t>nike-hj4175-289</t>
+  </si>
+  <si>
+    <t>Nike Dri-Fit Trail Gyorsan Száradó Sokoldalú</t>
+  </si>
+  <si>
+    <t>nike-hj4175-253</t>
+  </si>
+  <si>
+    <t>Men's NIKE AS M NK DF TRAIL AOP 6IN BRF S woven shorts</t>
+  </si>
+  <si>
+    <t>nike-fv7839-010</t>
+  </si>
+  <si>
+    <t>Nike PRO Compression Shorts</t>
+  </si>
+  <si>
+    <t>nike-fv7839-464</t>
+  </si>
+  <si>
+    <t>Nike Pro Quick-Drying Slim Fit Yoga Shorts Women's Shorts</t>
+  </si>
+  <si>
+    <t>light blue</t>
+  </si>
+  <si>
+    <t>nike-hm6094-345</t>
+  </si>
+  <si>
+    <t>Nike Pro Comfortable Fashionable Versatile Soft Cycling Pants Women's Bottoms Blue</t>
+  </si>
+  <si>
+    <t>nike-dv7798-063</t>
+  </si>
+  <si>
+    <t>NIKE Women Sportswear Sportswear Classics High-Waisted</t>
   </si>
 </sst>
 </file>
@@ -4415,6 +4454,1056 @@
         <v>113</v>
       </c>
     </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>157</v>
+      </c>
+      <c r="B99" t="s">
+        <v>158</v>
+      </c>
+      <c r="C99" t="s">
+        <v>18</v>
+      </c>
+      <c r="D99" t="s">
+        <v>48</v>
+      </c>
+      <c r="E99">
+        <v>151990</v>
+      </c>
+      <c r="F99">
+        <v>1</v>
+      </c>
+      <c r="G99" t="s">
+        <v>84</v>
+      </c>
+      <c r="H99" t="s">
+        <v>84</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>0</v>
+      </c>
+      <c r="K99" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>157</v>
+      </c>
+      <c r="B100" t="s">
+        <v>158</v>
+      </c>
+      <c r="C100" t="s">
+        <v>18</v>
+      </c>
+      <c r="D100" t="s">
+        <v>29</v>
+      </c>
+      <c r="E100">
+        <v>151990</v>
+      </c>
+      <c r="F100">
+        <v>1</v>
+      </c>
+      <c r="G100" t="s">
+        <v>84</v>
+      </c>
+      <c r="H100" t="s">
+        <v>84</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>0</v>
+      </c>
+      <c r="K100" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>157</v>
+      </c>
+      <c r="B101" t="s">
+        <v>158</v>
+      </c>
+      <c r="C101" t="s">
+        <v>18</v>
+      </c>
+      <c r="D101" t="s">
+        <v>25</v>
+      </c>
+      <c r="E101">
+        <v>151990</v>
+      </c>
+      <c r="F101">
+        <v>1</v>
+      </c>
+      <c r="G101" t="s">
+        <v>84</v>
+      </c>
+      <c r="H101" t="s">
+        <v>84</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>0</v>
+      </c>
+      <c r="K101" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>157</v>
+      </c>
+      <c r="B102" t="s">
+        <v>158</v>
+      </c>
+      <c r="C102" t="s">
+        <v>18</v>
+      </c>
+      <c r="D102" t="s">
+        <v>19</v>
+      </c>
+      <c r="E102">
+        <v>151990</v>
+      </c>
+      <c r="F102">
+        <v>1</v>
+      </c>
+      <c r="G102" t="s">
+        <v>84</v>
+      </c>
+      <c r="H102" t="s">
+        <v>84</v>
+      </c>
+      <c r="I102">
+        <v>0</v>
+      </c>
+      <c r="J102">
+        <v>0</v>
+      </c>
+      <c r="K102" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>157</v>
+      </c>
+      <c r="B103" t="s">
+        <v>158</v>
+      </c>
+      <c r="C103" t="s">
+        <v>18</v>
+      </c>
+      <c r="D103" t="s">
+        <v>130</v>
+      </c>
+      <c r="E103">
+        <v>151990</v>
+      </c>
+      <c r="F103">
+        <v>1</v>
+      </c>
+      <c r="G103" t="s">
+        <v>84</v>
+      </c>
+      <c r="H103" t="s">
+        <v>84</v>
+      </c>
+      <c r="I103">
+        <v>0</v>
+      </c>
+      <c r="J103">
+        <v>0</v>
+      </c>
+      <c r="K103" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>159</v>
+      </c>
+      <c r="B104" t="s">
+        <v>160</v>
+      </c>
+      <c r="C104" t="s">
+        <v>18</v>
+      </c>
+      <c r="D104" t="s">
+        <v>48</v>
+      </c>
+      <c r="E104">
+        <v>151990</v>
+      </c>
+      <c r="F104">
+        <v>1</v>
+      </c>
+      <c r="G104" t="s">
+        <v>84</v>
+      </c>
+      <c r="H104" t="s">
+        <v>84</v>
+      </c>
+      <c r="I104">
+        <v>0</v>
+      </c>
+      <c r="J104">
+        <v>0</v>
+      </c>
+      <c r="K104" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>159</v>
+      </c>
+      <c r="B105" t="s">
+        <v>160</v>
+      </c>
+      <c r="C105" t="s">
+        <v>18</v>
+      </c>
+      <c r="D105" t="s">
+        <v>29</v>
+      </c>
+      <c r="E105">
+        <v>151990</v>
+      </c>
+      <c r="F105">
+        <v>1</v>
+      </c>
+      <c r="G105" t="s">
+        <v>84</v>
+      </c>
+      <c r="H105" t="s">
+        <v>84</v>
+      </c>
+      <c r="I105">
+        <v>0</v>
+      </c>
+      <c r="J105">
+        <v>0</v>
+      </c>
+      <c r="K105" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>159</v>
+      </c>
+      <c r="B106" t="s">
+        <v>160</v>
+      </c>
+      <c r="C106" t="s">
+        <v>18</v>
+      </c>
+      <c r="D106" t="s">
+        <v>25</v>
+      </c>
+      <c r="E106">
+        <v>151990</v>
+      </c>
+      <c r="F106">
+        <v>1</v>
+      </c>
+      <c r="G106" t="s">
+        <v>84</v>
+      </c>
+      <c r="H106" t="s">
+        <v>84</v>
+      </c>
+      <c r="I106">
+        <v>0</v>
+      </c>
+      <c r="J106">
+        <v>0</v>
+      </c>
+      <c r="K106" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>159</v>
+      </c>
+      <c r="B107" t="s">
+        <v>160</v>
+      </c>
+      <c r="C107" t="s">
+        <v>18</v>
+      </c>
+      <c r="D107" t="s">
+        <v>19</v>
+      </c>
+      <c r="E107">
+        <v>151990</v>
+      </c>
+      <c r="F107">
+        <v>1</v>
+      </c>
+      <c r="G107" t="s">
+        <v>84</v>
+      </c>
+      <c r="H107" t="s">
+        <v>84</v>
+      </c>
+      <c r="I107">
+        <v>0</v>
+      </c>
+      <c r="J107">
+        <v>0</v>
+      </c>
+      <c r="K107" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>159</v>
+      </c>
+      <c r="B108" t="s">
+        <v>160</v>
+      </c>
+      <c r="C108" t="s">
+        <v>18</v>
+      </c>
+      <c r="D108" t="s">
+        <v>130</v>
+      </c>
+      <c r="E108">
+        <v>151990</v>
+      </c>
+      <c r="F108">
+        <v>1</v>
+      </c>
+      <c r="G108" t="s">
+        <v>84</v>
+      </c>
+      <c r="H108" t="s">
+        <v>84</v>
+      </c>
+      <c r="I108">
+        <v>0</v>
+      </c>
+      <c r="J108">
+        <v>0</v>
+      </c>
+      <c r="K108" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>161</v>
+      </c>
+      <c r="B109" t="s">
+        <v>162</v>
+      </c>
+      <c r="C109" t="s">
+        <v>18</v>
+      </c>
+      <c r="D109" t="s">
+        <v>102</v>
+      </c>
+      <c r="E109">
+        <v>119990</v>
+      </c>
+      <c r="F109">
+        <v>1</v>
+      </c>
+      <c r="G109" t="s">
+        <v>20</v>
+      </c>
+      <c r="H109" t="s">
+        <v>20</v>
+      </c>
+      <c r="I109">
+        <v>0</v>
+      </c>
+      <c r="J109">
+        <v>0</v>
+      </c>
+      <c r="K109" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s">
+        <v>161</v>
+      </c>
+      <c r="B110" t="s">
+        <v>162</v>
+      </c>
+      <c r="C110" t="s">
+        <v>18</v>
+      </c>
+      <c r="D110" t="s">
+        <v>48</v>
+      </c>
+      <c r="E110">
+        <v>210990</v>
+      </c>
+      <c r="F110">
+        <v>1</v>
+      </c>
+      <c r="G110" t="s">
+        <v>20</v>
+      </c>
+      <c r="H110" t="s">
+        <v>20</v>
+      </c>
+      <c r="I110">
+        <v>0</v>
+      </c>
+      <c r="J110">
+        <v>0</v>
+      </c>
+      <c r="K110" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s">
+        <v>161</v>
+      </c>
+      <c r="B111" t="s">
+        <v>162</v>
+      </c>
+      <c r="C111" t="s">
+        <v>18</v>
+      </c>
+      <c r="D111" t="s">
+        <v>29</v>
+      </c>
+      <c r="E111">
+        <v>210990</v>
+      </c>
+      <c r="F111">
+        <v>1</v>
+      </c>
+      <c r="G111" t="s">
+        <v>20</v>
+      </c>
+      <c r="H111" t="s">
+        <v>20</v>
+      </c>
+      <c r="I111">
+        <v>0</v>
+      </c>
+      <c r="J111">
+        <v>0</v>
+      </c>
+      <c r="K111" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s">
+        <v>161</v>
+      </c>
+      <c r="B112" t="s">
+        <v>162</v>
+      </c>
+      <c r="C112" t="s">
+        <v>18</v>
+      </c>
+      <c r="D112" t="s">
+        <v>19</v>
+      </c>
+      <c r="E112">
+        <v>210990</v>
+      </c>
+      <c r="F112">
+        <v>1</v>
+      </c>
+      <c r="G112" t="s">
+        <v>20</v>
+      </c>
+      <c r="H112" t="s">
+        <v>20</v>
+      </c>
+      <c r="I112">
+        <v>0</v>
+      </c>
+      <c r="J112">
+        <v>0</v>
+      </c>
+      <c r="K112" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s">
+        <v>163</v>
+      </c>
+      <c r="B113" t="s">
+        <v>164</v>
+      </c>
+      <c r="C113" t="s">
+        <v>18</v>
+      </c>
+      <c r="D113" t="s">
+        <v>102</v>
+      </c>
+      <c r="E113">
+        <v>108990</v>
+      </c>
+      <c r="F113">
+        <v>1</v>
+      </c>
+      <c r="G113" t="s">
+        <v>20</v>
+      </c>
+      <c r="H113" t="s">
+        <v>20</v>
+      </c>
+      <c r="I113">
+        <v>0</v>
+      </c>
+      <c r="J113">
+        <v>0</v>
+      </c>
+      <c r="K113" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s">
+        <v>163</v>
+      </c>
+      <c r="B114" t="s">
+        <v>164</v>
+      </c>
+      <c r="C114" t="s">
+        <v>18</v>
+      </c>
+      <c r="D114" t="s">
+        <v>48</v>
+      </c>
+      <c r="E114">
+        <v>114990</v>
+      </c>
+      <c r="F114">
+        <v>1</v>
+      </c>
+      <c r="G114" t="s">
+        <v>20</v>
+      </c>
+      <c r="H114" t="s">
+        <v>20</v>
+      </c>
+      <c r="I114">
+        <v>0</v>
+      </c>
+      <c r="J114">
+        <v>0</v>
+      </c>
+      <c r="K114" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s">
+        <v>163</v>
+      </c>
+      <c r="B115" t="s">
+        <v>164</v>
+      </c>
+      <c r="C115" t="s">
+        <v>18</v>
+      </c>
+      <c r="D115" t="s">
+        <v>29</v>
+      </c>
+      <c r="E115">
+        <v>124990</v>
+      </c>
+      <c r="F115">
+        <v>1</v>
+      </c>
+      <c r="G115" t="s">
+        <v>20</v>
+      </c>
+      <c r="H115" t="s">
+        <v>20</v>
+      </c>
+      <c r="I115">
+        <v>0</v>
+      </c>
+      <c r="J115">
+        <v>0</v>
+      </c>
+      <c r="K115" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s">
+        <v>163</v>
+      </c>
+      <c r="B116" t="s">
+        <v>164</v>
+      </c>
+      <c r="C116" t="s">
+        <v>18</v>
+      </c>
+      <c r="D116" t="s">
+        <v>19</v>
+      </c>
+      <c r="E116">
+        <v>183990</v>
+      </c>
+      <c r="F116">
+        <v>1</v>
+      </c>
+      <c r="G116" t="s">
+        <v>20</v>
+      </c>
+      <c r="H116" t="s">
+        <v>20</v>
+      </c>
+      <c r="I116">
+        <v>0</v>
+      </c>
+      <c r="J116">
+        <v>0</v>
+      </c>
+      <c r="K116" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s">
+        <v>163</v>
+      </c>
+      <c r="B117" t="s">
+        <v>164</v>
+      </c>
+      <c r="C117" t="s">
+        <v>18</v>
+      </c>
+      <c r="D117" t="s">
+        <v>130</v>
+      </c>
+      <c r="E117">
+        <v>140990</v>
+      </c>
+      <c r="F117">
+        <v>1</v>
+      </c>
+      <c r="G117" t="s">
+        <v>20</v>
+      </c>
+      <c r="H117" t="s">
+        <v>20</v>
+      </c>
+      <c r="I117">
+        <v>0</v>
+      </c>
+      <c r="J117">
+        <v>0</v>
+      </c>
+      <c r="K117" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s">
+        <v>166</v>
+      </c>
+      <c r="B118" t="s">
+        <v>167</v>
+      </c>
+      <c r="C118" t="s">
+        <v>18</v>
+      </c>
+      <c r="D118" t="s">
+        <v>102</v>
+      </c>
+      <c r="E118">
+        <v>140990</v>
+      </c>
+      <c r="F118">
+        <v>1</v>
+      </c>
+      <c r="G118" t="s">
+        <v>20</v>
+      </c>
+      <c r="H118" t="s">
+        <v>20</v>
+      </c>
+      <c r="I118">
+        <v>0</v>
+      </c>
+      <c r="J118">
+        <v>0</v>
+      </c>
+      <c r="K118" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s">
+        <v>166</v>
+      </c>
+      <c r="B119" t="s">
+        <v>167</v>
+      </c>
+      <c r="C119" t="s">
+        <v>18</v>
+      </c>
+      <c r="D119" t="s">
+        <v>48</v>
+      </c>
+      <c r="E119">
+        <v>140990</v>
+      </c>
+      <c r="F119">
+        <v>1</v>
+      </c>
+      <c r="G119" t="s">
+        <v>20</v>
+      </c>
+      <c r="H119" t="s">
+        <v>20</v>
+      </c>
+      <c r="I119">
+        <v>0</v>
+      </c>
+      <c r="J119">
+        <v>0</v>
+      </c>
+      <c r="K119" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
+        <v>166</v>
+      </c>
+      <c r="B120" t="s">
+        <v>167</v>
+      </c>
+      <c r="C120" t="s">
+        <v>18</v>
+      </c>
+      <c r="D120" t="s">
+        <v>29</v>
+      </c>
+      <c r="E120">
+        <v>140990</v>
+      </c>
+      <c r="F120">
+        <v>1</v>
+      </c>
+      <c r="G120" t="s">
+        <v>20</v>
+      </c>
+      <c r="H120" t="s">
+        <v>20</v>
+      </c>
+      <c r="I120">
+        <v>0</v>
+      </c>
+      <c r="J120">
+        <v>0</v>
+      </c>
+      <c r="K120" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>166</v>
+      </c>
+      <c r="B121" t="s">
+        <v>167</v>
+      </c>
+      <c r="C121" t="s">
+        <v>18</v>
+      </c>
+      <c r="D121" t="s">
+        <v>25</v>
+      </c>
+      <c r="E121">
+        <v>140990</v>
+      </c>
+      <c r="F121">
+        <v>1</v>
+      </c>
+      <c r="G121" t="s">
+        <v>20</v>
+      </c>
+      <c r="H121" t="s">
+        <v>20</v>
+      </c>
+      <c r="I121">
+        <v>0</v>
+      </c>
+      <c r="J121">
+        <v>0</v>
+      </c>
+      <c r="K121" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s">
+        <v>166</v>
+      </c>
+      <c r="B122" t="s">
+        <v>167</v>
+      </c>
+      <c r="C122" t="s">
+        <v>18</v>
+      </c>
+      <c r="D122" t="s">
+        <v>19</v>
+      </c>
+      <c r="E122">
+        <v>140990</v>
+      </c>
+      <c r="F122">
+        <v>1</v>
+      </c>
+      <c r="G122" t="s">
+        <v>20</v>
+      </c>
+      <c r="H122" t="s">
+        <v>20</v>
+      </c>
+      <c r="I122">
+        <v>0</v>
+      </c>
+      <c r="J122">
+        <v>0</v>
+      </c>
+      <c r="K122" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s">
+        <v>166</v>
+      </c>
+      <c r="B123" t="s">
+        <v>167</v>
+      </c>
+      <c r="C123" t="s">
+        <v>18</v>
+      </c>
+      <c r="D123" t="s">
+        <v>130</v>
+      </c>
+      <c r="E123">
+        <v>140990</v>
+      </c>
+      <c r="F123">
+        <v>1</v>
+      </c>
+      <c r="G123" t="s">
+        <v>20</v>
+      </c>
+      <c r="H123" t="s">
+        <v>20</v>
+      </c>
+      <c r="I123">
+        <v>0</v>
+      </c>
+      <c r="J123">
+        <v>0</v>
+      </c>
+      <c r="K123" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s">
+        <v>168</v>
+      </c>
+      <c r="B124" t="s">
+        <v>169</v>
+      </c>
+      <c r="C124" t="s">
+        <v>18</v>
+      </c>
+      <c r="D124" t="s">
+        <v>48</v>
+      </c>
+      <c r="E124">
+        <v>92990</v>
+      </c>
+      <c r="F124">
+        <v>1</v>
+      </c>
+      <c r="G124" t="s">
+        <v>20</v>
+      </c>
+      <c r="H124" t="s">
+        <v>20</v>
+      </c>
+      <c r="I124">
+        <v>0</v>
+      </c>
+      <c r="J124">
+        <v>0</v>
+      </c>
+      <c r="K124" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s">
+        <v>168</v>
+      </c>
+      <c r="B125" t="s">
+        <v>169</v>
+      </c>
+      <c r="C125" t="s">
+        <v>18</v>
+      </c>
+      <c r="D125" t="s">
+        <v>29</v>
+      </c>
+      <c r="E125">
+        <v>92990</v>
+      </c>
+      <c r="F125">
+        <v>1</v>
+      </c>
+      <c r="G125" t="s">
+        <v>20</v>
+      </c>
+      <c r="H125" t="s">
+        <v>20</v>
+      </c>
+      <c r="I125">
+        <v>0</v>
+      </c>
+      <c r="J125">
+        <v>0</v>
+      </c>
+      <c r="K125" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s">
+        <v>168</v>
+      </c>
+      <c r="B126" t="s">
+        <v>169</v>
+      </c>
+      <c r="C126" t="s">
+        <v>18</v>
+      </c>
+      <c r="D126" t="s">
+        <v>25</v>
+      </c>
+      <c r="E126">
+        <v>92990</v>
+      </c>
+      <c r="F126">
+        <v>1</v>
+      </c>
+      <c r="G126" t="s">
+        <v>20</v>
+      </c>
+      <c r="H126" t="s">
+        <v>20</v>
+      </c>
+      <c r="I126">
+        <v>0</v>
+      </c>
+      <c r="J126">
+        <v>0</v>
+      </c>
+      <c r="K126" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s">
+        <v>168</v>
+      </c>
+      <c r="B127" t="s">
+        <v>169</v>
+      </c>
+      <c r="C127" t="s">
+        <v>18</v>
+      </c>
+      <c r="D127" t="s">
+        <v>19</v>
+      </c>
+      <c r="E127">
+        <v>92990</v>
+      </c>
+      <c r="F127">
+        <v>1</v>
+      </c>
+      <c r="G127" t="s">
+        <v>20</v>
+      </c>
+      <c r="H127" t="s">
+        <v>20</v>
+      </c>
+      <c r="I127">
+        <v>0</v>
+      </c>
+      <c r="J127">
+        <v>0</v>
+      </c>
+      <c r="K127" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s">
+        <v>168</v>
+      </c>
+      <c r="B128" t="s">
+        <v>169</v>
+      </c>
+      <c r="C128" t="s">
+        <v>18</v>
+      </c>
+      <c r="D128" t="s">
+        <v>130</v>
+      </c>
+      <c r="E128">
+        <v>92990</v>
+      </c>
+      <c r="F128">
+        <v>1</v>
+      </c>
+      <c r="G128" t="s">
+        <v>20</v>
+      </c>
+      <c r="H128" t="s">
+        <v>20</v>
+      </c>
+      <c r="I128">
+        <v>0</v>
+      </c>
+      <c r="J128">
+        <v>0</v>
+      </c>
+      <c r="K128" t="s">
+        <v>105</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/data/catalogo_jusp.xlsx
+++ b/data/catalogo_jusp.xlsx
@@ -528,6 +528,12 @@
   </si>
   <si>
     <t>NIKE Women Sportswear Sportswear Classics High-Waisted</t>
+  </si>
+  <si>
+    <t>nike-fz6568-551</t>
+  </si>
+  <si>
+    <t>NIKE Women's AS W NY DF INDY STRPY LL BRA</t>
   </si>
 </sst>
 </file>
@@ -5504,6 +5510,111 @@
         <v>105</v>
       </c>
     </row>
+    <row r="129">
+      <c r="A129" t="s">
+        <v>170</v>
+      </c>
+      <c r="B129" t="s">
+        <v>171</v>
+      </c>
+      <c r="C129" t="s">
+        <v>18</v>
+      </c>
+      <c r="D129" t="s">
+        <v>29</v>
+      </c>
+      <c r="E129">
+        <v>108990</v>
+      </c>
+      <c r="F129">
+        <v>1</v>
+      </c>
+      <c r="G129" t="s">
+        <v>20</v>
+      </c>
+      <c r="H129" t="s">
+        <v>20</v>
+      </c>
+      <c r="I129">
+        <v>0</v>
+      </c>
+      <c r="J129">
+        <v>0</v>
+      </c>
+      <c r="K129" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s">
+        <v>170</v>
+      </c>
+      <c r="B130" t="s">
+        <v>171</v>
+      </c>
+      <c r="C130" t="s">
+        <v>18</v>
+      </c>
+      <c r="D130" t="s">
+        <v>25</v>
+      </c>
+      <c r="E130">
+        <v>108990</v>
+      </c>
+      <c r="F130">
+        <v>1</v>
+      </c>
+      <c r="G130" t="s">
+        <v>20</v>
+      </c>
+      <c r="H130" t="s">
+        <v>20</v>
+      </c>
+      <c r="I130">
+        <v>0</v>
+      </c>
+      <c r="J130">
+        <v>0</v>
+      </c>
+      <c r="K130" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s">
+        <v>170</v>
+      </c>
+      <c r="B131" t="s">
+        <v>171</v>
+      </c>
+      <c r="C131" t="s">
+        <v>18</v>
+      </c>
+      <c r="D131" t="s">
+        <v>19</v>
+      </c>
+      <c r="E131">
+        <v>108990</v>
+      </c>
+      <c r="F131">
+        <v>1</v>
+      </c>
+      <c r="G131" t="s">
+        <v>20</v>
+      </c>
+      <c r="H131" t="s">
+        <v>20</v>
+      </c>
+      <c r="I131">
+        <v>0</v>
+      </c>
+      <c r="J131">
+        <v>0</v>
+      </c>
+      <c r="K131" t="s">
+        <v>33</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/data/catalogo_jusp.xlsx
+++ b/data/catalogo_jusp.xlsx
@@ -134,7 +134,7 @@
     <t>Sujetador deportivo Nike Swoosh</t>
   </si>
   <si>
-    <t>bright pink</t>
+    <t>pink</t>
   </si>
   <si>
     <t>nike-fb4081-100</t>
@@ -179,7 +179,7 @@
     <t>nike-dq5135-043</t>
   </si>
   <si>
-    <t>light grey</t>
+    <t>grey</t>
   </si>
   <si>
     <t>jordan-cw2427-386</t>
@@ -188,7 +188,7 @@
     <t>JORDAN BRAND AS W J JUMPMAN</t>
   </si>
   <si>
-    <t>olive green</t>
+    <t>green</t>
   </si>
   <si>
     <t>nike-bv3637-010</t>
@@ -212,7 +212,7 @@
     <t>Puma</t>
   </si>
   <si>
-    <t>slate blue</t>
+    <t>teal</t>
   </si>
   <si>
     <t xml:space="preserve">puma-526429 </t>
@@ -335,9 +335,6 @@
     <t>NIKE Dri-FIT Pro Cropped Printed Women's Training Tank</t>
   </si>
   <si>
-    <t>grey</t>
-  </si>
-  <si>
     <t>puma-622575-01</t>
   </si>
   <si>
@@ -350,9 +347,6 @@
     <t xml:space="preserve">Jordan Jumpman </t>
   </si>
   <si>
-    <t>green</t>
-  </si>
-  <si>
     <t>nike-hq5684-345</t>
   </si>
   <si>
@@ -401,9 +395,6 @@
     <t>Nike Dri-FIT Ace Kids' Swoosh Visor</t>
   </si>
   <si>
-    <t>Kisd</t>
-  </si>
-  <si>
     <t>nike-if1805-010</t>
   </si>
   <si>
@@ -515,7 +506,7 @@
     <t>Nike Pro Quick-Drying Slim Fit Yoga Shorts Women's Shorts</t>
   </si>
   <si>
-    <t>light blue</t>
+    <t>blue</t>
   </si>
   <si>
     <t>nike-hm6094-345</t>
@@ -534,6 +525,231 @@
   </si>
   <si>
     <t>NIKE Women's AS W NY DF INDY STRPY LL BRA</t>
+  </si>
+  <si>
+    <t>nike-fz0831-844</t>
+  </si>
+  <si>
+    <t>Gorra de béisbol NIKE auténtica para niños</t>
+  </si>
+  <si>
+    <t>(única)Azul claro</t>
+  </si>
+  <si>
+    <t>(única)Naranja rosa</t>
+  </si>
+  <si>
+    <t>nike-ib5469-010</t>
+  </si>
+  <si>
+    <t>Nike As M Nsw Club Fz Hoodie Ft Gce</t>
+  </si>
+  <si>
+    <t>nike-fq7646-104</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Nike Offcourt Slides 'Valentines Day</t>
+  </si>
+  <si>
+    <t>35.5</t>
+  </si>
+  <si>
+    <t>nike-fz1037-010</t>
+  </si>
+  <si>
+    <t>Nike LeBron Standard Issue Basketball Track Pants</t>
+  </si>
+  <si>
+    <t>nike-hq7990-010</t>
+  </si>
+  <si>
+    <t>Nike Standard Issue Dri-Fit Casual Pants</t>
+  </si>
+  <si>
+    <t>nike-hq7990-063</t>
+  </si>
+  <si>
+    <t>Nike Sports Pants</t>
+  </si>
+  <si>
+    <t>Grey</t>
+  </si>
+  <si>
+    <t>nike-fd1066-699</t>
+  </si>
+  <si>
+    <t>Nike INDY Sports Bra</t>
+  </si>
+  <si>
+    <t>nike-fd1066-100</t>
+  </si>
+  <si>
+    <t>Nike women's sports bra with adjustable straps</t>
+  </si>
+  <si>
+    <t>adidas-jn3788</t>
+  </si>
+  <si>
+    <t>SPORTSWEAR LOUNGE Baseball Cap</t>
+  </si>
+  <si>
+    <t>Adidas</t>
+  </si>
+  <si>
+    <t>nike-fq3551-207</t>
+  </si>
+  <si>
+    <t>NIKE ALATE MINIMALIST WOMEN'S LIGHT-SUPPORT PADDED CONVERTIBLE SPORTS BRA</t>
+  </si>
+  <si>
+    <t>nike-fd1069-856</t>
+  </si>
+  <si>
+    <t>NIKE Women's Sports Bra - High Support</t>
+  </si>
+  <si>
+    <t>orange</t>
+  </si>
+  <si>
+    <t>nike-fd1069-017</t>
+  </si>
+  <si>
+    <t>Nike As W Nk Df Indy Hgh Spt Bra</t>
+  </si>
+  <si>
+    <t>nike-dx5470-010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nike Dri-Fit Academy 23 </t>
+  </si>
+  <si>
+    <t>nike-hv8700-699</t>
+  </si>
+  <si>
+    <t>Nike unisex Love Heart cap</t>
+  </si>
+  <si>
+    <t>única</t>
+  </si>
+  <si>
+    <t>nike-ib5450-010</t>
+  </si>
+  <si>
+    <t>NIKE AS M NSW PREMIUM FLC GCEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M </t>
+  </si>
+  <si>
+    <t>nike-fq2094-237</t>
+  </si>
+  <si>
+    <t>Nike Court Heritage Dri-Fit Komfortabel Myk Løs Fukttransporterende Genser</t>
+  </si>
+  <si>
+    <t>brown</t>
+  </si>
+  <si>
+    <t>Beige</t>
+  </si>
+  <si>
+    <t>nike-fv3738-338</t>
+  </si>
+  <si>
+    <t>Nike SB KEARNY</t>
+  </si>
+  <si>
+    <t>nike-hv7111-100</t>
+  </si>
+  <si>
+    <t>Nike Swim one-piece swimsuit</t>
+  </si>
+  <si>
+    <t>nike-fz6174-010</t>
+  </si>
+  <si>
+    <t>Nike one-piece swimsuit</t>
+  </si>
+  <si>
+    <t>nike-hf5983-600</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Air Jordan Hydrip 'Digital Pink Racer Pink</t>
+  </si>
+  <si>
+    <t>23,5 7C</t>
+  </si>
+  <si>
+    <t>25 8C</t>
+  </si>
+  <si>
+    <t>26 9C</t>
+  </si>
+  <si>
+    <t>27 10C</t>
+  </si>
+  <si>
+    <t>nike-fj5353-901</t>
+  </si>
+  <si>
+    <t>3-piece set in black, red and white</t>
+  </si>
+  <si>
+    <t>73 12M</t>
+  </si>
+  <si>
+    <t>80 18M</t>
+  </si>
+  <si>
+    <t>90 24M</t>
+  </si>
+  <si>
+    <t>nike-fz2859-010</t>
+  </si>
+  <si>
+    <t>Nike Sportswear Chill Knit</t>
+  </si>
+  <si>
+    <t>nike-fz7449-652</t>
+  </si>
+  <si>
+    <t>Nike Victory Dri-Fit Swoosh Comfortable Casual Polo</t>
+  </si>
+  <si>
+    <t>nike-fn5849-436</t>
+  </si>
+  <si>
+    <t>Jordan Sport Jam Men's Warm-Up Jacket</t>
+  </si>
+  <si>
+    <t>nike-fn5851-436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JORDAN BRAND AS M J SPRT JAM WARM UP PANT </t>
+  </si>
+  <si>
+    <t>lacoste-rk7589-241749</t>
+  </si>
+  <si>
+    <t>Cap with emblem</t>
+  </si>
+  <si>
+    <t>lacoste-rk2509-203016</t>
+  </si>
+  <si>
+    <t>LACOSTE Oversized Crocodile Cotton Gabardine Cap</t>
+  </si>
+  <si>
+    <t>lacoste-rk3385-252157</t>
+  </si>
+  <si>
+    <t>Crocodile Graphic Baseball Cap</t>
+  </si>
+  <si>
+    <t>lacoste-th2422</t>
+  </si>
+  <si>
+    <t>Lacoste crew neck sleeveless t-shirt</t>
   </si>
 </sst>
 </file>
@@ -2532,7 +2748,7 @@
         <v>0</v>
       </c>
       <c r="K43" t="s">
-        <v>105</v>
+        <v>53</v>
       </c>
     </row>
     <row r="44">
@@ -2567,7 +2783,7 @@
         <v>0</v>
       </c>
       <c r="K44" t="s">
-        <v>105</v>
+        <v>53</v>
       </c>
     </row>
     <row r="45">
@@ -2602,7 +2818,7 @@
         <v>0</v>
       </c>
       <c r="K45" t="s">
-        <v>105</v>
+        <v>53</v>
       </c>
     </row>
     <row r="46">
@@ -2637,15 +2853,15 @@
         <v>0</v>
       </c>
       <c r="K46" t="s">
-        <v>105</v>
+        <v>53</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
+        <v>105</v>
+      </c>
+      <c r="B47" t="s">
         <v>106</v>
-      </c>
-      <c r="B47" t="s">
-        <v>107</v>
       </c>
       <c r="C47" t="s">
         <v>63</v>
@@ -2677,10 +2893,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
+        <v>105</v>
+      </c>
+      <c r="B48" t="s">
         <v>106</v>
-      </c>
-      <c r="B48" t="s">
-        <v>107</v>
       </c>
       <c r="C48" t="s">
         <v>63</v>
@@ -2712,10 +2928,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
+        <v>107</v>
+      </c>
+      <c r="B49" t="s">
         <v>108</v>
-      </c>
-      <c r="B49" t="s">
-        <v>109</v>
       </c>
       <c r="C49" t="s">
         <v>28</v>
@@ -2742,15 +2958,15 @@
         <v>0</v>
       </c>
       <c r="K49" t="s">
-        <v>110</v>
+        <v>56</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B50" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C50" t="s">
         <v>18</v>
@@ -2777,15 +2993,15 @@
         <v>0</v>
       </c>
       <c r="K50" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B51" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C51" t="s">
         <v>18</v>
@@ -2812,15 +3028,15 @@
         <v>0</v>
       </c>
       <c r="K51" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B52" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C52" t="s">
         <v>18</v>
@@ -2847,15 +3063,15 @@
         <v>0</v>
       </c>
       <c r="K52" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B53" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C53" t="s">
         <v>18</v>
@@ -2870,10 +3086,10 @@
         <v>1</v>
       </c>
       <c r="G53" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H53" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="I53">
         <v>0</v>
@@ -2887,10 +3103,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B54" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C54" t="s">
         <v>18</v>
@@ -2905,10 +3121,10 @@
         <v>1</v>
       </c>
       <c r="G54" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H54" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="I54">
         <v>0</v>
@@ -2922,16 +3138,16 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
+        <v>115</v>
+      </c>
+      <c r="B55" t="s">
+        <v>116</v>
+      </c>
+      <c r="C55" t="s">
         <v>117</v>
       </c>
-      <c r="B55" t="s">
+      <c r="D55" t="s">
         <v>118</v>
-      </c>
-      <c r="C55" t="s">
-        <v>119</v>
-      </c>
-      <c r="D55" t="s">
-        <v>120</v>
       </c>
       <c r="E55">
         <v>179990</v>
@@ -2940,10 +3156,10 @@
         <v>1</v>
       </c>
       <c r="G55" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H55" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="I55">
         <v>0</v>
@@ -2957,16 +3173,16 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B56" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C56" t="s">
         <v>18</v>
       </c>
       <c r="D56" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E56">
         <v>159990</v>
@@ -2975,10 +3191,10 @@
         <v>1</v>
       </c>
       <c r="G56" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H56" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="I56">
         <v>0</v>
@@ -2992,10 +3208,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B57" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C57" t="s">
         <v>18</v>
@@ -3010,10 +3226,10 @@
         <v>1</v>
       </c>
       <c r="G57" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H57" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="I57">
         <v>0</v>
@@ -3027,10 +3243,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B58" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C58" t="s">
         <v>18</v>
@@ -3045,10 +3261,10 @@
         <v>1</v>
       </c>
       <c r="G58" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H58" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="I58">
         <v>0</v>
@@ -3062,10 +3278,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B59" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C59" t="s">
         <v>18</v>
@@ -3080,10 +3296,10 @@
         <v>1</v>
       </c>
       <c r="G59" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H59" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="I59">
         <v>0</v>
@@ -3097,10 +3313,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B60" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C60" t="s">
         <v>18</v>
@@ -3115,10 +3331,10 @@
         <v>1</v>
       </c>
       <c r="G60" t="s">
-        <v>127</v>
+        <v>75</v>
       </c>
       <c r="H60" t="s">
-        <v>127</v>
+        <v>75</v>
       </c>
       <c r="I60">
         <v>0</v>
@@ -3132,10 +3348,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B61" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C61" t="s">
         <v>18</v>
@@ -3167,10 +3383,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B62" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C62" t="s">
         <v>28</v>
@@ -3202,10 +3418,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B63" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C63" t="s">
         <v>28</v>
@@ -3237,10 +3453,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B64" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C64" t="s">
         <v>28</v>
@@ -3272,16 +3488,16 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B65" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C65" t="s">
         <v>28</v>
       </c>
       <c r="D65" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E65">
         <v>134990</v>
@@ -3307,10 +3523,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B66" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C66" t="s">
         <v>28</v>
@@ -3342,10 +3558,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B67" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C67" t="s">
         <v>28</v>
@@ -3377,10 +3593,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B68" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C68" t="s">
         <v>28</v>
@@ -3412,10 +3628,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B69" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C69" t="s">
         <v>28</v>
@@ -3442,15 +3658,15 @@
         <v>0</v>
       </c>
       <c r="K69" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B70" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C70" t="s">
         <v>28</v>
@@ -3477,15 +3693,15 @@
         <v>0</v>
       </c>
       <c r="K70" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B71" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C71" t="s">
         <v>28</v>
@@ -3517,10 +3733,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B72" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C72" t="s">
         <v>28</v>
@@ -3552,10 +3768,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B73" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C73" t="s">
         <v>28</v>
@@ -3582,21 +3798,21 @@
         <v>0</v>
       </c>
       <c r="K73" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B74" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C74" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D74" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E74">
         <v>140990</v>
@@ -3605,7 +3821,7 @@
         <v>1</v>
       </c>
       <c r="G74" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H74" t="s">
         <v>71</v>
@@ -3622,16 +3838,16 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
+        <v>137</v>
+      </c>
+      <c r="B75" t="s">
+        <v>138</v>
+      </c>
+      <c r="C75" t="s">
+        <v>117</v>
+      </c>
+      <c r="D75" t="s">
         <v>140</v>
-      </c>
-      <c r="B75" t="s">
-        <v>141</v>
-      </c>
-      <c r="C75" t="s">
-        <v>119</v>
-      </c>
-      <c r="D75" t="s">
-        <v>143</v>
       </c>
       <c r="E75">
         <v>145990</v>
@@ -3640,7 +3856,7 @@
         <v>1</v>
       </c>
       <c r="G75" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H75" t="s">
         <v>71</v>
@@ -3657,10 +3873,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B76" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C76" t="s">
         <v>18</v>
@@ -3692,10 +3908,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B77" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C77" t="s">
         <v>18</v>
@@ -3727,10 +3943,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B78" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C78" t="s">
         <v>18</v>
@@ -3762,10 +3978,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B79" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C79" t="s">
         <v>18</v>
@@ -3797,16 +4013,16 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B80" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C80" t="s">
         <v>18</v>
       </c>
       <c r="D80" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E80" s="4">
         <v>199990</v>
@@ -3832,10 +4048,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B81" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C81" t="s">
         <v>28</v>
@@ -3867,10 +4083,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B82" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C82" t="s">
         <v>28</v>
@@ -3902,10 +4118,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B83" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C83" t="s">
         <v>28</v>
@@ -3937,10 +4153,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B84" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C84" t="s">
         <v>28</v>
@@ -3972,10 +4188,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B85" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C85" t="s">
         <v>18</v>
@@ -4002,15 +4218,15 @@
         <v>0</v>
       </c>
       <c r="K85" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B86" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C86" t="s">
         <v>18</v>
@@ -4037,15 +4253,15 @@
         <v>0</v>
       </c>
       <c r="K86" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B87" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C87" t="s">
         <v>18</v>
@@ -4072,15 +4288,15 @@
         <v>0</v>
       </c>
       <c r="K87" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B88" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C88" t="s">
         <v>18</v>
@@ -4107,21 +4323,21 @@
         <v>0</v>
       </c>
       <c r="K88" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B89" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C89" t="s">
         <v>18</v>
       </c>
       <c r="D89" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E89">
         <v>269990</v>
@@ -4142,15 +4358,15 @@
         <v>0</v>
       </c>
       <c r="K89" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B90" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C90" t="s">
         <v>18</v>
@@ -4182,10 +4398,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B91" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C91" t="s">
         <v>18</v>
@@ -4217,10 +4433,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B92" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C92" t="s">
         <v>18</v>
@@ -4252,16 +4468,16 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B93" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C93" t="s">
         <v>18</v>
       </c>
       <c r="D93" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E93">
         <v>199990</v>
@@ -4287,10 +4503,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B94" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C94" t="s">
         <v>28</v>
@@ -4322,10 +4538,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B95" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C95" t="s">
         <v>28</v>
@@ -4357,10 +4573,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B96" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C96" t="s">
         <v>28</v>
@@ -4392,10 +4608,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B97" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C97" t="s">
         <v>28</v>
@@ -4427,10 +4643,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B98" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C98" t="s">
         <v>18</v>
@@ -4457,15 +4673,15 @@
         <v>0</v>
       </c>
       <c r="K98" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B99" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C99" t="s">
         <v>18</v>
@@ -4492,15 +4708,15 @@
         <v>0</v>
       </c>
       <c r="K99" t="s">
-        <v>105</v>
+        <v>53</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B100" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C100" t="s">
         <v>18</v>
@@ -4527,15 +4743,15 @@
         <v>0</v>
       </c>
       <c r="K100" t="s">
-        <v>105</v>
+        <v>53</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B101" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C101" t="s">
         <v>18</v>
@@ -4562,15 +4778,15 @@
         <v>0</v>
       </c>
       <c r="K101" t="s">
-        <v>105</v>
+        <v>53</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B102" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C102" t="s">
         <v>18</v>
@@ -4597,21 +4813,21 @@
         <v>0</v>
       </c>
       <c r="K102" t="s">
-        <v>105</v>
+        <v>53</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B103" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C103" t="s">
         <v>18</v>
       </c>
       <c r="D103" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E103">
         <v>151990</v>
@@ -4632,15 +4848,15 @@
         <v>0</v>
       </c>
       <c r="K103" t="s">
-        <v>105</v>
+        <v>53</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B104" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C104" t="s">
         <v>18</v>
@@ -4672,10 +4888,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B105" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C105" t="s">
         <v>18</v>
@@ -4707,10 +4923,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B106" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C106" t="s">
         <v>18</v>
@@ -4742,10 +4958,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B107" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C107" t="s">
         <v>18</v>
@@ -4777,16 +4993,16 @@
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B108" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C108" t="s">
         <v>18</v>
       </c>
       <c r="D108" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E108">
         <v>151990</v>
@@ -4812,10 +5028,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B109" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C109" t="s">
         <v>18</v>
@@ -4847,10 +5063,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B110" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C110" t="s">
         <v>18</v>
@@ -4882,10 +5098,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B111" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C111" t="s">
         <v>18</v>
@@ -4917,10 +5133,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B112" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C112" t="s">
         <v>18</v>
@@ -4952,10 +5168,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B113" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C113" t="s">
         <v>18</v>
@@ -4982,15 +5198,15 @@
         <v>0</v>
       </c>
       <c r="K113" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B114" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C114" t="s">
         <v>18</v>
@@ -5017,15 +5233,15 @@
         <v>0</v>
       </c>
       <c r="K114" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B115" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C115" t="s">
         <v>18</v>
@@ -5052,15 +5268,15 @@
         <v>0</v>
       </c>
       <c r="K115" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B116" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C116" t="s">
         <v>18</v>
@@ -5087,21 +5303,21 @@
         <v>0</v>
       </c>
       <c r="K116" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B117" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C117" t="s">
         <v>18</v>
       </c>
       <c r="D117" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E117">
         <v>140990</v>
@@ -5122,15 +5338,15 @@
         <v>0</v>
       </c>
       <c r="K117" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B118" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C118" t="s">
         <v>18</v>
@@ -5157,15 +5373,15 @@
         <v>0</v>
       </c>
       <c r="K118" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B119" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C119" t="s">
         <v>18</v>
@@ -5192,15 +5408,15 @@
         <v>0</v>
       </c>
       <c r="K119" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B120" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C120" t="s">
         <v>18</v>
@@ -5227,15 +5443,15 @@
         <v>0</v>
       </c>
       <c r="K120" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B121" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C121" t="s">
         <v>18</v>
@@ -5262,15 +5478,15 @@
         <v>0</v>
       </c>
       <c r="K121" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B122" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C122" t="s">
         <v>18</v>
@@ -5297,21 +5513,21 @@
         <v>0</v>
       </c>
       <c r="K122" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B123" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C123" t="s">
         <v>18</v>
       </c>
       <c r="D123" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E123">
         <v>140990</v>
@@ -5332,15 +5548,15 @@
         <v>0</v>
       </c>
       <c r="K123" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B124" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C124" t="s">
         <v>18</v>
@@ -5367,15 +5583,15 @@
         <v>0</v>
       </c>
       <c r="K124" t="s">
-        <v>105</v>
+        <v>53</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B125" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C125" t="s">
         <v>18</v>
@@ -5402,15 +5618,15 @@
         <v>0</v>
       </c>
       <c r="K125" t="s">
-        <v>105</v>
+        <v>53</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B126" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C126" t="s">
         <v>18</v>
@@ -5437,15 +5653,15 @@
         <v>0</v>
       </c>
       <c r="K126" t="s">
-        <v>105</v>
+        <v>53</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B127" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C127" t="s">
         <v>18</v>
@@ -5472,21 +5688,21 @@
         <v>0</v>
       </c>
       <c r="K127" t="s">
-        <v>105</v>
+        <v>53</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B128" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C128" t="s">
         <v>18</v>
       </c>
       <c r="D128" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E128">
         <v>92990</v>
@@ -5507,15 +5723,15 @@
         <v>0</v>
       </c>
       <c r="K128" t="s">
-        <v>105</v>
+        <v>53</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B129" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C129" t="s">
         <v>18</v>
@@ -5547,10 +5763,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B130" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C130" t="s">
         <v>18</v>
@@ -5582,10 +5798,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B131" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C131" t="s">
         <v>18</v>
@@ -5612,6 +5828,3191 @@
         <v>0</v>
       </c>
       <c r="K131" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s">
+        <v>169</v>
+      </c>
+      <c r="B132" t="s">
+        <v>170</v>
+      </c>
+      <c r="C132" t="s">
+        <v>18</v>
+      </c>
+      <c r="D132" t="s">
+        <v>171</v>
+      </c>
+      <c r="E132">
+        <v>81990</v>
+      </c>
+      <c r="F132">
+        <v>1</v>
+      </c>
+      <c r="G132" t="s">
+        <v>75</v>
+      </c>
+      <c r="H132" t="s">
+        <v>75</v>
+      </c>
+      <c r="I132">
+        <v>0</v>
+      </c>
+      <c r="J132">
+        <v>0</v>
+      </c>
+      <c r="K132" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s">
+        <v>169</v>
+      </c>
+      <c r="B133" t="s">
+        <v>170</v>
+      </c>
+      <c r="C133" t="s">
+        <v>18</v>
+      </c>
+      <c r="D133" t="s">
+        <v>172</v>
+      </c>
+      <c r="E133">
+        <v>81990</v>
+      </c>
+      <c r="F133">
+        <v>1</v>
+      </c>
+      <c r="G133" t="s">
+        <v>75</v>
+      </c>
+      <c r="H133" t="s">
+        <v>75</v>
+      </c>
+      <c r="I133">
+        <v>0</v>
+      </c>
+      <c r="J133">
+        <v>0</v>
+      </c>
+      <c r="K133" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s">
+        <v>173</v>
+      </c>
+      <c r="B134" t="s">
+        <v>174</v>
+      </c>
+      <c r="C134" t="s">
+        <v>18</v>
+      </c>
+      <c r="D134" t="s">
+        <v>48</v>
+      </c>
+      <c r="E134">
+        <v>125990</v>
+      </c>
+      <c r="F134">
+        <v>1</v>
+      </c>
+      <c r="G134" t="s">
+        <v>84</v>
+      </c>
+      <c r="H134" t="s">
+        <v>84</v>
+      </c>
+      <c r="I134">
+        <v>0</v>
+      </c>
+      <c r="J134">
+        <v>0</v>
+      </c>
+      <c r="K134" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s">
+        <v>173</v>
+      </c>
+      <c r="B135" t="s">
+        <v>174</v>
+      </c>
+      <c r="C135" t="s">
+        <v>18</v>
+      </c>
+      <c r="D135" t="s">
+        <v>29</v>
+      </c>
+      <c r="E135">
+        <v>125990</v>
+      </c>
+      <c r="F135">
+        <v>1</v>
+      </c>
+      <c r="G135" t="s">
+        <v>84</v>
+      </c>
+      <c r="H135" t="s">
+        <v>84</v>
+      </c>
+      <c r="I135">
+        <v>0</v>
+      </c>
+      <c r="J135">
+        <v>0</v>
+      </c>
+      <c r="K135" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s">
+        <v>175</v>
+      </c>
+      <c r="B136" t="s">
+        <v>176</v>
+      </c>
+      <c r="C136" t="s">
+        <v>18</v>
+      </c>
+      <c r="D136" t="s">
+        <v>177</v>
+      </c>
+      <c r="E136">
+        <v>125990</v>
+      </c>
+      <c r="F136">
+        <v>1</v>
+      </c>
+      <c r="G136" t="s">
+        <v>20</v>
+      </c>
+      <c r="H136" t="s">
+        <v>71</v>
+      </c>
+      <c r="I136">
+        <v>0</v>
+      </c>
+      <c r="J136">
+        <v>0</v>
+      </c>
+      <c r="K136" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s">
+        <v>175</v>
+      </c>
+      <c r="B137" t="s">
+        <v>176</v>
+      </c>
+      <c r="C137" t="s">
+        <v>18</v>
+      </c>
+      <c r="D137">
+        <v>38</v>
+      </c>
+      <c r="E137">
+        <v>125990</v>
+      </c>
+      <c r="F137">
+        <v>1</v>
+      </c>
+      <c r="G137" t="s">
+        <v>20</v>
+      </c>
+      <c r="H137" t="s">
+        <v>71</v>
+      </c>
+      <c r="I137">
+        <v>0</v>
+      </c>
+      <c r="J137">
+        <v>0</v>
+      </c>
+      <c r="K137" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s">
+        <v>175</v>
+      </c>
+      <c r="B138" t="s">
+        <v>176</v>
+      </c>
+      <c r="C138" t="s">
+        <v>18</v>
+      </c>
+      <c r="D138">
+        <v>39</v>
+      </c>
+      <c r="E138">
+        <v>125990</v>
+      </c>
+      <c r="F138">
+        <v>1</v>
+      </c>
+      <c r="G138" t="s">
+        <v>20</v>
+      </c>
+      <c r="H138" t="s">
+        <v>71</v>
+      </c>
+      <c r="I138">
+        <v>0</v>
+      </c>
+      <c r="J138">
+        <v>0</v>
+      </c>
+      <c r="K138" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s">
+        <v>175</v>
+      </c>
+      <c r="B139" t="s">
+        <v>176</v>
+      </c>
+      <c r="C139" t="s">
+        <v>18</v>
+      </c>
+      <c r="D139">
+        <v>42</v>
+      </c>
+      <c r="E139">
+        <v>125990</v>
+      </c>
+      <c r="F139">
+        <v>1</v>
+      </c>
+      <c r="G139" t="s">
+        <v>20</v>
+      </c>
+      <c r="H139" t="s">
+        <v>71</v>
+      </c>
+      <c r="I139">
+        <v>0</v>
+      </c>
+      <c r="J139">
+        <v>0</v>
+      </c>
+      <c r="K139" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s">
+        <v>178</v>
+      </c>
+      <c r="B140" t="s">
+        <v>179</v>
+      </c>
+      <c r="C140" t="s">
+        <v>18</v>
+      </c>
+      <c r="D140" t="s">
+        <v>29</v>
+      </c>
+      <c r="E140">
+        <v>145990</v>
+      </c>
+      <c r="F140">
+        <v>1</v>
+      </c>
+      <c r="G140" t="s">
+        <v>84</v>
+      </c>
+      <c r="H140" t="s">
+        <v>84</v>
+      </c>
+      <c r="I140">
+        <v>0</v>
+      </c>
+      <c r="J140">
+        <v>0</v>
+      </c>
+      <c r="K140" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
+        <v>178</v>
+      </c>
+      <c r="B141" t="s">
+        <v>179</v>
+      </c>
+      <c r="C141" t="s">
+        <v>18</v>
+      </c>
+      <c r="D141" t="s">
+        <v>25</v>
+      </c>
+      <c r="E141">
+        <v>145990</v>
+      </c>
+      <c r="F141">
+        <v>1</v>
+      </c>
+      <c r="G141" t="s">
+        <v>84</v>
+      </c>
+      <c r="H141" t="s">
+        <v>84</v>
+      </c>
+      <c r="I141">
+        <v>0</v>
+      </c>
+      <c r="J141">
+        <v>0</v>
+      </c>
+      <c r="K141" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s">
+        <v>178</v>
+      </c>
+      <c r="B142" t="s">
+        <v>179</v>
+      </c>
+      <c r="C142" t="s">
+        <v>18</v>
+      </c>
+      <c r="D142" t="s">
+        <v>19</v>
+      </c>
+      <c r="E142">
+        <v>145990</v>
+      </c>
+      <c r="F142">
+        <v>1</v>
+      </c>
+      <c r="G142" t="s">
+        <v>84</v>
+      </c>
+      <c r="H142" t="s">
+        <v>84</v>
+      </c>
+      <c r="I142">
+        <v>0</v>
+      </c>
+      <c r="J142">
+        <v>0</v>
+      </c>
+      <c r="K142" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s">
+        <v>178</v>
+      </c>
+      <c r="B143" t="s">
+        <v>179</v>
+      </c>
+      <c r="C143" t="s">
+        <v>18</v>
+      </c>
+      <c r="D143" t="s">
+        <v>127</v>
+      </c>
+      <c r="E143">
+        <v>145990</v>
+      </c>
+      <c r="F143">
+        <v>1</v>
+      </c>
+      <c r="G143" t="s">
+        <v>84</v>
+      </c>
+      <c r="H143" t="s">
+        <v>84</v>
+      </c>
+      <c r="I143">
+        <v>0</v>
+      </c>
+      <c r="J143">
+        <v>0</v>
+      </c>
+      <c r="K143" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s">
+        <v>180</v>
+      </c>
+      <c r="B144" t="s">
+        <v>181</v>
+      </c>
+      <c r="C144" t="s">
+        <v>18</v>
+      </c>
+      <c r="D144" t="s">
+        <v>48</v>
+      </c>
+      <c r="E144">
+        <v>199990</v>
+      </c>
+      <c r="F144">
+        <v>1</v>
+      </c>
+      <c r="G144" t="s">
+        <v>84</v>
+      </c>
+      <c r="H144" t="s">
+        <v>84</v>
+      </c>
+      <c r="I144">
+        <v>0</v>
+      </c>
+      <c r="J144">
+        <v>0</v>
+      </c>
+      <c r="K144" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s">
+        <v>180</v>
+      </c>
+      <c r="B145" t="s">
+        <v>181</v>
+      </c>
+      <c r="C145" t="s">
+        <v>18</v>
+      </c>
+      <c r="D145" t="s">
+        <v>29</v>
+      </c>
+      <c r="E145">
+        <v>199990</v>
+      </c>
+      <c r="F145">
+        <v>1</v>
+      </c>
+      <c r="G145" t="s">
+        <v>84</v>
+      </c>
+      <c r="H145" t="s">
+        <v>84</v>
+      </c>
+      <c r="I145">
+        <v>0</v>
+      </c>
+      <c r="J145">
+        <v>0</v>
+      </c>
+      <c r="K145" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s">
+        <v>180</v>
+      </c>
+      <c r="B146" t="s">
+        <v>181</v>
+      </c>
+      <c r="C146" t="s">
+        <v>18</v>
+      </c>
+      <c r="D146" t="s">
+        <v>25</v>
+      </c>
+      <c r="E146">
+        <v>199990</v>
+      </c>
+      <c r="F146">
+        <v>1</v>
+      </c>
+      <c r="G146" t="s">
+        <v>84</v>
+      </c>
+      <c r="H146" t="s">
+        <v>84</v>
+      </c>
+      <c r="I146">
+        <v>0</v>
+      </c>
+      <c r="J146">
+        <v>0</v>
+      </c>
+      <c r="K146" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s">
+        <v>180</v>
+      </c>
+      <c r="B147" t="s">
+        <v>181</v>
+      </c>
+      <c r="C147" t="s">
+        <v>18</v>
+      </c>
+      <c r="D147" t="s">
+        <v>19</v>
+      </c>
+      <c r="E147">
+        <v>199990</v>
+      </c>
+      <c r="F147">
+        <v>1</v>
+      </c>
+      <c r="G147" t="s">
+        <v>84</v>
+      </c>
+      <c r="H147" t="s">
+        <v>84</v>
+      </c>
+      <c r="I147">
+        <v>0</v>
+      </c>
+      <c r="J147">
+        <v>0</v>
+      </c>
+      <c r="K147" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s">
+        <v>180</v>
+      </c>
+      <c r="B148" t="s">
+        <v>181</v>
+      </c>
+      <c r="C148" t="s">
+        <v>18</v>
+      </c>
+      <c r="D148" t="s">
+        <v>127</v>
+      </c>
+      <c r="E148">
+        <v>199990</v>
+      </c>
+      <c r="F148">
+        <v>1</v>
+      </c>
+      <c r="G148" t="s">
+        <v>84</v>
+      </c>
+      <c r="H148" t="s">
+        <v>84</v>
+      </c>
+      <c r="I148">
+        <v>0</v>
+      </c>
+      <c r="J148">
+        <v>0</v>
+      </c>
+      <c r="K148" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s">
+        <v>182</v>
+      </c>
+      <c r="B149" t="s">
+        <v>183</v>
+      </c>
+      <c r="C149" t="s">
+        <v>18</v>
+      </c>
+      <c r="D149" t="s">
+        <v>127</v>
+      </c>
+      <c r="E149">
+        <v>159990</v>
+      </c>
+      <c r="F149">
+        <v>1</v>
+      </c>
+      <c r="G149" t="s">
+        <v>84</v>
+      </c>
+      <c r="H149" t="s">
+        <v>84</v>
+      </c>
+      <c r="I149">
+        <v>0</v>
+      </c>
+      <c r="J149">
+        <v>0</v>
+      </c>
+      <c r="K149" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s">
+        <v>182</v>
+      </c>
+      <c r="B150" t="s">
+        <v>183</v>
+      </c>
+      <c r="C150" t="s">
+        <v>18</v>
+      </c>
+      <c r="D150" t="s">
+        <v>25</v>
+      </c>
+      <c r="E150">
+        <v>199990</v>
+      </c>
+      <c r="F150">
+        <v>1</v>
+      </c>
+      <c r="G150" t="s">
+        <v>84</v>
+      </c>
+      <c r="H150" t="s">
+        <v>84</v>
+      </c>
+      <c r="I150">
+        <v>0</v>
+      </c>
+      <c r="J150">
+        <v>0</v>
+      </c>
+      <c r="K150" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s">
+        <v>182</v>
+      </c>
+      <c r="B151" t="s">
+        <v>183</v>
+      </c>
+      <c r="C151" t="s">
+        <v>18</v>
+      </c>
+      <c r="D151" t="s">
+        <v>19</v>
+      </c>
+      <c r="E151">
+        <v>199990</v>
+      </c>
+      <c r="F151">
+        <v>1</v>
+      </c>
+      <c r="G151" t="s">
+        <v>84</v>
+      </c>
+      <c r="H151" t="s">
+        <v>84</v>
+      </c>
+      <c r="I151">
+        <v>0</v>
+      </c>
+      <c r="J151">
+        <v>0</v>
+      </c>
+      <c r="K151" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s">
+        <v>185</v>
+      </c>
+      <c r="B152" t="s">
+        <v>186</v>
+      </c>
+      <c r="C152" t="s">
+        <v>18</v>
+      </c>
+      <c r="D152" t="s">
+        <v>29</v>
+      </c>
+      <c r="E152">
+        <v>109990</v>
+      </c>
+      <c r="F152">
+        <v>1</v>
+      </c>
+      <c r="G152" t="s">
+        <v>20</v>
+      </c>
+      <c r="H152" t="s">
+        <v>20</v>
+      </c>
+      <c r="I152">
+        <v>0</v>
+      </c>
+      <c r="J152">
+        <v>0</v>
+      </c>
+      <c r="K152" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s">
+        <v>185</v>
+      </c>
+      <c r="B153" t="s">
+        <v>186</v>
+      </c>
+      <c r="C153" t="s">
+        <v>18</v>
+      </c>
+      <c r="D153" t="s">
+        <v>25</v>
+      </c>
+      <c r="E153">
+        <v>109990</v>
+      </c>
+      <c r="F153">
+        <v>1</v>
+      </c>
+      <c r="G153" t="s">
+        <v>20</v>
+      </c>
+      <c r="H153" t="s">
+        <v>20</v>
+      </c>
+      <c r="I153">
+        <v>0</v>
+      </c>
+      <c r="J153">
+        <v>0</v>
+      </c>
+      <c r="K153" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s">
+        <v>185</v>
+      </c>
+      <c r="B154" t="s">
+        <v>186</v>
+      </c>
+      <c r="C154" t="s">
+        <v>18</v>
+      </c>
+      <c r="D154" t="s">
+        <v>19</v>
+      </c>
+      <c r="E154">
+        <v>109990</v>
+      </c>
+      <c r="F154">
+        <v>1</v>
+      </c>
+      <c r="G154" t="s">
+        <v>20</v>
+      </c>
+      <c r="H154" t="s">
+        <v>20</v>
+      </c>
+      <c r="I154">
+        <v>0</v>
+      </c>
+      <c r="J154">
+        <v>0</v>
+      </c>
+      <c r="K154" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s">
+        <v>187</v>
+      </c>
+      <c r="B155" t="s">
+        <v>188</v>
+      </c>
+      <c r="C155" t="s">
+        <v>18</v>
+      </c>
+      <c r="D155" t="s">
+        <v>19</v>
+      </c>
+      <c r="E155">
+        <v>115990</v>
+      </c>
+      <c r="F155">
+        <v>1</v>
+      </c>
+      <c r="G155" t="s">
+        <v>20</v>
+      </c>
+      <c r="H155" t="s">
+        <v>20</v>
+      </c>
+      <c r="I155">
+        <v>0</v>
+      </c>
+      <c r="J155">
+        <v>0</v>
+      </c>
+      <c r="K155" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s">
+        <v>187</v>
+      </c>
+      <c r="B156" t="s">
+        <v>188</v>
+      </c>
+      <c r="C156" t="s">
+        <v>18</v>
+      </c>
+      <c r="D156" t="s">
+        <v>25</v>
+      </c>
+      <c r="E156">
+        <v>119990</v>
+      </c>
+      <c r="F156">
+        <v>1</v>
+      </c>
+      <c r="G156" t="s">
+        <v>20</v>
+      </c>
+      <c r="H156" t="s">
+        <v>20</v>
+      </c>
+      <c r="I156">
+        <v>0</v>
+      </c>
+      <c r="J156">
+        <v>0</v>
+      </c>
+      <c r="K156" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s">
+        <v>189</v>
+      </c>
+      <c r="B157" t="s">
+        <v>190</v>
+      </c>
+      <c r="C157" t="s">
+        <v>191</v>
+      </c>
+      <c r="D157" t="s">
+        <v>69</v>
+      </c>
+      <c r="E157">
+        <v>85990</v>
+      </c>
+      <c r="F157">
+        <v>1</v>
+      </c>
+      <c r="G157" t="s">
+        <v>84</v>
+      </c>
+      <c r="H157" t="s">
+        <v>71</v>
+      </c>
+      <c r="I157">
+        <v>0</v>
+      </c>
+      <c r="J157">
+        <v>0</v>
+      </c>
+      <c r="K157" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s">
+        <v>192</v>
+      </c>
+      <c r="B158" t="s">
+        <v>193</v>
+      </c>
+      <c r="C158" t="s">
+        <v>18</v>
+      </c>
+      <c r="D158" t="s">
+        <v>48</v>
+      </c>
+      <c r="E158">
+        <v>105990</v>
+      </c>
+      <c r="F158">
+        <v>1</v>
+      </c>
+      <c r="G158" t="s">
+        <v>20</v>
+      </c>
+      <c r="H158" t="s">
+        <v>20</v>
+      </c>
+      <c r="I158">
+        <v>0</v>
+      </c>
+      <c r="J158">
+        <v>0</v>
+      </c>
+      <c r="K158" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s">
+        <v>192</v>
+      </c>
+      <c r="B159" t="s">
+        <v>193</v>
+      </c>
+      <c r="C159" t="s">
+        <v>18</v>
+      </c>
+      <c r="D159" t="s">
+        <v>29</v>
+      </c>
+      <c r="E159">
+        <v>105990</v>
+      </c>
+      <c r="F159">
+        <v>1</v>
+      </c>
+      <c r="G159" t="s">
+        <v>20</v>
+      </c>
+      <c r="H159" t="s">
+        <v>20</v>
+      </c>
+      <c r="I159">
+        <v>0</v>
+      </c>
+      <c r="J159">
+        <v>0</v>
+      </c>
+      <c r="K159" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s">
+        <v>192</v>
+      </c>
+      <c r="B160" t="s">
+        <v>193</v>
+      </c>
+      <c r="C160" t="s">
+        <v>18</v>
+      </c>
+      <c r="D160" t="s">
+        <v>25</v>
+      </c>
+      <c r="E160">
+        <v>105990</v>
+      </c>
+      <c r="F160">
+        <v>1</v>
+      </c>
+      <c r="G160" t="s">
+        <v>20</v>
+      </c>
+      <c r="H160" t="s">
+        <v>20</v>
+      </c>
+      <c r="I160">
+        <v>0</v>
+      </c>
+      <c r="J160">
+        <v>0</v>
+      </c>
+      <c r="K160" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s">
+        <v>192</v>
+      </c>
+      <c r="B161" t="s">
+        <v>193</v>
+      </c>
+      <c r="C161" t="s">
+        <v>18</v>
+      </c>
+      <c r="D161" t="s">
+        <v>19</v>
+      </c>
+      <c r="E161">
+        <v>105990</v>
+      </c>
+      <c r="F161">
+        <v>1</v>
+      </c>
+      <c r="G161" t="s">
+        <v>20</v>
+      </c>
+      <c r="H161" t="s">
+        <v>20</v>
+      </c>
+      <c r="I161">
+        <v>0</v>
+      </c>
+      <c r="J161">
+        <v>0</v>
+      </c>
+      <c r="K161" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s">
+        <v>194</v>
+      </c>
+      <c r="B162" t="s">
+        <v>195</v>
+      </c>
+      <c r="C162" t="s">
+        <v>18</v>
+      </c>
+      <c r="D162" t="s">
+        <v>48</v>
+      </c>
+      <c r="E162">
+        <v>119990</v>
+      </c>
+      <c r="F162">
+        <v>1</v>
+      </c>
+      <c r="G162" t="s">
+        <v>20</v>
+      </c>
+      <c r="H162" t="s">
+        <v>20</v>
+      </c>
+      <c r="I162">
+        <v>0</v>
+      </c>
+      <c r="J162">
+        <v>0</v>
+      </c>
+      <c r="K162" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s">
+        <v>194</v>
+      </c>
+      <c r="B163" t="s">
+        <v>195</v>
+      </c>
+      <c r="C163" t="s">
+        <v>18</v>
+      </c>
+      <c r="D163" t="s">
+        <v>25</v>
+      </c>
+      <c r="E163">
+        <v>189990</v>
+      </c>
+      <c r="F163">
+        <v>1</v>
+      </c>
+      <c r="G163" t="s">
+        <v>20</v>
+      </c>
+      <c r="H163" t="s">
+        <v>20</v>
+      </c>
+      <c r="I163">
+        <v>0</v>
+      </c>
+      <c r="J163">
+        <v>0</v>
+      </c>
+      <c r="K163" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s">
+        <v>197</v>
+      </c>
+      <c r="B164" t="s">
+        <v>198</v>
+      </c>
+      <c r="C164" t="s">
+        <v>18</v>
+      </c>
+      <c r="D164" t="s">
+        <v>29</v>
+      </c>
+      <c r="E164">
+        <v>179990</v>
+      </c>
+      <c r="F164">
+        <v>1</v>
+      </c>
+      <c r="G164" t="s">
+        <v>20</v>
+      </c>
+      <c r="H164" t="s">
+        <v>20</v>
+      </c>
+      <c r="I164">
+        <v>0</v>
+      </c>
+      <c r="J164">
+        <v>0</v>
+      </c>
+      <c r="K164" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s">
+        <v>197</v>
+      </c>
+      <c r="B165" t="s">
+        <v>198</v>
+      </c>
+      <c r="C165" t="s">
+        <v>18</v>
+      </c>
+      <c r="D165" t="s">
+        <v>25</v>
+      </c>
+      <c r="E165">
+        <v>179990</v>
+      </c>
+      <c r="F165">
+        <v>1</v>
+      </c>
+      <c r="G165" t="s">
+        <v>20</v>
+      </c>
+      <c r="H165" t="s">
+        <v>20</v>
+      </c>
+      <c r="I165">
+        <v>0</v>
+      </c>
+      <c r="J165">
+        <v>0</v>
+      </c>
+      <c r="K165" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s">
+        <v>197</v>
+      </c>
+      <c r="B166" t="s">
+        <v>198</v>
+      </c>
+      <c r="C166" t="s">
+        <v>18</v>
+      </c>
+      <c r="D166" t="s">
+        <v>19</v>
+      </c>
+      <c r="E166">
+        <v>130990</v>
+      </c>
+      <c r="F166">
+        <v>1</v>
+      </c>
+      <c r="G166" t="s">
+        <v>20</v>
+      </c>
+      <c r="H166" t="s">
+        <v>20</v>
+      </c>
+      <c r="I166">
+        <v>0</v>
+      </c>
+      <c r="J166">
+        <v>0</v>
+      </c>
+      <c r="K166" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s">
+        <v>199</v>
+      </c>
+      <c r="B167" t="s">
+        <v>200</v>
+      </c>
+      <c r="C167" t="s">
+        <v>18</v>
+      </c>
+      <c r="D167" t="s">
+        <v>25</v>
+      </c>
+      <c r="E167">
+        <v>109990</v>
+      </c>
+      <c r="F167">
+        <v>1</v>
+      </c>
+      <c r="G167" t="s">
+        <v>75</v>
+      </c>
+      <c r="H167" t="s">
+        <v>75</v>
+      </c>
+      <c r="I167">
+        <v>0</v>
+      </c>
+      <c r="J167">
+        <v>0</v>
+      </c>
+      <c r="K167" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s">
+        <v>199</v>
+      </c>
+      <c r="B168" t="s">
+        <v>200</v>
+      </c>
+      <c r="C168" t="s">
+        <v>18</v>
+      </c>
+      <c r="D168" t="s">
+        <v>19</v>
+      </c>
+      <c r="E168">
+        <v>109990</v>
+      </c>
+      <c r="F168">
+        <v>1</v>
+      </c>
+      <c r="G168" t="s">
+        <v>75</v>
+      </c>
+      <c r="H168" t="s">
+        <v>75</v>
+      </c>
+      <c r="I168">
+        <v>0</v>
+      </c>
+      <c r="J168">
+        <v>0</v>
+      </c>
+      <c r="K168" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s">
+        <v>201</v>
+      </c>
+      <c r="B169" t="s">
+        <v>202</v>
+      </c>
+      <c r="C169" t="s">
+        <v>18</v>
+      </c>
+      <c r="D169" t="s">
+        <v>203</v>
+      </c>
+      <c r="E169">
+        <v>82990</v>
+      </c>
+      <c r="F169">
+        <v>1</v>
+      </c>
+      <c r="G169" t="s">
+        <v>75</v>
+      </c>
+      <c r="H169" t="s">
+        <v>75</v>
+      </c>
+      <c r="I169">
+        <v>0</v>
+      </c>
+      <c r="J169">
+        <v>0</v>
+      </c>
+      <c r="K169" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s">
+        <v>201</v>
+      </c>
+      <c r="B170" t="s">
+        <v>202</v>
+      </c>
+      <c r="C170" t="s">
+        <v>18</v>
+      </c>
+      <c r="D170" t="s">
+        <v>203</v>
+      </c>
+      <c r="E170">
+        <v>82990</v>
+      </c>
+      <c r="F170">
+        <v>1</v>
+      </c>
+      <c r="G170" t="s">
+        <v>75</v>
+      </c>
+      <c r="H170" t="s">
+        <v>75</v>
+      </c>
+      <c r="I170">
+        <v>0</v>
+      </c>
+      <c r="J170">
+        <v>0</v>
+      </c>
+      <c r="K170" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s">
+        <v>204</v>
+      </c>
+      <c r="B171" t="s">
+        <v>205</v>
+      </c>
+      <c r="C171" t="s">
+        <v>18</v>
+      </c>
+      <c r="D171" t="s">
+        <v>206</v>
+      </c>
+      <c r="E171">
+        <v>119990</v>
+      </c>
+      <c r="F171">
+        <v>1</v>
+      </c>
+      <c r="G171" t="s">
+        <v>84</v>
+      </c>
+      <c r="H171" t="s">
+        <v>84</v>
+      </c>
+      <c r="I171">
+        <v>0</v>
+      </c>
+      <c r="J171">
+        <v>0</v>
+      </c>
+      <c r="K171" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s">
+        <v>204</v>
+      </c>
+      <c r="B172" t="s">
+        <v>205</v>
+      </c>
+      <c r="C172" t="s">
+        <v>18</v>
+      </c>
+      <c r="D172" t="s">
+        <v>25</v>
+      </c>
+      <c r="E172">
+        <v>119990</v>
+      </c>
+      <c r="F172">
+        <v>1</v>
+      </c>
+      <c r="G172" t="s">
+        <v>84</v>
+      </c>
+      <c r="H172" t="s">
+        <v>84</v>
+      </c>
+      <c r="I172">
+        <v>0</v>
+      </c>
+      <c r="J172">
+        <v>0</v>
+      </c>
+      <c r="K172" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s">
+        <v>204</v>
+      </c>
+      <c r="B173" t="s">
+        <v>205</v>
+      </c>
+      <c r="C173" t="s">
+        <v>18</v>
+      </c>
+      <c r="D173" t="s">
+        <v>19</v>
+      </c>
+      <c r="E173">
+        <v>119990</v>
+      </c>
+      <c r="F173">
+        <v>1</v>
+      </c>
+      <c r="G173" t="s">
+        <v>84</v>
+      </c>
+      <c r="H173" t="s">
+        <v>84</v>
+      </c>
+      <c r="I173">
+        <v>0</v>
+      </c>
+      <c r="J173">
+        <v>0</v>
+      </c>
+      <c r="K173" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s">
+        <v>204</v>
+      </c>
+      <c r="B174" t="s">
+        <v>205</v>
+      </c>
+      <c r="C174" t="s">
+        <v>18</v>
+      </c>
+      <c r="D174" t="s">
+        <v>206</v>
+      </c>
+      <c r="E174">
+        <v>119990</v>
+      </c>
+      <c r="F174">
+        <v>1</v>
+      </c>
+      <c r="G174" t="s">
+        <v>84</v>
+      </c>
+      <c r="H174" t="s">
+        <v>84</v>
+      </c>
+      <c r="I174">
+        <v>0</v>
+      </c>
+      <c r="J174">
+        <v>0</v>
+      </c>
+      <c r="K174" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s">
+        <v>204</v>
+      </c>
+      <c r="B175" t="s">
+        <v>205</v>
+      </c>
+      <c r="C175" t="s">
+        <v>18</v>
+      </c>
+      <c r="D175" t="s">
+        <v>25</v>
+      </c>
+      <c r="E175">
+        <v>119990</v>
+      </c>
+      <c r="F175">
+        <v>1</v>
+      </c>
+      <c r="G175" t="s">
+        <v>84</v>
+      </c>
+      <c r="H175" t="s">
+        <v>84</v>
+      </c>
+      <c r="I175">
+        <v>0</v>
+      </c>
+      <c r="J175">
+        <v>0</v>
+      </c>
+      <c r="K175" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s">
+        <v>204</v>
+      </c>
+      <c r="B176" t="s">
+        <v>205</v>
+      </c>
+      <c r="C176" t="s">
+        <v>18</v>
+      </c>
+      <c r="D176" t="s">
+        <v>19</v>
+      </c>
+      <c r="E176">
+        <v>119990</v>
+      </c>
+      <c r="F176">
+        <v>1</v>
+      </c>
+      <c r="G176" t="s">
+        <v>84</v>
+      </c>
+      <c r="H176" t="s">
+        <v>84</v>
+      </c>
+      <c r="I176">
+        <v>0</v>
+      </c>
+      <c r="J176">
+        <v>0</v>
+      </c>
+      <c r="K176" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s">
+        <v>207</v>
+      </c>
+      <c r="B177" t="s">
+        <v>208</v>
+      </c>
+      <c r="C177" t="s">
+        <v>18</v>
+      </c>
+      <c r="D177" t="s">
+        <v>48</v>
+      </c>
+      <c r="E177">
+        <v>129990</v>
+      </c>
+      <c r="F177">
+        <v>1</v>
+      </c>
+      <c r="G177" t="s">
+        <v>84</v>
+      </c>
+      <c r="H177" t="s">
+        <v>84</v>
+      </c>
+      <c r="I177">
+        <v>0</v>
+      </c>
+      <c r="J177">
+        <v>0</v>
+      </c>
+      <c r="K177" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s">
+        <v>207</v>
+      </c>
+      <c r="B178" t="s">
+        <v>208</v>
+      </c>
+      <c r="C178" t="s">
+        <v>18</v>
+      </c>
+      <c r="D178" t="s">
+        <v>29</v>
+      </c>
+      <c r="E178">
+        <v>119990</v>
+      </c>
+      <c r="F178">
+        <v>1</v>
+      </c>
+      <c r="G178" t="s">
+        <v>84</v>
+      </c>
+      <c r="H178" t="s">
+        <v>84</v>
+      </c>
+      <c r="I178">
+        <v>0</v>
+      </c>
+      <c r="J178">
+        <v>0</v>
+      </c>
+      <c r="K178" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s">
+        <v>207</v>
+      </c>
+      <c r="B179" t="s">
+        <v>208</v>
+      </c>
+      <c r="C179" t="s">
+        <v>18</v>
+      </c>
+      <c r="D179" t="s">
+        <v>25</v>
+      </c>
+      <c r="E179">
+        <v>119990</v>
+      </c>
+      <c r="F179">
+        <v>1</v>
+      </c>
+      <c r="G179" t="s">
+        <v>84</v>
+      </c>
+      <c r="H179" t="s">
+        <v>84</v>
+      </c>
+      <c r="I179">
+        <v>0</v>
+      </c>
+      <c r="J179">
+        <v>0</v>
+      </c>
+      <c r="K179" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s">
+        <v>207</v>
+      </c>
+      <c r="B180" t="s">
+        <v>208</v>
+      </c>
+      <c r="C180" t="s">
+        <v>18</v>
+      </c>
+      <c r="D180" t="s">
+        <v>127</v>
+      </c>
+      <c r="E180">
+        <v>119990</v>
+      </c>
+      <c r="F180">
+        <v>1</v>
+      </c>
+      <c r="G180" t="s">
+        <v>84</v>
+      </c>
+      <c r="H180" t="s">
+        <v>84</v>
+      </c>
+      <c r="I180">
+        <v>0</v>
+      </c>
+      <c r="J180">
+        <v>0</v>
+      </c>
+      <c r="K180" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s">
+        <v>207</v>
+      </c>
+      <c r="B181" t="s">
+        <v>208</v>
+      </c>
+      <c r="C181" t="s">
+        <v>18</v>
+      </c>
+      <c r="D181" t="s">
+        <v>48</v>
+      </c>
+      <c r="E181">
+        <v>129990</v>
+      </c>
+      <c r="F181">
+        <v>1</v>
+      </c>
+      <c r="G181" t="s">
+        <v>84</v>
+      </c>
+      <c r="H181" t="s">
+        <v>84</v>
+      </c>
+      <c r="I181">
+        <v>0</v>
+      </c>
+      <c r="J181">
+        <v>0</v>
+      </c>
+      <c r="K181" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s">
+        <v>207</v>
+      </c>
+      <c r="B182" t="s">
+        <v>208</v>
+      </c>
+      <c r="C182" t="s">
+        <v>18</v>
+      </c>
+      <c r="D182" t="s">
+        <v>29</v>
+      </c>
+      <c r="E182">
+        <v>119990</v>
+      </c>
+      <c r="F182">
+        <v>1</v>
+      </c>
+      <c r="G182" t="s">
+        <v>84</v>
+      </c>
+      <c r="H182" t="s">
+        <v>84</v>
+      </c>
+      <c r="I182">
+        <v>0</v>
+      </c>
+      <c r="J182">
+        <v>0</v>
+      </c>
+      <c r="K182" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s">
+        <v>207</v>
+      </c>
+      <c r="B183" t="s">
+        <v>208</v>
+      </c>
+      <c r="C183" t="s">
+        <v>18</v>
+      </c>
+      <c r="D183" t="s">
+        <v>25</v>
+      </c>
+      <c r="E183">
+        <v>119990</v>
+      </c>
+      <c r="F183">
+        <v>1</v>
+      </c>
+      <c r="G183" t="s">
+        <v>84</v>
+      </c>
+      <c r="H183" t="s">
+        <v>84</v>
+      </c>
+      <c r="I183">
+        <v>0</v>
+      </c>
+      <c r="J183">
+        <v>0</v>
+      </c>
+      <c r="K183" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s">
+        <v>207</v>
+      </c>
+      <c r="B184" t="s">
+        <v>208</v>
+      </c>
+      <c r="C184" t="s">
+        <v>18</v>
+      </c>
+      <c r="D184" t="s">
+        <v>19</v>
+      </c>
+      <c r="E184">
+        <v>119990</v>
+      </c>
+      <c r="F184">
+        <v>1</v>
+      </c>
+      <c r="G184" t="s">
+        <v>84</v>
+      </c>
+      <c r="H184" t="s">
+        <v>84</v>
+      </c>
+      <c r="I184">
+        <v>0</v>
+      </c>
+      <c r="J184">
+        <v>0</v>
+      </c>
+      <c r="K184" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s">
+        <v>207</v>
+      </c>
+      <c r="B185" t="s">
+        <v>208</v>
+      </c>
+      <c r="C185" t="s">
+        <v>18</v>
+      </c>
+      <c r="D185" t="s">
+        <v>127</v>
+      </c>
+      <c r="E185">
+        <v>119990</v>
+      </c>
+      <c r="F185">
+        <v>1</v>
+      </c>
+      <c r="G185" t="s">
+        <v>84</v>
+      </c>
+      <c r="H185" t="s">
+        <v>84</v>
+      </c>
+      <c r="I185">
+        <v>0</v>
+      </c>
+      <c r="J185">
+        <v>0</v>
+      </c>
+      <c r="K185" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s">
+        <v>211</v>
+      </c>
+      <c r="B186" t="s">
+        <v>212</v>
+      </c>
+      <c r="C186" t="s">
+        <v>18</v>
+      </c>
+      <c r="D186" t="s">
+        <v>102</v>
+      </c>
+      <c r="E186">
+        <v>165990</v>
+      </c>
+      <c r="F186">
+        <v>1</v>
+      </c>
+      <c r="G186" t="s">
+        <v>84</v>
+      </c>
+      <c r="H186" t="s">
+        <v>84</v>
+      </c>
+      <c r="I186">
+        <v>0</v>
+      </c>
+      <c r="J186">
+        <v>0</v>
+      </c>
+      <c r="K186" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s">
+        <v>211</v>
+      </c>
+      <c r="B187" t="s">
+        <v>212</v>
+      </c>
+      <c r="C187" t="s">
+        <v>18</v>
+      </c>
+      <c r="D187" t="s">
+        <v>29</v>
+      </c>
+      <c r="E187">
+        <v>149990</v>
+      </c>
+      <c r="F187">
+        <v>1</v>
+      </c>
+      <c r="G187" t="s">
+        <v>84</v>
+      </c>
+      <c r="H187" t="s">
+        <v>84</v>
+      </c>
+      <c r="I187">
+        <v>0</v>
+      </c>
+      <c r="J187">
+        <v>0</v>
+      </c>
+      <c r="K187" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s">
+        <v>211</v>
+      </c>
+      <c r="B188" t="s">
+        <v>212</v>
+      </c>
+      <c r="C188" t="s">
+        <v>18</v>
+      </c>
+      <c r="D188" t="s">
+        <v>25</v>
+      </c>
+      <c r="E188">
+        <v>149990</v>
+      </c>
+      <c r="F188">
+        <v>1</v>
+      </c>
+      <c r="G188" t="s">
+        <v>84</v>
+      </c>
+      <c r="H188" t="s">
+        <v>84</v>
+      </c>
+      <c r="I188">
+        <v>0</v>
+      </c>
+      <c r="J188">
+        <v>0</v>
+      </c>
+      <c r="K188" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s">
+        <v>211</v>
+      </c>
+      <c r="B189" t="s">
+        <v>212</v>
+      </c>
+      <c r="C189" t="s">
+        <v>18</v>
+      </c>
+      <c r="D189" t="s">
+        <v>19</v>
+      </c>
+      <c r="E189">
+        <v>149990</v>
+      </c>
+      <c r="F189">
+        <v>1</v>
+      </c>
+      <c r="G189" t="s">
+        <v>84</v>
+      </c>
+      <c r="H189" t="s">
+        <v>84</v>
+      </c>
+      <c r="I189">
+        <v>0</v>
+      </c>
+      <c r="J189">
+        <v>0</v>
+      </c>
+      <c r="K189" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s">
+        <v>211</v>
+      </c>
+      <c r="B190" t="s">
+        <v>212</v>
+      </c>
+      <c r="C190" t="s">
+        <v>18</v>
+      </c>
+      <c r="D190" t="s">
+        <v>127</v>
+      </c>
+      <c r="E190">
+        <v>149990</v>
+      </c>
+      <c r="F190">
+        <v>1</v>
+      </c>
+      <c r="G190" t="s">
+        <v>84</v>
+      </c>
+      <c r="H190" t="s">
+        <v>84</v>
+      </c>
+      <c r="I190">
+        <v>0</v>
+      </c>
+      <c r="J190">
+        <v>0</v>
+      </c>
+      <c r="K190" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s">
+        <v>213</v>
+      </c>
+      <c r="B191" t="s">
+        <v>214</v>
+      </c>
+      <c r="C191" t="s">
+        <v>18</v>
+      </c>
+      <c r="D191" t="s">
+        <v>102</v>
+      </c>
+      <c r="E191">
+        <v>189990</v>
+      </c>
+      <c r="F191">
+        <v>1</v>
+      </c>
+      <c r="G191" t="s">
+        <v>20</v>
+      </c>
+      <c r="H191" t="s">
+        <v>20</v>
+      </c>
+      <c r="I191">
+        <v>0</v>
+      </c>
+      <c r="J191">
+        <v>0</v>
+      </c>
+      <c r="K191" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s">
+        <v>213</v>
+      </c>
+      <c r="B192" t="s">
+        <v>214</v>
+      </c>
+      <c r="C192" t="s">
+        <v>18</v>
+      </c>
+      <c r="D192" t="s">
+        <v>29</v>
+      </c>
+      <c r="E192">
+        <v>189990</v>
+      </c>
+      <c r="F192">
+        <v>1</v>
+      </c>
+      <c r="G192" t="s">
+        <v>20</v>
+      </c>
+      <c r="H192" t="s">
+        <v>20</v>
+      </c>
+      <c r="I192">
+        <v>0</v>
+      </c>
+      <c r="J192">
+        <v>0</v>
+      </c>
+      <c r="K192" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s">
+        <v>213</v>
+      </c>
+      <c r="B193" t="s">
+        <v>214</v>
+      </c>
+      <c r="C193" t="s">
+        <v>18</v>
+      </c>
+      <c r="D193" t="s">
+        <v>25</v>
+      </c>
+      <c r="E193">
+        <v>189990</v>
+      </c>
+      <c r="F193">
+        <v>1</v>
+      </c>
+      <c r="G193" t="s">
+        <v>20</v>
+      </c>
+      <c r="H193" t="s">
+        <v>20</v>
+      </c>
+      <c r="I193">
+        <v>0</v>
+      </c>
+      <c r="J193">
+        <v>0</v>
+      </c>
+      <c r="K193" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s">
+        <v>215</v>
+      </c>
+      <c r="B194" t="s">
+        <v>216</v>
+      </c>
+      <c r="C194" t="s">
+        <v>18</v>
+      </c>
+      <c r="D194" t="s">
+        <v>48</v>
+      </c>
+      <c r="E194">
+        <v>185990</v>
+      </c>
+      <c r="F194">
+        <v>1</v>
+      </c>
+      <c r="G194" t="s">
+        <v>20</v>
+      </c>
+      <c r="H194" t="s">
+        <v>20</v>
+      </c>
+      <c r="I194">
+        <v>0</v>
+      </c>
+      <c r="J194">
+        <v>0</v>
+      </c>
+      <c r="K194" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s">
+        <v>215</v>
+      </c>
+      <c r="B195" t="s">
+        <v>216</v>
+      </c>
+      <c r="C195" t="s">
+        <v>18</v>
+      </c>
+      <c r="D195" t="s">
+        <v>25</v>
+      </c>
+      <c r="E195">
+        <v>185990</v>
+      </c>
+      <c r="F195">
+        <v>1</v>
+      </c>
+      <c r="G195" t="s">
+        <v>20</v>
+      </c>
+      <c r="H195" t="s">
+        <v>20</v>
+      </c>
+      <c r="I195">
+        <v>0</v>
+      </c>
+      <c r="J195">
+        <v>0</v>
+      </c>
+      <c r="K195" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s">
+        <v>215</v>
+      </c>
+      <c r="B196" t="s">
+        <v>216</v>
+      </c>
+      <c r="C196" t="s">
+        <v>18</v>
+      </c>
+      <c r="D196" t="s">
+        <v>19</v>
+      </c>
+      <c r="E196">
+        <v>185990</v>
+      </c>
+      <c r="F196">
+        <v>1</v>
+      </c>
+      <c r="G196" t="s">
+        <v>20</v>
+      </c>
+      <c r="H196" t="s">
+        <v>20</v>
+      </c>
+      <c r="I196">
+        <v>0</v>
+      </c>
+      <c r="J196">
+        <v>0</v>
+      </c>
+      <c r="K196" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="s">
+        <v>217</v>
+      </c>
+      <c r="B197" t="s">
+        <v>218</v>
+      </c>
+      <c r="C197" t="s">
+        <v>28</v>
+      </c>
+      <c r="D197" t="s">
+        <v>219</v>
+      </c>
+      <c r="E197">
+        <v>125990</v>
+      </c>
+      <c r="F197">
+        <v>1</v>
+      </c>
+      <c r="G197" t="s">
+        <v>75</v>
+      </c>
+      <c r="H197" t="s">
+        <v>75</v>
+      </c>
+      <c r="I197">
+        <v>0</v>
+      </c>
+      <c r="J197">
+        <v>0</v>
+      </c>
+      <c r="K197" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s">
+        <v>217</v>
+      </c>
+      <c r="B198" t="s">
+        <v>218</v>
+      </c>
+      <c r="C198" t="s">
+        <v>28</v>
+      </c>
+      <c r="D198" t="s">
+        <v>220</v>
+      </c>
+      <c r="E198">
+        <v>125990</v>
+      </c>
+      <c r="F198">
+        <v>1</v>
+      </c>
+      <c r="G198" t="s">
+        <v>75</v>
+      </c>
+      <c r="H198" t="s">
+        <v>75</v>
+      </c>
+      <c r="I198">
+        <v>0</v>
+      </c>
+      <c r="J198">
+        <v>0</v>
+      </c>
+      <c r="K198" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s">
+        <v>217</v>
+      </c>
+      <c r="B199" t="s">
+        <v>218</v>
+      </c>
+      <c r="C199" t="s">
+        <v>28</v>
+      </c>
+      <c r="D199" t="s">
+        <v>221</v>
+      </c>
+      <c r="E199">
+        <v>125990</v>
+      </c>
+      <c r="F199">
+        <v>1</v>
+      </c>
+      <c r="G199" t="s">
+        <v>75</v>
+      </c>
+      <c r="H199" t="s">
+        <v>75</v>
+      </c>
+      <c r="I199">
+        <v>0</v>
+      </c>
+      <c r="J199">
+        <v>0</v>
+      </c>
+      <c r="K199" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s">
+        <v>217</v>
+      </c>
+      <c r="B200" t="s">
+        <v>218</v>
+      </c>
+      <c r="C200" t="s">
+        <v>28</v>
+      </c>
+      <c r="D200" t="s">
+        <v>222</v>
+      </c>
+      <c r="E200">
+        <v>125990</v>
+      </c>
+      <c r="F200">
+        <v>1</v>
+      </c>
+      <c r="G200" t="s">
+        <v>75</v>
+      </c>
+      <c r="H200" t="s">
+        <v>75</v>
+      </c>
+      <c r="I200">
+        <v>0</v>
+      </c>
+      <c r="J200">
+        <v>0</v>
+      </c>
+      <c r="K200" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s">
+        <v>223</v>
+      </c>
+      <c r="B201" t="s">
+        <v>224</v>
+      </c>
+      <c r="C201" t="s">
+        <v>28</v>
+      </c>
+      <c r="D201" t="s">
+        <v>225</v>
+      </c>
+      <c r="E201">
+        <v>129990</v>
+      </c>
+      <c r="F201">
+        <v>1</v>
+      </c>
+      <c r="G201" t="s">
+        <v>75</v>
+      </c>
+      <c r="H201" t="s">
+        <v>75</v>
+      </c>
+      <c r="I201">
+        <v>0</v>
+      </c>
+      <c r="J201">
+        <v>0</v>
+      </c>
+      <c r="K201" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="s">
+        <v>223</v>
+      </c>
+      <c r="B202" t="s">
+        <v>224</v>
+      </c>
+      <c r="C202" t="s">
+        <v>28</v>
+      </c>
+      <c r="D202" t="s">
+        <v>226</v>
+      </c>
+      <c r="E202">
+        <v>129990</v>
+      </c>
+      <c r="F202">
+        <v>1</v>
+      </c>
+      <c r="G202" t="s">
+        <v>75</v>
+      </c>
+      <c r="H202" t="s">
+        <v>75</v>
+      </c>
+      <c r="I202">
+        <v>0</v>
+      </c>
+      <c r="J202">
+        <v>0</v>
+      </c>
+      <c r="K202" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="s">
+        <v>223</v>
+      </c>
+      <c r="B203" t="s">
+        <v>224</v>
+      </c>
+      <c r="C203" t="s">
+        <v>28</v>
+      </c>
+      <c r="D203" t="s">
+        <v>227</v>
+      </c>
+      <c r="E203">
+        <v>129990</v>
+      </c>
+      <c r="F203">
+        <v>1</v>
+      </c>
+      <c r="G203" t="s">
+        <v>75</v>
+      </c>
+      <c r="H203" t="s">
+        <v>75</v>
+      </c>
+      <c r="I203">
+        <v>0</v>
+      </c>
+      <c r="J203">
+        <v>0</v>
+      </c>
+      <c r="K203" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="s">
+        <v>228</v>
+      </c>
+      <c r="B204" t="s">
+        <v>229</v>
+      </c>
+      <c r="C204" t="s">
+        <v>18</v>
+      </c>
+      <c r="D204" t="s">
+        <v>29</v>
+      </c>
+      <c r="E204">
+        <v>125990</v>
+      </c>
+      <c r="F204">
+        <v>1</v>
+      </c>
+      <c r="G204" t="s">
+        <v>84</v>
+      </c>
+      <c r="H204" t="s">
+        <v>84</v>
+      </c>
+      <c r="I204">
+        <v>0</v>
+      </c>
+      <c r="J204">
+        <v>0</v>
+      </c>
+      <c r="K204" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="s">
+        <v>228</v>
+      </c>
+      <c r="B205" t="s">
+        <v>229</v>
+      </c>
+      <c r="C205" t="s">
+        <v>18</v>
+      </c>
+      <c r="D205" t="s">
+        <v>25</v>
+      </c>
+      <c r="E205">
+        <v>125990</v>
+      </c>
+      <c r="F205">
+        <v>1</v>
+      </c>
+      <c r="G205" t="s">
+        <v>84</v>
+      </c>
+      <c r="H205" t="s">
+        <v>84</v>
+      </c>
+      <c r="I205">
+        <v>0</v>
+      </c>
+      <c r="J205">
+        <v>0</v>
+      </c>
+      <c r="K205" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="s">
+        <v>228</v>
+      </c>
+      <c r="B206" t="s">
+        <v>229</v>
+      </c>
+      <c r="C206" t="s">
+        <v>18</v>
+      </c>
+      <c r="D206" t="s">
+        <v>19</v>
+      </c>
+      <c r="E206">
+        <v>125990</v>
+      </c>
+      <c r="F206">
+        <v>1</v>
+      </c>
+      <c r="G206" t="s">
+        <v>84</v>
+      </c>
+      <c r="H206" t="s">
+        <v>84</v>
+      </c>
+      <c r="I206">
+        <v>0</v>
+      </c>
+      <c r="J206">
+        <v>0</v>
+      </c>
+      <c r="K206" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="s">
+        <v>230</v>
+      </c>
+      <c r="B207" t="s">
+        <v>231</v>
+      </c>
+      <c r="C207" t="s">
+        <v>18</v>
+      </c>
+      <c r="D207" t="s">
+        <v>48</v>
+      </c>
+      <c r="E207">
+        <v>140990</v>
+      </c>
+      <c r="F207">
+        <v>1</v>
+      </c>
+      <c r="G207" t="s">
+        <v>84</v>
+      </c>
+      <c r="H207" t="s">
+        <v>84</v>
+      </c>
+      <c r="I207">
+        <v>0</v>
+      </c>
+      <c r="J207">
+        <v>0</v>
+      </c>
+      <c r="K207" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="s">
+        <v>230</v>
+      </c>
+      <c r="B208" t="s">
+        <v>231</v>
+      </c>
+      <c r="C208" t="s">
+        <v>18</v>
+      </c>
+      <c r="D208" t="s">
+        <v>29</v>
+      </c>
+      <c r="E208">
+        <v>140990</v>
+      </c>
+      <c r="F208">
+        <v>1</v>
+      </c>
+      <c r="G208" t="s">
+        <v>84</v>
+      </c>
+      <c r="H208" t="s">
+        <v>84</v>
+      </c>
+      <c r="I208">
+        <v>0</v>
+      </c>
+      <c r="J208">
+        <v>0</v>
+      </c>
+      <c r="K208" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="s">
+        <v>230</v>
+      </c>
+      <c r="B209" t="s">
+        <v>231</v>
+      </c>
+      <c r="C209" t="s">
+        <v>18</v>
+      </c>
+      <c r="D209" t="s">
+        <v>19</v>
+      </c>
+      <c r="E209">
+        <v>140990</v>
+      </c>
+      <c r="F209">
+        <v>1</v>
+      </c>
+      <c r="G209" t="s">
+        <v>84</v>
+      </c>
+      <c r="H209" t="s">
+        <v>84</v>
+      </c>
+      <c r="I209">
+        <v>0</v>
+      </c>
+      <c r="J209">
+        <v>0</v>
+      </c>
+      <c r="K209" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="s">
+        <v>230</v>
+      </c>
+      <c r="B210" t="s">
+        <v>231</v>
+      </c>
+      <c r="C210" t="s">
+        <v>18</v>
+      </c>
+      <c r="D210" t="s">
+        <v>127</v>
+      </c>
+      <c r="E210">
+        <v>140990</v>
+      </c>
+      <c r="F210">
+        <v>1</v>
+      </c>
+      <c r="G210" t="s">
+        <v>84</v>
+      </c>
+      <c r="H210" t="s">
+        <v>84</v>
+      </c>
+      <c r="I210">
+        <v>0</v>
+      </c>
+      <c r="J210">
+        <v>0</v>
+      </c>
+      <c r="K210" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="s">
+        <v>232</v>
+      </c>
+      <c r="B211" t="s">
+        <v>233</v>
+      </c>
+      <c r="C211" t="s">
+        <v>28</v>
+      </c>
+      <c r="D211" t="s">
+        <v>29</v>
+      </c>
+      <c r="E211">
+        <v>195990</v>
+      </c>
+      <c r="F211">
+        <v>1</v>
+      </c>
+      <c r="G211" t="s">
+        <v>84</v>
+      </c>
+      <c r="H211" t="s">
+        <v>84</v>
+      </c>
+      <c r="I211">
+        <v>0</v>
+      </c>
+      <c r="J211">
+        <v>0</v>
+      </c>
+      <c r="K211" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="s">
+        <v>232</v>
+      </c>
+      <c r="B212" t="s">
+        <v>233</v>
+      </c>
+      <c r="C212" t="s">
+        <v>28</v>
+      </c>
+      <c r="D212" t="s">
+        <v>25</v>
+      </c>
+      <c r="E212">
+        <v>195990</v>
+      </c>
+      <c r="F212">
+        <v>1</v>
+      </c>
+      <c r="G212" t="s">
+        <v>84</v>
+      </c>
+      <c r="H212" t="s">
+        <v>84</v>
+      </c>
+      <c r="I212">
+        <v>0</v>
+      </c>
+      <c r="J212">
+        <v>0</v>
+      </c>
+      <c r="K212" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="s">
+        <v>234</v>
+      </c>
+      <c r="B213" t="s">
+        <v>235</v>
+      </c>
+      <c r="C213" t="s">
+        <v>28</v>
+      </c>
+      <c r="D213" t="s">
+        <v>48</v>
+      </c>
+      <c r="E213">
+        <v>140900</v>
+      </c>
+      <c r="F213">
+        <v>1</v>
+      </c>
+      <c r="G213" t="s">
+        <v>84</v>
+      </c>
+      <c r="H213" t="s">
+        <v>84</v>
+      </c>
+      <c r="I213">
+        <v>0</v>
+      </c>
+      <c r="J213">
+        <v>0</v>
+      </c>
+      <c r="K213" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="s">
+        <v>234</v>
+      </c>
+      <c r="B214" t="s">
+        <v>235</v>
+      </c>
+      <c r="C214" t="s">
+        <v>28</v>
+      </c>
+      <c r="D214" t="s">
+        <v>29</v>
+      </c>
+      <c r="E214">
+        <v>130990</v>
+      </c>
+      <c r="F214">
+        <v>1</v>
+      </c>
+      <c r="G214" t="s">
+        <v>84</v>
+      </c>
+      <c r="H214" t="s">
+        <v>84</v>
+      </c>
+      <c r="I214">
+        <v>0</v>
+      </c>
+      <c r="J214">
+        <v>0</v>
+      </c>
+      <c r="K214" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="s">
+        <v>234</v>
+      </c>
+      <c r="B215" t="s">
+        <v>235</v>
+      </c>
+      <c r="C215" t="s">
+        <v>28</v>
+      </c>
+      <c r="D215" t="s">
+        <v>25</v>
+      </c>
+      <c r="E215">
+        <v>130990</v>
+      </c>
+      <c r="F215">
+        <v>1</v>
+      </c>
+      <c r="G215" t="s">
+        <v>84</v>
+      </c>
+      <c r="H215" t="s">
+        <v>84</v>
+      </c>
+      <c r="I215">
+        <v>0</v>
+      </c>
+      <c r="J215">
+        <v>0</v>
+      </c>
+      <c r="K215" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="s">
+        <v>234</v>
+      </c>
+      <c r="B216" t="s">
+        <v>235</v>
+      </c>
+      <c r="C216" t="s">
+        <v>28</v>
+      </c>
+      <c r="D216" t="s">
+        <v>19</v>
+      </c>
+      <c r="E216">
+        <v>130990</v>
+      </c>
+      <c r="F216">
+        <v>1</v>
+      </c>
+      <c r="G216" t="s">
+        <v>84</v>
+      </c>
+      <c r="H216" t="s">
+        <v>84</v>
+      </c>
+      <c r="I216">
+        <v>0</v>
+      </c>
+      <c r="J216">
+        <v>0</v>
+      </c>
+      <c r="K216" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="s">
+        <v>234</v>
+      </c>
+      <c r="B217" t="s">
+        <v>235</v>
+      </c>
+      <c r="C217" t="s">
+        <v>28</v>
+      </c>
+      <c r="D217" t="s">
+        <v>127</v>
+      </c>
+      <c r="E217">
+        <v>130990</v>
+      </c>
+      <c r="F217">
+        <v>1</v>
+      </c>
+      <c r="G217" t="s">
+        <v>84</v>
+      </c>
+      <c r="H217" t="s">
+        <v>84</v>
+      </c>
+      <c r="I217">
+        <v>0</v>
+      </c>
+      <c r="J217">
+        <v>0</v>
+      </c>
+      <c r="K217" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="s">
+        <v>236</v>
+      </c>
+      <c r="B218" t="s">
+        <v>237</v>
+      </c>
+      <c r="C218" t="s">
+        <v>117</v>
+      </c>
+      <c r="D218" t="s">
+        <v>118</v>
+      </c>
+      <c r="E218">
+        <v>149990</v>
+      </c>
+      <c r="F218">
+        <v>1</v>
+      </c>
+      <c r="G218" t="s">
+        <v>114</v>
+      </c>
+      <c r="H218" t="s">
+        <v>71</v>
+      </c>
+      <c r="I218">
+        <v>0</v>
+      </c>
+      <c r="J218">
+        <v>0</v>
+      </c>
+      <c r="K218" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="s">
+        <v>238</v>
+      </c>
+      <c r="B219" t="s">
+        <v>239</v>
+      </c>
+      <c r="C219" t="s">
+        <v>117</v>
+      </c>
+      <c r="D219" t="s">
+        <v>48</v>
+      </c>
+      <c r="E219">
+        <v>145990</v>
+      </c>
+      <c r="F219">
+        <v>1</v>
+      </c>
+      <c r="G219" t="s">
+        <v>114</v>
+      </c>
+      <c r="H219" t="s">
+        <v>71</v>
+      </c>
+      <c r="I219">
+        <v>0</v>
+      </c>
+      <c r="J219">
+        <v>0</v>
+      </c>
+      <c r="K219" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="s">
+        <v>240</v>
+      </c>
+      <c r="B220" t="s">
+        <v>241</v>
+      </c>
+      <c r="C220" t="s">
+        <v>117</v>
+      </c>
+      <c r="D220" t="s">
+        <v>118</v>
+      </c>
+      <c r="E220">
+        <v>279000</v>
+      </c>
+      <c r="F220">
+        <v>1</v>
+      </c>
+      <c r="G220" t="s">
+        <v>114</v>
+      </c>
+      <c r="H220" t="s">
+        <v>71</v>
+      </c>
+      <c r="I220">
+        <v>0</v>
+      </c>
+      <c r="J220">
+        <v>0</v>
+      </c>
+      <c r="K220" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="s">
+        <v>242</v>
+      </c>
+      <c r="B221" t="s">
+        <v>243</v>
+      </c>
+      <c r="C221" t="s">
+        <v>117</v>
+      </c>
+      <c r="D221" t="s">
+        <v>48</v>
+      </c>
+      <c r="E221">
+        <v>169990</v>
+      </c>
+      <c r="F221">
+        <v>1</v>
+      </c>
+      <c r="G221" t="s">
+        <v>84</v>
+      </c>
+      <c r="H221" t="s">
+        <v>84</v>
+      </c>
+      <c r="I221">
+        <v>0</v>
+      </c>
+      <c r="J221">
+        <v>0</v>
+      </c>
+      <c r="K221" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="s">
+        <v>242</v>
+      </c>
+      <c r="B222" t="s">
+        <v>243</v>
+      </c>
+      <c r="C222" t="s">
+        <v>117</v>
+      </c>
+      <c r="D222" t="s">
+        <v>29</v>
+      </c>
+      <c r="E222">
+        <v>169990</v>
+      </c>
+      <c r="F222">
+        <v>1</v>
+      </c>
+      <c r="G222" t="s">
+        <v>84</v>
+      </c>
+      <c r="H222" t="s">
+        <v>84</v>
+      </c>
+      <c r="I222">
+        <v>0</v>
+      </c>
+      <c r="J222">
+        <v>0</v>
+      </c>
+      <c r="K222" t="s">
         <v>33</v>
       </c>
     </row>

--- a/data/catalogo_jusp.xlsx
+++ b/data/catalogo_jusp.xlsx
@@ -89,6 +89,27 @@
     <t>TRUE</t>
   </si>
   <si>
+    <t>nike-ir1526-500</t>
+  </si>
+  <si>
+    <t>Nike Dunk Low Neon Lights</t>
+  </si>
+  <si>
+    <t>men</t>
+  </si>
+  <si>
+    <t>purple</t>
+  </si>
+  <si>
+    <t>40.5</t>
+  </si>
+  <si>
+    <t>sneakers</t>
+  </si>
+  <si>
+    <t>42.5</t>
+  </si>
+  <si>
     <t>nike-cn5263-010</t>
   </si>
   <si>
@@ -272,9 +293,6 @@
     <t>S/M</t>
   </si>
   <si>
-    <t>men</t>
-  </si>
-  <si>
     <t>beige</t>
   </si>
   <si>
@@ -288,9 +306,6 @@
   </si>
   <si>
     <t xml:space="preserve">Nike Pants </t>
-  </si>
-  <si>
-    <t>purple</t>
   </si>
   <si>
     <t>nike-dri-fit-quick-dry-running-compression-training-sports-tank-top-women</t>
@@ -1205,10 +1220,10 @@
         <v>22</v>
       </c>
       <c r="N2" s="3">
-        <v>46134</v>
+        <v>46143</v>
       </c>
       <c r="O2" s="3">
-        <v>46136</v>
+        <v>46144</v>
       </c>
       <c r="P2" t="s">
         <v>22</v>
@@ -1224,180 +1239,164 @@
       <c r="C3" t="s">
         <v>18</v>
       </c>
-      <c r="D3" t="s">
-        <v>25</v>
+      <c r="D3">
+        <v>40</v>
       </c>
       <c r="E3">
-        <v>99990</v>
+        <v>599990</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H3" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L3">
-        <v>30</v>
-      </c>
-      <c r="N3" s="3"/>
-      <c r="O3" s="3"/>
+        <v>26</v>
+      </c>
+      <c r="L3"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4">
+        <v>599990</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4" t="s">
         <v>26</v>
       </c>
-      <c r="B4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4">
-        <v>119990</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L4">
-        <v>30</v>
-      </c>
-      <c r="N4" s="3"/>
-      <c r="O4" s="3"/>
+      <c r="L4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="B5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
         <v>18</v>
       </c>
-      <c r="D5" t="s">
-        <v>32</v>
+      <c r="D5">
+        <v>41</v>
       </c>
       <c r="E5">
-        <v>95990</v>
+        <v>599990</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H5" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>33</v>
-      </c>
-      <c r="L5">
-        <v>45</v>
-      </c>
-      <c r="N5" s="3"/>
-      <c r="O5" s="3"/>
+        <v>26</v>
+      </c>
+      <c r="L5"/>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s">
         <v>18</v>
       </c>
-      <c r="D6" t="s">
-        <v>19</v>
+      <c r="D6">
+        <v>42</v>
       </c>
       <c r="E6">
-        <v>110990</v>
+        <v>599990</v>
       </c>
       <c r="F6">
         <v>1</v>
       </c>
       <c r="G6" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H6" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>33</v>
-      </c>
-      <c r="L6">
-        <v>20</v>
-      </c>
-      <c r="N6" s="3"/>
-      <c r="O6" s="3"/>
+        <v>26</v>
+      </c>
+      <c r="L6"/>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="B7" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="C7" t="s">
         <v>18</v>
       </c>
       <c r="D7" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E7">
-        <v>195990</v>
+        <v>599990</v>
       </c>
       <c r="F7">
         <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H7" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -1406,35 +1405,34 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>38</v>
-      </c>
-      <c r="N7" s="3"/>
-      <c r="O7" s="3"/>
+        <v>26</v>
+      </c>
+      <c r="L7"/>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="B8" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s">
         <v>18</v>
       </c>
-      <c r="D8" t="s">
-        <v>19</v>
+      <c r="D8">
+        <v>43</v>
       </c>
       <c r="E8">
-        <v>205990</v>
+        <v>599990</v>
       </c>
       <c r="F8">
         <v>1</v>
       </c>
       <c r="G8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H8" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -1443,226 +1441,151 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>38</v>
-      </c>
-      <c r="N8" s="3"/>
-      <c r="O8" s="3"/>
+        <v>26</v>
+      </c>
+      <c r="L8"/>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="C9" t="s">
         <v>18</v>
       </c>
-      <c r="D9" t="s">
-        <v>19</v>
+      <c r="D9">
+        <v>44</v>
       </c>
       <c r="E9">
-        <v>139990</v>
+        <v>599990</v>
       </c>
       <c r="F9">
         <v>1</v>
       </c>
       <c r="G9" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H9" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="I9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>33</v>
-      </c>
-      <c r="L9">
-        <v>20</v>
-      </c>
-      <c r="N9" s="3"/>
-      <c r="O9" s="3"/>
+        <v>26</v>
+      </c>
+      <c r="L9"/>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="B10" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="C10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10">
+        <v>45</v>
+      </c>
+      <c r="E10">
+        <v>599990</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10" t="s">
+        <v>25</v>
+      </c>
+      <c r="H10" t="s">
         <v>28</v>
       </c>
-      <c r="D10" t="s">
-        <v>29</v>
-      </c>
-      <c r="E10">
-        <v>125990</v>
-      </c>
-      <c r="F10">
-        <v>1</v>
-      </c>
-      <c r="G10" t="s">
-        <v>20</v>
-      </c>
-      <c r="H10" t="s">
-        <v>20</v>
-      </c>
       <c r="I10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>43</v>
-      </c>
-      <c r="L10">
-        <v>35</v>
-      </c>
-      <c r="N10" s="3"/>
-      <c r="O10" s="3"/>
+        <v>26</v>
+      </c>
+      <c r="L10"/>
     </row>
     <row r="11">
-      <c r="A11" t="s">
-        <v>44</v>
-      </c>
-      <c r="B11" t="s">
-        <v>45</v>
-      </c>
-      <c r="C11" t="s">
-        <v>18</v>
-      </c>
-      <c r="D11" t="s">
-        <v>29</v>
-      </c>
-      <c r="E11">
-        <v>99990</v>
-      </c>
-      <c r="F11">
-        <v>1</v>
-      </c>
-      <c r="G11" t="s">
-        <v>20</v>
-      </c>
-      <c r="H11" t="s">
-        <v>20</v>
-      </c>
-      <c r="I11">
-        <v>1</v>
-      </c>
-      <c r="J11">
-        <v>1</v>
-      </c>
-      <c r="K11" t="s">
-        <v>21</v>
-      </c>
-      <c r="L11">
-        <v>25</v>
-      </c>
-      <c r="N11" s="3"/>
-      <c r="O11" s="3"/>
+      <c r="A11"/>
+      <c r="B11"/>
+      <c r="C11"/>
+      <c r="D11"/>
+      <c r="E11"/>
+      <c r="F11"/>
+      <c r="G11"/>
+      <c r="H11"/>
+      <c r="I11"/>
+      <c r="J11"/>
+      <c r="K11"/>
+      <c r="L11"/>
+      <c r="M11"/>
+      <c r="N11"/>
+      <c r="O11"/>
+      <c r="P11"/>
     </row>
     <row r="12">
-      <c r="A12" t="s">
-        <v>44</v>
-      </c>
-      <c r="B12" t="s">
-        <v>45</v>
-      </c>
-      <c r="C12" t="s">
-        <v>18</v>
-      </c>
-      <c r="D12" t="s">
-        <v>25</v>
-      </c>
-      <c r="E12">
-        <v>99990</v>
-      </c>
-      <c r="F12">
-        <v>1</v>
-      </c>
-      <c r="G12" t="s">
-        <v>20</v>
-      </c>
-      <c r="H12" t="s">
-        <v>20</v>
-      </c>
-      <c r="I12">
-        <v>1</v>
-      </c>
-      <c r="J12">
-        <v>1</v>
-      </c>
-      <c r="K12" t="s">
-        <v>21</v>
-      </c>
-      <c r="L12">
-        <v>25</v>
-      </c>
+      <c r="A12"/>
+      <c r="B12"/>
+      <c r="C12"/>
+      <c r="D12"/>
+      <c r="E12"/>
+      <c r="F12"/>
+      <c r="G12"/>
+      <c r="H12"/>
+      <c r="I12"/>
+      <c r="J12"/>
+      <c r="K12"/>
+      <c r="L12"/>
+      <c r="M12"/>
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
+      <c r="P12"/>
     </row>
     <row r="13">
-      <c r="A13" t="s">
-        <v>46</v>
-      </c>
-      <c r="B13" t="s">
-        <v>47</v>
-      </c>
-      <c r="C13" t="s">
-        <v>18</v>
-      </c>
-      <c r="D13" t="s">
-        <v>48</v>
-      </c>
-      <c r="E13">
-        <v>109990</v>
-      </c>
-      <c r="F13">
-        <v>1</v>
-      </c>
-      <c r="G13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H13" t="s">
-        <v>20</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13" t="s">
-        <v>33</v>
-      </c>
-      <c r="L13">
-        <v>30</v>
-      </c>
+      <c r="A13"/>
+      <c r="B13"/>
+      <c r="C13"/>
+      <c r="D13"/>
+      <c r="E13"/>
+      <c r="F13"/>
+      <c r="G13"/>
+      <c r="H13"/>
+      <c r="I13"/>
+      <c r="J13"/>
+      <c r="K13"/>
+      <c r="L13"/>
+      <c r="M13"/>
       <c r="N13" s="3"/>
       <c r="O13" s="3"/>
+      <c r="P13"/>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="B14" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="C14" t="s">
         <v>18</v>
       </c>
       <c r="D14" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E14">
-        <v>119990</v>
+        <v>99990</v>
       </c>
       <c r="F14">
         <v>1</v>
@@ -1674,13 +1597,13 @@
         <v>20</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="L14">
         <v>30</v>
@@ -1690,16 +1613,16 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="B15" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D15" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="E15">
         <v>119990</v>
@@ -1714,13 +1637,13 @@
         <v>20</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="L15">
         <v>30</v>
@@ -1730,19 +1653,19 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="B16" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C16" t="s">
         <v>18</v>
       </c>
       <c r="D16" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="E16">
-        <v>119990</v>
+        <v>95990</v>
       </c>
       <c r="F16">
         <v>1</v>
@@ -1760,29 +1683,29 @@
         <v>1</v>
       </c>
       <c r="K16" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="L16">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="B17" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="C17" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D17" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E17">
-        <v>119990</v>
+        <v>110990</v>
       </c>
       <c r="F17">
         <v>1</v>
@@ -1800,29 +1723,29 @@
         <v>1</v>
       </c>
       <c r="K17" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="L17">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="B18" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C18" t="s">
         <v>18</v>
       </c>
       <c r="D18" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E18">
-        <v>99990</v>
+        <v>195990</v>
       </c>
       <c r="F18">
         <v>1</v>
@@ -1834,35 +1757,32 @@
         <v>20</v>
       </c>
       <c r="I18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>21</v>
-      </c>
-      <c r="L18">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="B19" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="C19" t="s">
         <v>18</v>
       </c>
       <c r="D19" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E19">
-        <v>86990</v>
+        <v>205990</v>
       </c>
       <c r="F19">
         <v>1</v>
@@ -1874,26 +1794,23 @@
         <v>20</v>
       </c>
       <c r="I19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>21</v>
-      </c>
-      <c r="L19">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="B20" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="C20" t="s">
         <v>18</v>
@@ -1902,7 +1819,7 @@
         <v>19</v>
       </c>
       <c r="E20">
-        <v>86990</v>
+        <v>139990</v>
       </c>
       <c r="F20">
         <v>1</v>
@@ -1920,29 +1837,29 @@
         <v>1</v>
       </c>
       <c r="K20" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="L20">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="N20" s="3"/>
       <c r="O20" s="3"/>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="B21" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="C21" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="D21" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="E21">
-        <v>96990</v>
+        <v>125990</v>
       </c>
       <c r="F21">
         <v>1</v>
@@ -1960,29 +1877,29 @@
         <v>1</v>
       </c>
       <c r="K21" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="L21">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="N21" s="3"/>
       <c r="O21" s="3"/>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="B22" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="C22" t="s">
-        <v>63</v>
+        <v>18</v>
       </c>
       <c r="D22" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="E22">
-        <v>95990</v>
+        <v>99990</v>
       </c>
       <c r="F22">
         <v>1</v>
@@ -2010,65 +1927,68 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="B23" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="C23" t="s">
         <v>18</v>
       </c>
       <c r="D23" t="s">
-        <v>69</v>
+        <v>32</v>
       </c>
       <c r="E23">
-        <v>129990</v>
+        <v>99990</v>
       </c>
       <c r="F23">
         <v>1</v>
       </c>
       <c r="G23" t="s">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="H23" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="s">
         <v>21</v>
       </c>
+      <c r="L23">
+        <v>25</v>
+      </c>
       <c r="N23" s="3"/>
       <c r="O23" s="3"/>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="B24" t="s">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="C24" t="s">
         <v>18</v>
       </c>
       <c r="D24" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="E24">
-        <v>88990</v>
+        <v>109990</v>
       </c>
       <c r="F24">
         <v>1</v>
       </c>
       <c r="G24" t="s">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="H24" t="s">
-        <v>76</v>
+        <v>20</v>
       </c>
       <c r="I24">
         <v>0</v>
@@ -2077,36 +1997,38 @@
         <v>0</v>
       </c>
       <c r="K24" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="L24">
-        <v>5</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="N24" s="3"/>
+      <c r="O24" s="3"/>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="B25" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="C25" t="s">
         <v>18</v>
       </c>
       <c r="D25" t="s">
-        <v>77</v>
+        <v>36</v>
       </c>
       <c r="E25">
-        <v>88990</v>
+        <v>119990</v>
       </c>
       <c r="F25">
         <v>1</v>
       </c>
       <c r="G25" t="s">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="H25" t="s">
-        <v>76</v>
+        <v>20</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -2115,27 +2037,29 @@
         <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="L25">
-        <v>5</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="N25" s="3"/>
+      <c r="O25" s="3"/>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="B26" t="s">
-        <v>79</v>
+        <v>57</v>
       </c>
       <c r="C26" t="s">
         <v>18</v>
       </c>
       <c r="D26" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="E26">
-        <v>89990</v>
+        <v>119990</v>
       </c>
       <c r="F26">
         <v>1</v>
@@ -2153,24 +2077,29 @@
         <v>0</v>
       </c>
       <c r="K26" t="s">
-        <v>80</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="L26">
+        <v>30</v>
+      </c>
+      <c r="N26" s="3"/>
+      <c r="O26" s="3"/>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="B27" t="s">
-        <v>79</v>
+        <v>57</v>
       </c>
       <c r="C27" t="s">
         <v>18</v>
       </c>
       <c r="D27" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E27">
-        <v>89990</v>
+        <v>119990</v>
       </c>
       <c r="F27">
         <v>1</v>
@@ -2182,135 +2111,155 @@
         <v>20</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="s">
-        <v>80</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="L27">
+        <v>30</v>
+      </c>
+      <c r="N27" s="3"/>
+      <c r="O27" s="3"/>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="B28" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="C28" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D28" t="s">
-        <v>83</v>
+        <v>36</v>
       </c>
       <c r="E28">
-        <v>75990</v>
+        <v>119990</v>
       </c>
       <c r="F28">
         <v>1</v>
       </c>
       <c r="G28" t="s">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="H28" t="s">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="s">
-        <v>85</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="L28">
+        <v>35</v>
+      </c>
+      <c r="N28" s="3"/>
+      <c r="O28" s="3"/>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="B29" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="C29" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D29" t="s">
-        <v>86</v>
+        <v>36</v>
       </c>
       <c r="E29">
-        <v>79990</v>
+        <v>99990</v>
       </c>
       <c r="F29">
         <v>1</v>
       </c>
       <c r="G29" t="s">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="H29" t="s">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="s">
-        <v>85</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="L29">
+        <v>25</v>
+      </c>
+      <c r="N29" s="3"/>
+      <c r="O29" s="3"/>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="B30" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="C30" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D30" t="s">
-        <v>87</v>
+        <v>32</v>
       </c>
       <c r="E30">
-        <v>78990</v>
+        <v>86990</v>
       </c>
       <c r="F30">
         <v>1</v>
       </c>
       <c r="G30" t="s">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="H30" t="s">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" t="s">
-        <v>85</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="L30">
+        <v>30</v>
+      </c>
+      <c r="N30" s="3"/>
+      <c r="O30" s="3"/>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="B31" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="C31" t="s">
         <v>18</v>
       </c>
       <c r="D31" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E31">
-        <v>69990</v>
+        <v>86990</v>
       </c>
       <c r="F31">
         <v>1</v>
@@ -2322,30 +2271,35 @@
         <v>20</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="s">
-        <v>90</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="L31">
+        <v>30</v>
+      </c>
+      <c r="N31" s="3"/>
+      <c r="O31" s="3"/>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>91</v>
+        <v>68</v>
       </c>
       <c r="B32" t="s">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="C32" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="D32" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E32">
-        <v>139990</v>
+        <v>96990</v>
       </c>
       <c r="F32">
         <v>1</v>
@@ -2357,74 +2311,84 @@
         <v>20</v>
       </c>
       <c r="I32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="s">
-        <v>33</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="L32">
+        <v>25</v>
+      </c>
+      <c r="N32" s="3"/>
+      <c r="O32" s="3"/>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="B33" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="C33" t="s">
-        <v>18</v>
-      </c>
-      <c r="D33">
-        <v>7</v>
+        <v>70</v>
+      </c>
+      <c r="D33" t="s">
+        <v>32</v>
       </c>
       <c r="E33">
-        <v>99990</v>
+        <v>95990</v>
       </c>
       <c r="F33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G33" t="s">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="H33" t="s">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="I33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" t="s">
-        <v>85</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="L33">
+        <v>25</v>
+      </c>
+      <c r="N33" s="3"/>
+      <c r="O33" s="3"/>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="B34" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="C34" t="s">
         <v>18</v>
       </c>
       <c r="D34" t="s">
-        <v>25</v>
-      </c>
-      <c r="E34" s="4">
-        <v>119990</v>
+        <v>76</v>
+      </c>
+      <c r="E34">
+        <v>129990</v>
       </c>
       <c r="F34">
         <v>1</v>
       </c>
       <c r="G34" t="s">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="H34" t="s">
-        <v>20</v>
+        <v>78</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -2433,34 +2397,36 @@
         <v>0</v>
       </c>
       <c r="K34" t="s">
-        <v>33</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="N34" s="3"/>
+      <c r="O34" s="3"/>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="B35" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="C35" t="s">
         <v>18</v>
       </c>
       <c r="D35" t="s">
+        <v>81</v>
+      </c>
+      <c r="E35">
+        <v>88990</v>
+      </c>
+      <c r="F35">
+        <v>1</v>
+      </c>
+      <c r="G35" t="s">
+        <v>82</v>
+      </c>
+      <c r="H35" t="s">
         <v>83</v>
       </c>
-      <c r="E35">
-        <v>65990</v>
-      </c>
-      <c r="F35">
-        <v>1</v>
-      </c>
-      <c r="G35" t="s">
-        <v>84</v>
-      </c>
-      <c r="H35" t="s">
-        <v>84</v>
-      </c>
       <c r="I35">
         <v>0</v>
       </c>
@@ -2468,33 +2434,36 @@
         <v>0</v>
       </c>
       <c r="K35" t="s">
-        <v>99</v>
+        <v>21</v>
+      </c>
+      <c r="L35">
+        <v>5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="B36" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="C36" t="s">
         <v>18</v>
       </c>
       <c r="D36" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E36">
-        <v>75990</v>
+        <v>88990</v>
       </c>
       <c r="F36">
         <v>1</v>
       </c>
       <c r="G36" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H36" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -2503,59 +2472,62 @@
         <v>0</v>
       </c>
       <c r="K36" t="s">
-        <v>99</v>
+        <v>21</v>
+      </c>
+      <c r="L36">
+        <v>5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="B37" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="C37" t="s">
         <v>18</v>
       </c>
       <c r="D37" t="s">
+        <v>55</v>
+      </c>
+      <c r="E37">
+        <v>89990</v>
+      </c>
+      <c r="F37">
+        <v>1</v>
+      </c>
+      <c r="G37" t="s">
+        <v>20</v>
+      </c>
+      <c r="H37" t="s">
+        <v>20</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37" t="s">
         <v>87</v>
-      </c>
-      <c r="E37">
-        <v>85990</v>
-      </c>
-      <c r="F37">
-        <v>1</v>
-      </c>
-      <c r="G37" t="s">
-        <v>84</v>
-      </c>
-      <c r="H37" t="s">
-        <v>84</v>
-      </c>
-      <c r="I37">
-        <v>0</v>
-      </c>
-      <c r="J37">
-        <v>0</v>
-      </c>
-      <c r="K37" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B38" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="C38" t="s">
         <v>18</v>
       </c>
       <c r="D38" t="s">
-        <v>102</v>
+        <v>36</v>
       </c>
       <c r="E38">
-        <v>79990</v>
+        <v>89990</v>
       </c>
       <c r="F38">
         <v>1</v>
@@ -2573,33 +2545,33 @@
         <v>0</v>
       </c>
       <c r="K38" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="B39" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="C39" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D39" t="s">
-        <v>48</v>
+        <v>90</v>
       </c>
       <c r="E39">
-        <v>79990</v>
+        <v>75990</v>
       </c>
       <c r="F39">
         <v>1</v>
       </c>
       <c r="G39" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H39" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I39">
         <v>0</v>
@@ -2608,21 +2580,21 @@
         <v>0</v>
       </c>
       <c r="K39" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="B40" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="C40" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D40" t="s">
-        <v>29</v>
+        <v>92</v>
       </c>
       <c r="E40">
         <v>79990</v>
@@ -2631,10 +2603,10 @@
         <v>1</v>
       </c>
       <c r="G40" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H40" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I40">
         <v>0</v>
@@ -2643,33 +2615,33 @@
         <v>0</v>
       </c>
       <c r="K40" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="B41" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="C41" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D41" t="s">
-        <v>25</v>
+        <v>93</v>
       </c>
       <c r="E41">
-        <v>79990</v>
+        <v>78990</v>
       </c>
       <c r="F41">
         <v>1</v>
       </c>
       <c r="G41" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H41" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I41">
         <v>0</v>
@@ -2678,24 +2650,24 @@
         <v>0</v>
       </c>
       <c r="K41" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="B42" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="C42" t="s">
         <v>18</v>
       </c>
       <c r="D42" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="E42">
-        <v>79990</v>
+        <v>69990</v>
       </c>
       <c r="F42">
         <v>1</v>
@@ -2713,24 +2685,24 @@
         <v>0</v>
       </c>
       <c r="K42" t="s">
-        <v>85</v>
+        <v>26</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="B43" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C43" t="s">
         <v>18</v>
       </c>
       <c r="D43" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="E43">
-        <v>155990</v>
+        <v>139990</v>
       </c>
       <c r="F43">
         <v>1</v>
@@ -2748,33 +2720,33 @@
         <v>0</v>
       </c>
       <c r="K43" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="B44" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C44" t="s">
         <v>18</v>
       </c>
-      <c r="D44" t="s">
-        <v>29</v>
+      <c r="D44">
+        <v>7</v>
       </c>
       <c r="E44">
-        <v>155990</v>
+        <v>99990</v>
       </c>
       <c r="F44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G44" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H44" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I44">
         <v>0</v>
@@ -2783,24 +2755,24 @@
         <v>0</v>
       </c>
       <c r="K44" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B45" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C45" t="s">
         <v>18</v>
       </c>
       <c r="D45" t="s">
-        <v>25</v>
-      </c>
-      <c r="E45">
-        <v>155990</v>
+        <v>32</v>
+      </c>
+      <c r="E45" s="4">
+        <v>119990</v>
       </c>
       <c r="F45">
         <v>1</v>
@@ -2818,68 +2790,68 @@
         <v>0</v>
       </c>
       <c r="K45" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
+        <v>102</v>
+      </c>
+      <c r="B46" t="s">
         <v>103</v>
       </c>
-      <c r="B46" t="s">
+      <c r="C46" t="s">
+        <v>18</v>
+      </c>
+      <c r="D46" t="s">
+        <v>90</v>
+      </c>
+      <c r="E46">
+        <v>65990</v>
+      </c>
+      <c r="F46">
+        <v>1</v>
+      </c>
+      <c r="G46" t="s">
+        <v>25</v>
+      </c>
+      <c r="H46" t="s">
+        <v>25</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46" t="s">
         <v>104</v>
-      </c>
-      <c r="C46" t="s">
-        <v>18</v>
-      </c>
-      <c r="D46" t="s">
-        <v>19</v>
-      </c>
-      <c r="E46">
-        <v>155990</v>
-      </c>
-      <c r="F46">
-        <v>1</v>
-      </c>
-      <c r="G46" t="s">
-        <v>20</v>
-      </c>
-      <c r="H46" t="s">
-        <v>20</v>
-      </c>
-      <c r="I46">
-        <v>0</v>
-      </c>
-      <c r="J46">
-        <v>0</v>
-      </c>
-      <c r="K46" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B47" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C47" t="s">
-        <v>63</v>
+        <v>18</v>
       </c>
       <c r="D47" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="E47">
-        <v>49990</v>
+        <v>75990</v>
       </c>
       <c r="F47">
         <v>1</v>
       </c>
       <c r="G47" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H47" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I47">
         <v>0</v>
@@ -2888,33 +2860,33 @@
         <v>0</v>
       </c>
       <c r="K47" t="s">
-        <v>21</v>
+        <v>104</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B48" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C48" t="s">
-        <v>63</v>
+        <v>18</v>
       </c>
       <c r="D48" t="s">
-        <v>29</v>
+        <v>93</v>
       </c>
       <c r="E48">
-        <v>49990</v>
+        <v>85990</v>
       </c>
       <c r="F48">
         <v>1</v>
       </c>
       <c r="G48" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H48" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I48">
         <v>0</v>
@@ -2923,24 +2895,24 @@
         <v>0</v>
       </c>
       <c r="K48" t="s">
-        <v>21</v>
+        <v>104</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
+        <v>105</v>
+      </c>
+      <c r="B49" t="s">
+        <v>106</v>
+      </c>
+      <c r="C49" t="s">
+        <v>18</v>
+      </c>
+      <c r="D49" t="s">
         <v>107</v>
       </c>
-      <c r="B49" t="s">
-        <v>108</v>
-      </c>
-      <c r="C49" t="s">
-        <v>28</v>
-      </c>
-      <c r="D49" t="s">
-        <v>29</v>
-      </c>
       <c r="E49">
-        <v>135990</v>
+        <v>79990</v>
       </c>
       <c r="F49">
         <v>1</v>
@@ -2958,24 +2930,24 @@
         <v>0</v>
       </c>
       <c r="K49" t="s">
-        <v>56</v>
+        <v>91</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B50" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C50" t="s">
         <v>18</v>
       </c>
       <c r="D50" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="E50">
-        <v>155990</v>
+        <v>79990</v>
       </c>
       <c r="F50">
         <v>1</v>
@@ -2993,24 +2965,24 @@
         <v>0</v>
       </c>
       <c r="K50" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B51" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C51" t="s">
         <v>18</v>
       </c>
       <c r="D51" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="E51">
-        <v>155990</v>
+        <v>79990</v>
       </c>
       <c r="F51">
         <v>1</v>
@@ -3028,24 +3000,24 @@
         <v>0</v>
       </c>
       <c r="K51" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B52" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C52" t="s">
         <v>18</v>
       </c>
       <c r="D52" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E52">
-        <v>155990</v>
+        <v>79990</v>
       </c>
       <c r="F52">
         <v>1</v>
@@ -3063,33 +3035,33 @@
         <v>0</v>
       </c>
       <c r="K52" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="B53" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="C53" t="s">
         <v>18</v>
       </c>
       <c r="D53" t="s">
-        <v>86</v>
+        <v>19</v>
       </c>
       <c r="E53">
-        <v>129990</v>
+        <v>79990</v>
       </c>
       <c r="F53">
         <v>1</v>
       </c>
       <c r="G53" t="s">
-        <v>114</v>
+        <v>20</v>
       </c>
       <c r="H53" t="s">
-        <v>114</v>
+        <v>20</v>
       </c>
       <c r="I53">
         <v>0</v>
@@ -3098,33 +3070,33 @@
         <v>0</v>
       </c>
       <c r="K53" t="s">
-        <v>21</v>
+        <v>91</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B54" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C54" t="s">
         <v>18</v>
       </c>
       <c r="D54" t="s">
-        <v>87</v>
+        <v>55</v>
       </c>
       <c r="E54">
-        <v>129990</v>
+        <v>155990</v>
       </c>
       <c r="F54">
         <v>1</v>
       </c>
       <c r="G54" t="s">
-        <v>114</v>
+        <v>20</v>
       </c>
       <c r="H54" t="s">
-        <v>114</v>
+        <v>20</v>
       </c>
       <c r="I54">
         <v>0</v>
@@ -3133,33 +3105,33 @@
         <v>0</v>
       </c>
       <c r="K54" t="s">
-        <v>21</v>
+        <v>60</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="B55" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="C55" t="s">
-        <v>117</v>
+        <v>18</v>
       </c>
       <c r="D55" t="s">
-        <v>118</v>
+        <v>36</v>
       </c>
       <c r="E55">
-        <v>179990</v>
+        <v>155990</v>
       </c>
       <c r="F55">
         <v>1</v>
       </c>
       <c r="G55" t="s">
-        <v>114</v>
+        <v>20</v>
       </c>
       <c r="H55" t="s">
-        <v>114</v>
+        <v>20</v>
       </c>
       <c r="I55">
         <v>0</v>
@@ -3168,33 +3140,33 @@
         <v>0</v>
       </c>
       <c r="K55" t="s">
-        <v>21</v>
+        <v>60</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="B56" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="C56" t="s">
         <v>18</v>
       </c>
       <c r="D56" t="s">
-        <v>118</v>
+        <v>32</v>
       </c>
       <c r="E56">
-        <v>159990</v>
+        <v>155990</v>
       </c>
       <c r="F56">
         <v>1</v>
       </c>
       <c r="G56" t="s">
-        <v>114</v>
+        <v>20</v>
       </c>
       <c r="H56" t="s">
-        <v>114</v>
+        <v>20</v>
       </c>
       <c r="I56">
         <v>0</v>
@@ -3203,33 +3175,33 @@
         <v>0</v>
       </c>
       <c r="K56" t="s">
-        <v>21</v>
+        <v>60</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="B57" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="C57" t="s">
         <v>18</v>
       </c>
       <c r="D57" t="s">
-        <v>83</v>
+        <v>19</v>
       </c>
       <c r="E57">
-        <v>134990</v>
+        <v>155990</v>
       </c>
       <c r="F57">
         <v>1</v>
       </c>
       <c r="G57" t="s">
-        <v>114</v>
+        <v>20</v>
       </c>
       <c r="H57" t="s">
-        <v>114</v>
+        <v>20</v>
       </c>
       <c r="I57">
         <v>0</v>
@@ -3238,33 +3210,33 @@
         <v>0</v>
       </c>
       <c r="K57" t="s">
-        <v>21</v>
+        <v>60</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="B58" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="C58" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="D58" t="s">
-        <v>86</v>
+        <v>55</v>
       </c>
       <c r="E58">
-        <v>134990</v>
+        <v>49990</v>
       </c>
       <c r="F58">
         <v>1</v>
       </c>
       <c r="G58" t="s">
-        <v>114</v>
+        <v>20</v>
       </c>
       <c r="H58" t="s">
-        <v>114</v>
+        <v>20</v>
       </c>
       <c r="I58">
         <v>0</v>
@@ -3278,28 +3250,28 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="B59" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="C59" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="D59" t="s">
-        <v>87</v>
+        <v>36</v>
       </c>
       <c r="E59">
-        <v>134990</v>
+        <v>49990</v>
       </c>
       <c r="F59">
         <v>1</v>
       </c>
       <c r="G59" t="s">
-        <v>114</v>
+        <v>20</v>
       </c>
       <c r="H59" t="s">
-        <v>114</v>
+        <v>20</v>
       </c>
       <c r="I59">
         <v>0</v>
@@ -3313,28 +3285,28 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="B60" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="C60" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D60" t="s">
-        <v>69</v>
+        <v>36</v>
       </c>
       <c r="E60">
-        <v>79990</v>
+        <v>135990</v>
       </c>
       <c r="F60">
         <v>1</v>
       </c>
       <c r="G60" t="s">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="H60" t="s">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="I60">
         <v>0</v>
@@ -3343,33 +3315,33 @@
         <v>0</v>
       </c>
       <c r="K60" t="s">
-        <v>21</v>
+        <v>63</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="B61" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="C61" t="s">
         <v>18</v>
       </c>
       <c r="D61" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="E61">
-        <v>134990</v>
+        <v>155990</v>
       </c>
       <c r="F61">
         <v>1</v>
       </c>
       <c r="G61" t="s">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="H61" t="s">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="I61">
         <v>0</v>
@@ -3378,33 +3350,33 @@
         <v>0</v>
       </c>
       <c r="K61" t="s">
-        <v>21</v>
+        <v>116</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="B62" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="C62" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D62" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E62">
-        <v>134990</v>
+        <v>155990</v>
       </c>
       <c r="F62">
         <v>1</v>
       </c>
       <c r="G62" t="s">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="H62" t="s">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="I62">
         <v>0</v>
@@ -3413,33 +3385,33 @@
         <v>0</v>
       </c>
       <c r="K62" t="s">
-        <v>21</v>
+        <v>116</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="B63" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="C63" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D63" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E63">
-        <v>134990</v>
+        <v>155990</v>
       </c>
       <c r="F63">
         <v>1</v>
       </c>
       <c r="G63" t="s">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="H63" t="s">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="I63">
         <v>0</v>
@@ -3448,33 +3420,33 @@
         <v>0</v>
       </c>
       <c r="K63" t="s">
-        <v>21</v>
+        <v>116</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="B64" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="C64" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D64" t="s">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="E64">
-        <v>134990</v>
+        <v>129990</v>
       </c>
       <c r="F64">
         <v>1</v>
       </c>
       <c r="G64" t="s">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="H64" t="s">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="I64">
         <v>0</v>
@@ -3488,28 +3460,28 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="B65" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="C65" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D65" t="s">
-        <v>127</v>
+        <v>93</v>
       </c>
       <c r="E65">
-        <v>134990</v>
+        <v>129990</v>
       </c>
       <c r="F65">
         <v>1</v>
       </c>
       <c r="G65" t="s">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="H65" t="s">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="I65">
         <v>0</v>
@@ -3523,28 +3495,28 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B66" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="C66" t="s">
-        <v>28</v>
+        <v>122</v>
       </c>
       <c r="D66" t="s">
-        <v>48</v>
+        <v>123</v>
       </c>
       <c r="E66">
-        <v>119990</v>
+        <v>179990</v>
       </c>
       <c r="F66">
         <v>1</v>
       </c>
       <c r="G66" t="s">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="H66" t="s">
-        <v>71</v>
+        <v>119</v>
       </c>
       <c r="I66">
         <v>0</v>
@@ -3558,28 +3530,28 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="B67" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C67" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D67" t="s">
-        <v>29</v>
+        <v>123</v>
       </c>
       <c r="E67">
-        <v>119990</v>
+        <v>159990</v>
       </c>
       <c r="F67">
         <v>1</v>
       </c>
       <c r="G67" t="s">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="H67" t="s">
-        <v>71</v>
+        <v>119</v>
       </c>
       <c r="I67">
         <v>0</v>
@@ -3593,28 +3565,28 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B68" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C68" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D68" t="s">
-        <v>25</v>
+        <v>90</v>
       </c>
       <c r="E68">
-        <v>119990</v>
+        <v>134990</v>
       </c>
       <c r="F68">
         <v>1</v>
       </c>
       <c r="G68" t="s">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="H68" t="s">
-        <v>71</v>
+        <v>119</v>
       </c>
       <c r="I68">
         <v>0</v>
@@ -3628,28 +3600,28 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B69" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C69" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D69" t="s">
-        <v>29</v>
+        <v>92</v>
       </c>
       <c r="E69">
-        <v>119990</v>
+        <v>134990</v>
       </c>
       <c r="F69">
         <v>1</v>
       </c>
       <c r="G69" t="s">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="H69" t="s">
-        <v>71</v>
+        <v>119</v>
       </c>
       <c r="I69">
         <v>0</v>
@@ -3658,33 +3630,33 @@
         <v>0</v>
       </c>
       <c r="K69" t="s">
-        <v>132</v>
+        <v>21</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B70" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C70" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D70" t="s">
-        <v>25</v>
+        <v>93</v>
       </c>
       <c r="E70">
-        <v>119990</v>
+        <v>134990</v>
       </c>
       <c r="F70">
         <v>1</v>
       </c>
       <c r="G70" t="s">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="H70" t="s">
-        <v>71</v>
+        <v>119</v>
       </c>
       <c r="I70">
         <v>0</v>
@@ -3693,33 +3665,33 @@
         <v>0</v>
       </c>
       <c r="K70" t="s">
-        <v>132</v>
+        <v>21</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B71" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C71" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D71" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="E71">
-        <v>39990</v>
+        <v>79990</v>
       </c>
       <c r="F71">
         <v>1</v>
       </c>
       <c r="G71" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H71" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="I71">
         <v>0</v>
@@ -3733,28 +3705,28 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B72" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C72" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D72" t="s">
-        <v>87</v>
+        <v>55</v>
       </c>
       <c r="E72">
-        <v>39990</v>
+        <v>134990</v>
       </c>
       <c r="F72">
         <v>1</v>
       </c>
       <c r="G72" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="H72" t="s">
-        <v>71</v>
+        <v>25</v>
       </c>
       <c r="I72">
         <v>0</v>
@@ -3768,28 +3740,28 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="B73" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C73" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D73" t="s">
-        <v>87</v>
+        <v>36</v>
       </c>
       <c r="E73">
-        <v>39990</v>
+        <v>134990</v>
       </c>
       <c r="F73">
         <v>1</v>
       </c>
       <c r="G73" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="H73" t="s">
-        <v>71</v>
+        <v>25</v>
       </c>
       <c r="I73">
         <v>0</v>
@@ -3798,33 +3770,33 @@
         <v>0</v>
       </c>
       <c r="K73" t="s">
-        <v>132</v>
+        <v>21</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="B74" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="C74" t="s">
-        <v>117</v>
+        <v>35</v>
       </c>
       <c r="D74" t="s">
-        <v>139</v>
+        <v>32</v>
       </c>
       <c r="E74">
-        <v>140990</v>
+        <v>134990</v>
       </c>
       <c r="F74">
         <v>1</v>
       </c>
       <c r="G74" t="s">
-        <v>114</v>
+        <v>25</v>
       </c>
       <c r="H74" t="s">
-        <v>71</v>
+        <v>25</v>
       </c>
       <c r="I74">
         <v>0</v>
@@ -3833,33 +3805,33 @@
         <v>0</v>
       </c>
       <c r="K74" t="s">
-        <v>85</v>
+        <v>21</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="B75" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="C75" t="s">
-        <v>117</v>
+        <v>35</v>
       </c>
       <c r="D75" t="s">
-        <v>140</v>
+        <v>19</v>
       </c>
       <c r="E75">
-        <v>145990</v>
+        <v>134990</v>
       </c>
       <c r="F75">
         <v>1</v>
       </c>
       <c r="G75" t="s">
-        <v>114</v>
+        <v>25</v>
       </c>
       <c r="H75" t="s">
-        <v>71</v>
+        <v>25</v>
       </c>
       <c r="I75">
         <v>0</v>
@@ -3868,33 +3840,33 @@
         <v>0</v>
       </c>
       <c r="K75" t="s">
-        <v>85</v>
+        <v>21</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="B76" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="C76" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D76" t="s">
-        <v>48</v>
-      </c>
-      <c r="E76" s="4">
-        <v>199990</v>
+        <v>132</v>
+      </c>
+      <c r="E76">
+        <v>134990</v>
       </c>
       <c r="F76">
         <v>1</v>
       </c>
       <c r="G76" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="H76" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="I76">
         <v>0</v>
@@ -3903,33 +3875,33 @@
         <v>0</v>
       </c>
       <c r="K76" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="B77" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="C77" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D77" t="s">
-        <v>29</v>
-      </c>
-      <c r="E77" s="4">
-        <v>199990</v>
+        <v>55</v>
+      </c>
+      <c r="E77">
+        <v>119990</v>
       </c>
       <c r="F77">
         <v>1</v>
       </c>
       <c r="G77" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="H77" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="I77">
         <v>0</v>
@@ -3938,33 +3910,33 @@
         <v>0</v>
       </c>
       <c r="K77" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="B78" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="C78" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D78" t="s">
-        <v>25</v>
-      </c>
-      <c r="E78" s="4">
-        <v>199990</v>
+        <v>36</v>
+      </c>
+      <c r="E78">
+        <v>119990</v>
       </c>
       <c r="F78">
         <v>1</v>
       </c>
       <c r="G78" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="H78" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="I78">
         <v>0</v>
@@ -3973,33 +3945,33 @@
         <v>0</v>
       </c>
       <c r="K78" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="B79" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="C79" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D79" t="s">
-        <v>19</v>
-      </c>
-      <c r="E79" s="4">
-        <v>199990</v>
+        <v>32</v>
+      </c>
+      <c r="E79">
+        <v>119990</v>
       </c>
       <c r="F79">
         <v>1</v>
       </c>
       <c r="G79" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="H79" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="I79">
         <v>0</v>
@@ -4008,33 +3980,33 @@
         <v>0</v>
       </c>
       <c r="K79" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="B80" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="C80" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D80" t="s">
-        <v>127</v>
-      </c>
-      <c r="E80" s="4">
-        <v>199990</v>
+        <v>36</v>
+      </c>
+      <c r="E80">
+        <v>119990</v>
       </c>
       <c r="F80">
         <v>1</v>
       </c>
       <c r="G80" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="H80" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="I80">
         <v>0</v>
@@ -4043,33 +4015,33 @@
         <v>0</v>
       </c>
       <c r="K80" t="s">
-        <v>33</v>
+        <v>137</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B81" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="C81" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D81" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="E81">
-        <v>155990</v>
+        <v>119990</v>
       </c>
       <c r="F81">
         <v>1</v>
       </c>
       <c r="G81" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="H81" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="I81">
         <v>0</v>
@@ -4078,33 +4050,33 @@
         <v>0</v>
       </c>
       <c r="K81" t="s">
-        <v>21</v>
+        <v>137</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B82" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C82" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D82" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="E82">
-        <v>155990</v>
+        <v>39990</v>
       </c>
       <c r="F82">
         <v>1</v>
       </c>
       <c r="G82" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="H82" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="I82">
         <v>0</v>
@@ -4118,28 +4090,28 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B83" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C83" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D83" t="s">
-        <v>25</v>
+        <v>93</v>
       </c>
       <c r="E83">
-        <v>155990</v>
+        <v>39990</v>
       </c>
       <c r="F83">
         <v>1</v>
       </c>
       <c r="G83" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="H83" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="I83">
         <v>0</v>
@@ -4153,28 +4125,28 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B84" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C84" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D84" t="s">
-        <v>19</v>
+        <v>93</v>
       </c>
       <c r="E84">
-        <v>155990</v>
+        <v>39990</v>
       </c>
       <c r="F84">
         <v>1</v>
       </c>
       <c r="G84" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="H84" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="I84">
         <v>0</v>
@@ -4183,33 +4155,33 @@
         <v>0</v>
       </c>
       <c r="K84" t="s">
-        <v>21</v>
+        <v>137</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B85" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C85" t="s">
-        <v>18</v>
+        <v>122</v>
       </c>
       <c r="D85" t="s">
-        <v>48</v>
+        <v>144</v>
       </c>
       <c r="E85">
-        <v>269990</v>
+        <v>140990</v>
       </c>
       <c r="F85">
         <v>1</v>
       </c>
       <c r="G85" t="s">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="H85" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="I85">
         <v>0</v>
@@ -4218,33 +4190,33 @@
         <v>0</v>
       </c>
       <c r="K85" t="s">
-        <v>147</v>
+        <v>91</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
+        <v>142</v>
+      </c>
+      <c r="B86" t="s">
+        <v>143</v>
+      </c>
+      <c r="C86" t="s">
+        <v>122</v>
+      </c>
+      <c r="D86" t="s">
         <v>145</v>
       </c>
-      <c r="B86" t="s">
-        <v>146</v>
-      </c>
-      <c r="C86" t="s">
-        <v>18</v>
-      </c>
-      <c r="D86" t="s">
-        <v>29</v>
-      </c>
       <c r="E86">
-        <v>269990</v>
+        <v>145990</v>
       </c>
       <c r="F86">
         <v>1</v>
       </c>
       <c r="G86" t="s">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="H86" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="I86">
         <v>0</v>
@@ -4253,33 +4225,33 @@
         <v>0</v>
       </c>
       <c r="K86" t="s">
-        <v>147</v>
+        <v>91</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B87" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C87" t="s">
         <v>18</v>
       </c>
       <c r="D87" t="s">
-        <v>25</v>
-      </c>
-      <c r="E87">
-        <v>269990</v>
+        <v>55</v>
+      </c>
+      <c r="E87" s="4">
+        <v>199990</v>
       </c>
       <c r="F87">
         <v>1</v>
       </c>
       <c r="G87" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="H87" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="I87">
         <v>0</v>
@@ -4288,33 +4260,33 @@
         <v>0</v>
       </c>
       <c r="K87" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B88" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C88" t="s">
         <v>18</v>
       </c>
       <c r="D88" t="s">
-        <v>19</v>
-      </c>
-      <c r="E88">
-        <v>269990</v>
+        <v>36</v>
+      </c>
+      <c r="E88" s="4">
+        <v>199990</v>
       </c>
       <c r="F88">
         <v>1</v>
       </c>
       <c r="G88" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="H88" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="I88">
         <v>0</v>
@@ -4323,33 +4295,33 @@
         <v>0</v>
       </c>
       <c r="K88" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B89" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C89" t="s">
         <v>18</v>
       </c>
       <c r="D89" t="s">
-        <v>127</v>
-      </c>
-      <c r="E89">
-        <v>269990</v>
+        <v>32</v>
+      </c>
+      <c r="E89" s="4">
+        <v>199990</v>
       </c>
       <c r="F89">
         <v>1</v>
       </c>
       <c r="G89" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="H89" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="I89">
         <v>0</v>
@@ -4358,33 +4330,33 @@
         <v>0</v>
       </c>
       <c r="K89" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B90" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C90" t="s">
         <v>18</v>
       </c>
       <c r="D90" t="s">
-        <v>29</v>
-      </c>
-      <c r="E90">
+        <v>19</v>
+      </c>
+      <c r="E90" s="4">
         <v>199990</v>
       </c>
       <c r="F90">
         <v>1</v>
       </c>
       <c r="G90" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="H90" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="I90">
         <v>0</v>
@@ -4393,33 +4365,33 @@
         <v>0</v>
       </c>
       <c r="K90" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B91" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C91" t="s">
         <v>18</v>
       </c>
       <c r="D91" t="s">
-        <v>25</v>
-      </c>
-      <c r="E91">
+        <v>132</v>
+      </c>
+      <c r="E91" s="4">
         <v>199990</v>
       </c>
       <c r="F91">
         <v>1</v>
       </c>
       <c r="G91" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="H91" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="I91">
         <v>0</v>
@@ -4428,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="K91" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="92">
@@ -4439,22 +4411,22 @@
         <v>149</v>
       </c>
       <c r="C92" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D92" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E92">
-        <v>199990</v>
+        <v>155990</v>
       </c>
       <c r="F92">
         <v>1</v>
       </c>
       <c r="G92" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="H92" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="I92">
         <v>0</v>
@@ -4463,7 +4435,7 @@
         <v>0</v>
       </c>
       <c r="K92" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
     </row>
     <row r="93">
@@ -4474,22 +4446,22 @@
         <v>149</v>
       </c>
       <c r="C93" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D93" t="s">
-        <v>127</v>
+        <v>36</v>
       </c>
       <c r="E93">
-        <v>199990</v>
+        <v>155990</v>
       </c>
       <c r="F93">
         <v>1</v>
       </c>
       <c r="G93" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="H93" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="I93">
         <v>0</v>
@@ -4498,33 +4470,33 @@
         <v>0</v>
       </c>
       <c r="K93" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B94" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C94" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D94" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="E94">
-        <v>194990</v>
+        <v>155990</v>
       </c>
       <c r="F94">
         <v>1</v>
       </c>
       <c r="G94" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="H94" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="I94">
         <v>0</v>
@@ -4538,28 +4510,28 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B95" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C95" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D95" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E95">
-        <v>194990</v>
+        <v>155990</v>
       </c>
       <c r="F95">
         <v>1</v>
       </c>
       <c r="G95" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="H95" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="I95">
         <v>0</v>
@@ -4579,22 +4551,22 @@
         <v>151</v>
       </c>
       <c r="C96" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D96" t="s">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="E96">
-        <v>194990</v>
+        <v>269990</v>
       </c>
       <c r="F96">
         <v>1</v>
       </c>
       <c r="G96" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="H96" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="I96">
         <v>0</v>
@@ -4603,7 +4575,7 @@
         <v>0</v>
       </c>
       <c r="K96" t="s">
-        <v>21</v>
+        <v>152</v>
       </c>
     </row>
     <row r="97">
@@ -4614,22 +4586,22 @@
         <v>151</v>
       </c>
       <c r="C97" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D97" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="E97">
-        <v>194990</v>
+        <v>269990</v>
       </c>
       <c r="F97">
         <v>1</v>
       </c>
       <c r="G97" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="H97" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="I97">
         <v>0</v>
@@ -4638,68 +4610,68 @@
         <v>0</v>
       </c>
       <c r="K97" t="s">
-        <v>21</v>
+        <v>152</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
+        <v>150</v>
+      </c>
+      <c r="B98" t="s">
+        <v>151</v>
+      </c>
+      <c r="C98" t="s">
+        <v>18</v>
+      </c>
+      <c r="D98" t="s">
+        <v>32</v>
+      </c>
+      <c r="E98">
+        <v>269990</v>
+      </c>
+      <c r="F98">
+        <v>1</v>
+      </c>
+      <c r="G98" t="s">
+        <v>25</v>
+      </c>
+      <c r="H98" t="s">
+        <v>25</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>0</v>
+      </c>
+      <c r="K98" t="s">
         <v>152</v>
-      </c>
-      <c r="B98" t="s">
-        <v>153</v>
-      </c>
-      <c r="C98" t="s">
-        <v>18</v>
-      </c>
-      <c r="D98" t="s">
-        <v>48</v>
-      </c>
-      <c r="E98">
-        <v>202990</v>
-      </c>
-      <c r="F98">
-        <v>1</v>
-      </c>
-      <c r="G98" t="s">
-        <v>20</v>
-      </c>
-      <c r="H98" t="s">
-        <v>20</v>
-      </c>
-      <c r="I98">
-        <v>0</v>
-      </c>
-      <c r="J98">
-        <v>0</v>
-      </c>
-      <c r="K98" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B99" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C99" t="s">
         <v>18</v>
       </c>
       <c r="D99" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="E99">
-        <v>151990</v>
+        <v>269990</v>
       </c>
       <c r="F99">
         <v>1</v>
       </c>
       <c r="G99" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="H99" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="I99">
         <v>0</v>
@@ -4708,33 +4680,33 @@
         <v>0</v>
       </c>
       <c r="K99" t="s">
-        <v>53</v>
+        <v>152</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B100" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C100" t="s">
         <v>18</v>
       </c>
       <c r="D100" t="s">
-        <v>29</v>
+        <v>132</v>
       </c>
       <c r="E100">
-        <v>151990</v>
+        <v>269990</v>
       </c>
       <c r="F100">
         <v>1</v>
       </c>
       <c r="G100" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="H100" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="I100">
         <v>0</v>
@@ -4743,33 +4715,33 @@
         <v>0</v>
       </c>
       <c r="K100" t="s">
-        <v>53</v>
+        <v>152</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
+        <v>153</v>
+      </c>
+      <c r="B101" t="s">
         <v>154</v>
       </c>
-      <c r="B101" t="s">
-        <v>155</v>
-      </c>
       <c r="C101" t="s">
         <v>18</v>
       </c>
       <c r="D101" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="E101">
-        <v>151990</v>
+        <v>199990</v>
       </c>
       <c r="F101">
         <v>1</v>
       </c>
       <c r="G101" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="H101" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="I101">
         <v>0</v>
@@ -4778,33 +4750,33 @@
         <v>0</v>
       </c>
       <c r="K101" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
+        <v>153</v>
+      </c>
+      <c r="B102" t="s">
         <v>154</v>
       </c>
-      <c r="B102" t="s">
-        <v>155</v>
-      </c>
       <c r="C102" t="s">
         <v>18</v>
       </c>
       <c r="D102" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E102">
-        <v>151990</v>
+        <v>199990</v>
       </c>
       <c r="F102">
         <v>1</v>
       </c>
       <c r="G102" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="H102" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="I102">
         <v>0</v>
@@ -4813,33 +4785,33 @@
         <v>0</v>
       </c>
       <c r="K102" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
+        <v>153</v>
+      </c>
+      <c r="B103" t="s">
         <v>154</v>
       </c>
-      <c r="B103" t="s">
-        <v>155</v>
-      </c>
       <c r="C103" t="s">
         <v>18</v>
       </c>
       <c r="D103" t="s">
-        <v>127</v>
+        <v>19</v>
       </c>
       <c r="E103">
-        <v>151990</v>
+        <v>199990</v>
       </c>
       <c r="F103">
         <v>1</v>
       </c>
       <c r="G103" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="H103" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="I103">
         <v>0</v>
@@ -4848,33 +4820,33 @@
         <v>0</v>
       </c>
       <c r="K103" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B104" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C104" t="s">
         <v>18</v>
       </c>
       <c r="D104" t="s">
-        <v>48</v>
+        <v>132</v>
       </c>
       <c r="E104">
-        <v>151990</v>
+        <v>199990</v>
       </c>
       <c r="F104">
         <v>1</v>
       </c>
       <c r="G104" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="H104" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="I104">
         <v>0</v>
@@ -4883,33 +4855,33 @@
         <v>0</v>
       </c>
       <c r="K104" t="s">
-        <v>85</v>
+        <v>40</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
+        <v>155</v>
+      </c>
+      <c r="B105" t="s">
         <v>156</v>
       </c>
-      <c r="B105" t="s">
-        <v>157</v>
-      </c>
       <c r="C105" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D105" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="E105">
-        <v>151990</v>
+        <v>194990</v>
       </c>
       <c r="F105">
         <v>1</v>
       </c>
       <c r="G105" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="H105" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="I105">
         <v>0</v>
@@ -4918,33 +4890,33 @@
         <v>0</v>
       </c>
       <c r="K105" t="s">
-        <v>85</v>
+        <v>21</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
+        <v>155</v>
+      </c>
+      <c r="B106" t="s">
         <v>156</v>
       </c>
-      <c r="B106" t="s">
-        <v>157</v>
-      </c>
       <c r="C106" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D106" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="E106">
-        <v>151990</v>
+        <v>194990</v>
       </c>
       <c r="F106">
         <v>1</v>
       </c>
       <c r="G106" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="H106" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="I106">
         <v>0</v>
@@ -4953,33 +4925,33 @@
         <v>0</v>
       </c>
       <c r="K106" t="s">
-        <v>85</v>
+        <v>21</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
+        <v>155</v>
+      </c>
+      <c r="B107" t="s">
         <v>156</v>
       </c>
-      <c r="B107" t="s">
-        <v>157</v>
-      </c>
       <c r="C107" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D107" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E107">
-        <v>151990</v>
+        <v>194990</v>
       </c>
       <c r="F107">
         <v>1</v>
       </c>
       <c r="G107" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="H107" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="I107">
         <v>0</v>
@@ -4988,33 +4960,33 @@
         <v>0</v>
       </c>
       <c r="K107" t="s">
-        <v>85</v>
+        <v>21</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
+        <v>155</v>
+      </c>
+      <c r="B108" t="s">
         <v>156</v>
       </c>
-      <c r="B108" t="s">
-        <v>157</v>
-      </c>
       <c r="C108" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D108" t="s">
-        <v>127</v>
+        <v>19</v>
       </c>
       <c r="E108">
-        <v>151990</v>
+        <v>194990</v>
       </c>
       <c r="F108">
         <v>1</v>
       </c>
       <c r="G108" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="H108" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="I108">
         <v>0</v>
@@ -5023,24 +4995,24 @@
         <v>0</v>
       </c>
       <c r="K108" t="s">
-        <v>85</v>
+        <v>21</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
+        <v>157</v>
+      </c>
+      <c r="B109" t="s">
         <v>158</v>
       </c>
-      <c r="B109" t="s">
-        <v>159</v>
-      </c>
       <c r="C109" t="s">
         <v>18</v>
       </c>
       <c r="D109" t="s">
-        <v>102</v>
+        <v>55</v>
       </c>
       <c r="E109">
-        <v>119990</v>
+        <v>202990</v>
       </c>
       <c r="F109">
         <v>1</v>
@@ -5058,33 +5030,33 @@
         <v>0</v>
       </c>
       <c r="K109" t="s">
-        <v>21</v>
+        <v>116</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B110" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C110" t="s">
         <v>18</v>
       </c>
       <c r="D110" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="E110">
-        <v>210990</v>
+        <v>151990</v>
       </c>
       <c r="F110">
         <v>1</v>
       </c>
       <c r="G110" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H110" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I110">
         <v>0</v>
@@ -5093,33 +5065,33 @@
         <v>0</v>
       </c>
       <c r="K110" t="s">
-        <v>21</v>
+        <v>60</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B111" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C111" t="s">
         <v>18</v>
       </c>
       <c r="D111" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="E111">
-        <v>210990</v>
+        <v>151990</v>
       </c>
       <c r="F111">
         <v>1</v>
       </c>
       <c r="G111" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H111" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I111">
         <v>0</v>
@@ -5128,33 +5100,33 @@
         <v>0</v>
       </c>
       <c r="K111" t="s">
-        <v>21</v>
+        <v>60</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B112" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C112" t="s">
         <v>18</v>
       </c>
       <c r="D112" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E112">
-        <v>210990</v>
+        <v>151990</v>
       </c>
       <c r="F112">
         <v>1</v>
       </c>
       <c r="G112" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H112" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I112">
         <v>0</v>
@@ -5163,33 +5135,33 @@
         <v>0</v>
       </c>
       <c r="K112" t="s">
-        <v>21</v>
+        <v>60</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
+        <v>159</v>
+      </c>
+      <c r="B113" t="s">
         <v>160</v>
       </c>
-      <c r="B113" t="s">
-        <v>161</v>
-      </c>
       <c r="C113" t="s">
         <v>18</v>
       </c>
       <c r="D113" t="s">
-        <v>102</v>
+        <v>19</v>
       </c>
       <c r="E113">
-        <v>108990</v>
+        <v>151990</v>
       </c>
       <c r="F113">
         <v>1</v>
       </c>
       <c r="G113" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H113" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I113">
         <v>0</v>
@@ -5198,33 +5170,33 @@
         <v>0</v>
       </c>
       <c r="K113" t="s">
-        <v>162</v>
+        <v>60</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
+        <v>159</v>
+      </c>
+      <c r="B114" t="s">
         <v>160</v>
       </c>
-      <c r="B114" t="s">
-        <v>161</v>
-      </c>
       <c r="C114" t="s">
         <v>18</v>
       </c>
       <c r="D114" t="s">
-        <v>48</v>
+        <v>132</v>
       </c>
       <c r="E114">
-        <v>114990</v>
+        <v>151990</v>
       </c>
       <c r="F114">
         <v>1</v>
       </c>
       <c r="G114" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H114" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I114">
         <v>0</v>
@@ -5233,33 +5205,33 @@
         <v>0</v>
       </c>
       <c r="K114" t="s">
-        <v>162</v>
+        <v>60</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B115" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C115" t="s">
         <v>18</v>
       </c>
       <c r="D115" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="E115">
-        <v>124990</v>
+        <v>151990</v>
       </c>
       <c r="F115">
         <v>1</v>
       </c>
       <c r="G115" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H115" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I115">
         <v>0</v>
@@ -5268,33 +5240,33 @@
         <v>0</v>
       </c>
       <c r="K115" t="s">
-        <v>162</v>
+        <v>91</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B116" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C116" t="s">
         <v>18</v>
       </c>
       <c r="D116" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="E116">
-        <v>183990</v>
+        <v>151990</v>
       </c>
       <c r="F116">
         <v>1</v>
       </c>
       <c r="G116" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H116" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I116">
         <v>0</v>
@@ -5303,33 +5275,33 @@
         <v>0</v>
       </c>
       <c r="K116" t="s">
-        <v>162</v>
+        <v>91</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B117" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C117" t="s">
         <v>18</v>
       </c>
       <c r="D117" t="s">
-        <v>127</v>
+        <v>32</v>
       </c>
       <c r="E117">
-        <v>140990</v>
+        <v>151990</v>
       </c>
       <c r="F117">
         <v>1</v>
       </c>
       <c r="G117" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H117" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I117">
         <v>0</v>
@@ -5338,33 +5310,33 @@
         <v>0</v>
       </c>
       <c r="K117" t="s">
-        <v>162</v>
+        <v>91</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B118" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C118" t="s">
         <v>18</v>
       </c>
       <c r="D118" t="s">
-        <v>102</v>
+        <v>19</v>
       </c>
       <c r="E118">
-        <v>140990</v>
+        <v>151990</v>
       </c>
       <c r="F118">
         <v>1</v>
       </c>
       <c r="G118" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H118" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I118">
         <v>0</v>
@@ -5373,33 +5345,33 @@
         <v>0</v>
       </c>
       <c r="K118" t="s">
-        <v>162</v>
+        <v>91</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B119" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C119" t="s">
         <v>18</v>
       </c>
       <c r="D119" t="s">
-        <v>48</v>
+        <v>132</v>
       </c>
       <c r="E119">
-        <v>140990</v>
+        <v>151990</v>
       </c>
       <c r="F119">
         <v>1</v>
       </c>
       <c r="G119" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H119" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I119">
         <v>0</v>
@@ -5408,7 +5380,7 @@
         <v>0</v>
       </c>
       <c r="K119" t="s">
-        <v>162</v>
+        <v>91</v>
       </c>
     </row>
     <row r="120">
@@ -5422,10 +5394,10 @@
         <v>18</v>
       </c>
       <c r="D120" t="s">
-        <v>29</v>
+        <v>107</v>
       </c>
       <c r="E120">
-        <v>140990</v>
+        <v>119990</v>
       </c>
       <c r="F120">
         <v>1</v>
@@ -5443,7 +5415,7 @@
         <v>0</v>
       </c>
       <c r="K120" t="s">
-        <v>162</v>
+        <v>21</v>
       </c>
     </row>
     <row r="121">
@@ -5457,10 +5429,10 @@
         <v>18</v>
       </c>
       <c r="D121" t="s">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="E121">
-        <v>140990</v>
+        <v>210990</v>
       </c>
       <c r="F121">
         <v>1</v>
@@ -5478,7 +5450,7 @@
         <v>0</v>
       </c>
       <c r="K121" t="s">
-        <v>162</v>
+        <v>21</v>
       </c>
     </row>
     <row r="122">
@@ -5492,10 +5464,10 @@
         <v>18</v>
       </c>
       <c r="D122" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="E122">
-        <v>140990</v>
+        <v>210990</v>
       </c>
       <c r="F122">
         <v>1</v>
@@ -5513,7 +5485,7 @@
         <v>0</v>
       </c>
       <c r="K122" t="s">
-        <v>162</v>
+        <v>21</v>
       </c>
     </row>
     <row r="123">
@@ -5527,10 +5499,10 @@
         <v>18</v>
       </c>
       <c r="D123" t="s">
-        <v>127</v>
+        <v>19</v>
       </c>
       <c r="E123">
-        <v>140990</v>
+        <v>210990</v>
       </c>
       <c r="F123">
         <v>1</v>
@@ -5548,7 +5520,7 @@
         <v>0</v>
       </c>
       <c r="K123" t="s">
-        <v>162</v>
+        <v>21</v>
       </c>
     </row>
     <row r="124">
@@ -5562,10 +5534,10 @@
         <v>18</v>
       </c>
       <c r="D124" t="s">
-        <v>48</v>
+        <v>107</v>
       </c>
       <c r="E124">
-        <v>92990</v>
+        <v>108990</v>
       </c>
       <c r="F124">
         <v>1</v>
@@ -5583,7 +5555,7 @@
         <v>0</v>
       </c>
       <c r="K124" t="s">
-        <v>53</v>
+        <v>167</v>
       </c>
     </row>
     <row r="125">
@@ -5597,10 +5569,10 @@
         <v>18</v>
       </c>
       <c r="D125" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="E125">
-        <v>92990</v>
+        <v>114990</v>
       </c>
       <c r="F125">
         <v>1</v>
@@ -5618,7 +5590,7 @@
         <v>0</v>
       </c>
       <c r="K125" t="s">
-        <v>53</v>
+        <v>167</v>
       </c>
     </row>
     <row r="126">
@@ -5632,10 +5604,10 @@
         <v>18</v>
       </c>
       <c r="D126" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="E126">
-        <v>92990</v>
+        <v>124990</v>
       </c>
       <c r="F126">
         <v>1</v>
@@ -5653,7 +5625,7 @@
         <v>0</v>
       </c>
       <c r="K126" t="s">
-        <v>53</v>
+        <v>167</v>
       </c>
     </row>
     <row r="127">
@@ -5670,7 +5642,7 @@
         <v>19</v>
       </c>
       <c r="E127">
-        <v>92990</v>
+        <v>183990</v>
       </c>
       <c r="F127">
         <v>1</v>
@@ -5688,7 +5660,7 @@
         <v>0</v>
       </c>
       <c r="K127" t="s">
-        <v>53</v>
+        <v>167</v>
       </c>
     </row>
     <row r="128">
@@ -5702,10 +5674,10 @@
         <v>18</v>
       </c>
       <c r="D128" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="E128">
-        <v>92990</v>
+        <v>140990</v>
       </c>
       <c r="F128">
         <v>1</v>
@@ -5723,138 +5695,138 @@
         <v>0</v>
       </c>
       <c r="K128" t="s">
-        <v>53</v>
+        <v>167</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
+        <v>168</v>
+      </c>
+      <c r="B129" t="s">
+        <v>169</v>
+      </c>
+      <c r="C129" t="s">
+        <v>18</v>
+      </c>
+      <c r="D129" t="s">
+        <v>107</v>
+      </c>
+      <c r="E129">
+        <v>140990</v>
+      </c>
+      <c r="F129">
+        <v>1</v>
+      </c>
+      <c r="G129" t="s">
+        <v>20</v>
+      </c>
+      <c r="H129" t="s">
+        <v>20</v>
+      </c>
+      <c r="I129">
+        <v>0</v>
+      </c>
+      <c r="J129">
+        <v>0</v>
+      </c>
+      <c r="K129" t="s">
         <v>167</v>
-      </c>
-      <c r="B129" t="s">
-        <v>168</v>
-      </c>
-      <c r="C129" t="s">
-        <v>18</v>
-      </c>
-      <c r="D129" t="s">
-        <v>29</v>
-      </c>
-      <c r="E129">
-        <v>108990</v>
-      </c>
-      <c r="F129">
-        <v>1</v>
-      </c>
-      <c r="G129" t="s">
-        <v>20</v>
-      </c>
-      <c r="H129" t="s">
-        <v>20</v>
-      </c>
-      <c r="I129">
-        <v>0</v>
-      </c>
-      <c r="J129">
-        <v>0</v>
-      </c>
-      <c r="K129" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
+        <v>168</v>
+      </c>
+      <c r="B130" t="s">
+        <v>169</v>
+      </c>
+      <c r="C130" t="s">
+        <v>18</v>
+      </c>
+      <c r="D130" t="s">
+        <v>55</v>
+      </c>
+      <c r="E130">
+        <v>140990</v>
+      </c>
+      <c r="F130">
+        <v>1</v>
+      </c>
+      <c r="G130" t="s">
+        <v>20</v>
+      </c>
+      <c r="H130" t="s">
+        <v>20</v>
+      </c>
+      <c r="I130">
+        <v>0</v>
+      </c>
+      <c r="J130">
+        <v>0</v>
+      </c>
+      <c r="K130" t="s">
         <v>167</v>
-      </c>
-      <c r="B130" t="s">
-        <v>168</v>
-      </c>
-      <c r="C130" t="s">
-        <v>18</v>
-      </c>
-      <c r="D130" t="s">
-        <v>25</v>
-      </c>
-      <c r="E130">
-        <v>108990</v>
-      </c>
-      <c r="F130">
-        <v>1</v>
-      </c>
-      <c r="G130" t="s">
-        <v>20</v>
-      </c>
-      <c r="H130" t="s">
-        <v>20</v>
-      </c>
-      <c r="I130">
-        <v>0</v>
-      </c>
-      <c r="J130">
-        <v>0</v>
-      </c>
-      <c r="K130" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
+        <v>168</v>
+      </c>
+      <c r="B131" t="s">
+        <v>169</v>
+      </c>
+      <c r="C131" t="s">
+        <v>18</v>
+      </c>
+      <c r="D131" t="s">
+        <v>36</v>
+      </c>
+      <c r="E131">
+        <v>140990</v>
+      </c>
+      <c r="F131">
+        <v>1</v>
+      </c>
+      <c r="G131" t="s">
+        <v>20</v>
+      </c>
+      <c r="H131" t="s">
+        <v>20</v>
+      </c>
+      <c r="I131">
+        <v>0</v>
+      </c>
+      <c r="J131">
+        <v>0</v>
+      </c>
+      <c r="K131" t="s">
         <v>167</v>
-      </c>
-      <c r="B131" t="s">
-        <v>168</v>
-      </c>
-      <c r="C131" t="s">
-        <v>18</v>
-      </c>
-      <c r="D131" t="s">
-        <v>19</v>
-      </c>
-      <c r="E131">
-        <v>108990</v>
-      </c>
-      <c r="F131">
-        <v>1</v>
-      </c>
-      <c r="G131" t="s">
-        <v>20</v>
-      </c>
-      <c r="H131" t="s">
-        <v>20</v>
-      </c>
-      <c r="I131">
-        <v>0</v>
-      </c>
-      <c r="J131">
-        <v>0</v>
-      </c>
-      <c r="K131" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
+        <v>168</v>
+      </c>
+      <c r="B132" t="s">
         <v>169</v>
       </c>
-      <c r="B132" t="s">
-        <v>170</v>
-      </c>
       <c r="C132" t="s">
         <v>18</v>
       </c>
       <c r="D132" t="s">
-        <v>171</v>
+        <v>32</v>
       </c>
       <c r="E132">
-        <v>81990</v>
+        <v>140990</v>
       </c>
       <c r="F132">
         <v>1</v>
       </c>
       <c r="G132" t="s">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="H132" t="s">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="I132">
         <v>0</v>
@@ -5863,33 +5835,33 @@
         <v>0</v>
       </c>
       <c r="K132" t="s">
-        <v>111</v>
+        <v>167</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s">
+        <v>168</v>
+      </c>
+      <c r="B133" t="s">
         <v>169</v>
       </c>
-      <c r="B133" t="s">
-        <v>170</v>
-      </c>
       <c r="C133" t="s">
         <v>18</v>
       </c>
       <c r="D133" t="s">
-        <v>172</v>
+        <v>19</v>
       </c>
       <c r="E133">
-        <v>81990</v>
+        <v>140990</v>
       </c>
       <c r="F133">
         <v>1</v>
       </c>
       <c r="G133" t="s">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="H133" t="s">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="I133">
         <v>0</v>
@@ -5898,33 +5870,33 @@
         <v>0</v>
       </c>
       <c r="K133" t="s">
-        <v>111</v>
+        <v>167</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="B134" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="C134" t="s">
         <v>18</v>
       </c>
       <c r="D134" t="s">
-        <v>48</v>
+        <v>132</v>
       </c>
       <c r="E134">
-        <v>125990</v>
+        <v>140990</v>
       </c>
       <c r="F134">
         <v>1</v>
       </c>
       <c r="G134" t="s">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="H134" t="s">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="I134">
         <v>0</v>
@@ -5933,33 +5905,33 @@
         <v>0</v>
       </c>
       <c r="K134" t="s">
-        <v>21</v>
+        <v>167</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B135" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C135" t="s">
         <v>18</v>
       </c>
       <c r="D135" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="E135">
-        <v>125990</v>
+        <v>92990</v>
       </c>
       <c r="F135">
         <v>1</v>
       </c>
       <c r="G135" t="s">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="H135" t="s">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="I135">
         <v>0</v>
@@ -5968,24 +5940,24 @@
         <v>0</v>
       </c>
       <c r="K135" t="s">
-        <v>21</v>
+        <v>60</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="B136" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="C136" t="s">
         <v>18</v>
       </c>
       <c r="D136" t="s">
-        <v>177</v>
+        <v>36</v>
       </c>
       <c r="E136">
-        <v>125990</v>
+        <v>92990</v>
       </c>
       <c r="F136">
         <v>1</v>
@@ -5994,7 +5966,7 @@
         <v>20</v>
       </c>
       <c r="H136" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
       <c r="I136">
         <v>0</v>
@@ -6003,24 +5975,24 @@
         <v>0</v>
       </c>
       <c r="K136" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="B137" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="C137" t="s">
         <v>18</v>
       </c>
-      <c r="D137">
-        <v>38</v>
+      <c r="D137" t="s">
+        <v>32</v>
       </c>
       <c r="E137">
-        <v>125990</v>
+        <v>92990</v>
       </c>
       <c r="F137">
         <v>1</v>
@@ -6029,7 +6001,7 @@
         <v>20</v>
       </c>
       <c r="H137" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
       <c r="I137">
         <v>0</v>
@@ -6038,24 +6010,24 @@
         <v>0</v>
       </c>
       <c r="K137" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="B138" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="C138" t="s">
         <v>18</v>
       </c>
-      <c r="D138">
-        <v>39</v>
+      <c r="D138" t="s">
+        <v>19</v>
       </c>
       <c r="E138">
-        <v>125990</v>
+        <v>92990</v>
       </c>
       <c r="F138">
         <v>1</v>
@@ -6064,7 +6036,7 @@
         <v>20</v>
       </c>
       <c r="H138" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
       <c r="I138">
         <v>0</v>
@@ -6073,24 +6045,24 @@
         <v>0</v>
       </c>
       <c r="K138" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="B139" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="C139" t="s">
         <v>18</v>
       </c>
-      <c r="D139">
-        <v>42</v>
+      <c r="D139" t="s">
+        <v>132</v>
       </c>
       <c r="E139">
-        <v>125990</v>
+        <v>92990</v>
       </c>
       <c r="F139">
         <v>1</v>
@@ -6099,7 +6071,7 @@
         <v>20</v>
       </c>
       <c r="H139" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
       <c r="I139">
         <v>0</v>
@@ -6108,33 +6080,33 @@
         <v>0</v>
       </c>
       <c r="K139" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="B140" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C140" t="s">
         <v>18</v>
       </c>
       <c r="D140" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="E140">
-        <v>145990</v>
+        <v>108990</v>
       </c>
       <c r="F140">
         <v>1</v>
       </c>
       <c r="G140" t="s">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="H140" t="s">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="I140">
         <v>0</v>
@@ -6143,33 +6115,33 @@
         <v>0</v>
       </c>
       <c r="K140" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="B141" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C141" t="s">
         <v>18</v>
       </c>
       <c r="D141" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E141">
-        <v>145990</v>
+        <v>108990</v>
       </c>
       <c r="F141">
         <v>1</v>
       </c>
       <c r="G141" t="s">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="H141" t="s">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="I141">
         <v>0</v>
@@ -6178,15 +6150,15 @@
         <v>0</v>
       </c>
       <c r="K141" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="B142" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C142" t="s">
         <v>18</v>
@@ -6195,16 +6167,16 @@
         <v>19</v>
       </c>
       <c r="E142">
-        <v>145990</v>
+        <v>108990</v>
       </c>
       <c r="F142">
         <v>1</v>
       </c>
       <c r="G142" t="s">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="H142" t="s">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="I142">
         <v>0</v>
@@ -6213,33 +6185,33 @@
         <v>0</v>
       </c>
       <c r="K142" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B143" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C143" t="s">
         <v>18</v>
       </c>
       <c r="D143" t="s">
-        <v>127</v>
+        <v>176</v>
       </c>
       <c r="E143">
-        <v>145990</v>
+        <v>81990</v>
       </c>
       <c r="F143">
         <v>1</v>
       </c>
       <c r="G143" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H143" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I143">
         <v>0</v>
@@ -6248,33 +6220,33 @@
         <v>0</v>
       </c>
       <c r="K143" t="s">
-        <v>21</v>
+        <v>116</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="B144" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="C144" t="s">
         <v>18</v>
       </c>
       <c r="D144" t="s">
-        <v>48</v>
+        <v>177</v>
       </c>
       <c r="E144">
-        <v>199990</v>
+        <v>81990</v>
       </c>
       <c r="F144">
         <v>1</v>
       </c>
       <c r="G144" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H144" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I144">
         <v>0</v>
@@ -6283,33 +6255,33 @@
         <v>0</v>
       </c>
       <c r="K144" t="s">
-        <v>21</v>
+        <v>116</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B145" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C145" t="s">
         <v>18</v>
       </c>
       <c r="D145" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="E145">
-        <v>199990</v>
+        <v>125990</v>
       </c>
       <c r="F145">
         <v>1</v>
       </c>
       <c r="G145" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="H145" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="I145">
         <v>0</v>
@@ -6323,28 +6295,28 @@
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B146" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C146" t="s">
         <v>18</v>
       </c>
       <c r="D146" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="E146">
-        <v>199990</v>
+        <v>125990</v>
       </c>
       <c r="F146">
         <v>1</v>
       </c>
       <c r="G146" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="H146" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="I146">
         <v>0</v>
@@ -6367,19 +6339,19 @@
         <v>18</v>
       </c>
       <c r="D147" t="s">
-        <v>19</v>
+        <v>182</v>
       </c>
       <c r="E147">
-        <v>199990</v>
+        <v>125990</v>
       </c>
       <c r="F147">
         <v>1</v>
       </c>
       <c r="G147" t="s">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="H147" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="I147">
         <v>0</v>
@@ -6388,7 +6360,7 @@
         <v>0</v>
       </c>
       <c r="K147" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
     </row>
     <row r="148">
@@ -6401,20 +6373,20 @@
       <c r="C148" t="s">
         <v>18</v>
       </c>
-      <c r="D148" t="s">
-        <v>127</v>
+      <c r="D148">
+        <v>38</v>
       </c>
       <c r="E148">
-        <v>199990</v>
+        <v>125990</v>
       </c>
       <c r="F148">
         <v>1</v>
       </c>
       <c r="G148" t="s">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="H148" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="I148">
         <v>0</v>
@@ -6423,33 +6395,33 @@
         <v>0</v>
       </c>
       <c r="K148" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B149" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C149" t="s">
         <v>18</v>
       </c>
-      <c r="D149" t="s">
-        <v>127</v>
+      <c r="D149">
+        <v>39</v>
       </c>
       <c r="E149">
-        <v>159990</v>
+        <v>125990</v>
       </c>
       <c r="F149">
         <v>1</v>
       </c>
       <c r="G149" t="s">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="H149" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="I149">
         <v>0</v>
@@ -6458,33 +6430,33 @@
         <v>0</v>
       </c>
       <c r="K149" t="s">
-        <v>184</v>
+        <v>45</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B150" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C150" t="s">
         <v>18</v>
       </c>
-      <c r="D150" t="s">
-        <v>25</v>
+      <c r="D150">
+        <v>42</v>
       </c>
       <c r="E150">
-        <v>199990</v>
+        <v>125990</v>
       </c>
       <c r="F150">
         <v>1</v>
       </c>
       <c r="G150" t="s">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="H150" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="I150">
         <v>0</v>
@@ -6493,33 +6465,33 @@
         <v>0</v>
       </c>
       <c r="K150" t="s">
-        <v>184</v>
+        <v>45</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B151" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C151" t="s">
         <v>18</v>
       </c>
       <c r="D151" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="E151">
-        <v>199990</v>
+        <v>145990</v>
       </c>
       <c r="F151">
         <v>1</v>
       </c>
       <c r="G151" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="H151" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="I151">
         <v>0</v>
@@ -6528,33 +6500,33 @@
         <v>0</v>
       </c>
       <c r="K151" t="s">
-        <v>184</v>
+        <v>21</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B152" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C152" t="s">
         <v>18</v>
       </c>
       <c r="D152" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E152">
-        <v>109990</v>
+        <v>145990</v>
       </c>
       <c r="F152">
         <v>1</v>
       </c>
       <c r="G152" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H152" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I152">
         <v>0</v>
@@ -6563,33 +6535,33 @@
         <v>0</v>
       </c>
       <c r="K152" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B153" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C153" t="s">
         <v>18</v>
       </c>
       <c r="D153" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E153">
-        <v>109990</v>
+        <v>145990</v>
       </c>
       <c r="F153">
         <v>1</v>
       </c>
       <c r="G153" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H153" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I153">
         <v>0</v>
@@ -6598,33 +6570,33 @@
         <v>0</v>
       </c>
       <c r="K153" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B154" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C154" t="s">
         <v>18</v>
       </c>
       <c r="D154" t="s">
-        <v>19</v>
+        <v>132</v>
       </c>
       <c r="E154">
-        <v>109990</v>
+        <v>145990</v>
       </c>
       <c r="F154">
         <v>1</v>
       </c>
       <c r="G154" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H154" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I154">
         <v>0</v>
@@ -6633,33 +6605,33 @@
         <v>0</v>
       </c>
       <c r="K154" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B155" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C155" t="s">
         <v>18</v>
       </c>
       <c r="D155" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E155">
-        <v>115990</v>
+        <v>199990</v>
       </c>
       <c r="F155">
         <v>1</v>
       </c>
       <c r="G155" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H155" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I155">
         <v>0</v>
@@ -6668,33 +6640,33 @@
         <v>0</v>
       </c>
       <c r="K155" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B156" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C156" t="s">
         <v>18</v>
       </c>
       <c r="D156" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="E156">
-        <v>119990</v>
+        <v>199990</v>
       </c>
       <c r="F156">
         <v>1</v>
       </c>
       <c r="G156" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H156" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I156">
         <v>0</v>
@@ -6703,33 +6675,33 @@
         <v>0</v>
       </c>
       <c r="K156" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B157" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C157" t="s">
-        <v>191</v>
+        <v>18</v>
       </c>
       <c r="D157" t="s">
-        <v>69</v>
+        <v>32</v>
       </c>
       <c r="E157">
-        <v>85990</v>
+        <v>199990</v>
       </c>
       <c r="F157">
         <v>1</v>
       </c>
       <c r="G157" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="H157" t="s">
-        <v>71</v>
+        <v>25</v>
       </c>
       <c r="I157">
         <v>0</v>
@@ -6743,28 +6715,28 @@
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="B158" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C158" t="s">
         <v>18</v>
       </c>
       <c r="D158" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="E158">
-        <v>105990</v>
+        <v>199990</v>
       </c>
       <c r="F158">
         <v>1</v>
       </c>
       <c r="G158" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H158" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I158">
         <v>0</v>
@@ -6773,33 +6745,33 @@
         <v>0</v>
       </c>
       <c r="K158" t="s">
-        <v>85</v>
+        <v>21</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="B159" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C159" t="s">
         <v>18</v>
       </c>
       <c r="D159" t="s">
-        <v>29</v>
+        <v>132</v>
       </c>
       <c r="E159">
-        <v>105990</v>
+        <v>199990</v>
       </c>
       <c r="F159">
         <v>1</v>
       </c>
       <c r="G159" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H159" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I159">
         <v>0</v>
@@ -6808,33 +6780,33 @@
         <v>0</v>
       </c>
       <c r="K159" t="s">
-        <v>85</v>
+        <v>21</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="B160" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="C160" t="s">
         <v>18</v>
       </c>
       <c r="D160" t="s">
-        <v>25</v>
+        <v>132</v>
       </c>
       <c r="E160">
-        <v>105990</v>
+        <v>159990</v>
       </c>
       <c r="F160">
         <v>1</v>
       </c>
       <c r="G160" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H160" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I160">
         <v>0</v>
@@ -6843,33 +6815,33 @@
         <v>0</v>
       </c>
       <c r="K160" t="s">
-        <v>85</v>
+        <v>189</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="B161" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="C161" t="s">
         <v>18</v>
       </c>
       <c r="D161" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E161">
-        <v>105990</v>
+        <v>199990</v>
       </c>
       <c r="F161">
         <v>1</v>
       </c>
       <c r="G161" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H161" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I161">
         <v>0</v>
@@ -6878,33 +6850,33 @@
         <v>0</v>
       </c>
       <c r="K161" t="s">
-        <v>85</v>
+        <v>189</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="B162" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="C162" t="s">
         <v>18</v>
       </c>
       <c r="D162" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="E162">
-        <v>119990</v>
+        <v>199990</v>
       </c>
       <c r="F162">
         <v>1</v>
       </c>
       <c r="G162" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H162" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I162">
         <v>0</v>
@@ -6913,24 +6885,24 @@
         <v>0</v>
       </c>
       <c r="K162" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="B163" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C163" t="s">
         <v>18</v>
       </c>
       <c r="D163" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="E163">
-        <v>189990</v>
+        <v>109990</v>
       </c>
       <c r="F163">
         <v>1</v>
@@ -6948,24 +6920,24 @@
         <v>0</v>
       </c>
       <c r="K163" t="s">
-        <v>196</v>
+        <v>45</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="B164" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="C164" t="s">
         <v>18</v>
       </c>
       <c r="D164" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E164">
-        <v>179990</v>
+        <v>109990</v>
       </c>
       <c r="F164">
         <v>1</v>
@@ -6983,24 +6955,24 @@
         <v>0</v>
       </c>
       <c r="K164" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="B165" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="C165" t="s">
         <v>18</v>
       </c>
       <c r="D165" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E165">
-        <v>179990</v>
+        <v>109990</v>
       </c>
       <c r="F165">
         <v>1</v>
@@ -7018,15 +6990,15 @@
         <v>0</v>
       </c>
       <c r="K165" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="B166" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="C166" t="s">
         <v>18</v>
@@ -7035,7 +7007,7 @@
         <v>19</v>
       </c>
       <c r="E166">
-        <v>130990</v>
+        <v>115990</v>
       </c>
       <c r="F166">
         <v>1</v>
@@ -7053,33 +7025,33 @@
         <v>0</v>
       </c>
       <c r="K166" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="B167" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="C167" t="s">
         <v>18</v>
       </c>
       <c r="D167" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E167">
-        <v>109990</v>
+        <v>119990</v>
       </c>
       <c r="F167">
         <v>1</v>
       </c>
       <c r="G167" t="s">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="H167" t="s">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="I167">
         <v>0</v>
@@ -7088,33 +7060,33 @@
         <v>0</v>
       </c>
       <c r="K167" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="B168" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="C168" t="s">
-        <v>18</v>
+        <v>196</v>
       </c>
       <c r="D168" t="s">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="E168">
-        <v>109990</v>
+        <v>85990</v>
       </c>
       <c r="F168">
         <v>1</v>
       </c>
       <c r="G168" t="s">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="H168" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I168">
         <v>0</v>
@@ -7128,28 +7100,28 @@
     </row>
     <row r="169">
       <c r="A169" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B169" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C169" t="s">
         <v>18</v>
       </c>
       <c r="D169" t="s">
-        <v>203</v>
+        <v>55</v>
       </c>
       <c r="E169">
-        <v>82990</v>
+        <v>105990</v>
       </c>
       <c r="F169">
         <v>1</v>
       </c>
       <c r="G169" t="s">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="H169" t="s">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="I169">
         <v>0</v>
@@ -7158,33 +7130,33 @@
         <v>0</v>
       </c>
       <c r="K169" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B170" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C170" t="s">
         <v>18</v>
       </c>
       <c r="D170" t="s">
-        <v>203</v>
+        <v>36</v>
       </c>
       <c r="E170">
-        <v>82990</v>
+        <v>105990</v>
       </c>
       <c r="F170">
         <v>1</v>
       </c>
       <c r="G170" t="s">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="H170" t="s">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="I170">
         <v>0</v>
@@ -7193,33 +7165,33 @@
         <v>0</v>
       </c>
       <c r="K170" t="s">
-        <v>21</v>
+        <v>91</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="B171" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="C171" t="s">
         <v>18</v>
       </c>
       <c r="D171" t="s">
-        <v>206</v>
+        <v>32</v>
       </c>
       <c r="E171">
-        <v>119990</v>
+        <v>105990</v>
       </c>
       <c r="F171">
         <v>1</v>
       </c>
       <c r="G171" t="s">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="H171" t="s">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="I171">
         <v>0</v>
@@ -7228,33 +7200,33 @@
         <v>0</v>
       </c>
       <c r="K171" t="s">
-        <v>21</v>
+        <v>91</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="B172" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="C172" t="s">
         <v>18</v>
       </c>
       <c r="D172" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E172">
-        <v>119990</v>
+        <v>105990</v>
       </c>
       <c r="F172">
         <v>1</v>
       </c>
       <c r="G172" t="s">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="H172" t="s">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="I172">
         <v>0</v>
@@ -7263,21 +7235,21 @@
         <v>0</v>
       </c>
       <c r="K172" t="s">
-        <v>21</v>
+        <v>91</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="B173" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C173" t="s">
         <v>18</v>
       </c>
       <c r="D173" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E173">
         <v>119990</v>
@@ -7286,10 +7258,10 @@
         <v>1</v>
       </c>
       <c r="G173" t="s">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="H173" t="s">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="I173">
         <v>0</v>
@@ -7298,33 +7270,33 @@
         <v>0</v>
       </c>
       <c r="K173" t="s">
-        <v>21</v>
+        <v>201</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="B174" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C174" t="s">
         <v>18</v>
       </c>
       <c r="D174" t="s">
-        <v>206</v>
+        <v>32</v>
       </c>
       <c r="E174">
-        <v>119990</v>
+        <v>189990</v>
       </c>
       <c r="F174">
         <v>1</v>
       </c>
       <c r="G174" t="s">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="H174" t="s">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="I174">
         <v>0</v>
@@ -7333,33 +7305,33 @@
         <v>0</v>
       </c>
       <c r="K174" t="s">
-        <v>43</v>
+        <v>201</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B175" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C175" t="s">
         <v>18</v>
       </c>
       <c r="D175" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="E175">
-        <v>119990</v>
+        <v>179990</v>
       </c>
       <c r="F175">
         <v>1</v>
       </c>
       <c r="G175" t="s">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="H175" t="s">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="I175">
         <v>0</v>
@@ -7368,33 +7340,33 @@
         <v>0</v>
       </c>
       <c r="K175" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B176" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C176" t="s">
         <v>18</v>
       </c>
       <c r="D176" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E176">
-        <v>119990</v>
+        <v>179990</v>
       </c>
       <c r="F176">
         <v>1</v>
       </c>
       <c r="G176" t="s">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="H176" t="s">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="I176">
         <v>0</v>
@@ -7403,33 +7375,33 @@
         <v>0</v>
       </c>
       <c r="K176" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="B177" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="C177" t="s">
         <v>18</v>
       </c>
       <c r="D177" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="E177">
-        <v>129990</v>
+        <v>130990</v>
       </c>
       <c r="F177">
         <v>1</v>
       </c>
       <c r="G177" t="s">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="H177" t="s">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="I177">
         <v>0</v>
@@ -7438,33 +7410,33 @@
         <v>0</v>
       </c>
       <c r="K177" t="s">
-        <v>209</v>
+        <v>71</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B178" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C178" t="s">
         <v>18</v>
       </c>
       <c r="D178" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E178">
-        <v>119990</v>
+        <v>109990</v>
       </c>
       <c r="F178">
         <v>1</v>
       </c>
       <c r="G178" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H178" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I178">
         <v>0</v>
@@ -7473,33 +7445,33 @@
         <v>0</v>
       </c>
       <c r="K178" t="s">
-        <v>209</v>
+        <v>21</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B179" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C179" t="s">
         <v>18</v>
       </c>
       <c r="D179" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E179">
-        <v>119990</v>
+        <v>109990</v>
       </c>
       <c r="F179">
         <v>1</v>
       </c>
       <c r="G179" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H179" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I179">
         <v>0</v>
@@ -7508,33 +7480,33 @@
         <v>0</v>
       </c>
       <c r="K179" t="s">
-        <v>209</v>
+        <v>21</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="s">
+        <v>206</v>
+      </c>
+      <c r="B180" t="s">
         <v>207</v>
       </c>
-      <c r="B180" t="s">
+      <c r="C180" t="s">
+        <v>18</v>
+      </c>
+      <c r="D180" t="s">
         <v>208</v>
       </c>
-      <c r="C180" t="s">
-        <v>18</v>
-      </c>
-      <c r="D180" t="s">
-        <v>127</v>
-      </c>
       <c r="E180">
-        <v>119990</v>
+        <v>82990</v>
       </c>
       <c r="F180">
         <v>1</v>
       </c>
       <c r="G180" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H180" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I180">
         <v>0</v>
@@ -7543,33 +7515,33 @@
         <v>0</v>
       </c>
       <c r="K180" t="s">
-        <v>209</v>
+        <v>87</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="s">
+        <v>206</v>
+      </c>
+      <c r="B181" t="s">
         <v>207</v>
       </c>
-      <c r="B181" t="s">
+      <c r="C181" t="s">
+        <v>18</v>
+      </c>
+      <c r="D181" t="s">
         <v>208</v>
       </c>
-      <c r="C181" t="s">
-        <v>18</v>
-      </c>
-      <c r="D181" t="s">
-        <v>48</v>
-      </c>
       <c r="E181">
-        <v>129990</v>
+        <v>82990</v>
       </c>
       <c r="F181">
         <v>1</v>
       </c>
       <c r="G181" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H181" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I181">
         <v>0</v>
@@ -7578,21 +7550,21 @@
         <v>0</v>
       </c>
       <c r="K181" t="s">
-        <v>210</v>
+        <v>21</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B182" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C182" t="s">
         <v>18</v>
       </c>
       <c r="D182" t="s">
-        <v>29</v>
+        <v>211</v>
       </c>
       <c r="E182">
         <v>119990</v>
@@ -7601,10 +7573,10 @@
         <v>1</v>
       </c>
       <c r="G182" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="H182" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="I182">
         <v>0</v>
@@ -7613,21 +7585,21 @@
         <v>0</v>
       </c>
       <c r="K182" t="s">
-        <v>210</v>
+        <v>21</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B183" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C183" t="s">
         <v>18</v>
       </c>
       <c r="D183" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E183">
         <v>119990</v>
@@ -7636,10 +7608,10 @@
         <v>1</v>
       </c>
       <c r="G183" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="H183" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="I183">
         <v>0</v>
@@ -7648,15 +7620,15 @@
         <v>0</v>
       </c>
       <c r="K183" t="s">
-        <v>210</v>
+        <v>21</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B184" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C184" t="s">
         <v>18</v>
@@ -7671,10 +7643,10 @@
         <v>1</v>
       </c>
       <c r="G184" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="H184" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="I184">
         <v>0</v>
@@ -7683,21 +7655,21 @@
         <v>0</v>
       </c>
       <c r="K184" t="s">
-        <v>210</v>
+        <v>21</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B185" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C185" t="s">
         <v>18</v>
       </c>
       <c r="D185" t="s">
-        <v>127</v>
+        <v>211</v>
       </c>
       <c r="E185">
         <v>119990</v>
@@ -7706,10 +7678,10 @@
         <v>1</v>
       </c>
       <c r="G185" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="H185" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="I185">
         <v>0</v>
@@ -7718,33 +7690,33 @@
         <v>0</v>
       </c>
       <c r="K185" t="s">
-        <v>210</v>
+        <v>50</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B186" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C186" t="s">
         <v>18</v>
       </c>
       <c r="D186" t="s">
-        <v>102</v>
+        <v>32</v>
       </c>
       <c r="E186">
-        <v>165990</v>
+        <v>119990</v>
       </c>
       <c r="F186">
         <v>1</v>
       </c>
       <c r="G186" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="H186" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="I186">
         <v>0</v>
@@ -7753,33 +7725,33 @@
         <v>0</v>
       </c>
       <c r="K186" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B187" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C187" t="s">
         <v>18</v>
       </c>
       <c r="D187" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E187">
-        <v>149990</v>
+        <v>119990</v>
       </c>
       <c r="F187">
         <v>1</v>
       </c>
       <c r="G187" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="H187" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="I187">
         <v>0</v>
@@ -7788,33 +7760,33 @@
         <v>0</v>
       </c>
       <c r="K187" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B188" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C188" t="s">
         <v>18</v>
       </c>
       <c r="D188" t="s">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="E188">
-        <v>149990</v>
+        <v>129990</v>
       </c>
       <c r="F188">
         <v>1</v>
       </c>
       <c r="G188" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="H188" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="I188">
         <v>0</v>
@@ -7823,33 +7795,33 @@
         <v>0</v>
       </c>
       <c r="K188" t="s">
-        <v>56</v>
+        <v>214</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B189" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C189" t="s">
         <v>18</v>
       </c>
       <c r="D189" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="E189">
-        <v>149990</v>
+        <v>119990</v>
       </c>
       <c r="F189">
         <v>1</v>
       </c>
       <c r="G189" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="H189" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="I189">
         <v>0</v>
@@ -7858,33 +7830,33 @@
         <v>0</v>
       </c>
       <c r="K189" t="s">
-        <v>56</v>
+        <v>214</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B190" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C190" t="s">
         <v>18</v>
       </c>
       <c r="D190" t="s">
-        <v>127</v>
+        <v>32</v>
       </c>
       <c r="E190">
-        <v>149990</v>
+        <v>119990</v>
       </c>
       <c r="F190">
         <v>1</v>
       </c>
       <c r="G190" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="H190" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="I190">
         <v>0</v>
@@ -7893,68 +7865,68 @@
         <v>0</v>
       </c>
       <c r="K190" t="s">
-        <v>56</v>
+        <v>214</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="s">
+        <v>212</v>
+      </c>
+      <c r="B191" t="s">
         <v>213</v>
       </c>
-      <c r="B191" t="s">
+      <c r="C191" t="s">
+        <v>18</v>
+      </c>
+      <c r="D191" t="s">
+        <v>132</v>
+      </c>
+      <c r="E191">
+        <v>119990</v>
+      </c>
+      <c r="F191">
+        <v>1</v>
+      </c>
+      <c r="G191" t="s">
+        <v>25</v>
+      </c>
+      <c r="H191" t="s">
+        <v>25</v>
+      </c>
+      <c r="I191">
+        <v>0</v>
+      </c>
+      <c r="J191">
+        <v>0</v>
+      </c>
+      <c r="K191" t="s">
         <v>214</v>
-      </c>
-      <c r="C191" t="s">
-        <v>18</v>
-      </c>
-      <c r="D191" t="s">
-        <v>102</v>
-      </c>
-      <c r="E191">
-        <v>189990</v>
-      </c>
-      <c r="F191">
-        <v>1</v>
-      </c>
-      <c r="G191" t="s">
-        <v>20</v>
-      </c>
-      <c r="H191" t="s">
-        <v>20</v>
-      </c>
-      <c r="I191">
-        <v>0</v>
-      </c>
-      <c r="J191">
-        <v>0</v>
-      </c>
-      <c r="K191" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="s">
+        <v>212</v>
+      </c>
+      <c r="B192" t="s">
         <v>213</v>
       </c>
-      <c r="B192" t="s">
-        <v>214</v>
-      </c>
       <c r="C192" t="s">
         <v>18</v>
       </c>
       <c r="D192" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="E192">
-        <v>189990</v>
+        <v>129990</v>
       </c>
       <c r="F192">
         <v>1</v>
       </c>
       <c r="G192" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H192" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I192">
         <v>0</v>
@@ -7963,33 +7935,33 @@
         <v>0</v>
       </c>
       <c r="K192" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="s">
+        <v>212</v>
+      </c>
+      <c r="B193" t="s">
         <v>213</v>
       </c>
-      <c r="B193" t="s">
-        <v>214</v>
-      </c>
       <c r="C193" t="s">
         <v>18</v>
       </c>
       <c r="D193" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="E193">
-        <v>189990</v>
+        <v>119990</v>
       </c>
       <c r="F193">
         <v>1</v>
       </c>
       <c r="G193" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H193" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I193">
         <v>0</v>
@@ -7998,138 +7970,138 @@
         <v>0</v>
       </c>
       <c r="K193" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="s">
+        <v>212</v>
+      </c>
+      <c r="B194" t="s">
+        <v>213</v>
+      </c>
+      <c r="C194" t="s">
+        <v>18</v>
+      </c>
+      <c r="D194" t="s">
+        <v>32</v>
+      </c>
+      <c r="E194">
+        <v>119990</v>
+      </c>
+      <c r="F194">
+        <v>1</v>
+      </c>
+      <c r="G194" t="s">
+        <v>25</v>
+      </c>
+      <c r="H194" t="s">
+        <v>25</v>
+      </c>
+      <c r="I194">
+        <v>0</v>
+      </c>
+      <c r="J194">
+        <v>0</v>
+      </c>
+      <c r="K194" t="s">
         <v>215</v>
-      </c>
-      <c r="B194" t="s">
-        <v>216</v>
-      </c>
-      <c r="C194" t="s">
-        <v>18</v>
-      </c>
-      <c r="D194" t="s">
-        <v>48</v>
-      </c>
-      <c r="E194">
-        <v>185990</v>
-      </c>
-      <c r="F194">
-        <v>1</v>
-      </c>
-      <c r="G194" t="s">
-        <v>20</v>
-      </c>
-      <c r="H194" t="s">
-        <v>20</v>
-      </c>
-      <c r="I194">
-        <v>0</v>
-      </c>
-      <c r="J194">
-        <v>0</v>
-      </c>
-      <c r="K194" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="s">
+        <v>212</v>
+      </c>
+      <c r="B195" t="s">
+        <v>213</v>
+      </c>
+      <c r="C195" t="s">
+        <v>18</v>
+      </c>
+      <c r="D195" t="s">
+        <v>19</v>
+      </c>
+      <c r="E195">
+        <v>119990</v>
+      </c>
+      <c r="F195">
+        <v>1</v>
+      </c>
+      <c r="G195" t="s">
+        <v>25</v>
+      </c>
+      <c r="H195" t="s">
+        <v>25</v>
+      </c>
+      <c r="I195">
+        <v>0</v>
+      </c>
+      <c r="J195">
+        <v>0</v>
+      </c>
+      <c r="K195" t="s">
         <v>215</v>
-      </c>
-      <c r="B195" t="s">
-        <v>216</v>
-      </c>
-      <c r="C195" t="s">
-        <v>18</v>
-      </c>
-      <c r="D195" t="s">
-        <v>25</v>
-      </c>
-      <c r="E195">
-        <v>185990</v>
-      </c>
-      <c r="F195">
-        <v>1</v>
-      </c>
-      <c r="G195" t="s">
-        <v>20</v>
-      </c>
-      <c r="H195" t="s">
-        <v>20</v>
-      </c>
-      <c r="I195">
-        <v>0</v>
-      </c>
-      <c r="J195">
-        <v>0</v>
-      </c>
-      <c r="K195" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="s">
+        <v>212</v>
+      </c>
+      <c r="B196" t="s">
+        <v>213</v>
+      </c>
+      <c r="C196" t="s">
+        <v>18</v>
+      </c>
+      <c r="D196" t="s">
+        <v>132</v>
+      </c>
+      <c r="E196">
+        <v>119990</v>
+      </c>
+      <c r="F196">
+        <v>1</v>
+      </c>
+      <c r="G196" t="s">
+        <v>25</v>
+      </c>
+      <c r="H196" t="s">
+        <v>25</v>
+      </c>
+      <c r="I196">
+        <v>0</v>
+      </c>
+      <c r="J196">
+        <v>0</v>
+      </c>
+      <c r="K196" t="s">
         <v>215</v>
-      </c>
-      <c r="B196" t="s">
-        <v>216</v>
-      </c>
-      <c r="C196" t="s">
-        <v>18</v>
-      </c>
-      <c r="D196" t="s">
-        <v>19</v>
-      </c>
-      <c r="E196">
-        <v>185990</v>
-      </c>
-      <c r="F196">
-        <v>1</v>
-      </c>
-      <c r="G196" t="s">
-        <v>20</v>
-      </c>
-      <c r="H196" t="s">
-        <v>20</v>
-      </c>
-      <c r="I196">
-        <v>0</v>
-      </c>
-      <c r="J196">
-        <v>0</v>
-      </c>
-      <c r="K196" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="s">
+        <v>216</v>
+      </c>
+      <c r="B197" t="s">
         <v>217</v>
       </c>
-      <c r="B197" t="s">
-        <v>218</v>
-      </c>
       <c r="C197" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D197" t="s">
-        <v>219</v>
+        <v>107</v>
       </c>
       <c r="E197">
-        <v>125990</v>
+        <v>165990</v>
       </c>
       <c r="F197">
         <v>1</v>
       </c>
       <c r="G197" t="s">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="H197" t="s">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="I197">
         <v>0</v>
@@ -8138,33 +8110,33 @@
         <v>0</v>
       </c>
       <c r="K197" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="s">
+        <v>216</v>
+      </c>
+      <c r="B198" t="s">
         <v>217</v>
       </c>
-      <c r="B198" t="s">
-        <v>218</v>
-      </c>
       <c r="C198" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D198" t="s">
-        <v>220</v>
+        <v>36</v>
       </c>
       <c r="E198">
-        <v>125990</v>
+        <v>149990</v>
       </c>
       <c r="F198">
         <v>1</v>
       </c>
       <c r="G198" t="s">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="H198" t="s">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="I198">
         <v>0</v>
@@ -8173,33 +8145,33 @@
         <v>0</v>
       </c>
       <c r="K198" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="s">
+        <v>216</v>
+      </c>
+      <c r="B199" t="s">
         <v>217</v>
       </c>
-      <c r="B199" t="s">
-        <v>218</v>
-      </c>
       <c r="C199" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D199" t="s">
-        <v>221</v>
+        <v>32</v>
       </c>
       <c r="E199">
-        <v>125990</v>
+        <v>149990</v>
       </c>
       <c r="F199">
         <v>1</v>
       </c>
       <c r="G199" t="s">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="H199" t="s">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="I199">
         <v>0</v>
@@ -8208,33 +8180,33 @@
         <v>0</v>
       </c>
       <c r="K199" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="s">
+        <v>216</v>
+      </c>
+      <c r="B200" t="s">
         <v>217</v>
       </c>
-      <c r="B200" t="s">
-        <v>218</v>
-      </c>
       <c r="C200" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D200" t="s">
-        <v>222</v>
+        <v>19</v>
       </c>
       <c r="E200">
-        <v>125990</v>
+        <v>149990</v>
       </c>
       <c r="F200">
         <v>1</v>
       </c>
       <c r="G200" t="s">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="H200" t="s">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="I200">
         <v>0</v>
@@ -8243,33 +8215,33 @@
         <v>0</v>
       </c>
       <c r="K200" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="B201" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="C201" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D201" t="s">
-        <v>225</v>
+        <v>132</v>
       </c>
       <c r="E201">
-        <v>129990</v>
+        <v>149990</v>
       </c>
       <c r="F201">
         <v>1</v>
       </c>
       <c r="G201" t="s">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="H201" t="s">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="I201">
         <v>0</v>
@@ -8278,33 +8250,33 @@
         <v>0</v>
       </c>
       <c r="K201" t="s">
-        <v>21</v>
+        <v>63</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="B202" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="C202" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D202" t="s">
-        <v>226</v>
+        <v>107</v>
       </c>
       <c r="E202">
-        <v>129990</v>
+        <v>189990</v>
       </c>
       <c r="F202">
         <v>1</v>
       </c>
       <c r="G202" t="s">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="H202" t="s">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="I202">
         <v>0</v>
@@ -8313,33 +8285,33 @@
         <v>0</v>
       </c>
       <c r="K202" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="B203" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="C203" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D203" t="s">
-        <v>227</v>
+        <v>36</v>
       </c>
       <c r="E203">
-        <v>129990</v>
+        <v>189990</v>
       </c>
       <c r="F203">
         <v>1</v>
       </c>
       <c r="G203" t="s">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="H203" t="s">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="I203">
         <v>0</v>
@@ -8348,33 +8320,33 @@
         <v>0</v>
       </c>
       <c r="K203" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="B204" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="C204" t="s">
         <v>18</v>
       </c>
       <c r="D204" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E204">
-        <v>125990</v>
+        <v>189990</v>
       </c>
       <c r="F204">
         <v>1</v>
       </c>
       <c r="G204" t="s">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="H204" t="s">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="I204">
         <v>0</v>
@@ -8383,33 +8355,33 @@
         <v>0</v>
       </c>
       <c r="K204" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="B205" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="C205" t="s">
         <v>18</v>
       </c>
       <c r="D205" t="s">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="E205">
-        <v>125990</v>
+        <v>185990</v>
       </c>
       <c r="F205">
         <v>1</v>
       </c>
       <c r="G205" t="s">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="H205" t="s">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="I205">
         <v>0</v>
@@ -8423,28 +8395,28 @@
     </row>
     <row r="206">
       <c r="A206" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="B206" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="C206" t="s">
         <v>18</v>
       </c>
       <c r="D206" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E206">
-        <v>125990</v>
+        <v>185990</v>
       </c>
       <c r="F206">
         <v>1</v>
       </c>
       <c r="G206" t="s">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="H206" t="s">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="I206">
         <v>0</v>
@@ -8458,28 +8430,28 @@
     </row>
     <row r="207">
       <c r="A207" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B207" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="C207" t="s">
         <v>18</v>
       </c>
       <c r="D207" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="E207">
-        <v>140990</v>
+        <v>185990</v>
       </c>
       <c r="F207">
         <v>1</v>
       </c>
       <c r="G207" t="s">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="H207" t="s">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="I207">
         <v>0</v>
@@ -8488,33 +8460,33 @@
         <v>0</v>
       </c>
       <c r="K207" t="s">
-        <v>209</v>
+        <v>21</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="B208" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="C208" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D208" t="s">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="E208">
-        <v>140990</v>
+        <v>125990</v>
       </c>
       <c r="F208">
         <v>1</v>
       </c>
       <c r="G208" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H208" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I208">
         <v>0</v>
@@ -8523,33 +8495,33 @@
         <v>0</v>
       </c>
       <c r="K208" t="s">
-        <v>209</v>
+        <v>87</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="B209" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="C209" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D209" t="s">
-        <v>19</v>
+        <v>225</v>
       </c>
       <c r="E209">
-        <v>140990</v>
+        <v>125990</v>
       </c>
       <c r="F209">
         <v>1</v>
       </c>
       <c r="G209" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H209" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I209">
         <v>0</v>
@@ -8558,33 +8530,33 @@
         <v>0</v>
       </c>
       <c r="K209" t="s">
-        <v>209</v>
+        <v>87</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="B210" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="C210" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D210" t="s">
-        <v>127</v>
+        <v>226</v>
       </c>
       <c r="E210">
-        <v>140990</v>
+        <v>125990</v>
       </c>
       <c r="F210">
         <v>1</v>
       </c>
       <c r="G210" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H210" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I210">
         <v>0</v>
@@ -8593,33 +8565,33 @@
         <v>0</v>
       </c>
       <c r="K210" t="s">
-        <v>209</v>
+        <v>87</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="B211" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="C211" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D211" t="s">
-        <v>29</v>
+        <v>227</v>
       </c>
       <c r="E211">
-        <v>195990</v>
+        <v>125990</v>
       </c>
       <c r="F211">
         <v>1</v>
       </c>
       <c r="G211" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H211" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I211">
         <v>0</v>
@@ -8628,33 +8600,33 @@
         <v>0</v>
       </c>
       <c r="K211" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="B212" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="C212" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D212" t="s">
-        <v>25</v>
+        <v>230</v>
       </c>
       <c r="E212">
-        <v>195990</v>
+        <v>129990</v>
       </c>
       <c r="F212">
         <v>1</v>
       </c>
       <c r="G212" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H212" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I212">
         <v>0</v>
@@ -8663,33 +8635,33 @@
         <v>0</v>
       </c>
       <c r="K212" t="s">
-        <v>111</v>
+        <v>21</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="B213" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="C213" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D213" t="s">
-        <v>48</v>
+        <v>231</v>
       </c>
       <c r="E213">
-        <v>140900</v>
+        <v>129990</v>
       </c>
       <c r="F213">
         <v>1</v>
       </c>
       <c r="G213" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H213" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I213">
         <v>0</v>
@@ -8698,33 +8670,33 @@
         <v>0</v>
       </c>
       <c r="K213" t="s">
-        <v>111</v>
+        <v>21</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="B214" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="C214" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D214" t="s">
-        <v>29</v>
+        <v>232</v>
       </c>
       <c r="E214">
-        <v>130990</v>
+        <v>129990</v>
       </c>
       <c r="F214">
         <v>1</v>
       </c>
       <c r="G214" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H214" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I214">
         <v>0</v>
@@ -8733,33 +8705,33 @@
         <v>0</v>
       </c>
       <c r="K214" t="s">
-        <v>111</v>
+        <v>21</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="s">
+        <v>233</v>
+      </c>
+      <c r="B215" t="s">
         <v>234</v>
       </c>
-      <c r="B215" t="s">
-        <v>235</v>
-      </c>
       <c r="C215" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D215" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="E215">
-        <v>130990</v>
+        <v>125990</v>
       </c>
       <c r="F215">
         <v>1</v>
       </c>
       <c r="G215" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="H215" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="I215">
         <v>0</v>
@@ -8768,33 +8740,33 @@
         <v>0</v>
       </c>
       <c r="K215" t="s">
-        <v>111</v>
+        <v>21</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="s">
+        <v>233</v>
+      </c>
+      <c r="B216" t="s">
         <v>234</v>
       </c>
-      <c r="B216" t="s">
-        <v>235</v>
-      </c>
       <c r="C216" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D216" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E216">
-        <v>130990</v>
+        <v>125990</v>
       </c>
       <c r="F216">
         <v>1</v>
       </c>
       <c r="G216" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="H216" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="I216">
         <v>0</v>
@@ -8803,33 +8775,33 @@
         <v>0</v>
       </c>
       <c r="K216" t="s">
-        <v>111</v>
+        <v>21</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="s">
+        <v>233</v>
+      </c>
+      <c r="B217" t="s">
         <v>234</v>
       </c>
-      <c r="B217" t="s">
-        <v>235</v>
-      </c>
       <c r="C217" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D217" t="s">
-        <v>127</v>
+        <v>19</v>
       </c>
       <c r="E217">
-        <v>130990</v>
+        <v>125990</v>
       </c>
       <c r="F217">
         <v>1</v>
       </c>
       <c r="G217" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="H217" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="I217">
         <v>0</v>
@@ -8838,33 +8810,33 @@
         <v>0</v>
       </c>
       <c r="K217" t="s">
-        <v>111</v>
+        <v>21</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="s">
+        <v>235</v>
+      </c>
+      <c r="B218" t="s">
         <v>236</v>
       </c>
-      <c r="B218" t="s">
-        <v>237</v>
-      </c>
       <c r="C218" t="s">
-        <v>117</v>
+        <v>18</v>
       </c>
       <c r="D218" t="s">
-        <v>118</v>
+        <v>55</v>
       </c>
       <c r="E218">
-        <v>149990</v>
+        <v>140990</v>
       </c>
       <c r="F218">
         <v>1</v>
       </c>
       <c r="G218" t="s">
-        <v>114</v>
+        <v>25</v>
       </c>
       <c r="H218" t="s">
-        <v>71</v>
+        <v>25</v>
       </c>
       <c r="I218">
         <v>0</v>
@@ -8873,33 +8845,33 @@
         <v>0</v>
       </c>
       <c r="K218" t="s">
-        <v>21</v>
+        <v>214</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B219" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C219" t="s">
-        <v>117</v>
+        <v>18</v>
       </c>
       <c r="D219" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="E219">
-        <v>145990</v>
+        <v>140990</v>
       </c>
       <c r="F219">
         <v>1</v>
       </c>
       <c r="G219" t="s">
-        <v>114</v>
+        <v>25</v>
       </c>
       <c r="H219" t="s">
-        <v>71</v>
+        <v>25</v>
       </c>
       <c r="I219">
         <v>0</v>
@@ -8908,33 +8880,33 @@
         <v>0</v>
       </c>
       <c r="K219" t="s">
-        <v>56</v>
+        <v>214</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="B220" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="C220" t="s">
-        <v>117</v>
+        <v>18</v>
       </c>
       <c r="D220" t="s">
-        <v>118</v>
+        <v>19</v>
       </c>
       <c r="E220">
-        <v>279000</v>
+        <v>140990</v>
       </c>
       <c r="F220">
         <v>1</v>
       </c>
       <c r="G220" t="s">
-        <v>114</v>
+        <v>25</v>
       </c>
       <c r="H220" t="s">
-        <v>71</v>
+        <v>25</v>
       </c>
       <c r="I220">
         <v>0</v>
@@ -8943,33 +8915,33 @@
         <v>0</v>
       </c>
       <c r="K220" t="s">
-        <v>33</v>
+        <v>214</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="B221" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="C221" t="s">
-        <v>117</v>
+        <v>18</v>
       </c>
       <c r="D221" t="s">
-        <v>48</v>
+        <v>132</v>
       </c>
       <c r="E221">
-        <v>169990</v>
+        <v>140990</v>
       </c>
       <c r="F221">
         <v>1</v>
       </c>
       <c r="G221" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="H221" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="I221">
         <v>0</v>
@@ -8978,42 +8950,427 @@
         <v>0</v>
       </c>
       <c r="K221" t="s">
-        <v>33</v>
+        <v>214</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="s">
+        <v>237</v>
+      </c>
+      <c r="B222" t="s">
+        <v>238</v>
+      </c>
+      <c r="C222" t="s">
+        <v>35</v>
+      </c>
+      <c r="D222" t="s">
+        <v>36</v>
+      </c>
+      <c r="E222">
+        <v>195990</v>
+      </c>
+      <c r="F222">
+        <v>1</v>
+      </c>
+      <c r="G222" t="s">
+        <v>25</v>
+      </c>
+      <c r="H222" t="s">
+        <v>25</v>
+      </c>
+      <c r="I222">
+        <v>0</v>
+      </c>
+      <c r="J222">
+        <v>0</v>
+      </c>
+      <c r="K222" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="s">
+        <v>237</v>
+      </c>
+      <c r="B223" t="s">
+        <v>238</v>
+      </c>
+      <c r="C223" t="s">
+        <v>35</v>
+      </c>
+      <c r="D223" t="s">
+        <v>32</v>
+      </c>
+      <c r="E223">
+        <v>195990</v>
+      </c>
+      <c r="F223">
+        <v>1</v>
+      </c>
+      <c r="G223" t="s">
+        <v>25</v>
+      </c>
+      <c r="H223" t="s">
+        <v>25</v>
+      </c>
+      <c r="I223">
+        <v>0</v>
+      </c>
+      <c r="J223">
+        <v>0</v>
+      </c>
+      <c r="K223" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="s">
+        <v>239</v>
+      </c>
+      <c r="B224" t="s">
+        <v>240</v>
+      </c>
+      <c r="C224" t="s">
+        <v>35</v>
+      </c>
+      <c r="D224" t="s">
+        <v>55</v>
+      </c>
+      <c r="E224">
+        <v>140900</v>
+      </c>
+      <c r="F224">
+        <v>1</v>
+      </c>
+      <c r="G224" t="s">
+        <v>25</v>
+      </c>
+      <c r="H224" t="s">
+        <v>25</v>
+      </c>
+      <c r="I224">
+        <v>0</v>
+      </c>
+      <c r="J224">
+        <v>0</v>
+      </c>
+      <c r="K224" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="s">
+        <v>239</v>
+      </c>
+      <c r="B225" t="s">
+        <v>240</v>
+      </c>
+      <c r="C225" t="s">
+        <v>35</v>
+      </c>
+      <c r="D225" t="s">
+        <v>36</v>
+      </c>
+      <c r="E225">
+        <v>130990</v>
+      </c>
+      <c r="F225">
+        <v>1</v>
+      </c>
+      <c r="G225" t="s">
+        <v>25</v>
+      </c>
+      <c r="H225" t="s">
+        <v>25</v>
+      </c>
+      <c r="I225">
+        <v>0</v>
+      </c>
+      <c r="J225">
+        <v>0</v>
+      </c>
+      <c r="K225" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="s">
+        <v>239</v>
+      </c>
+      <c r="B226" t="s">
+        <v>240</v>
+      </c>
+      <c r="C226" t="s">
+        <v>35</v>
+      </c>
+      <c r="D226" t="s">
+        <v>32</v>
+      </c>
+      <c r="E226">
+        <v>130990</v>
+      </c>
+      <c r="F226">
+        <v>1</v>
+      </c>
+      <c r="G226" t="s">
+        <v>25</v>
+      </c>
+      <c r="H226" t="s">
+        <v>25</v>
+      </c>
+      <c r="I226">
+        <v>0</v>
+      </c>
+      <c r="J226">
+        <v>0</v>
+      </c>
+      <c r="K226" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="s">
+        <v>239</v>
+      </c>
+      <c r="B227" t="s">
+        <v>240</v>
+      </c>
+      <c r="C227" t="s">
+        <v>35</v>
+      </c>
+      <c r="D227" t="s">
+        <v>19</v>
+      </c>
+      <c r="E227">
+        <v>130990</v>
+      </c>
+      <c r="F227">
+        <v>1</v>
+      </c>
+      <c r="G227" t="s">
+        <v>25</v>
+      </c>
+      <c r="H227" t="s">
+        <v>25</v>
+      </c>
+      <c r="I227">
+        <v>0</v>
+      </c>
+      <c r="J227">
+        <v>0</v>
+      </c>
+      <c r="K227" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="s">
+        <v>239</v>
+      </c>
+      <c r="B228" t="s">
+        <v>240</v>
+      </c>
+      <c r="C228" t="s">
+        <v>35</v>
+      </c>
+      <c r="D228" t="s">
+        <v>132</v>
+      </c>
+      <c r="E228">
+        <v>130990</v>
+      </c>
+      <c r="F228">
+        <v>1</v>
+      </c>
+      <c r="G228" t="s">
+        <v>25</v>
+      </c>
+      <c r="H228" t="s">
+        <v>25</v>
+      </c>
+      <c r="I228">
+        <v>0</v>
+      </c>
+      <c r="J228">
+        <v>0</v>
+      </c>
+      <c r="K228" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="s">
+        <v>241</v>
+      </c>
+      <c r="B229" t="s">
         <v>242</v>
       </c>
-      <c r="B222" t="s">
+      <c r="C229" t="s">
+        <v>122</v>
+      </c>
+      <c r="D229" t="s">
+        <v>123</v>
+      </c>
+      <c r="E229">
+        <v>149990</v>
+      </c>
+      <c r="F229">
+        <v>1</v>
+      </c>
+      <c r="G229" t="s">
+        <v>119</v>
+      </c>
+      <c r="H229" t="s">
+        <v>78</v>
+      </c>
+      <c r="I229">
+        <v>0</v>
+      </c>
+      <c r="J229">
+        <v>0</v>
+      </c>
+      <c r="K229" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="s">
         <v>243</v>
       </c>
-      <c r="C222" t="s">
-        <v>117</v>
-      </c>
-      <c r="D222" t="s">
-        <v>29</v>
-      </c>
-      <c r="E222">
+      <c r="B230" t="s">
+        <v>244</v>
+      </c>
+      <c r="C230" t="s">
+        <v>122</v>
+      </c>
+      <c r="D230" t="s">
+        <v>55</v>
+      </c>
+      <c r="E230">
+        <v>145990</v>
+      </c>
+      <c r="F230">
+        <v>1</v>
+      </c>
+      <c r="G230" t="s">
+        <v>119</v>
+      </c>
+      <c r="H230" t="s">
+        <v>78</v>
+      </c>
+      <c r="I230">
+        <v>0</v>
+      </c>
+      <c r="J230">
+        <v>0</v>
+      </c>
+      <c r="K230" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="s">
+        <v>245</v>
+      </c>
+      <c r="B231" t="s">
+        <v>246</v>
+      </c>
+      <c r="C231" t="s">
+        <v>122</v>
+      </c>
+      <c r="D231" t="s">
+        <v>123</v>
+      </c>
+      <c r="E231">
+        <v>279000</v>
+      </c>
+      <c r="F231">
+        <v>1</v>
+      </c>
+      <c r="G231" t="s">
+        <v>119</v>
+      </c>
+      <c r="H231" t="s">
+        <v>78</v>
+      </c>
+      <c r="I231">
+        <v>0</v>
+      </c>
+      <c r="J231">
+        <v>0</v>
+      </c>
+      <c r="K231" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="s">
+        <v>247</v>
+      </c>
+      <c r="B232" t="s">
+        <v>248</v>
+      </c>
+      <c r="C232" t="s">
+        <v>122</v>
+      </c>
+      <c r="D232" t="s">
+        <v>55</v>
+      </c>
+      <c r="E232">
         <v>169990</v>
       </c>
-      <c r="F222">
-        <v>1</v>
-      </c>
-      <c r="G222" t="s">
-        <v>84</v>
-      </c>
-      <c r="H222" t="s">
-        <v>84</v>
-      </c>
-      <c r="I222">
-        <v>0</v>
-      </c>
-      <c r="J222">
-        <v>0</v>
-      </c>
-      <c r="K222" t="s">
-        <v>33</v>
+      <c r="F232">
+        <v>1</v>
+      </c>
+      <c r="G232" t="s">
+        <v>25</v>
+      </c>
+      <c r="H232" t="s">
+        <v>25</v>
+      </c>
+      <c r="I232">
+        <v>0</v>
+      </c>
+      <c r="J232">
+        <v>0</v>
+      </c>
+      <c r="K232" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="s">
+        <v>247</v>
+      </c>
+      <c r="B233" t="s">
+        <v>248</v>
+      </c>
+      <c r="C233" t="s">
+        <v>122</v>
+      </c>
+      <c r="D233" t="s">
+        <v>36</v>
+      </c>
+      <c r="E233">
+        <v>169990</v>
+      </c>
+      <c r="F233">
+        <v>1</v>
+      </c>
+      <c r="G233" t="s">
+        <v>25</v>
+      </c>
+      <c r="H233" t="s">
+        <v>25</v>
+      </c>
+      <c r="I233">
+        <v>0</v>
+      </c>
+      <c r="J233">
+        <v>0</v>
+      </c>
+      <c r="K233" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/data/catalogo_jusp.xlsx
+++ b/data/catalogo_jusp.xlsx
@@ -1263,7 +1263,9 @@
       <c r="K3" t="s">
         <v>26</v>
       </c>
-      <c r="L3"/>
+      <c r="L3">
+        <v>10</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
@@ -1299,7 +1301,9 @@
       <c r="K4" t="s">
         <v>26</v>
       </c>
-      <c r="L4"/>
+      <c r="L4">
+        <v>10</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
@@ -1335,7 +1339,9 @@
       <c r="K5" t="s">
         <v>26</v>
       </c>
-      <c r="L5"/>
+      <c r="L5">
+        <v>10</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
@@ -1371,7 +1377,9 @@
       <c r="K6" t="s">
         <v>26</v>
       </c>
-      <c r="L6"/>
+      <c r="L6">
+        <v>10</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
@@ -1407,7 +1415,9 @@
       <c r="K7" t="s">
         <v>26</v>
       </c>
-      <c r="L7"/>
+      <c r="L7">
+        <v>10</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
@@ -1443,7 +1453,9 @@
       <c r="K8" t="s">
         <v>26</v>
       </c>
-      <c r="L8"/>
+      <c r="L8">
+        <v>10</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
@@ -1479,7 +1491,9 @@
       <c r="K9" t="s">
         <v>26</v>
       </c>
-      <c r="L9"/>
+      <c r="L9">
+        <v>10</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
@@ -1515,77 +1529,145 @@
       <c r="K10" t="s">
         <v>26</v>
       </c>
-      <c r="L10"/>
+      <c r="L10">
+        <v>10</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11"/>
-      <c r="B11"/>
-      <c r="C11"/>
-      <c r="D11"/>
-      <c r="E11"/>
-      <c r="F11"/>
-      <c r="G11"/>
-      <c r="H11"/>
-      <c r="I11"/>
-      <c r="J11"/>
-      <c r="K11"/>
-      <c r="L11"/>
-      <c r="M11"/>
-      <c r="N11"/>
-      <c r="O11"/>
-      <c r="P11"/>
+      <c r="A11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11">
+        <v>99990</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H11" t="s">
+        <v>20</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11" t="s">
+        <v>21</v>
+      </c>
+      <c r="L11">
+        <v>30</v>
+      </c>
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
     </row>
     <row r="12">
-      <c r="A12"/>
-      <c r="B12"/>
-      <c r="C12"/>
-      <c r="D12"/>
-      <c r="E12"/>
-      <c r="F12"/>
-      <c r="G12"/>
-      <c r="H12"/>
-      <c r="I12"/>
-      <c r="J12"/>
-      <c r="K12"/>
-      <c r="L12"/>
-      <c r="M12"/>
+      <c r="A12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" t="s">
+        <v>35</v>
+      </c>
+      <c r="D12" t="s">
+        <v>36</v>
+      </c>
+      <c r="E12">
+        <v>119990</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12" t="s">
+        <v>20</v>
+      </c>
+      <c r="H12" t="s">
+        <v>20</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="K12" t="s">
+        <v>21</v>
+      </c>
+      <c r="L12">
+        <v>30</v>
+      </c>
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
-      <c r="P12"/>
     </row>
     <row r="13">
-      <c r="A13"/>
-      <c r="B13"/>
-      <c r="C13"/>
-      <c r="D13"/>
-      <c r="E13"/>
-      <c r="F13"/>
-      <c r="G13"/>
-      <c r="H13"/>
-      <c r="I13"/>
-      <c r="J13"/>
-      <c r="K13"/>
-      <c r="L13"/>
-      <c r="M13"/>
+      <c r="A13" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E13">
+        <v>95990</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H13" t="s">
+        <v>20</v>
+      </c>
+      <c r="I13">
+        <v>1</v>
+      </c>
+      <c r="J13">
+        <v>1</v>
+      </c>
+      <c r="K13" t="s">
+        <v>40</v>
+      </c>
+      <c r="L13">
+        <v>45</v>
+      </c>
       <c r="N13" s="3"/>
       <c r="O13" s="3"/>
-      <c r="P13"/>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="B14" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="C14" t="s">
         <v>18</v>
       </c>
       <c r="D14" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="E14">
-        <v>99990</v>
+        <v>110990</v>
       </c>
       <c r="F14">
         <v>1</v>
@@ -1603,29 +1685,29 @@
         <v>1</v>
       </c>
       <c r="K14" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="L14">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="C15" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="D15" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E15">
-        <v>119990</v>
+        <v>195990</v>
       </c>
       <c r="F15">
         <v>1</v>
@@ -1637,35 +1719,32 @@
         <v>20</v>
       </c>
       <c r="I15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>21</v>
-      </c>
-      <c r="L15">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B16" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C16" t="s">
         <v>18</v>
       </c>
       <c r="D16" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="E16">
-        <v>95990</v>
+        <v>205990</v>
       </c>
       <c r="F16">
         <v>1</v>
@@ -1677,15 +1756,12 @@
         <v>20</v>
       </c>
       <c r="I16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>40</v>
-      </c>
-      <c r="L16">
         <v>45</v>
       </c>
       <c r="N16" s="3"/>
@@ -1693,10 +1769,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B17" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C17" t="s">
         <v>18</v>
@@ -1705,7 +1781,7 @@
         <v>19</v>
       </c>
       <c r="E17">
-        <v>110990</v>
+        <v>139990</v>
       </c>
       <c r="F17">
         <v>1</v>
@@ -1733,19 +1809,19 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B18" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C18" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D18" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E18">
-        <v>195990</v>
+        <v>125990</v>
       </c>
       <c r="F18">
         <v>1</v>
@@ -1757,32 +1833,35 @@
         <v>20</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="s">
-        <v>45</v>
+        <v>50</v>
+      </c>
+      <c r="L18">
+        <v>35</v>
       </c>
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="B19" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="C19" t="s">
         <v>18</v>
       </c>
       <c r="D19" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="E19">
-        <v>205990</v>
+        <v>99990</v>
       </c>
       <c r="F19">
         <v>1</v>
@@ -1794,32 +1873,35 @@
         <v>20</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="s">
-        <v>45</v>
+        <v>21</v>
+      </c>
+      <c r="L19">
+        <v>25</v>
       </c>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B20" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C20" t="s">
         <v>18</v>
       </c>
       <c r="D20" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E20">
-        <v>139990</v>
+        <v>99990</v>
       </c>
       <c r="F20">
         <v>1</v>
@@ -1837,29 +1919,29 @@
         <v>1</v>
       </c>
       <c r="K20" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="L20">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="N20" s="3"/>
       <c r="O20" s="3"/>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B21" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C21" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="D21" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="E21">
-        <v>125990</v>
+        <v>109990</v>
       </c>
       <c r="F21">
         <v>1</v>
@@ -1871,26 +1953,26 @@
         <v>20</v>
       </c>
       <c r="I21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="L21">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="N21" s="3"/>
       <c r="O21" s="3"/>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B22" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C22" t="s">
         <v>18</v>
@@ -1899,7 +1981,7 @@
         <v>36</v>
       </c>
       <c r="E22">
-        <v>99990</v>
+        <v>119990</v>
       </c>
       <c r="F22">
         <v>1</v>
@@ -1911,26 +1993,26 @@
         <v>20</v>
       </c>
       <c r="I22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="L22">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N22" s="3"/>
       <c r="O22" s="3"/>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B23" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C23" t="s">
         <v>18</v>
@@ -1939,7 +2021,7 @@
         <v>32</v>
       </c>
       <c r="E23">
-        <v>99990</v>
+        <v>119990</v>
       </c>
       <c r="F23">
         <v>1</v>
@@ -1951,35 +2033,35 @@
         <v>20</v>
       </c>
       <c r="I23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="L23">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N23" s="3"/>
       <c r="O23" s="3"/>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="B24" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C24" t="s">
         <v>18</v>
       </c>
       <c r="D24" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="E24">
-        <v>109990</v>
+        <v>119990</v>
       </c>
       <c r="F24">
         <v>1</v>
@@ -1991,13 +2073,13 @@
         <v>20</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="L24">
         <v>30</v>
@@ -2007,13 +2089,13 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B25" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C25" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D25" t="s">
         <v>36</v>
@@ -2031,35 +2113,35 @@
         <v>20</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="L25">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="N25" s="3"/>
       <c r="O25" s="3"/>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="B26" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="C26" t="s">
         <v>18</v>
       </c>
       <c r="D26" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E26">
-        <v>119990</v>
+        <v>99990</v>
       </c>
       <c r="F26">
         <v>1</v>
@@ -2071,26 +2153,26 @@
         <v>20</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="L26">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N26" s="3"/>
       <c r="O26" s="3"/>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="B27" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="C27" t="s">
         <v>18</v>
@@ -2099,7 +2181,7 @@
         <v>32</v>
       </c>
       <c r="E27">
-        <v>119990</v>
+        <v>86990</v>
       </c>
       <c r="F27">
         <v>1</v>
@@ -2117,7 +2199,7 @@
         <v>1</v>
       </c>
       <c r="K27" t="s">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="L27">
         <v>30</v>
@@ -2127,19 +2209,19 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B28" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C28" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="D28" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="E28">
-        <v>119990</v>
+        <v>86990</v>
       </c>
       <c r="F28">
         <v>1</v>
@@ -2157,29 +2239,29 @@
         <v>1</v>
       </c>
       <c r="K28" t="s">
-        <v>63</v>
+        <v>21</v>
       </c>
       <c r="L28">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="N28" s="3"/>
       <c r="O28" s="3"/>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B29" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C29" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="D29" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E29">
-        <v>99990</v>
+        <v>96990</v>
       </c>
       <c r="F29">
         <v>1</v>
@@ -2197,7 +2279,7 @@
         <v>1</v>
       </c>
       <c r="K29" t="s">
-        <v>21</v>
+        <v>71</v>
       </c>
       <c r="L29">
         <v>25</v>
@@ -2207,19 +2289,19 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="B30" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C30" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="D30" t="s">
         <v>32</v>
       </c>
       <c r="E30">
-        <v>86990</v>
+        <v>95990</v>
       </c>
       <c r="F30">
         <v>1</v>
@@ -2240,155 +2322,148 @@
         <v>21</v>
       </c>
       <c r="L30">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N30" s="3"/>
       <c r="O30" s="3"/>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="B31" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="C31" t="s">
         <v>18</v>
       </c>
       <c r="D31" t="s">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="E31">
-        <v>86990</v>
+        <v>129990</v>
       </c>
       <c r="F31">
         <v>1</v>
       </c>
       <c r="G31" t="s">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="H31" t="s">
-        <v>20</v>
+        <v>78</v>
       </c>
       <c r="I31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K31" t="s">
         <v>21</v>
       </c>
-      <c r="L31">
-        <v>30</v>
-      </c>
       <c r="N31" s="3"/>
       <c r="O31" s="3"/>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="B32" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="C32" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="D32" t="s">
-        <v>32</v>
+        <v>81</v>
       </c>
       <c r="E32">
-        <v>96990</v>
+        <v>88990</v>
       </c>
       <c r="F32">
         <v>1</v>
       </c>
       <c r="G32" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="H32" t="s">
-        <v>20</v>
+        <v>83</v>
       </c>
       <c r="I32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32" t="s">
-        <v>71</v>
+        <v>21</v>
       </c>
       <c r="L32">
-        <v>25</v>
-      </c>
-      <c r="N32" s="3"/>
-      <c r="O32" s="3"/>
+        <v>5</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="B33" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="C33" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="D33" t="s">
-        <v>32</v>
+        <v>84</v>
       </c>
       <c r="E33">
-        <v>95990</v>
+        <v>88990</v>
       </c>
       <c r="F33">
         <v>1</v>
       </c>
       <c r="G33" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="H33" t="s">
-        <v>20</v>
+        <v>83</v>
       </c>
       <c r="I33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K33" t="s">
         <v>21</v>
       </c>
       <c r="L33">
-        <v>25</v>
-      </c>
-      <c r="N33" s="3"/>
-      <c r="O33" s="3"/>
+        <v>5</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="B34" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="C34" t="s">
         <v>18</v>
       </c>
       <c r="D34" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="E34">
-        <v>129990</v>
+        <v>89990</v>
       </c>
       <c r="F34">
         <v>1</v>
       </c>
       <c r="G34" t="s">
-        <v>77</v>
+        <v>20</v>
       </c>
       <c r="H34" t="s">
-        <v>78</v>
+        <v>20</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -2397,35 +2472,33 @@
         <v>0</v>
       </c>
       <c r="K34" t="s">
-        <v>21</v>
-      </c>
-      <c r="N34" s="3"/>
-      <c r="O34" s="3"/>
+        <v>87</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="B35" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C35" t="s">
         <v>18</v>
       </c>
       <c r="D35" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="E35">
-        <v>88990</v>
+        <v>89990</v>
       </c>
       <c r="F35">
         <v>1</v>
       </c>
       <c r="G35" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="H35" t="s">
-        <v>83</v>
+        <v>20</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -2434,36 +2507,33 @@
         <v>0</v>
       </c>
       <c r="K35" t="s">
-        <v>21</v>
-      </c>
-      <c r="L35">
-        <v>5</v>
+        <v>87</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="B36" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="C36" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D36" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="E36">
-        <v>88990</v>
+        <v>75990</v>
       </c>
       <c r="F36">
         <v>1</v>
       </c>
       <c r="G36" t="s">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="H36" t="s">
-        <v>83</v>
+        <v>25</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -2472,36 +2542,33 @@
         <v>0</v>
       </c>
       <c r="K36" t="s">
-        <v>21</v>
-      </c>
-      <c r="L36">
-        <v>5</v>
+        <v>91</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B37" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C37" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D37" t="s">
-        <v>55</v>
+        <v>92</v>
       </c>
       <c r="E37">
-        <v>89990</v>
+        <v>79990</v>
       </c>
       <c r="F37">
         <v>1</v>
       </c>
       <c r="G37" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H37" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -2510,33 +2577,33 @@
         <v>0</v>
       </c>
       <c r="K37" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B38" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C38" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D38" t="s">
-        <v>36</v>
+        <v>93</v>
       </c>
       <c r="E38">
-        <v>89990</v>
+        <v>78990</v>
       </c>
       <c r="F38">
         <v>1</v>
       </c>
       <c r="G38" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H38" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -2545,33 +2612,33 @@
         <v>0</v>
       </c>
       <c r="K38" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B39" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C39" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="D39" t="s">
-        <v>90</v>
+        <v>36</v>
       </c>
       <c r="E39">
-        <v>75990</v>
+        <v>69990</v>
       </c>
       <c r="F39">
         <v>1</v>
       </c>
       <c r="G39" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H39" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I39">
         <v>0</v>
@@ -2580,33 +2647,33 @@
         <v>0</v>
       </c>
       <c r="K39" t="s">
-        <v>91</v>
+        <v>26</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="B40" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="C40" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="D40" t="s">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="E40">
-        <v>79990</v>
+        <v>139990</v>
       </c>
       <c r="F40">
         <v>1</v>
       </c>
       <c r="G40" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H40" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I40">
         <v>0</v>
@@ -2615,27 +2682,27 @@
         <v>0</v>
       </c>
       <c r="K40" t="s">
-        <v>91</v>
+        <v>40</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="B41" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="C41" t="s">
-        <v>35</v>
-      </c>
-      <c r="D41" t="s">
-        <v>93</v>
+        <v>18</v>
+      </c>
+      <c r="D41">
+        <v>7</v>
       </c>
       <c r="E41">
-        <v>78990</v>
+        <v>99990</v>
       </c>
       <c r="F41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G41" t="s">
         <v>25</v>
@@ -2655,19 +2722,19 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="B42" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="C42" t="s">
         <v>18</v>
       </c>
       <c r="D42" t="s">
-        <v>36</v>
-      </c>
-      <c r="E42">
-        <v>69990</v>
+        <v>32</v>
+      </c>
+      <c r="E42" s="4">
+        <v>119990</v>
       </c>
       <c r="F42">
         <v>1</v>
@@ -2685,33 +2752,33 @@
         <v>0</v>
       </c>
       <c r="K42" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="B43" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="C43" t="s">
         <v>18</v>
       </c>
       <c r="D43" t="s">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="E43">
-        <v>139990</v>
+        <v>65990</v>
       </c>
       <c r="F43">
         <v>1</v>
       </c>
       <c r="G43" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H43" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I43">
         <v>0</v>
@@ -2720,27 +2787,27 @@
         <v>0</v>
       </c>
       <c r="K43" t="s">
-        <v>40</v>
+        <v>104</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B44" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C44" t="s">
         <v>18</v>
       </c>
-      <c r="D44">
-        <v>7</v>
+      <c r="D44" t="s">
+        <v>92</v>
       </c>
       <c r="E44">
-        <v>99990</v>
+        <v>75990</v>
       </c>
       <c r="F44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G44" t="s">
         <v>25</v>
@@ -2755,33 +2822,33 @@
         <v>0</v>
       </c>
       <c r="K44" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B45" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C45" t="s">
         <v>18</v>
       </c>
       <c r="D45" t="s">
-        <v>32</v>
-      </c>
-      <c r="E45" s="4">
-        <v>119990</v>
+        <v>93</v>
+      </c>
+      <c r="E45">
+        <v>85990</v>
       </c>
       <c r="F45">
         <v>1</v>
       </c>
       <c r="G45" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H45" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I45">
         <v>0</v>
@@ -2790,33 +2857,33 @@
         <v>0</v>
       </c>
       <c r="K45" t="s">
-        <v>40</v>
+        <v>104</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B46" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C46" t="s">
         <v>18</v>
       </c>
       <c r="D46" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="E46">
-        <v>65990</v>
+        <v>79990</v>
       </c>
       <c r="F46">
         <v>1</v>
       </c>
       <c r="G46" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H46" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I46">
         <v>0</v>
@@ -2825,33 +2892,33 @@
         <v>0</v>
       </c>
       <c r="K46" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B47" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C47" t="s">
         <v>18</v>
       </c>
       <c r="D47" t="s">
-        <v>92</v>
+        <v>55</v>
       </c>
       <c r="E47">
-        <v>75990</v>
+        <v>79990</v>
       </c>
       <c r="F47">
         <v>1</v>
       </c>
       <c r="G47" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H47" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I47">
         <v>0</v>
@@ -2860,33 +2927,33 @@
         <v>0</v>
       </c>
       <c r="K47" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B48" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C48" t="s">
         <v>18</v>
       </c>
       <c r="D48" t="s">
-        <v>93</v>
+        <v>36</v>
       </c>
       <c r="E48">
-        <v>85990</v>
+        <v>79990</v>
       </c>
       <c r="F48">
         <v>1</v>
       </c>
       <c r="G48" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H48" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I48">
         <v>0</v>
@@ -2895,7 +2962,7 @@
         <v>0</v>
       </c>
       <c r="K48" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
     </row>
     <row r="49">
@@ -2909,7 +2976,7 @@
         <v>18</v>
       </c>
       <c r="D49" t="s">
-        <v>107</v>
+        <v>32</v>
       </c>
       <c r="E49">
         <v>79990</v>
@@ -2944,7 +3011,7 @@
         <v>18</v>
       </c>
       <c r="D50" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="E50">
         <v>79990</v>
@@ -2970,19 +3037,19 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B51" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C51" t="s">
         <v>18</v>
       </c>
       <c r="D51" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="E51">
-        <v>79990</v>
+        <v>155990</v>
       </c>
       <c r="F51">
         <v>1</v>
@@ -3000,24 +3067,24 @@
         <v>0</v>
       </c>
       <c r="K51" t="s">
-        <v>91</v>
+        <v>60</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B52" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C52" t="s">
         <v>18</v>
       </c>
       <c r="D52" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E52">
-        <v>79990</v>
+        <v>155990</v>
       </c>
       <c r="F52">
         <v>1</v>
@@ -3035,24 +3102,24 @@
         <v>0</v>
       </c>
       <c r="K52" t="s">
-        <v>91</v>
+        <v>60</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B53" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C53" t="s">
         <v>18</v>
       </c>
       <c r="D53" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E53">
-        <v>79990</v>
+        <v>155990</v>
       </c>
       <c r="F53">
         <v>1</v>
@@ -3070,7 +3137,7 @@
         <v>0</v>
       </c>
       <c r="K53" t="s">
-        <v>91</v>
+        <v>60</v>
       </c>
     </row>
     <row r="54">
@@ -3084,7 +3151,7 @@
         <v>18</v>
       </c>
       <c r="D54" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="E54">
         <v>155990</v>
@@ -3110,19 +3177,19 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B55" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C55" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="D55" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="E55">
-        <v>155990</v>
+        <v>49990</v>
       </c>
       <c r="F55">
         <v>1</v>
@@ -3140,24 +3207,24 @@
         <v>0</v>
       </c>
       <c r="K55" t="s">
-        <v>60</v>
+        <v>21</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B56" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C56" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="D56" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E56">
-        <v>155990</v>
+        <v>49990</v>
       </c>
       <c r="F56">
         <v>1</v>
@@ -3175,24 +3242,24 @@
         <v>0</v>
       </c>
       <c r="K56" t="s">
-        <v>60</v>
+        <v>21</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B57" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C57" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D57" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="E57">
-        <v>155990</v>
+        <v>135990</v>
       </c>
       <c r="F57">
         <v>1</v>
@@ -3210,24 +3277,24 @@
         <v>0</v>
       </c>
       <c r="K57" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B58" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C58" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="D58" t="s">
         <v>55</v>
       </c>
       <c r="E58">
-        <v>49990</v>
+        <v>155990</v>
       </c>
       <c r="F58">
         <v>1</v>
@@ -3245,24 +3312,24 @@
         <v>0</v>
       </c>
       <c r="K58" t="s">
-        <v>21</v>
+        <v>116</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B59" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C59" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="D59" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E59">
-        <v>49990</v>
+        <v>155990</v>
       </c>
       <c r="F59">
         <v>1</v>
@@ -3280,24 +3347,24 @@
         <v>0</v>
       </c>
       <c r="K59" t="s">
-        <v>21</v>
+        <v>116</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B60" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C60" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="D60" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="E60">
-        <v>135990</v>
+        <v>155990</v>
       </c>
       <c r="F60">
         <v>1</v>
@@ -3315,33 +3382,33 @@
         <v>0</v>
       </c>
       <c r="K60" t="s">
-        <v>63</v>
+        <v>116</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B61" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C61" t="s">
         <v>18</v>
       </c>
       <c r="D61" t="s">
-        <v>55</v>
+        <v>92</v>
       </c>
       <c r="E61">
-        <v>155990</v>
+        <v>129990</v>
       </c>
       <c r="F61">
         <v>1</v>
       </c>
       <c r="G61" t="s">
-        <v>20</v>
+        <v>119</v>
       </c>
       <c r="H61" t="s">
-        <v>20</v>
+        <v>119</v>
       </c>
       <c r="I61">
         <v>0</v>
@@ -3350,33 +3417,33 @@
         <v>0</v>
       </c>
       <c r="K61" t="s">
-        <v>116</v>
+        <v>21</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B62" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C62" t="s">
         <v>18</v>
       </c>
       <c r="D62" t="s">
-        <v>32</v>
+        <v>93</v>
       </c>
       <c r="E62">
-        <v>155990</v>
+        <v>129990</v>
       </c>
       <c r="F62">
         <v>1</v>
       </c>
       <c r="G62" t="s">
-        <v>20</v>
+        <v>119</v>
       </c>
       <c r="H62" t="s">
-        <v>20</v>
+        <v>119</v>
       </c>
       <c r="I62">
         <v>0</v>
@@ -3385,33 +3452,33 @@
         <v>0</v>
       </c>
       <c r="K62" t="s">
-        <v>116</v>
+        <v>21</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="B63" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="C63" t="s">
-        <v>18</v>
+        <v>122</v>
       </c>
       <c r="D63" t="s">
-        <v>19</v>
+        <v>123</v>
       </c>
       <c r="E63">
-        <v>155990</v>
+        <v>179990</v>
       </c>
       <c r="F63">
         <v>1</v>
       </c>
       <c r="G63" t="s">
-        <v>20</v>
+        <v>119</v>
       </c>
       <c r="H63" t="s">
-        <v>20</v>
+        <v>119</v>
       </c>
       <c r="I63">
         <v>0</v>
@@ -3420,24 +3487,24 @@
         <v>0</v>
       </c>
       <c r="K63" t="s">
-        <v>116</v>
+        <v>21</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="B64" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="C64" t="s">
         <v>18</v>
       </c>
       <c r="D64" t="s">
-        <v>92</v>
+        <v>123</v>
       </c>
       <c r="E64">
-        <v>129990</v>
+        <v>159990</v>
       </c>
       <c r="F64">
         <v>1</v>
@@ -3460,19 +3527,19 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="B65" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="C65" t="s">
         <v>18</v>
       </c>
       <c r="D65" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E65">
-        <v>129990</v>
+        <v>134990</v>
       </c>
       <c r="F65">
         <v>1</v>
@@ -3495,19 +3562,19 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="B66" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="C66" t="s">
-        <v>122</v>
+        <v>18</v>
       </c>
       <c r="D66" t="s">
-        <v>123</v>
+        <v>92</v>
       </c>
       <c r="E66">
-        <v>179990</v>
+        <v>134990</v>
       </c>
       <c r="F66">
         <v>1</v>
@@ -3530,19 +3597,19 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B67" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C67" t="s">
         <v>18</v>
       </c>
       <c r="D67" t="s">
-        <v>123</v>
+        <v>93</v>
       </c>
       <c r="E67">
-        <v>159990</v>
+        <v>134990</v>
       </c>
       <c r="F67">
         <v>1</v>
@@ -3565,28 +3632,28 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B68" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C68" t="s">
         <v>18</v>
       </c>
       <c r="D68" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="E68">
-        <v>134990</v>
+        <v>79990</v>
       </c>
       <c r="F68">
         <v>1</v>
       </c>
       <c r="G68" t="s">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="H68" t="s">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="I68">
         <v>0</v>
@@ -3600,16 +3667,16 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B69" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C69" t="s">
         <v>18</v>
       </c>
       <c r="D69" t="s">
-        <v>92</v>
+        <v>55</v>
       </c>
       <c r="E69">
         <v>134990</v>
@@ -3618,10 +3685,10 @@
         <v>1</v>
       </c>
       <c r="G69" t="s">
-        <v>119</v>
+        <v>25</v>
       </c>
       <c r="H69" t="s">
-        <v>119</v>
+        <v>25</v>
       </c>
       <c r="I69">
         <v>0</v>
@@ -3635,16 +3702,16 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B70" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C70" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D70" t="s">
-        <v>93</v>
+        <v>36</v>
       </c>
       <c r="E70">
         <v>134990</v>
@@ -3653,10 +3720,10 @@
         <v>1</v>
       </c>
       <c r="G70" t="s">
-        <v>119</v>
+        <v>25</v>
       </c>
       <c r="H70" t="s">
-        <v>119</v>
+        <v>25</v>
       </c>
       <c r="I70">
         <v>0</v>
@@ -3670,28 +3737,28 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B71" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C71" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D71" t="s">
-        <v>76</v>
+        <v>32</v>
       </c>
       <c r="E71">
-        <v>79990</v>
+        <v>134990</v>
       </c>
       <c r="F71">
         <v>1</v>
       </c>
       <c r="G71" t="s">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="H71" t="s">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="I71">
         <v>0</v>
@@ -3711,10 +3778,10 @@
         <v>131</v>
       </c>
       <c r="C72" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D72" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="E72">
         <v>134990</v>
@@ -3749,7 +3816,7 @@
         <v>35</v>
       </c>
       <c r="D73" t="s">
-        <v>36</v>
+        <v>132</v>
       </c>
       <c r="E73">
         <v>134990</v>
@@ -3775,19 +3842,19 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B74" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C74" t="s">
         <v>35</v>
       </c>
       <c r="D74" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="E74">
-        <v>134990</v>
+        <v>119990</v>
       </c>
       <c r="F74">
         <v>1</v>
@@ -3796,7 +3863,7 @@
         <v>25</v>
       </c>
       <c r="H74" t="s">
-        <v>25</v>
+        <v>78</v>
       </c>
       <c r="I74">
         <v>0</v>
@@ -3810,19 +3877,19 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B75" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C75" t="s">
         <v>35</v>
       </c>
       <c r="D75" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="E75">
-        <v>134990</v>
+        <v>119990</v>
       </c>
       <c r="F75">
         <v>1</v>
@@ -3831,7 +3898,7 @@
         <v>25</v>
       </c>
       <c r="H75" t="s">
-        <v>25</v>
+        <v>78</v>
       </c>
       <c r="I75">
         <v>0</v>
@@ -3845,19 +3912,19 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B76" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C76" t="s">
         <v>35</v>
       </c>
       <c r="D76" t="s">
-        <v>132</v>
+        <v>32</v>
       </c>
       <c r="E76">
-        <v>134990</v>
+        <v>119990</v>
       </c>
       <c r="F76">
         <v>1</v>
@@ -3866,7 +3933,7 @@
         <v>25</v>
       </c>
       <c r="H76" t="s">
-        <v>25</v>
+        <v>78</v>
       </c>
       <c r="I76">
         <v>0</v>
@@ -3880,16 +3947,16 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B77" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C77" t="s">
         <v>35</v>
       </c>
       <c r="D77" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="E77">
         <v>119990</v>
@@ -3910,21 +3977,21 @@
         <v>0</v>
       </c>
       <c r="K77" t="s">
-        <v>21</v>
+        <v>137</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B78" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C78" t="s">
         <v>35</v>
       </c>
       <c r="D78" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E78">
         <v>119990</v>
@@ -3945,24 +4012,24 @@
         <v>0</v>
       </c>
       <c r="K78" t="s">
-        <v>21</v>
+        <v>137</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="B79" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="C79" t="s">
         <v>35</v>
       </c>
       <c r="D79" t="s">
-        <v>32</v>
+        <v>90</v>
       </c>
       <c r="E79">
-        <v>119990</v>
+        <v>39990</v>
       </c>
       <c r="F79">
         <v>1</v>
@@ -3985,19 +4052,19 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B80" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C80" t="s">
         <v>35</v>
       </c>
       <c r="D80" t="s">
-        <v>36</v>
+        <v>93</v>
       </c>
       <c r="E80">
-        <v>119990</v>
+        <v>39990</v>
       </c>
       <c r="F80">
         <v>1</v>
@@ -4015,24 +4082,24 @@
         <v>0</v>
       </c>
       <c r="K80" t="s">
-        <v>137</v>
+        <v>21</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="B81" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="C81" t="s">
         <v>35</v>
       </c>
       <c r="D81" t="s">
-        <v>32</v>
+        <v>93</v>
       </c>
       <c r="E81">
-        <v>119990</v>
+        <v>39990</v>
       </c>
       <c r="F81">
         <v>1</v>
@@ -4055,25 +4122,25 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B82" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C82" t="s">
-        <v>35</v>
+        <v>122</v>
       </c>
       <c r="D82" t="s">
-        <v>90</v>
+        <v>144</v>
       </c>
       <c r="E82">
-        <v>39990</v>
+        <v>140990</v>
       </c>
       <c r="F82">
         <v>1</v>
       </c>
       <c r="G82" t="s">
-        <v>25</v>
+        <v>119</v>
       </c>
       <c r="H82" t="s">
         <v>78</v>
@@ -4085,30 +4152,30 @@
         <v>0</v>
       </c>
       <c r="K82" t="s">
-        <v>21</v>
+        <v>91</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B83" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C83" t="s">
-        <v>35</v>
+        <v>122</v>
       </c>
       <c r="D83" t="s">
-        <v>93</v>
+        <v>145</v>
       </c>
       <c r="E83">
-        <v>39990</v>
+        <v>145990</v>
       </c>
       <c r="F83">
         <v>1</v>
       </c>
       <c r="G83" t="s">
-        <v>25</v>
+        <v>119</v>
       </c>
       <c r="H83" t="s">
         <v>78</v>
@@ -4120,24 +4187,24 @@
         <v>0</v>
       </c>
       <c r="K83" t="s">
-        <v>21</v>
+        <v>91</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="B84" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="C84" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="D84" t="s">
-        <v>93</v>
-      </c>
-      <c r="E84">
-        <v>39990</v>
+        <v>55</v>
+      </c>
+      <c r="E84" s="4">
+        <v>199990</v>
       </c>
       <c r="F84">
         <v>1</v>
@@ -4146,7 +4213,7 @@
         <v>25</v>
       </c>
       <c r="H84" t="s">
-        <v>78</v>
+        <v>25</v>
       </c>
       <c r="I84">
         <v>0</v>
@@ -4155,33 +4222,33 @@
         <v>0</v>
       </c>
       <c r="K84" t="s">
-        <v>137</v>
+        <v>40</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B85" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C85" t="s">
-        <v>122</v>
+        <v>18</v>
       </c>
       <c r="D85" t="s">
-        <v>144</v>
-      </c>
-      <c r="E85">
-        <v>140990</v>
+        <v>36</v>
+      </c>
+      <c r="E85" s="4">
+        <v>199990</v>
       </c>
       <c r="F85">
         <v>1</v>
       </c>
       <c r="G85" t="s">
-        <v>119</v>
+        <v>25</v>
       </c>
       <c r="H85" t="s">
-        <v>78</v>
+        <v>25</v>
       </c>
       <c r="I85">
         <v>0</v>
@@ -4190,33 +4257,33 @@
         <v>0</v>
       </c>
       <c r="K85" t="s">
-        <v>91</v>
+        <v>40</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B86" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C86" t="s">
-        <v>122</v>
+        <v>18</v>
       </c>
       <c r="D86" t="s">
-        <v>145</v>
-      </c>
-      <c r="E86">
-        <v>145990</v>
+        <v>32</v>
+      </c>
+      <c r="E86" s="4">
+        <v>199990</v>
       </c>
       <c r="F86">
         <v>1</v>
       </c>
       <c r="G86" t="s">
-        <v>119</v>
+        <v>25</v>
       </c>
       <c r="H86" t="s">
-        <v>78</v>
+        <v>25</v>
       </c>
       <c r="I86">
         <v>0</v>
@@ -4225,7 +4292,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="s">
-        <v>91</v>
+        <v>40</v>
       </c>
     </row>
     <row r="87">
@@ -4239,7 +4306,7 @@
         <v>18</v>
       </c>
       <c r="D87" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="E87" s="4">
         <v>199990</v>
@@ -4274,7 +4341,7 @@
         <v>18</v>
       </c>
       <c r="D88" t="s">
-        <v>36</v>
+        <v>132</v>
       </c>
       <c r="E88" s="4">
         <v>199990</v>
@@ -4300,19 +4367,19 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B89" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C89" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D89" t="s">
-        <v>32</v>
-      </c>
-      <c r="E89" s="4">
-        <v>199990</v>
+        <v>55</v>
+      </c>
+      <c r="E89">
+        <v>155990</v>
       </c>
       <c r="F89">
         <v>1</v>
@@ -4330,24 +4397,24 @@
         <v>0</v>
       </c>
       <c r="K89" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B90" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C90" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D90" t="s">
-        <v>19</v>
-      </c>
-      <c r="E90" s="4">
-        <v>199990</v>
+        <v>36</v>
+      </c>
+      <c r="E90">
+        <v>155990</v>
       </c>
       <c r="F90">
         <v>1</v>
@@ -4365,24 +4432,24 @@
         <v>0</v>
       </c>
       <c r="K90" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B91" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C91" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D91" t="s">
-        <v>132</v>
-      </c>
-      <c r="E91" s="4">
-        <v>199990</v>
+        <v>32</v>
+      </c>
+      <c r="E91">
+        <v>155990</v>
       </c>
       <c r="F91">
         <v>1</v>
@@ -4400,7 +4467,7 @@
         <v>0</v>
       </c>
       <c r="K91" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
     </row>
     <row r="92">
@@ -4414,7 +4481,7 @@
         <v>35</v>
       </c>
       <c r="D92" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="E92">
         <v>155990</v>
@@ -4440,19 +4507,19 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B93" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C93" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="D93" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="E93">
-        <v>155990</v>
+        <v>269990</v>
       </c>
       <c r="F93">
         <v>1</v>
@@ -4470,24 +4537,24 @@
         <v>0</v>
       </c>
       <c r="K93" t="s">
-        <v>21</v>
+        <v>152</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B94" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C94" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="D94" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E94">
-        <v>155990</v>
+        <v>269990</v>
       </c>
       <c r="F94">
         <v>1</v>
@@ -4505,24 +4572,24 @@
         <v>0</v>
       </c>
       <c r="K94" t="s">
-        <v>21</v>
+        <v>152</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B95" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C95" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="D95" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E95">
-        <v>155990</v>
+        <v>269990</v>
       </c>
       <c r="F95">
         <v>1</v>
@@ -4540,7 +4607,7 @@
         <v>0</v>
       </c>
       <c r="K95" t="s">
-        <v>21</v>
+        <v>152</v>
       </c>
     </row>
     <row r="96">
@@ -4554,7 +4621,7 @@
         <v>18</v>
       </c>
       <c r="D96" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="E96">
         <v>269990</v>
@@ -4589,7 +4656,7 @@
         <v>18</v>
       </c>
       <c r="D97" t="s">
-        <v>36</v>
+        <v>132</v>
       </c>
       <c r="E97">
         <v>269990</v>
@@ -4615,19 +4682,19 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B98" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C98" t="s">
         <v>18</v>
       </c>
       <c r="D98" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E98">
-        <v>269990</v>
+        <v>199990</v>
       </c>
       <c r="F98">
         <v>1</v>
@@ -4645,24 +4712,24 @@
         <v>0</v>
       </c>
       <c r="K98" t="s">
-        <v>152</v>
+        <v>40</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B99" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C99" t="s">
         <v>18</v>
       </c>
       <c r="D99" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E99">
-        <v>269990</v>
+        <v>199990</v>
       </c>
       <c r="F99">
         <v>1</v>
@@ -4680,24 +4747,24 @@
         <v>0</v>
       </c>
       <c r="K99" t="s">
-        <v>152</v>
+        <v>40</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B100" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C100" t="s">
         <v>18</v>
       </c>
       <c r="D100" t="s">
-        <v>132</v>
+        <v>19</v>
       </c>
       <c r="E100">
-        <v>269990</v>
+        <v>199990</v>
       </c>
       <c r="F100">
         <v>1</v>
@@ -4715,7 +4782,7 @@
         <v>0</v>
       </c>
       <c r="K100" t="s">
-        <v>152</v>
+        <v>40</v>
       </c>
     </row>
     <row r="101">
@@ -4729,7 +4796,7 @@
         <v>18</v>
       </c>
       <c r="D101" t="s">
-        <v>36</v>
+        <v>132</v>
       </c>
       <c r="E101">
         <v>199990</v>
@@ -4755,19 +4822,19 @@
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B102" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C102" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D102" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="E102">
-        <v>199990</v>
+        <v>194990</v>
       </c>
       <c r="F102">
         <v>1</v>
@@ -4785,24 +4852,24 @@
         <v>0</v>
       </c>
       <c r="K102" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B103" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C103" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D103" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="E103">
-        <v>199990</v>
+        <v>194990</v>
       </c>
       <c r="F103">
         <v>1</v>
@@ -4820,24 +4887,24 @@
         <v>0</v>
       </c>
       <c r="K103" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B104" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C104" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D104" t="s">
-        <v>132</v>
+        <v>32</v>
       </c>
       <c r="E104">
-        <v>199990</v>
+        <v>194990</v>
       </c>
       <c r="F104">
         <v>1</v>
@@ -4855,7 +4922,7 @@
         <v>0</v>
       </c>
       <c r="K104" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
     </row>
     <row r="105">
@@ -4869,7 +4936,7 @@
         <v>35</v>
       </c>
       <c r="D105" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="E105">
         <v>194990</v>
@@ -4895,28 +4962,28 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B106" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C106" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="D106" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="E106">
-        <v>194990</v>
+        <v>202990</v>
       </c>
       <c r="F106">
         <v>1</v>
       </c>
       <c r="G106" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H106" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I106">
         <v>0</v>
@@ -4925,24 +4992,24 @@
         <v>0</v>
       </c>
       <c r="K106" t="s">
-        <v>21</v>
+        <v>116</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B107" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="C107" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="D107" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="E107">
-        <v>194990</v>
+        <v>151990</v>
       </c>
       <c r="F107">
         <v>1</v>
@@ -4960,24 +5027,24 @@
         <v>0</v>
       </c>
       <c r="K107" t="s">
-        <v>21</v>
+        <v>60</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B108" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="C108" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="D108" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="E108">
-        <v>194990</v>
+        <v>151990</v>
       </c>
       <c r="F108">
         <v>1</v>
@@ -4995,33 +5062,33 @@
         <v>0</v>
       </c>
       <c r="K108" t="s">
-        <v>21</v>
+        <v>60</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B109" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C109" t="s">
         <v>18</v>
       </c>
       <c r="D109" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="E109">
-        <v>202990</v>
+        <v>151990</v>
       </c>
       <c r="F109">
         <v>1</v>
       </c>
       <c r="G109" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H109" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I109">
         <v>0</v>
@@ -5030,7 +5097,7 @@
         <v>0</v>
       </c>
       <c r="K109" t="s">
-        <v>116</v>
+        <v>60</v>
       </c>
     </row>
     <row r="110">
@@ -5044,7 +5111,7 @@
         <v>18</v>
       </c>
       <c r="D110" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="E110">
         <v>151990</v>
@@ -5079,7 +5146,7 @@
         <v>18</v>
       </c>
       <c r="D111" t="s">
-        <v>36</v>
+        <v>132</v>
       </c>
       <c r="E111">
         <v>151990</v>
@@ -5105,16 +5172,16 @@
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B112" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C112" t="s">
         <v>18</v>
       </c>
       <c r="D112" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="E112">
         <v>151990</v>
@@ -5135,21 +5202,21 @@
         <v>0</v>
       </c>
       <c r="K112" t="s">
-        <v>60</v>
+        <v>91</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B113" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C113" t="s">
         <v>18</v>
       </c>
       <c r="D113" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="E113">
         <v>151990</v>
@@ -5170,21 +5237,21 @@
         <v>0</v>
       </c>
       <c r="K113" t="s">
-        <v>60</v>
+        <v>91</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B114" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C114" t="s">
         <v>18</v>
       </c>
       <c r="D114" t="s">
-        <v>132</v>
+        <v>32</v>
       </c>
       <c r="E114">
         <v>151990</v>
@@ -5205,7 +5272,7 @@
         <v>0</v>
       </c>
       <c r="K114" t="s">
-        <v>60</v>
+        <v>91</v>
       </c>
     </row>
     <row r="115">
@@ -5219,7 +5286,7 @@
         <v>18</v>
       </c>
       <c r="D115" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="E115">
         <v>151990</v>
@@ -5254,7 +5321,7 @@
         <v>18</v>
       </c>
       <c r="D116" t="s">
-        <v>36</v>
+        <v>132</v>
       </c>
       <c r="E116">
         <v>151990</v>
@@ -5280,28 +5347,28 @@
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B117" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C117" t="s">
         <v>18</v>
       </c>
       <c r="D117" t="s">
-        <v>32</v>
+        <v>107</v>
       </c>
       <c r="E117">
-        <v>151990</v>
+        <v>119990</v>
       </c>
       <c r="F117">
         <v>1</v>
       </c>
       <c r="G117" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H117" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I117">
         <v>0</v>
@@ -5310,33 +5377,33 @@
         <v>0</v>
       </c>
       <c r="K117" t="s">
-        <v>91</v>
+        <v>21</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B118" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C118" t="s">
         <v>18</v>
       </c>
       <c r="D118" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E118">
-        <v>151990</v>
+        <v>210990</v>
       </c>
       <c r="F118">
         <v>1</v>
       </c>
       <c r="G118" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H118" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I118">
         <v>0</v>
@@ -5345,33 +5412,33 @@
         <v>0</v>
       </c>
       <c r="K118" t="s">
-        <v>91</v>
+        <v>21</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B119" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C119" t="s">
         <v>18</v>
       </c>
       <c r="D119" t="s">
-        <v>132</v>
+        <v>36</v>
       </c>
       <c r="E119">
-        <v>151990</v>
+        <v>210990</v>
       </c>
       <c r="F119">
         <v>1</v>
       </c>
       <c r="G119" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H119" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I119">
         <v>0</v>
@@ -5380,7 +5447,7 @@
         <v>0</v>
       </c>
       <c r="K119" t="s">
-        <v>91</v>
+        <v>21</v>
       </c>
     </row>
     <row r="120">
@@ -5394,10 +5461,10 @@
         <v>18</v>
       </c>
       <c r="D120" t="s">
-        <v>107</v>
+        <v>19</v>
       </c>
       <c r="E120">
-        <v>119990</v>
+        <v>210990</v>
       </c>
       <c r="F120">
         <v>1</v>
@@ -5420,19 +5487,19 @@
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B121" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C121" t="s">
         <v>18</v>
       </c>
       <c r="D121" t="s">
-        <v>55</v>
+        <v>107</v>
       </c>
       <c r="E121">
-        <v>210990</v>
+        <v>108990</v>
       </c>
       <c r="F121">
         <v>1</v>
@@ -5450,24 +5517,24 @@
         <v>0</v>
       </c>
       <c r="K121" t="s">
-        <v>21</v>
+        <v>167</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B122" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C122" t="s">
         <v>18</v>
       </c>
       <c r="D122" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="E122">
-        <v>210990</v>
+        <v>114990</v>
       </c>
       <c r="F122">
         <v>1</v>
@@ -5485,24 +5552,24 @@
         <v>0</v>
       </c>
       <c r="K122" t="s">
-        <v>21</v>
+        <v>167</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B123" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C123" t="s">
         <v>18</v>
       </c>
       <c r="D123" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="E123">
-        <v>210990</v>
+        <v>124990</v>
       </c>
       <c r="F123">
         <v>1</v>
@@ -5520,7 +5587,7 @@
         <v>0</v>
       </c>
       <c r="K123" t="s">
-        <v>21</v>
+        <v>167</v>
       </c>
     </row>
     <row r="124">
@@ -5534,10 +5601,10 @@
         <v>18</v>
       </c>
       <c r="D124" t="s">
-        <v>107</v>
+        <v>19</v>
       </c>
       <c r="E124">
-        <v>108990</v>
+        <v>183990</v>
       </c>
       <c r="F124">
         <v>1</v>
@@ -5569,10 +5636,10 @@
         <v>18</v>
       </c>
       <c r="D125" t="s">
-        <v>55</v>
+        <v>132</v>
       </c>
       <c r="E125">
-        <v>114990</v>
+        <v>140990</v>
       </c>
       <c r="F125">
         <v>1</v>
@@ -5595,19 +5662,19 @@
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B126" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C126" t="s">
         <v>18</v>
       </c>
       <c r="D126" t="s">
-        <v>36</v>
+        <v>107</v>
       </c>
       <c r="E126">
-        <v>124990</v>
+        <v>140990</v>
       </c>
       <c r="F126">
         <v>1</v>
@@ -5630,19 +5697,19 @@
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B127" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C127" t="s">
         <v>18</v>
       </c>
       <c r="D127" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E127">
-        <v>183990</v>
+        <v>140990</v>
       </c>
       <c r="F127">
         <v>1</v>
@@ -5665,16 +5732,16 @@
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B128" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C128" t="s">
         <v>18</v>
       </c>
       <c r="D128" t="s">
-        <v>132</v>
+        <v>36</v>
       </c>
       <c r="E128">
         <v>140990</v>
@@ -5709,7 +5776,7 @@
         <v>18</v>
       </c>
       <c r="D129" t="s">
-        <v>107</v>
+        <v>32</v>
       </c>
       <c r="E129">
         <v>140990</v>
@@ -5744,7 +5811,7 @@
         <v>18</v>
       </c>
       <c r="D130" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="E130">
         <v>140990</v>
@@ -5779,7 +5846,7 @@
         <v>18</v>
       </c>
       <c r="D131" t="s">
-        <v>36</v>
+        <v>132</v>
       </c>
       <c r="E131">
         <v>140990</v>
@@ -5805,19 +5872,19 @@
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B132" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C132" t="s">
         <v>18</v>
       </c>
       <c r="D132" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="E132">
-        <v>140990</v>
+        <v>92990</v>
       </c>
       <c r="F132">
         <v>1</v>
@@ -5835,24 +5902,24 @@
         <v>0</v>
       </c>
       <c r="K132" t="s">
-        <v>167</v>
+        <v>60</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B133" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C133" t="s">
         <v>18</v>
       </c>
       <c r="D133" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="E133">
-        <v>140990</v>
+        <v>92990</v>
       </c>
       <c r="F133">
         <v>1</v>
@@ -5870,24 +5937,24 @@
         <v>0</v>
       </c>
       <c r="K133" t="s">
-        <v>167</v>
+        <v>60</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B134" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C134" t="s">
         <v>18</v>
       </c>
       <c r="D134" t="s">
-        <v>132</v>
+        <v>32</v>
       </c>
       <c r="E134">
-        <v>140990</v>
+        <v>92990</v>
       </c>
       <c r="F134">
         <v>1</v>
@@ -5905,7 +5972,7 @@
         <v>0</v>
       </c>
       <c r="K134" t="s">
-        <v>167</v>
+        <v>60</v>
       </c>
     </row>
     <row r="135">
@@ -5919,7 +5986,7 @@
         <v>18</v>
       </c>
       <c r="D135" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="E135">
         <v>92990</v>
@@ -5954,7 +6021,7 @@
         <v>18</v>
       </c>
       <c r="D136" t="s">
-        <v>36</v>
+        <v>132</v>
       </c>
       <c r="E136">
         <v>92990</v>
@@ -5980,19 +6047,19 @@
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B137" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C137" t="s">
         <v>18</v>
       </c>
       <c r="D137" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E137">
-        <v>92990</v>
+        <v>108990</v>
       </c>
       <c r="F137">
         <v>1</v>
@@ -6010,24 +6077,24 @@
         <v>0</v>
       </c>
       <c r="K137" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B138" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C138" t="s">
         <v>18</v>
       </c>
       <c r="D138" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E138">
-        <v>92990</v>
+        <v>108990</v>
       </c>
       <c r="F138">
         <v>1</v>
@@ -6045,24 +6112,24 @@
         <v>0</v>
       </c>
       <c r="K138" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B139" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C139" t="s">
         <v>18</v>
       </c>
       <c r="D139" t="s">
-        <v>132</v>
+        <v>19</v>
       </c>
       <c r="E139">
-        <v>92990</v>
+        <v>108990</v>
       </c>
       <c r="F139">
         <v>1</v>
@@ -6080,33 +6147,33 @@
         <v>0</v>
       </c>
       <c r="K139" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B140" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C140" t="s">
         <v>18</v>
       </c>
       <c r="D140" t="s">
-        <v>36</v>
+        <v>176</v>
       </c>
       <c r="E140">
-        <v>108990</v>
+        <v>81990</v>
       </c>
       <c r="F140">
         <v>1</v>
       </c>
       <c r="G140" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="H140" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="I140">
         <v>0</v>
@@ -6115,33 +6182,33 @@
         <v>0</v>
       </c>
       <c r="K140" t="s">
-        <v>40</v>
+        <v>116</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B141" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C141" t="s">
         <v>18</v>
       </c>
       <c r="D141" t="s">
-        <v>32</v>
+        <v>177</v>
       </c>
       <c r="E141">
-        <v>108990</v>
+        <v>81990</v>
       </c>
       <c r="F141">
         <v>1</v>
       </c>
       <c r="G141" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="H141" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="I141">
         <v>0</v>
@@ -6150,33 +6217,33 @@
         <v>0</v>
       </c>
       <c r="K141" t="s">
-        <v>40</v>
+        <v>116</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="B142" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="C142" t="s">
         <v>18</v>
       </c>
       <c r="D142" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E142">
-        <v>108990</v>
+        <v>125990</v>
       </c>
       <c r="F142">
         <v>1</v>
       </c>
       <c r="G142" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H142" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I142">
         <v>0</v>
@@ -6185,33 +6252,33 @@
         <v>0</v>
       </c>
       <c r="K142" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B143" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C143" t="s">
         <v>18</v>
       </c>
       <c r="D143" t="s">
-        <v>176</v>
+        <v>36</v>
       </c>
       <c r="E143">
-        <v>81990</v>
+        <v>125990</v>
       </c>
       <c r="F143">
         <v>1</v>
       </c>
       <c r="G143" t="s">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="H143" t="s">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="I143">
         <v>0</v>
@@ -6220,33 +6287,33 @@
         <v>0</v>
       </c>
       <c r="K143" t="s">
-        <v>116</v>
+        <v>21</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="B144" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="C144" t="s">
         <v>18</v>
       </c>
       <c r="D144" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="E144">
-        <v>81990</v>
+        <v>125990</v>
       </c>
       <c r="F144">
         <v>1</v>
       </c>
       <c r="G144" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="H144" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="I144">
         <v>0</v>
@@ -6255,21 +6322,21 @@
         <v>0</v>
       </c>
       <c r="K144" t="s">
-        <v>116</v>
+        <v>45</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B145" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C145" t="s">
         <v>18</v>
       </c>
-      <c r="D145" t="s">
-        <v>55</v>
+      <c r="D145">
+        <v>38</v>
       </c>
       <c r="E145">
         <v>125990</v>
@@ -6278,10 +6345,10 @@
         <v>1</v>
       </c>
       <c r="G145" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H145" t="s">
-        <v>25</v>
+        <v>78</v>
       </c>
       <c r="I145">
         <v>0</v>
@@ -6290,21 +6357,21 @@
         <v>0</v>
       </c>
       <c r="K145" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B146" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C146" t="s">
         <v>18</v>
       </c>
-      <c r="D146" t="s">
-        <v>36</v>
+      <c r="D146">
+        <v>39</v>
       </c>
       <c r="E146">
         <v>125990</v>
@@ -6313,10 +6380,10 @@
         <v>1</v>
       </c>
       <c r="G146" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H146" t="s">
-        <v>25</v>
+        <v>78</v>
       </c>
       <c r="I146">
         <v>0</v>
@@ -6325,7 +6392,7 @@
         <v>0</v>
       </c>
       <c r="K146" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
     </row>
     <row r="147">
@@ -6338,8 +6405,8 @@
       <c r="C147" t="s">
         <v>18</v>
       </c>
-      <c r="D147" t="s">
-        <v>182</v>
+      <c r="D147">
+        <v>42</v>
       </c>
       <c r="E147">
         <v>125990</v>
@@ -6365,28 +6432,28 @@
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B148" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C148" t="s">
         <v>18</v>
       </c>
-      <c r="D148">
-        <v>38</v>
+      <c r="D148" t="s">
+        <v>36</v>
       </c>
       <c r="E148">
-        <v>125990</v>
+        <v>145990</v>
       </c>
       <c r="F148">
         <v>1</v>
       </c>
       <c r="G148" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H148" t="s">
-        <v>78</v>
+        <v>25</v>
       </c>
       <c r="I148">
         <v>0</v>
@@ -6395,33 +6462,33 @@
         <v>0</v>
       </c>
       <c r="K148" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B149" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C149" t="s">
         <v>18</v>
       </c>
-      <c r="D149">
-        <v>39</v>
+      <c r="D149" t="s">
+        <v>32</v>
       </c>
       <c r="E149">
-        <v>125990</v>
+        <v>145990</v>
       </c>
       <c r="F149">
         <v>1</v>
       </c>
       <c r="G149" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H149" t="s">
-        <v>78</v>
+        <v>25</v>
       </c>
       <c r="I149">
         <v>0</v>
@@ -6430,33 +6497,33 @@
         <v>0</v>
       </c>
       <c r="K149" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B150" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C150" t="s">
         <v>18</v>
       </c>
-      <c r="D150">
-        <v>42</v>
+      <c r="D150" t="s">
+        <v>19</v>
       </c>
       <c r="E150">
-        <v>125990</v>
+        <v>145990</v>
       </c>
       <c r="F150">
         <v>1</v>
       </c>
       <c r="G150" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H150" t="s">
-        <v>78</v>
+        <v>25</v>
       </c>
       <c r="I150">
         <v>0</v>
@@ -6465,7 +6532,7 @@
         <v>0</v>
       </c>
       <c r="K150" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
     </row>
     <row r="151">
@@ -6479,7 +6546,7 @@
         <v>18</v>
       </c>
       <c r="D151" t="s">
-        <v>36</v>
+        <v>132</v>
       </c>
       <c r="E151">
         <v>145990</v>
@@ -6505,19 +6572,19 @@
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B152" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C152" t="s">
         <v>18</v>
       </c>
       <c r="D152" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="E152">
-        <v>145990</v>
+        <v>199990</v>
       </c>
       <c r="F152">
         <v>1</v>
@@ -6540,19 +6607,19 @@
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B153" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C153" t="s">
         <v>18</v>
       </c>
       <c r="D153" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="E153">
-        <v>145990</v>
+        <v>199990</v>
       </c>
       <c r="F153">
         <v>1</v>
@@ -6575,19 +6642,19 @@
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B154" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C154" t="s">
         <v>18</v>
       </c>
       <c r="D154" t="s">
-        <v>132</v>
+        <v>32</v>
       </c>
       <c r="E154">
-        <v>145990</v>
+        <v>199990</v>
       </c>
       <c r="F154">
         <v>1</v>
@@ -6619,7 +6686,7 @@
         <v>18</v>
       </c>
       <c r="D155" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="E155">
         <v>199990</v>
@@ -6654,7 +6721,7 @@
         <v>18</v>
       </c>
       <c r="D156" t="s">
-        <v>36</v>
+        <v>132</v>
       </c>
       <c r="E156">
         <v>199990</v>
@@ -6680,19 +6747,19 @@
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B157" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C157" t="s">
         <v>18</v>
       </c>
       <c r="D157" t="s">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="E157">
-        <v>199990</v>
+        <v>159990</v>
       </c>
       <c r="F157">
         <v>1</v>
@@ -6710,21 +6777,21 @@
         <v>0</v>
       </c>
       <c r="K157" t="s">
-        <v>21</v>
+        <v>189</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B158" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C158" t="s">
         <v>18</v>
       </c>
       <c r="D158" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E158">
         <v>199990</v>
@@ -6745,21 +6812,21 @@
         <v>0</v>
       </c>
       <c r="K158" t="s">
-        <v>21</v>
+        <v>189</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B159" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C159" t="s">
         <v>18</v>
       </c>
       <c r="D159" t="s">
-        <v>132</v>
+        <v>19</v>
       </c>
       <c r="E159">
         <v>199990</v>
@@ -6780,33 +6847,33 @@
         <v>0</v>
       </c>
       <c r="K159" t="s">
-        <v>21</v>
+        <v>189</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B160" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C160" t="s">
         <v>18</v>
       </c>
       <c r="D160" t="s">
-        <v>132</v>
+        <v>36</v>
       </c>
       <c r="E160">
-        <v>159990</v>
+        <v>109990</v>
       </c>
       <c r="F160">
         <v>1</v>
       </c>
       <c r="G160" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H160" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I160">
         <v>0</v>
@@ -6815,15 +6882,15 @@
         <v>0</v>
       </c>
       <c r="K160" t="s">
-        <v>189</v>
+        <v>45</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B161" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C161" t="s">
         <v>18</v>
@@ -6832,16 +6899,16 @@
         <v>32</v>
       </c>
       <c r="E161">
-        <v>199990</v>
+        <v>109990</v>
       </c>
       <c r="F161">
         <v>1</v>
       </c>
       <c r="G161" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H161" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I161">
         <v>0</v>
@@ -6850,15 +6917,15 @@
         <v>0</v>
       </c>
       <c r="K161" t="s">
-        <v>189</v>
+        <v>45</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B162" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C162" t="s">
         <v>18</v>
@@ -6867,16 +6934,16 @@
         <v>19</v>
       </c>
       <c r="E162">
-        <v>199990</v>
+        <v>109990</v>
       </c>
       <c r="F162">
         <v>1</v>
       </c>
       <c r="G162" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H162" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I162">
         <v>0</v>
@@ -6885,24 +6952,24 @@
         <v>0</v>
       </c>
       <c r="K162" t="s">
-        <v>189</v>
+        <v>45</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B163" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C163" t="s">
         <v>18</v>
       </c>
       <c r="D163" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="E163">
-        <v>109990</v>
+        <v>115990</v>
       </c>
       <c r="F163">
         <v>1</v>
@@ -6920,15 +6987,15 @@
         <v>0</v>
       </c>
       <c r="K163" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B164" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C164" t="s">
         <v>18</v>
@@ -6937,7 +7004,7 @@
         <v>32</v>
       </c>
       <c r="E164">
-        <v>109990</v>
+        <v>119990</v>
       </c>
       <c r="F164">
         <v>1</v>
@@ -6955,33 +7022,33 @@
         <v>0</v>
       </c>
       <c r="K164" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="B165" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C165" t="s">
-        <v>18</v>
+        <v>196</v>
       </c>
       <c r="D165" t="s">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="E165">
-        <v>109990</v>
+        <v>85990</v>
       </c>
       <c r="F165">
         <v>1</v>
       </c>
       <c r="G165" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H165" t="s">
-        <v>20</v>
+        <v>78</v>
       </c>
       <c r="I165">
         <v>0</v>
@@ -6990,24 +7057,24 @@
         <v>0</v>
       </c>
       <c r="K165" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="B166" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="C166" t="s">
         <v>18</v>
       </c>
       <c r="D166" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E166">
-        <v>115990</v>
+        <v>105990</v>
       </c>
       <c r="F166">
         <v>1</v>
@@ -7025,24 +7092,24 @@
         <v>0</v>
       </c>
       <c r="K166" t="s">
-        <v>40</v>
+        <v>91</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="B167" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="C167" t="s">
         <v>18</v>
       </c>
       <c r="D167" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E167">
-        <v>119990</v>
+        <v>105990</v>
       </c>
       <c r="F167">
         <v>1</v>
@@ -7060,33 +7127,33 @@
         <v>0</v>
       </c>
       <c r="K167" t="s">
-        <v>40</v>
+        <v>91</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B168" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C168" t="s">
-        <v>196</v>
+        <v>18</v>
       </c>
       <c r="D168" t="s">
-        <v>76</v>
+        <v>32</v>
       </c>
       <c r="E168">
-        <v>85990</v>
+        <v>105990</v>
       </c>
       <c r="F168">
         <v>1</v>
       </c>
       <c r="G168" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H168" t="s">
-        <v>78</v>
+        <v>20</v>
       </c>
       <c r="I168">
         <v>0</v>
@@ -7095,7 +7162,7 @@
         <v>0</v>
       </c>
       <c r="K168" t="s">
-        <v>21</v>
+        <v>91</v>
       </c>
     </row>
     <row r="169">
@@ -7109,7 +7176,7 @@
         <v>18</v>
       </c>
       <c r="D169" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="E169">
         <v>105990</v>
@@ -7135,19 +7202,19 @@
     </row>
     <row r="170">
       <c r="A170" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B170" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C170" t="s">
         <v>18</v>
       </c>
       <c r="D170" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="E170">
-        <v>105990</v>
+        <v>119990</v>
       </c>
       <c r="F170">
         <v>1</v>
@@ -7165,15 +7232,15 @@
         <v>0</v>
       </c>
       <c r="K170" t="s">
-        <v>91</v>
+        <v>201</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B171" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C171" t="s">
         <v>18</v>
@@ -7182,7 +7249,7 @@
         <v>32</v>
       </c>
       <c r="E171">
-        <v>105990</v>
+        <v>189990</v>
       </c>
       <c r="F171">
         <v>1</v>
@@ -7200,24 +7267,24 @@
         <v>0</v>
       </c>
       <c r="K171" t="s">
-        <v>91</v>
+        <v>201</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="B172" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="C172" t="s">
         <v>18</v>
       </c>
       <c r="D172" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="E172">
-        <v>105990</v>
+        <v>179990</v>
       </c>
       <c r="F172">
         <v>1</v>
@@ -7235,24 +7302,24 @@
         <v>0</v>
       </c>
       <c r="K172" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B173" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C173" t="s">
         <v>18</v>
       </c>
       <c r="D173" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="E173">
-        <v>119990</v>
+        <v>179990</v>
       </c>
       <c r="F173">
         <v>1</v>
@@ -7270,24 +7337,24 @@
         <v>0</v>
       </c>
       <c r="K173" t="s">
-        <v>201</v>
+        <v>71</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B174" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C174" t="s">
         <v>18</v>
       </c>
       <c r="D174" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="E174">
-        <v>189990</v>
+        <v>130990</v>
       </c>
       <c r="F174">
         <v>1</v>
@@ -7305,33 +7372,33 @@
         <v>0</v>
       </c>
       <c r="K174" t="s">
-        <v>201</v>
+        <v>71</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B175" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C175" t="s">
         <v>18</v>
       </c>
       <c r="D175" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E175">
-        <v>179990</v>
+        <v>109990</v>
       </c>
       <c r="F175">
         <v>1</v>
       </c>
       <c r="G175" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="H175" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="I175">
         <v>0</v>
@@ -7340,33 +7407,33 @@
         <v>0</v>
       </c>
       <c r="K175" t="s">
-        <v>71</v>
+        <v>21</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B176" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C176" t="s">
         <v>18</v>
       </c>
       <c r="D176" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="E176">
-        <v>179990</v>
+        <v>109990</v>
       </c>
       <c r="F176">
         <v>1</v>
       </c>
       <c r="G176" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="H176" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="I176">
         <v>0</v>
@@ -7375,33 +7442,33 @@
         <v>0</v>
       </c>
       <c r="K176" t="s">
-        <v>71</v>
+        <v>21</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B177" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="C177" t="s">
         <v>18</v>
       </c>
       <c r="D177" t="s">
-        <v>19</v>
+        <v>208</v>
       </c>
       <c r="E177">
-        <v>130990</v>
+        <v>82990</v>
       </c>
       <c r="F177">
         <v>1</v>
       </c>
       <c r="G177" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="H177" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="I177">
         <v>0</v>
@@ -7410,24 +7477,24 @@
         <v>0</v>
       </c>
       <c r="K177" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B178" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C178" t="s">
         <v>18</v>
       </c>
       <c r="D178" t="s">
-        <v>32</v>
+        <v>208</v>
       </c>
       <c r="E178">
-        <v>109990</v>
+        <v>82990</v>
       </c>
       <c r="F178">
         <v>1</v>
@@ -7450,28 +7517,28 @@
     </row>
     <row r="179">
       <c r="A179" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="B179" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="C179" t="s">
         <v>18</v>
       </c>
       <c r="D179" t="s">
-        <v>19</v>
+        <v>211</v>
       </c>
       <c r="E179">
-        <v>109990</v>
+        <v>119990</v>
       </c>
       <c r="F179">
         <v>1</v>
       </c>
       <c r="G179" t="s">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="H179" t="s">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="I179">
         <v>0</v>
@@ -7485,28 +7552,28 @@
     </row>
     <row r="180">
       <c r="A180" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B180" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C180" t="s">
         <v>18</v>
       </c>
       <c r="D180" t="s">
-        <v>208</v>
+        <v>32</v>
       </c>
       <c r="E180">
-        <v>82990</v>
+        <v>119990</v>
       </c>
       <c r="F180">
         <v>1</v>
       </c>
       <c r="G180" t="s">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="H180" t="s">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="I180">
         <v>0</v>
@@ -7515,33 +7582,33 @@
         <v>0</v>
       </c>
       <c r="K180" t="s">
-        <v>87</v>
+        <v>21</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B181" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C181" t="s">
         <v>18</v>
       </c>
       <c r="D181" t="s">
-        <v>208</v>
+        <v>19</v>
       </c>
       <c r="E181">
-        <v>82990</v>
+        <v>119990</v>
       </c>
       <c r="F181">
         <v>1</v>
       </c>
       <c r="G181" t="s">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="H181" t="s">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="I181">
         <v>0</v>
@@ -7585,7 +7652,7 @@
         <v>0</v>
       </c>
       <c r="K182" t="s">
-        <v>21</v>
+        <v>50</v>
       </c>
     </row>
     <row r="183">
@@ -7620,7 +7687,7 @@
         <v>0</v>
       </c>
       <c r="K183" t="s">
-        <v>21</v>
+        <v>50</v>
       </c>
     </row>
     <row r="184">
@@ -7655,24 +7722,24 @@
         <v>0</v>
       </c>
       <c r="K184" t="s">
-        <v>21</v>
+        <v>50</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B185" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C185" t="s">
         <v>18</v>
       </c>
       <c r="D185" t="s">
-        <v>211</v>
+        <v>55</v>
       </c>
       <c r="E185">
-        <v>119990</v>
+        <v>129990</v>
       </c>
       <c r="F185">
         <v>1</v>
@@ -7690,21 +7757,21 @@
         <v>0</v>
       </c>
       <c r="K185" t="s">
-        <v>50</v>
+        <v>214</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B186" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C186" t="s">
         <v>18</v>
       </c>
       <c r="D186" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E186">
         <v>119990</v>
@@ -7725,21 +7792,21 @@
         <v>0</v>
       </c>
       <c r="K186" t="s">
-        <v>50</v>
+        <v>214</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B187" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C187" t="s">
         <v>18</v>
       </c>
       <c r="D187" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E187">
         <v>119990</v>
@@ -7760,7 +7827,7 @@
         <v>0</v>
       </c>
       <c r="K187" t="s">
-        <v>50</v>
+        <v>214</v>
       </c>
     </row>
     <row r="188">
@@ -7774,10 +7841,10 @@
         <v>18</v>
       </c>
       <c r="D188" t="s">
-        <v>55</v>
+        <v>132</v>
       </c>
       <c r="E188">
-        <v>129990</v>
+        <v>119990</v>
       </c>
       <c r="F188">
         <v>1</v>
@@ -7809,10 +7876,10 @@
         <v>18</v>
       </c>
       <c r="D189" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="E189">
-        <v>119990</v>
+        <v>129990</v>
       </c>
       <c r="F189">
         <v>1</v>
@@ -7830,7 +7897,7 @@
         <v>0</v>
       </c>
       <c r="K189" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="190">
@@ -7844,7 +7911,7 @@
         <v>18</v>
       </c>
       <c r="D190" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E190">
         <v>119990</v>
@@ -7865,7 +7932,7 @@
         <v>0</v>
       </c>
       <c r="K190" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="191">
@@ -7879,7 +7946,7 @@
         <v>18</v>
       </c>
       <c r="D191" t="s">
-        <v>132</v>
+        <v>32</v>
       </c>
       <c r="E191">
         <v>119990</v>
@@ -7900,7 +7967,7 @@
         <v>0</v>
       </c>
       <c r="K191" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="192">
@@ -7914,10 +7981,10 @@
         <v>18</v>
       </c>
       <c r="D192" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="E192">
-        <v>129990</v>
+        <v>119990</v>
       </c>
       <c r="F192">
         <v>1</v>
@@ -7949,7 +8016,7 @@
         <v>18</v>
       </c>
       <c r="D193" t="s">
-        <v>36</v>
+        <v>132</v>
       </c>
       <c r="E193">
         <v>119990</v>
@@ -7975,19 +8042,19 @@
     </row>
     <row r="194">
       <c r="A194" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B194" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="C194" t="s">
         <v>18</v>
       </c>
       <c r="D194" t="s">
-        <v>32</v>
+        <v>107</v>
       </c>
       <c r="E194">
-        <v>119990</v>
+        <v>165990</v>
       </c>
       <c r="F194">
         <v>1</v>
@@ -8005,24 +8072,24 @@
         <v>0</v>
       </c>
       <c r="K194" t="s">
-        <v>215</v>
+        <v>63</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B195" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="C195" t="s">
         <v>18</v>
       </c>
       <c r="D195" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="E195">
-        <v>119990</v>
+        <v>149990</v>
       </c>
       <c r="F195">
         <v>1</v>
@@ -8040,24 +8107,24 @@
         <v>0</v>
       </c>
       <c r="K195" t="s">
-        <v>215</v>
+        <v>63</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B196" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="C196" t="s">
         <v>18</v>
       </c>
       <c r="D196" t="s">
-        <v>132</v>
+        <v>32</v>
       </c>
       <c r="E196">
-        <v>119990</v>
+        <v>149990</v>
       </c>
       <c r="F196">
         <v>1</v>
@@ -8075,7 +8142,7 @@
         <v>0</v>
       </c>
       <c r="K196" t="s">
-        <v>215</v>
+        <v>63</v>
       </c>
     </row>
     <row r="197">
@@ -8089,10 +8156,10 @@
         <v>18</v>
       </c>
       <c r="D197" t="s">
-        <v>107</v>
+        <v>19</v>
       </c>
       <c r="E197">
-        <v>165990</v>
+        <v>149990</v>
       </c>
       <c r="F197">
         <v>1</v>
@@ -8124,7 +8191,7 @@
         <v>18</v>
       </c>
       <c r="D198" t="s">
-        <v>36</v>
+        <v>132</v>
       </c>
       <c r="E198">
         <v>149990</v>
@@ -8150,28 +8217,28 @@
     </row>
     <row r="199">
       <c r="A199" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B199" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C199" t="s">
         <v>18</v>
       </c>
       <c r="D199" t="s">
-        <v>32</v>
+        <v>107</v>
       </c>
       <c r="E199">
-        <v>149990</v>
+        <v>189990</v>
       </c>
       <c r="F199">
         <v>1</v>
       </c>
       <c r="G199" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H199" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I199">
         <v>0</v>
@@ -8180,33 +8247,33 @@
         <v>0</v>
       </c>
       <c r="K199" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B200" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C200" t="s">
         <v>18</v>
       </c>
       <c r="D200" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="E200">
-        <v>149990</v>
+        <v>189990</v>
       </c>
       <c r="F200">
         <v>1</v>
       </c>
       <c r="G200" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H200" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I200">
         <v>0</v>
@@ -8215,33 +8282,33 @@
         <v>0</v>
       </c>
       <c r="K200" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B201" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C201" t="s">
         <v>18</v>
       </c>
       <c r="D201" t="s">
-        <v>132</v>
+        <v>32</v>
       </c>
       <c r="E201">
-        <v>149990</v>
+        <v>189990</v>
       </c>
       <c r="F201">
         <v>1</v>
       </c>
       <c r="G201" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H201" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I201">
         <v>0</v>
@@ -8250,24 +8317,24 @@
         <v>0</v>
       </c>
       <c r="K201" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B202" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C202" t="s">
         <v>18</v>
       </c>
       <c r="D202" t="s">
-        <v>107</v>
+        <v>55</v>
       </c>
       <c r="E202">
-        <v>189990</v>
+        <v>185990</v>
       </c>
       <c r="F202">
         <v>1</v>
@@ -8285,24 +8352,24 @@
         <v>0</v>
       </c>
       <c r="K202" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B203" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C203" t="s">
         <v>18</v>
       </c>
       <c r="D203" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E203">
-        <v>189990</v>
+        <v>185990</v>
       </c>
       <c r="F203">
         <v>1</v>
@@ -8320,24 +8387,24 @@
         <v>0</v>
       </c>
       <c r="K203" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B204" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C204" t="s">
         <v>18</v>
       </c>
       <c r="D204" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="E204">
-        <v>189990</v>
+        <v>185990</v>
       </c>
       <c r="F204">
         <v>1</v>
@@ -8355,33 +8422,33 @@
         <v>0</v>
       </c>
       <c r="K204" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B205" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C205" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D205" t="s">
-        <v>55</v>
+        <v>224</v>
       </c>
       <c r="E205">
-        <v>185990</v>
+        <v>125990</v>
       </c>
       <c r="F205">
         <v>1</v>
       </c>
       <c r="G205" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="H205" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="I205">
         <v>0</v>
@@ -8390,33 +8457,33 @@
         <v>0</v>
       </c>
       <c r="K205" t="s">
-        <v>21</v>
+        <v>87</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B206" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C206" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D206" t="s">
-        <v>32</v>
+        <v>225</v>
       </c>
       <c r="E206">
-        <v>185990</v>
+        <v>125990</v>
       </c>
       <c r="F206">
         <v>1</v>
       </c>
       <c r="G206" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="H206" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="I206">
         <v>0</v>
@@ -8425,33 +8492,33 @@
         <v>0</v>
       </c>
       <c r="K206" t="s">
-        <v>21</v>
+        <v>87</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B207" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C207" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D207" t="s">
-        <v>19</v>
+        <v>226</v>
       </c>
       <c r="E207">
-        <v>185990</v>
+        <v>125990</v>
       </c>
       <c r="F207">
         <v>1</v>
       </c>
       <c r="G207" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="H207" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="I207">
         <v>0</v>
@@ -8460,7 +8527,7 @@
         <v>0</v>
       </c>
       <c r="K207" t="s">
-        <v>21</v>
+        <v>87</v>
       </c>
     </row>
     <row r="208">
@@ -8474,7 +8541,7 @@
         <v>35</v>
       </c>
       <c r="D208" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E208">
         <v>125990</v>
@@ -8500,19 +8567,19 @@
     </row>
     <row r="209">
       <c r="A209" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="B209" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="C209" t="s">
         <v>35</v>
       </c>
       <c r="D209" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="E209">
-        <v>125990</v>
+        <v>129990</v>
       </c>
       <c r="F209">
         <v>1</v>
@@ -8530,24 +8597,24 @@
         <v>0</v>
       </c>
       <c r="K209" t="s">
-        <v>87</v>
+        <v>21</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="B210" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="C210" t="s">
         <v>35</v>
       </c>
       <c r="D210" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="E210">
-        <v>125990</v>
+        <v>129990</v>
       </c>
       <c r="F210">
         <v>1</v>
@@ -8565,24 +8632,24 @@
         <v>0</v>
       </c>
       <c r="K210" t="s">
-        <v>87</v>
+        <v>21</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="B211" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="C211" t="s">
         <v>35</v>
       </c>
       <c r="D211" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="E211">
-        <v>125990</v>
+        <v>129990</v>
       </c>
       <c r="F211">
         <v>1</v>
@@ -8600,33 +8667,33 @@
         <v>0</v>
       </c>
       <c r="K211" t="s">
-        <v>87</v>
+        <v>21</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="B212" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="C212" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="D212" t="s">
-        <v>230</v>
+        <v>36</v>
       </c>
       <c r="E212">
-        <v>129990</v>
+        <v>125990</v>
       </c>
       <c r="F212">
         <v>1</v>
       </c>
       <c r="G212" t="s">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="H212" t="s">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="I212">
         <v>0</v>
@@ -8640,28 +8707,28 @@
     </row>
     <row r="213">
       <c r="A213" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="B213" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="C213" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="D213" t="s">
-        <v>231</v>
+        <v>32</v>
       </c>
       <c r="E213">
-        <v>129990</v>
+        <v>125990</v>
       </c>
       <c r="F213">
         <v>1</v>
       </c>
       <c r="G213" t="s">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="H213" t="s">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="I213">
         <v>0</v>
@@ -8675,28 +8742,28 @@
     </row>
     <row r="214">
       <c r="A214" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="B214" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="C214" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="D214" t="s">
-        <v>232</v>
+        <v>19</v>
       </c>
       <c r="E214">
-        <v>129990</v>
+        <v>125990</v>
       </c>
       <c r="F214">
         <v>1</v>
       </c>
       <c r="G214" t="s">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="H214" t="s">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="I214">
         <v>0</v>
@@ -8710,19 +8777,19 @@
     </row>
     <row r="215">
       <c r="A215" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B215" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C215" t="s">
         <v>18</v>
       </c>
       <c r="D215" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="E215">
-        <v>125990</v>
+        <v>140990</v>
       </c>
       <c r="F215">
         <v>1</v>
@@ -8740,24 +8807,24 @@
         <v>0</v>
       </c>
       <c r="K215" t="s">
-        <v>21</v>
+        <v>214</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B216" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C216" t="s">
         <v>18</v>
       </c>
       <c r="D216" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E216">
-        <v>125990</v>
+        <v>140990</v>
       </c>
       <c r="F216">
         <v>1</v>
@@ -8775,15 +8842,15 @@
         <v>0</v>
       </c>
       <c r="K216" t="s">
-        <v>21</v>
+        <v>214</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B217" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C217" t="s">
         <v>18</v>
@@ -8792,7 +8859,7 @@
         <v>19</v>
       </c>
       <c r="E217">
-        <v>125990</v>
+        <v>140990</v>
       </c>
       <c r="F217">
         <v>1</v>
@@ -8810,7 +8877,7 @@
         <v>0</v>
       </c>
       <c r="K217" t="s">
-        <v>21</v>
+        <v>214</v>
       </c>
     </row>
     <row r="218">
@@ -8824,7 +8891,7 @@
         <v>18</v>
       </c>
       <c r="D218" t="s">
-        <v>55</v>
+        <v>132</v>
       </c>
       <c r="E218">
         <v>140990</v>
@@ -8850,19 +8917,19 @@
     </row>
     <row r="219">
       <c r="A219" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B219" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C219" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D219" t="s">
         <v>36</v>
       </c>
       <c r="E219">
-        <v>140990</v>
+        <v>195990</v>
       </c>
       <c r="F219">
         <v>1</v>
@@ -8880,24 +8947,24 @@
         <v>0</v>
       </c>
       <c r="K219" t="s">
-        <v>214</v>
+        <v>116</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B220" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C220" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D220" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E220">
-        <v>140990</v>
+        <v>195990</v>
       </c>
       <c r="F220">
         <v>1</v>
@@ -8915,24 +8982,24 @@
         <v>0</v>
       </c>
       <c r="K220" t="s">
-        <v>214</v>
+        <v>116</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B221" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="C221" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D221" t="s">
-        <v>132</v>
+        <v>55</v>
       </c>
       <c r="E221">
-        <v>140990</v>
+        <v>140900</v>
       </c>
       <c r="F221">
         <v>1</v>
@@ -8950,15 +9017,15 @@
         <v>0</v>
       </c>
       <c r="K221" t="s">
-        <v>214</v>
+        <v>116</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B222" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C222" t="s">
         <v>35</v>
@@ -8967,7 +9034,7 @@
         <v>36</v>
       </c>
       <c r="E222">
-        <v>195990</v>
+        <v>130990</v>
       </c>
       <c r="F222">
         <v>1</v>
@@ -8990,10 +9057,10 @@
     </row>
     <row r="223">
       <c r="A223" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B223" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C223" t="s">
         <v>35</v>
@@ -9002,7 +9069,7 @@
         <v>32</v>
       </c>
       <c r="E223">
-        <v>195990</v>
+        <v>130990</v>
       </c>
       <c r="F223">
         <v>1</v>
@@ -9034,10 +9101,10 @@
         <v>35</v>
       </c>
       <c r="D224" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="E224">
-        <v>140900</v>
+        <v>130990</v>
       </c>
       <c r="F224">
         <v>1</v>
@@ -9069,7 +9136,7 @@
         <v>35</v>
       </c>
       <c r="D225" t="s">
-        <v>36</v>
+        <v>132</v>
       </c>
       <c r="E225">
         <v>130990</v>
@@ -9095,28 +9162,28 @@
     </row>
     <row r="226">
       <c r="A226" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B226" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C226" t="s">
-        <v>35</v>
+        <v>122</v>
       </c>
       <c r="D226" t="s">
-        <v>32</v>
+        <v>123</v>
       </c>
       <c r="E226">
-        <v>130990</v>
+        <v>149990</v>
       </c>
       <c r="F226">
         <v>1</v>
       </c>
       <c r="G226" t="s">
-        <v>25</v>
+        <v>119</v>
       </c>
       <c r="H226" t="s">
-        <v>25</v>
+        <v>78</v>
       </c>
       <c r="I226">
         <v>0</v>
@@ -9125,33 +9192,33 @@
         <v>0</v>
       </c>
       <c r="K226" t="s">
-        <v>116</v>
+        <v>21</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B227" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="C227" t="s">
-        <v>35</v>
+        <v>122</v>
       </c>
       <c r="D227" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E227">
-        <v>130990</v>
+        <v>145990</v>
       </c>
       <c r="F227">
         <v>1</v>
       </c>
       <c r="G227" t="s">
-        <v>25</v>
+        <v>119</v>
       </c>
       <c r="H227" t="s">
-        <v>25</v>
+        <v>78</v>
       </c>
       <c r="I227">
         <v>0</v>
@@ -9160,33 +9227,33 @@
         <v>0</v>
       </c>
       <c r="K227" t="s">
-        <v>116</v>
+        <v>63</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="B228" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="C228" t="s">
-        <v>35</v>
+        <v>122</v>
       </c>
       <c r="D228" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="E228">
-        <v>130990</v>
+        <v>279000</v>
       </c>
       <c r="F228">
         <v>1</v>
       </c>
       <c r="G228" t="s">
-        <v>25</v>
+        <v>119</v>
       </c>
       <c r="H228" t="s">
-        <v>25</v>
+        <v>78</v>
       </c>
       <c r="I228">
         <v>0</v>
@@ -9195,33 +9262,33 @@
         <v>0</v>
       </c>
       <c r="K228" t="s">
-        <v>116</v>
+        <v>40</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="B229" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="C229" t="s">
         <v>122</v>
       </c>
       <c r="D229" t="s">
-        <v>123</v>
+        <v>55</v>
       </c>
       <c r="E229">
-        <v>149990</v>
+        <v>169990</v>
       </c>
       <c r="F229">
         <v>1</v>
       </c>
       <c r="G229" t="s">
-        <v>119</v>
+        <v>25</v>
       </c>
       <c r="H229" t="s">
-        <v>78</v>
+        <v>25</v>
       </c>
       <c r="I229">
         <v>0</v>
@@ -9230,33 +9297,33 @@
         <v>0</v>
       </c>
       <c r="K229" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B230" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="C230" t="s">
         <v>122</v>
       </c>
       <c r="D230" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="E230">
-        <v>145990</v>
+        <v>169990</v>
       </c>
       <c r="F230">
         <v>1</v>
       </c>
       <c r="G230" t="s">
-        <v>119</v>
+        <v>25</v>
       </c>
       <c r="H230" t="s">
-        <v>78</v>
+        <v>25</v>
       </c>
       <c r="I230">
         <v>0</v>
@@ -9265,111 +9332,6 @@
         <v>0</v>
       </c>
       <c r="K230" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="s">
-        <v>245</v>
-      </c>
-      <c r="B231" t="s">
-        <v>246</v>
-      </c>
-      <c r="C231" t="s">
-        <v>122</v>
-      </c>
-      <c r="D231" t="s">
-        <v>123</v>
-      </c>
-      <c r="E231">
-        <v>279000</v>
-      </c>
-      <c r="F231">
-        <v>1</v>
-      </c>
-      <c r="G231" t="s">
-        <v>119</v>
-      </c>
-      <c r="H231" t="s">
-        <v>78</v>
-      </c>
-      <c r="I231">
-        <v>0</v>
-      </c>
-      <c r="J231">
-        <v>0</v>
-      </c>
-      <c r="K231" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="s">
-        <v>247</v>
-      </c>
-      <c r="B232" t="s">
-        <v>248</v>
-      </c>
-      <c r="C232" t="s">
-        <v>122</v>
-      </c>
-      <c r="D232" t="s">
-        <v>55</v>
-      </c>
-      <c r="E232">
-        <v>169990</v>
-      </c>
-      <c r="F232">
-        <v>1</v>
-      </c>
-      <c r="G232" t="s">
-        <v>25</v>
-      </c>
-      <c r="H232" t="s">
-        <v>25</v>
-      </c>
-      <c r="I232">
-        <v>0</v>
-      </c>
-      <c r="J232">
-        <v>0</v>
-      </c>
-      <c r="K232" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="s">
-        <v>247</v>
-      </c>
-      <c r="B233" t="s">
-        <v>248</v>
-      </c>
-      <c r="C233" t="s">
-        <v>122</v>
-      </c>
-      <c r="D233" t="s">
-        <v>36</v>
-      </c>
-      <c r="E233">
-        <v>169990</v>
-      </c>
-      <c r="F233">
-        <v>1</v>
-      </c>
-      <c r="G233" t="s">
-        <v>25</v>
-      </c>
-      <c r="H233" t="s">
-        <v>25</v>
-      </c>
-      <c r="I233">
-        <v>0</v>
-      </c>
-      <c r="J233">
-        <v>0</v>
-      </c>
-      <c r="K233" t="s">
         <v>40</v>
       </c>
     </row>

--- a/data/catalogo_jusp.xlsx
+++ b/data/catalogo_jusp.xlsx
@@ -1231,28 +1231,28 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
         <v>18</v>
       </c>
-      <c r="D3">
-        <v>40</v>
+      <c r="D3" t="s">
+        <v>19</v>
       </c>
       <c r="E3">
-        <v>599990</v>
+        <v>135990</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H3" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -1261,11 +1261,11 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>26</v>
-      </c>
-      <c r="L3">
-        <v>10</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="L3"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
@@ -1277,8 +1277,8 @@
       <c r="C4" t="s">
         <v>18</v>
       </c>
-      <c r="D4" t="s">
-        <v>27</v>
+      <c r="D4">
+        <v>40</v>
       </c>
       <c r="E4">
         <v>599990</v>
@@ -1290,7 +1290,7 @@
         <v>25</v>
       </c>
       <c r="H4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -1315,8 +1315,8 @@
       <c r="C5" t="s">
         <v>18</v>
       </c>
-      <c r="D5">
-        <v>41</v>
+      <c r="D5" t="s">
+        <v>27</v>
       </c>
       <c r="E5">
         <v>599990</v>
@@ -1354,7 +1354,7 @@
         <v>18</v>
       </c>
       <c r="D6">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E6">
         <v>599990</v>
@@ -1391,8 +1391,8 @@
       <c r="C7" t="s">
         <v>18</v>
       </c>
-      <c r="D7" t="s">
-        <v>29</v>
+      <c r="D7">
+        <v>42</v>
       </c>
       <c r="E7">
         <v>599990</v>
@@ -1429,8 +1429,8 @@
       <c r="C8" t="s">
         <v>18</v>
       </c>
-      <c r="D8">
-        <v>43</v>
+      <c r="D8" t="s">
+        <v>29</v>
       </c>
       <c r="E8">
         <v>599990</v>
@@ -1468,7 +1468,7 @@
         <v>18</v>
       </c>
       <c r="D9">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E9">
         <v>599990</v>
@@ -1506,7 +1506,7 @@
         <v>18</v>
       </c>
       <c r="D10">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E10">
         <v>599990</v>
@@ -1535,59 +1535,57 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C11" t="s">
         <v>18</v>
       </c>
-      <c r="D11" t="s">
-        <v>32</v>
+      <c r="D11">
+        <v>45</v>
       </c>
       <c r="E11">
-        <v>99990</v>
+        <v>599990</v>
       </c>
       <c r="F11">
         <v>1</v>
       </c>
       <c r="G11" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H11" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="I11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="L11">
-        <v>30</v>
-      </c>
-      <c r="N11" s="3"/>
-      <c r="O11" s="3"/>
+        <v>10</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="D12" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E12">
-        <v>119990</v>
+        <v>99990</v>
       </c>
       <c r="F12">
         <v>1</v>
@@ -1615,19 +1613,19 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B13" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C13" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D13" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E13">
-        <v>95990</v>
+        <v>119990</v>
       </c>
       <c r="F13">
         <v>1</v>
@@ -1645,29 +1643,29 @@
         <v>1</v>
       </c>
       <c r="K13" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="L13">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="N13" s="3"/>
       <c r="O13" s="3"/>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B14" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C14" t="s">
         <v>18</v>
       </c>
       <c r="D14" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="E14">
-        <v>110990</v>
+        <v>95990</v>
       </c>
       <c r="F14">
         <v>1</v>
@@ -1688,26 +1686,26 @@
         <v>40</v>
       </c>
       <c r="L14">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C15" t="s">
         <v>18</v>
       </c>
       <c r="D15" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="E15">
-        <v>195990</v>
+        <v>110990</v>
       </c>
       <c r="F15">
         <v>1</v>
@@ -1719,13 +1717,16 @@
         <v>20</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="s">
-        <v>45</v>
+        <v>40</v>
+      </c>
+      <c r="L15">
+        <v>20</v>
       </c>
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
@@ -1741,10 +1742,10 @@
         <v>18</v>
       </c>
       <c r="D16" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E16">
-        <v>205990</v>
+        <v>195990</v>
       </c>
       <c r="F16">
         <v>1</v>
@@ -1769,10 +1770,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B17" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C17" t="s">
         <v>18</v>
@@ -1781,7 +1782,7 @@
         <v>19</v>
       </c>
       <c r="E17">
-        <v>139990</v>
+        <v>205990</v>
       </c>
       <c r="F17">
         <v>1</v>
@@ -1793,35 +1794,32 @@
         <v>20</v>
       </c>
       <c r="I17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>40</v>
-      </c>
-      <c r="L17">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B18" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C18" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="D18" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="E18">
-        <v>125990</v>
+        <v>139990</v>
       </c>
       <c r="F18">
         <v>1</v>
@@ -1839,29 +1837,29 @@
         <v>1</v>
       </c>
       <c r="K18" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="L18">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B19" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C19" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D19" t="s">
         <v>36</v>
       </c>
       <c r="E19">
-        <v>99990</v>
+        <v>125990</v>
       </c>
       <c r="F19">
         <v>1</v>
@@ -1879,10 +1877,10 @@
         <v>1</v>
       </c>
       <c r="K19" t="s">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="L19">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
@@ -1898,7 +1896,7 @@
         <v>18</v>
       </c>
       <c r="D20" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E20">
         <v>99990</v>
@@ -1929,19 +1927,19 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B21" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C21" t="s">
         <v>18</v>
       </c>
       <c r="D21" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="E21">
-        <v>109990</v>
+        <v>99990</v>
       </c>
       <c r="F21">
         <v>1</v>
@@ -1953,35 +1951,35 @@
         <v>20</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="L21">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N21" s="3"/>
       <c r="O21" s="3"/>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B22" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C22" t="s">
         <v>18</v>
       </c>
       <c r="D22" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="E22">
-        <v>119990</v>
+        <v>109990</v>
       </c>
       <c r="F22">
         <v>1</v>
@@ -1999,7 +1997,7 @@
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="L22">
         <v>30</v>
@@ -2018,7 +2016,7 @@
         <v>18</v>
       </c>
       <c r="D23" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E23">
         <v>119990</v>
@@ -2049,7 +2047,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B24" t="s">
         <v>57</v>
@@ -2073,13 +2071,13 @@
         <v>20</v>
       </c>
       <c r="I24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="L24">
         <v>30</v>
@@ -2089,16 +2087,16 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B25" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C25" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="D25" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E25">
         <v>119990</v>
@@ -2119,29 +2117,29 @@
         <v>1</v>
       </c>
       <c r="K25" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="L25">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="N25" s="3"/>
       <c r="O25" s="3"/>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B26" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C26" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D26" t="s">
         <v>36</v>
       </c>
       <c r="E26">
-        <v>99990</v>
+        <v>119990</v>
       </c>
       <c r="F26">
         <v>1</v>
@@ -2159,29 +2157,29 @@
         <v>1</v>
       </c>
       <c r="K26" t="s">
-        <v>21</v>
+        <v>63</v>
       </c>
       <c r="L26">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="N26" s="3"/>
       <c r="O26" s="3"/>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B27" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C27" t="s">
         <v>18</v>
       </c>
       <c r="D27" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E27">
-        <v>86990</v>
+        <v>99990</v>
       </c>
       <c r="F27">
         <v>1</v>
@@ -2202,7 +2200,7 @@
         <v>21</v>
       </c>
       <c r="L27">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N27" s="3"/>
       <c r="O27" s="3"/>
@@ -2218,7 +2216,7 @@
         <v>18</v>
       </c>
       <c r="D28" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E28">
         <v>86990</v>
@@ -2249,19 +2247,19 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B29" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C29" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="D29" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="E29">
-        <v>96990</v>
+        <v>86990</v>
       </c>
       <c r="F29">
         <v>1</v>
@@ -2279,20 +2277,20 @@
         <v>1</v>
       </c>
       <c r="K29" t="s">
-        <v>71</v>
+        <v>21</v>
       </c>
       <c r="L29">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N29" s="3"/>
       <c r="O29" s="3"/>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B30" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C30" t="s">
         <v>70</v>
@@ -2301,7 +2299,7 @@
         <v>32</v>
       </c>
       <c r="E30">
-        <v>95990</v>
+        <v>96990</v>
       </c>
       <c r="F30">
         <v>1</v>
@@ -2319,7 +2317,7 @@
         <v>1</v>
       </c>
       <c r="K30" t="s">
-        <v>21</v>
+        <v>71</v>
       </c>
       <c r="L30">
         <v>25</v>
@@ -2329,65 +2327,68 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B31" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C31" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="D31" t="s">
-        <v>76</v>
+        <v>32</v>
       </c>
       <c r="E31">
-        <v>129990</v>
+        <v>95990</v>
       </c>
       <c r="F31">
         <v>1</v>
       </c>
       <c r="G31" t="s">
-        <v>77</v>
+        <v>20</v>
       </c>
       <c r="H31" t="s">
-        <v>78</v>
+        <v>20</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="s">
         <v>21</v>
       </c>
+      <c r="L31">
+        <v>25</v>
+      </c>
       <c r="N31" s="3"/>
       <c r="O31" s="3"/>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="B32" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C32" t="s">
         <v>18</v>
       </c>
       <c r="D32" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="E32">
-        <v>88990</v>
+        <v>129990</v>
       </c>
       <c r="F32">
         <v>1</v>
       </c>
       <c r="G32" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H32" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -2398,9 +2399,8 @@
       <c r="K32" t="s">
         <v>21</v>
       </c>
-      <c r="L32">
-        <v>5</v>
-      </c>
+      <c r="N32" s="3"/>
+      <c r="O32" s="3"/>
     </row>
     <row r="33">
       <c r="A33" t="s">
@@ -2413,7 +2413,7 @@
         <v>18</v>
       </c>
       <c r="D33" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E33">
         <v>88990</v>
@@ -2442,28 +2442,28 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="B34" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C34" t="s">
         <v>18</v>
       </c>
       <c r="D34" t="s">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="E34">
-        <v>89990</v>
+        <v>88990</v>
       </c>
       <c r="F34">
         <v>1</v>
       </c>
       <c r="G34" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="H34" t="s">
-        <v>20</v>
+        <v>83</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -2472,7 +2472,10 @@
         <v>0</v>
       </c>
       <c r="K34" t="s">
-        <v>87</v>
+        <v>21</v>
+      </c>
+      <c r="L34">
+        <v>5</v>
       </c>
     </row>
     <row r="35">
@@ -2486,7 +2489,7 @@
         <v>18</v>
       </c>
       <c r="D35" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="E35">
         <v>89990</v>
@@ -2512,28 +2515,28 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B36" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C36" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="D36" t="s">
-        <v>90</v>
+        <v>36</v>
       </c>
       <c r="E36">
-        <v>75990</v>
+        <v>89990</v>
       </c>
       <c r="F36">
         <v>1</v>
       </c>
       <c r="G36" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H36" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -2542,7 +2545,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="37">
@@ -2556,10 +2559,10 @@
         <v>35</v>
       </c>
       <c r="D37" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E37">
-        <v>79990</v>
+        <v>75990</v>
       </c>
       <c r="F37">
         <v>1</v>
@@ -2591,10 +2594,10 @@
         <v>35</v>
       </c>
       <c r="D38" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E38">
-        <v>78990</v>
+        <v>79990</v>
       </c>
       <c r="F38">
         <v>1</v>
@@ -2617,28 +2620,28 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B39" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="C39" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D39" t="s">
-        <v>36</v>
+        <v>93</v>
       </c>
       <c r="E39">
-        <v>69990</v>
+        <v>78990</v>
       </c>
       <c r="F39">
         <v>1</v>
       </c>
       <c r="G39" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H39" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I39">
         <v>0</v>
@@ -2647,24 +2650,24 @@
         <v>0</v>
       </c>
       <c r="K39" t="s">
-        <v>26</v>
+        <v>91</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B40" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C40" t="s">
         <v>18</v>
       </c>
       <c r="D40" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="E40">
-        <v>139990</v>
+        <v>69990</v>
       </c>
       <c r="F40">
         <v>1</v>
@@ -2682,33 +2685,33 @@
         <v>0</v>
       </c>
       <c r="K40" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B41" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C41" t="s">
         <v>18</v>
       </c>
-      <c r="D41">
-        <v>7</v>
+      <c r="D41" t="s">
+        <v>19</v>
       </c>
       <c r="E41">
-        <v>99990</v>
+        <v>139990</v>
       </c>
       <c r="F41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G41" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H41" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I41">
         <v>0</v>
@@ -2717,33 +2720,33 @@
         <v>0</v>
       </c>
       <c r="K41" t="s">
-        <v>91</v>
+        <v>40</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B42" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C42" t="s">
         <v>18</v>
       </c>
-      <c r="D42" t="s">
-        <v>32</v>
-      </c>
-      <c r="E42" s="4">
-        <v>119990</v>
+      <c r="D42">
+        <v>7</v>
+      </c>
+      <c r="E42">
+        <v>99990</v>
       </c>
       <c r="F42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G42" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H42" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -2752,33 +2755,33 @@
         <v>0</v>
       </c>
       <c r="K42" t="s">
-        <v>40</v>
+        <v>91</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B43" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C43" t="s">
         <v>18</v>
       </c>
       <c r="D43" t="s">
-        <v>90</v>
-      </c>
-      <c r="E43">
-        <v>65990</v>
+        <v>32</v>
+      </c>
+      <c r="E43" s="4">
+        <v>119990</v>
       </c>
       <c r="F43">
         <v>1</v>
       </c>
       <c r="G43" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H43" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I43">
         <v>0</v>
@@ -2787,7 +2790,7 @@
         <v>0</v>
       </c>
       <c r="K43" t="s">
-        <v>104</v>
+        <v>40</v>
       </c>
     </row>
     <row r="44">
@@ -2801,10 +2804,10 @@
         <v>18</v>
       </c>
       <c r="D44" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E44">
-        <v>75990</v>
+        <v>65990</v>
       </c>
       <c r="F44">
         <v>1</v>
@@ -2836,10 +2839,10 @@
         <v>18</v>
       </c>
       <c r="D45" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E45">
-        <v>85990</v>
+        <v>75990</v>
       </c>
       <c r="F45">
         <v>1</v>
@@ -2862,28 +2865,28 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B46" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C46" t="s">
         <v>18</v>
       </c>
       <c r="D46" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="E46">
-        <v>79990</v>
+        <v>85990</v>
       </c>
       <c r="F46">
         <v>1</v>
       </c>
       <c r="G46" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H46" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I46">
         <v>0</v>
@@ -2892,7 +2895,7 @@
         <v>0</v>
       </c>
       <c r="K46" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
     </row>
     <row r="47">
@@ -2906,7 +2909,7 @@
         <v>18</v>
       </c>
       <c r="D47" t="s">
-        <v>55</v>
+        <v>107</v>
       </c>
       <c r="E47">
         <v>79990</v>
@@ -2941,7 +2944,7 @@
         <v>18</v>
       </c>
       <c r="D48" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="E48">
         <v>79990</v>
@@ -2976,7 +2979,7 @@
         <v>18</v>
       </c>
       <c r="D49" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E49">
         <v>79990</v>
@@ -3011,7 +3014,7 @@
         <v>18</v>
       </c>
       <c r="D50" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E50">
         <v>79990</v>
@@ -3037,19 +3040,19 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B51" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C51" t="s">
         <v>18</v>
       </c>
       <c r="D51" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="E51">
-        <v>155990</v>
+        <v>79990</v>
       </c>
       <c r="F51">
         <v>1</v>
@@ -3067,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="K51" t="s">
-        <v>60</v>
+        <v>91</v>
       </c>
     </row>
     <row r="52">
@@ -3081,7 +3084,7 @@
         <v>18</v>
       </c>
       <c r="D52" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="E52">
         <v>155990</v>
@@ -3116,7 +3119,7 @@
         <v>18</v>
       </c>
       <c r="D53" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E53">
         <v>155990</v>
@@ -3151,7 +3154,7 @@
         <v>18</v>
       </c>
       <c r="D54" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E54">
         <v>155990</v>
@@ -3177,19 +3180,19 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B55" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C55" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="D55" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="E55">
-        <v>49990</v>
+        <v>155990</v>
       </c>
       <c r="F55">
         <v>1</v>
@@ -3207,7 +3210,7 @@
         <v>0</v>
       </c>
       <c r="K55" t="s">
-        <v>21</v>
+        <v>60</v>
       </c>
     </row>
     <row r="56">
@@ -3221,7 +3224,7 @@
         <v>70</v>
       </c>
       <c r="D56" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="E56">
         <v>49990</v>
@@ -3247,19 +3250,19 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B57" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C57" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="D57" t="s">
         <v>36</v>
       </c>
       <c r="E57">
-        <v>135990</v>
+        <v>49990</v>
       </c>
       <c r="F57">
         <v>1</v>
@@ -3277,24 +3280,24 @@
         <v>0</v>
       </c>
       <c r="K57" t="s">
-        <v>63</v>
+        <v>21</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B58" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C58" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D58" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="E58">
-        <v>155990</v>
+        <v>135990</v>
       </c>
       <c r="F58">
         <v>1</v>
@@ -3312,7 +3315,7 @@
         <v>0</v>
       </c>
       <c r="K58" t="s">
-        <v>116</v>
+        <v>63</v>
       </c>
     </row>
     <row r="59">
@@ -3326,7 +3329,7 @@
         <v>18</v>
       </c>
       <c r="D59" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="E59">
         <v>155990</v>
@@ -3361,7 +3364,7 @@
         <v>18</v>
       </c>
       <c r="D60" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E60">
         <v>155990</v>
@@ -3387,28 +3390,28 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B61" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C61" t="s">
         <v>18</v>
       </c>
       <c r="D61" t="s">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="E61">
-        <v>129990</v>
+        <v>155990</v>
       </c>
       <c r="F61">
         <v>1</v>
       </c>
       <c r="G61" t="s">
-        <v>119</v>
+        <v>20</v>
       </c>
       <c r="H61" t="s">
-        <v>119</v>
+        <v>20</v>
       </c>
       <c r="I61">
         <v>0</v>
@@ -3417,7 +3420,7 @@
         <v>0</v>
       </c>
       <c r="K61" t="s">
-        <v>21</v>
+        <v>116</v>
       </c>
     </row>
     <row r="62">
@@ -3431,7 +3434,7 @@
         <v>18</v>
       </c>
       <c r="D62" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E62">
         <v>129990</v>
@@ -3457,19 +3460,19 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B63" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C63" t="s">
-        <v>122</v>
+        <v>18</v>
       </c>
       <c r="D63" t="s">
-        <v>123</v>
+        <v>93</v>
       </c>
       <c r="E63">
-        <v>179990</v>
+        <v>129990</v>
       </c>
       <c r="F63">
         <v>1</v>
@@ -3492,19 +3495,19 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B64" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C64" t="s">
-        <v>18</v>
+        <v>122</v>
       </c>
       <c r="D64" t="s">
         <v>123</v>
       </c>
       <c r="E64">
-        <v>159990</v>
+        <v>179990</v>
       </c>
       <c r="F64">
         <v>1</v>
@@ -3527,19 +3530,19 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B65" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C65" t="s">
         <v>18</v>
       </c>
       <c r="D65" t="s">
-        <v>90</v>
+        <v>123</v>
       </c>
       <c r="E65">
-        <v>134990</v>
+        <v>159990</v>
       </c>
       <c r="F65">
         <v>1</v>
@@ -3571,7 +3574,7 @@
         <v>18</v>
       </c>
       <c r="D66" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E66">
         <v>134990</v>
@@ -3606,7 +3609,7 @@
         <v>18</v>
       </c>
       <c r="D67" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E67">
         <v>134990</v>
@@ -3632,28 +3635,28 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B68" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C68" t="s">
         <v>18</v>
       </c>
       <c r="D68" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="E68">
-        <v>79990</v>
+        <v>134990</v>
       </c>
       <c r="F68">
         <v>1</v>
       </c>
       <c r="G68" t="s">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="H68" t="s">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="I68">
         <v>0</v>
@@ -3667,28 +3670,28 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B69" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C69" t="s">
         <v>18</v>
       </c>
       <c r="D69" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="E69">
-        <v>134990</v>
+        <v>79990</v>
       </c>
       <c r="F69">
         <v>1</v>
       </c>
       <c r="G69" t="s">
-        <v>25</v>
+        <v>82</v>
       </c>
       <c r="H69" t="s">
-        <v>25</v>
+        <v>82</v>
       </c>
       <c r="I69">
         <v>0</v>
@@ -3708,10 +3711,10 @@
         <v>131</v>
       </c>
       <c r="C70" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="D70" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="E70">
         <v>134990</v>
@@ -3746,7 +3749,7 @@
         <v>35</v>
       </c>
       <c r="D71" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E71">
         <v>134990</v>
@@ -3781,7 +3784,7 @@
         <v>35</v>
       </c>
       <c r="D72" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E72">
         <v>134990</v>
@@ -3816,7 +3819,7 @@
         <v>35</v>
       </c>
       <c r="D73" t="s">
-        <v>132</v>
+        <v>19</v>
       </c>
       <c r="E73">
         <v>134990</v>
@@ -3842,19 +3845,19 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B74" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C74" t="s">
         <v>35</v>
       </c>
       <c r="D74" t="s">
-        <v>55</v>
+        <v>132</v>
       </c>
       <c r="E74">
-        <v>119990</v>
+        <v>134990</v>
       </c>
       <c r="F74">
         <v>1</v>
@@ -3863,7 +3866,7 @@
         <v>25</v>
       </c>
       <c r="H74" t="s">
-        <v>78</v>
+        <v>25</v>
       </c>
       <c r="I74">
         <v>0</v>
@@ -3886,7 +3889,7 @@
         <v>35</v>
       </c>
       <c r="D75" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="E75">
         <v>119990</v>
@@ -3921,7 +3924,7 @@
         <v>35</v>
       </c>
       <c r="D76" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E76">
         <v>119990</v>
@@ -3947,16 +3950,16 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B77" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C77" t="s">
         <v>35</v>
       </c>
       <c r="D77" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E77">
         <v>119990</v>
@@ -3977,7 +3980,7 @@
         <v>0</v>
       </c>
       <c r="K77" t="s">
-        <v>137</v>
+        <v>21</v>
       </c>
     </row>
     <row r="78">
@@ -3991,7 +3994,7 @@
         <v>35</v>
       </c>
       <c r="D78" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E78">
         <v>119990</v>
@@ -4017,19 +4020,19 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B79" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C79" t="s">
         <v>35</v>
       </c>
       <c r="D79" t="s">
-        <v>90</v>
+        <v>32</v>
       </c>
       <c r="E79">
-        <v>39990</v>
+        <v>119990</v>
       </c>
       <c r="F79">
         <v>1</v>
@@ -4047,7 +4050,7 @@
         <v>0</v>
       </c>
       <c r="K79" t="s">
-        <v>21</v>
+        <v>137</v>
       </c>
     </row>
     <row r="80">
@@ -4061,7 +4064,7 @@
         <v>35</v>
       </c>
       <c r="D80" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E80">
         <v>39990</v>
@@ -4087,10 +4090,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B81" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C81" t="s">
         <v>35</v>
@@ -4117,30 +4120,30 @@
         <v>0</v>
       </c>
       <c r="K81" t="s">
-        <v>137</v>
+        <v>21</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B82" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C82" t="s">
-        <v>122</v>
+        <v>35</v>
       </c>
       <c r="D82" t="s">
-        <v>144</v>
+        <v>93</v>
       </c>
       <c r="E82">
-        <v>140990</v>
+        <v>39990</v>
       </c>
       <c r="F82">
         <v>1</v>
       </c>
       <c r="G82" t="s">
-        <v>119</v>
+        <v>25</v>
       </c>
       <c r="H82" t="s">
         <v>78</v>
@@ -4152,7 +4155,7 @@
         <v>0</v>
       </c>
       <c r="K82" t="s">
-        <v>91</v>
+        <v>137</v>
       </c>
     </row>
     <row r="83">
@@ -4166,10 +4169,10 @@
         <v>122</v>
       </c>
       <c r="D83" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E83">
-        <v>145990</v>
+        <v>140990</v>
       </c>
       <c r="F83">
         <v>1</v>
@@ -4192,28 +4195,28 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="B84" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C84" t="s">
-        <v>18</v>
+        <v>122</v>
       </c>
       <c r="D84" t="s">
-        <v>55</v>
-      </c>
-      <c r="E84" s="4">
-        <v>199990</v>
+        <v>145</v>
+      </c>
+      <c r="E84">
+        <v>145990</v>
       </c>
       <c r="F84">
         <v>1</v>
       </c>
       <c r="G84" t="s">
-        <v>25</v>
+        <v>119</v>
       </c>
       <c r="H84" t="s">
-        <v>25</v>
+        <v>78</v>
       </c>
       <c r="I84">
         <v>0</v>
@@ -4222,7 +4225,7 @@
         <v>0</v>
       </c>
       <c r="K84" t="s">
-        <v>40</v>
+        <v>91</v>
       </c>
     </row>
     <row r="85">
@@ -4236,7 +4239,7 @@
         <v>18</v>
       </c>
       <c r="D85" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="E85" s="4">
         <v>199990</v>
@@ -4271,7 +4274,7 @@
         <v>18</v>
       </c>
       <c r="D86" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E86" s="4">
         <v>199990</v>
@@ -4306,7 +4309,7 @@
         <v>18</v>
       </c>
       <c r="D87" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E87" s="4">
         <v>199990</v>
@@ -4341,7 +4344,7 @@
         <v>18</v>
       </c>
       <c r="D88" t="s">
-        <v>132</v>
+        <v>19</v>
       </c>
       <c r="E88" s="4">
         <v>199990</v>
@@ -4367,19 +4370,19 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B89" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C89" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="D89" t="s">
-        <v>55</v>
-      </c>
-      <c r="E89">
-        <v>155990</v>
+        <v>132</v>
+      </c>
+      <c r="E89" s="4">
+        <v>199990</v>
       </c>
       <c r="F89">
         <v>1</v>
@@ -4397,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="K89" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
     </row>
     <row r="90">
@@ -4411,7 +4414,7 @@
         <v>35</v>
       </c>
       <c r="D90" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="E90">
         <v>155990</v>
@@ -4446,7 +4449,7 @@
         <v>35</v>
       </c>
       <c r="D91" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E91">
         <v>155990</v>
@@ -4481,7 +4484,7 @@
         <v>35</v>
       </c>
       <c r="D92" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E92">
         <v>155990</v>
@@ -4507,19 +4510,19 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B93" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C93" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D93" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="E93">
-        <v>269990</v>
+        <v>155990</v>
       </c>
       <c r="F93">
         <v>1</v>
@@ -4537,7 +4540,7 @@
         <v>0</v>
       </c>
       <c r="K93" t="s">
-        <v>152</v>
+        <v>21</v>
       </c>
     </row>
     <row r="94">
@@ -4551,7 +4554,7 @@
         <v>18</v>
       </c>
       <c r="D94" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="E94">
         <v>269990</v>
@@ -4586,7 +4589,7 @@
         <v>18</v>
       </c>
       <c r="D95" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E95">
         <v>269990</v>
@@ -4621,7 +4624,7 @@
         <v>18</v>
       </c>
       <c r="D96" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E96">
         <v>269990</v>
@@ -4656,7 +4659,7 @@
         <v>18</v>
       </c>
       <c r="D97" t="s">
-        <v>132</v>
+        <v>19</v>
       </c>
       <c r="E97">
         <v>269990</v>
@@ -4682,19 +4685,19 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B98" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C98" t="s">
         <v>18</v>
       </c>
       <c r="D98" t="s">
-        <v>36</v>
+        <v>132</v>
       </c>
       <c r="E98">
-        <v>199990</v>
+        <v>269990</v>
       </c>
       <c r="F98">
         <v>1</v>
@@ -4712,7 +4715,7 @@
         <v>0</v>
       </c>
       <c r="K98" t="s">
-        <v>40</v>
+        <v>152</v>
       </c>
     </row>
     <row r="99">
@@ -4726,7 +4729,7 @@
         <v>18</v>
       </c>
       <c r="D99" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E99">
         <v>199990</v>
@@ -4761,7 +4764,7 @@
         <v>18</v>
       </c>
       <c r="D100" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E100">
         <v>199990</v>
@@ -4796,7 +4799,7 @@
         <v>18</v>
       </c>
       <c r="D101" t="s">
-        <v>132</v>
+        <v>19</v>
       </c>
       <c r="E101">
         <v>199990</v>
@@ -4822,19 +4825,19 @@
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B102" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C102" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="D102" t="s">
-        <v>55</v>
+        <v>132</v>
       </c>
       <c r="E102">
-        <v>194990</v>
+        <v>199990</v>
       </c>
       <c r="F102">
         <v>1</v>
@@ -4852,7 +4855,7 @@
         <v>0</v>
       </c>
       <c r="K102" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
     </row>
     <row r="103">
@@ -4866,7 +4869,7 @@
         <v>35</v>
       </c>
       <c r="D103" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="E103">
         <v>194990</v>
@@ -4901,7 +4904,7 @@
         <v>35</v>
       </c>
       <c r="D104" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E104">
         <v>194990</v>
@@ -4936,7 +4939,7 @@
         <v>35</v>
       </c>
       <c r="D105" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E105">
         <v>194990</v>
@@ -4962,28 +4965,28 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B106" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C106" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D106" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="E106">
-        <v>202990</v>
+        <v>194990</v>
       </c>
       <c r="F106">
         <v>1</v>
       </c>
       <c r="G106" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H106" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I106">
         <v>0</v>
@@ -4992,15 +4995,15 @@
         <v>0</v>
       </c>
       <c r="K106" t="s">
-        <v>116</v>
+        <v>21</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B107" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C107" t="s">
         <v>18</v>
@@ -5009,16 +5012,16 @@
         <v>55</v>
       </c>
       <c r="E107">
-        <v>151990</v>
+        <v>202990</v>
       </c>
       <c r="F107">
         <v>1</v>
       </c>
       <c r="G107" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H107" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I107">
         <v>0</v>
@@ -5027,7 +5030,7 @@
         <v>0</v>
       </c>
       <c r="K107" t="s">
-        <v>60</v>
+        <v>116</v>
       </c>
     </row>
     <row r="108">
@@ -5041,7 +5044,7 @@
         <v>18</v>
       </c>
       <c r="D108" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="E108">
         <v>151990</v>
@@ -5076,7 +5079,7 @@
         <v>18</v>
       </c>
       <c r="D109" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E109">
         <v>151990</v>
@@ -5111,7 +5114,7 @@
         <v>18</v>
       </c>
       <c r="D110" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E110">
         <v>151990</v>
@@ -5146,7 +5149,7 @@
         <v>18</v>
       </c>
       <c r="D111" t="s">
-        <v>132</v>
+        <v>19</v>
       </c>
       <c r="E111">
         <v>151990</v>
@@ -5172,16 +5175,16 @@
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B112" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C112" t="s">
         <v>18</v>
       </c>
       <c r="D112" t="s">
-        <v>55</v>
+        <v>132</v>
       </c>
       <c r="E112">
         <v>151990</v>
@@ -5202,7 +5205,7 @@
         <v>0</v>
       </c>
       <c r="K112" t="s">
-        <v>91</v>
+        <v>60</v>
       </c>
     </row>
     <row r="113">
@@ -5216,7 +5219,7 @@
         <v>18</v>
       </c>
       <c r="D113" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="E113">
         <v>151990</v>
@@ -5251,7 +5254,7 @@
         <v>18</v>
       </c>
       <c r="D114" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E114">
         <v>151990</v>
@@ -5286,7 +5289,7 @@
         <v>18</v>
       </c>
       <c r="D115" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E115">
         <v>151990</v>
@@ -5321,7 +5324,7 @@
         <v>18</v>
       </c>
       <c r="D116" t="s">
-        <v>132</v>
+        <v>19</v>
       </c>
       <c r="E116">
         <v>151990</v>
@@ -5347,28 +5350,28 @@
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B117" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C117" t="s">
         <v>18</v>
       </c>
       <c r="D117" t="s">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="E117">
-        <v>119990</v>
+        <v>151990</v>
       </c>
       <c r="F117">
         <v>1</v>
       </c>
       <c r="G117" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H117" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I117">
         <v>0</v>
@@ -5377,7 +5380,7 @@
         <v>0</v>
       </c>
       <c r="K117" t="s">
-        <v>21</v>
+        <v>91</v>
       </c>
     </row>
     <row r="118">
@@ -5391,10 +5394,10 @@
         <v>18</v>
       </c>
       <c r="D118" t="s">
-        <v>55</v>
+        <v>107</v>
       </c>
       <c r="E118">
-        <v>210990</v>
+        <v>119990</v>
       </c>
       <c r="F118">
         <v>1</v>
@@ -5426,7 +5429,7 @@
         <v>18</v>
       </c>
       <c r="D119" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="E119">
         <v>210990</v>
@@ -5461,7 +5464,7 @@
         <v>18</v>
       </c>
       <c r="D120" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="E120">
         <v>210990</v>
@@ -5487,19 +5490,19 @@
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B121" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C121" t="s">
         <v>18</v>
       </c>
       <c r="D121" t="s">
-        <v>107</v>
+        <v>19</v>
       </c>
       <c r="E121">
-        <v>108990</v>
+        <v>210990</v>
       </c>
       <c r="F121">
         <v>1</v>
@@ -5517,7 +5520,7 @@
         <v>0</v>
       </c>
       <c r="K121" t="s">
-        <v>167</v>
+        <v>21</v>
       </c>
     </row>
     <row r="122">
@@ -5531,10 +5534,10 @@
         <v>18</v>
       </c>
       <c r="D122" t="s">
-        <v>55</v>
+        <v>107</v>
       </c>
       <c r="E122">
-        <v>114990</v>
+        <v>108990</v>
       </c>
       <c r="F122">
         <v>1</v>
@@ -5566,10 +5569,10 @@
         <v>18</v>
       </c>
       <c r="D123" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="E123">
-        <v>124990</v>
+        <v>114990</v>
       </c>
       <c r="F123">
         <v>1</v>
@@ -5601,10 +5604,10 @@
         <v>18</v>
       </c>
       <c r="D124" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="E124">
-        <v>183990</v>
+        <v>124990</v>
       </c>
       <c r="F124">
         <v>1</v>
@@ -5636,10 +5639,10 @@
         <v>18</v>
       </c>
       <c r="D125" t="s">
-        <v>132</v>
+        <v>19</v>
       </c>
       <c r="E125">
-        <v>140990</v>
+        <v>183990</v>
       </c>
       <c r="F125">
         <v>1</v>
@@ -5662,16 +5665,16 @@
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B126" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C126" t="s">
         <v>18</v>
       </c>
       <c r="D126" t="s">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="E126">
         <v>140990</v>
@@ -5706,7 +5709,7 @@
         <v>18</v>
       </c>
       <c r="D127" t="s">
-        <v>55</v>
+        <v>107</v>
       </c>
       <c r="E127">
         <v>140990</v>
@@ -5741,7 +5744,7 @@
         <v>18</v>
       </c>
       <c r="D128" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="E128">
         <v>140990</v>
@@ -5776,7 +5779,7 @@
         <v>18</v>
       </c>
       <c r="D129" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E129">
         <v>140990</v>
@@ -5811,7 +5814,7 @@
         <v>18</v>
       </c>
       <c r="D130" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E130">
         <v>140990</v>
@@ -5846,7 +5849,7 @@
         <v>18</v>
       </c>
       <c r="D131" t="s">
-        <v>132</v>
+        <v>19</v>
       </c>
       <c r="E131">
         <v>140990</v>
@@ -5872,19 +5875,19 @@
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B132" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C132" t="s">
         <v>18</v>
       </c>
       <c r="D132" t="s">
-        <v>55</v>
+        <v>132</v>
       </c>
       <c r="E132">
-        <v>92990</v>
+        <v>140990</v>
       </c>
       <c r="F132">
         <v>1</v>
@@ -5902,7 +5905,7 @@
         <v>0</v>
       </c>
       <c r="K132" t="s">
-        <v>60</v>
+        <v>167</v>
       </c>
     </row>
     <row r="133">
@@ -5916,7 +5919,7 @@
         <v>18</v>
       </c>
       <c r="D133" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="E133">
         <v>92990</v>
@@ -5951,7 +5954,7 @@
         <v>18</v>
       </c>
       <c r="D134" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E134">
         <v>92990</v>
@@ -5986,7 +5989,7 @@
         <v>18</v>
       </c>
       <c r="D135" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E135">
         <v>92990</v>
@@ -6021,7 +6024,7 @@
         <v>18</v>
       </c>
       <c r="D136" t="s">
-        <v>132</v>
+        <v>19</v>
       </c>
       <c r="E136">
         <v>92990</v>
@@ -6047,19 +6050,19 @@
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B137" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C137" t="s">
         <v>18</v>
       </c>
       <c r="D137" t="s">
-        <v>36</v>
+        <v>132</v>
       </c>
       <c r="E137">
-        <v>108990</v>
+        <v>92990</v>
       </c>
       <c r="F137">
         <v>1</v>
@@ -6077,7 +6080,7 @@
         <v>0</v>
       </c>
       <c r="K137" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="138">
@@ -6091,7 +6094,7 @@
         <v>18</v>
       </c>
       <c r="D138" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E138">
         <v>108990</v>
@@ -6126,7 +6129,7 @@
         <v>18</v>
       </c>
       <c r="D139" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E139">
         <v>108990</v>
@@ -6152,28 +6155,28 @@
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B140" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C140" t="s">
         <v>18</v>
       </c>
       <c r="D140" t="s">
-        <v>176</v>
+        <v>19</v>
       </c>
       <c r="E140">
-        <v>81990</v>
+        <v>108990</v>
       </c>
       <c r="F140">
         <v>1</v>
       </c>
       <c r="G140" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="H140" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="I140">
         <v>0</v>
@@ -6182,7 +6185,7 @@
         <v>0</v>
       </c>
       <c r="K140" t="s">
-        <v>116</v>
+        <v>40</v>
       </c>
     </row>
     <row r="141">
@@ -6196,7 +6199,7 @@
         <v>18</v>
       </c>
       <c r="D141" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E141">
         <v>81990</v>
@@ -6222,28 +6225,28 @@
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B142" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C142" t="s">
         <v>18</v>
       </c>
       <c r="D142" t="s">
-        <v>55</v>
+        <v>177</v>
       </c>
       <c r="E142">
-        <v>125990</v>
+        <v>81990</v>
       </c>
       <c r="F142">
         <v>1</v>
       </c>
       <c r="G142" t="s">
-        <v>25</v>
+        <v>82</v>
       </c>
       <c r="H142" t="s">
-        <v>25</v>
+        <v>82</v>
       </c>
       <c r="I142">
         <v>0</v>
@@ -6252,7 +6255,7 @@
         <v>0</v>
       </c>
       <c r="K142" t="s">
-        <v>21</v>
+        <v>116</v>
       </c>
     </row>
     <row r="143">
@@ -6266,7 +6269,7 @@
         <v>18</v>
       </c>
       <c r="D143" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="E143">
         <v>125990</v>
@@ -6292,16 +6295,16 @@
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B144" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C144" t="s">
         <v>18</v>
       </c>
       <c r="D144" t="s">
-        <v>182</v>
+        <v>36</v>
       </c>
       <c r="E144">
         <v>125990</v>
@@ -6310,10 +6313,10 @@
         <v>1</v>
       </c>
       <c r="G144" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H144" t="s">
-        <v>78</v>
+        <v>25</v>
       </c>
       <c r="I144">
         <v>0</v>
@@ -6322,7 +6325,7 @@
         <v>0</v>
       </c>
       <c r="K144" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
     </row>
     <row r="145">
@@ -6335,8 +6338,8 @@
       <c r="C145" t="s">
         <v>18</v>
       </c>
-      <c r="D145">
-        <v>38</v>
+      <c r="D145" t="s">
+        <v>182</v>
       </c>
       <c r="E145">
         <v>125990</v>
@@ -6371,7 +6374,7 @@
         <v>18</v>
       </c>
       <c r="D146">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E146">
         <v>125990</v>
@@ -6406,7 +6409,7 @@
         <v>18</v>
       </c>
       <c r="D147">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E147">
         <v>125990</v>
@@ -6432,28 +6435,28 @@
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B148" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C148" t="s">
         <v>18</v>
       </c>
-      <c r="D148" t="s">
-        <v>36</v>
+      <c r="D148">
+        <v>42</v>
       </c>
       <c r="E148">
-        <v>145990</v>
+        <v>125990</v>
       </c>
       <c r="F148">
         <v>1</v>
       </c>
       <c r="G148" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H148" t="s">
-        <v>25</v>
+        <v>78</v>
       </c>
       <c r="I148">
         <v>0</v>
@@ -6462,7 +6465,7 @@
         <v>0</v>
       </c>
       <c r="K148" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
     </row>
     <row r="149">
@@ -6476,7 +6479,7 @@
         <v>18</v>
       </c>
       <c r="D149" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E149">
         <v>145990</v>
@@ -6511,7 +6514,7 @@
         <v>18</v>
       </c>
       <c r="D150" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E150">
         <v>145990</v>
@@ -6546,7 +6549,7 @@
         <v>18</v>
       </c>
       <c r="D151" t="s">
-        <v>132</v>
+        <v>19</v>
       </c>
       <c r="E151">
         <v>145990</v>
@@ -6572,19 +6575,19 @@
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B152" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C152" t="s">
         <v>18</v>
       </c>
       <c r="D152" t="s">
-        <v>55</v>
+        <v>132</v>
       </c>
       <c r="E152">
-        <v>199990</v>
+        <v>145990</v>
       </c>
       <c r="F152">
         <v>1</v>
@@ -6616,7 +6619,7 @@
         <v>18</v>
       </c>
       <c r="D153" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="E153">
         <v>199990</v>
@@ -6651,7 +6654,7 @@
         <v>18</v>
       </c>
       <c r="D154" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E154">
         <v>199990</v>
@@ -6686,7 +6689,7 @@
         <v>18</v>
       </c>
       <c r="D155" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E155">
         <v>199990</v>
@@ -6721,7 +6724,7 @@
         <v>18</v>
       </c>
       <c r="D156" t="s">
-        <v>132</v>
+        <v>19</v>
       </c>
       <c r="E156">
         <v>199990</v>
@@ -6747,10 +6750,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B157" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C157" t="s">
         <v>18</v>
@@ -6759,7 +6762,7 @@
         <v>132</v>
       </c>
       <c r="E157">
-        <v>159990</v>
+        <v>199990</v>
       </c>
       <c r="F157">
         <v>1</v>
@@ -6777,7 +6780,7 @@
         <v>0</v>
       </c>
       <c r="K157" t="s">
-        <v>189</v>
+        <v>21</v>
       </c>
     </row>
     <row r="158">
@@ -6791,10 +6794,10 @@
         <v>18</v>
       </c>
       <c r="D158" t="s">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="E158">
-        <v>199990</v>
+        <v>159990</v>
       </c>
       <c r="F158">
         <v>1</v>
@@ -6826,7 +6829,7 @@
         <v>18</v>
       </c>
       <c r="D159" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E159">
         <v>199990</v>
@@ -6852,28 +6855,28 @@
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B160" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C160" t="s">
         <v>18</v>
       </c>
       <c r="D160" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="E160">
-        <v>109990</v>
+        <v>199990</v>
       </c>
       <c r="F160">
         <v>1</v>
       </c>
       <c r="G160" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H160" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I160">
         <v>0</v>
@@ -6882,7 +6885,7 @@
         <v>0</v>
       </c>
       <c r="K160" t="s">
-        <v>45</v>
+        <v>189</v>
       </c>
     </row>
     <row r="161">
@@ -6896,7 +6899,7 @@
         <v>18</v>
       </c>
       <c r="D161" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E161">
         <v>109990</v>
@@ -6931,7 +6934,7 @@
         <v>18</v>
       </c>
       <c r="D162" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E162">
         <v>109990</v>
@@ -6957,10 +6960,10 @@
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B163" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C163" t="s">
         <v>18</v>
@@ -6969,7 +6972,7 @@
         <v>19</v>
       </c>
       <c r="E163">
-        <v>115990</v>
+        <v>109990</v>
       </c>
       <c r="F163">
         <v>1</v>
@@ -6987,7 +6990,7 @@
         <v>0</v>
       </c>
       <c r="K163" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="164">
@@ -7001,10 +7004,10 @@
         <v>18</v>
       </c>
       <c r="D164" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="E164">
-        <v>119990</v>
+        <v>115990</v>
       </c>
       <c r="F164">
         <v>1</v>
@@ -7027,28 +7030,28 @@
     </row>
     <row r="165">
       <c r="A165" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B165" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C165" t="s">
-        <v>196</v>
+        <v>18</v>
       </c>
       <c r="D165" t="s">
-        <v>76</v>
+        <v>32</v>
       </c>
       <c r="E165">
-        <v>85990</v>
+        <v>119990</v>
       </c>
       <c r="F165">
         <v>1</v>
       </c>
       <c r="G165" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H165" t="s">
-        <v>78</v>
+        <v>20</v>
       </c>
       <c r="I165">
         <v>0</v>
@@ -7057,33 +7060,33 @@
         <v>0</v>
       </c>
       <c r="K165" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B166" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C166" t="s">
-        <v>18</v>
+        <v>196</v>
       </c>
       <c r="D166" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="E166">
-        <v>105990</v>
+        <v>85990</v>
       </c>
       <c r="F166">
         <v>1</v>
       </c>
       <c r="G166" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H166" t="s">
-        <v>20</v>
+        <v>78</v>
       </c>
       <c r="I166">
         <v>0</v>
@@ -7092,7 +7095,7 @@
         <v>0</v>
       </c>
       <c r="K166" t="s">
-        <v>91</v>
+        <v>21</v>
       </c>
     </row>
     <row r="167">
@@ -7106,7 +7109,7 @@
         <v>18</v>
       </c>
       <c r="D167" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="E167">
         <v>105990</v>
@@ -7141,7 +7144,7 @@
         <v>18</v>
       </c>
       <c r="D168" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E168">
         <v>105990</v>
@@ -7176,7 +7179,7 @@
         <v>18</v>
       </c>
       <c r="D169" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E169">
         <v>105990</v>
@@ -7202,19 +7205,19 @@
     </row>
     <row r="170">
       <c r="A170" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B170" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C170" t="s">
         <v>18</v>
       </c>
       <c r="D170" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="E170">
-        <v>119990</v>
+        <v>105990</v>
       </c>
       <c r="F170">
         <v>1</v>
@@ -7232,7 +7235,7 @@
         <v>0</v>
       </c>
       <c r="K170" t="s">
-        <v>201</v>
+        <v>91</v>
       </c>
     </row>
     <row r="171">
@@ -7246,10 +7249,10 @@
         <v>18</v>
       </c>
       <c r="D171" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="E171">
-        <v>189990</v>
+        <v>119990</v>
       </c>
       <c r="F171">
         <v>1</v>
@@ -7272,19 +7275,19 @@
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B172" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C172" t="s">
         <v>18</v>
       </c>
       <c r="D172" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E172">
-        <v>179990</v>
+        <v>189990</v>
       </c>
       <c r="F172">
         <v>1</v>
@@ -7302,7 +7305,7 @@
         <v>0</v>
       </c>
       <c r="K172" t="s">
-        <v>71</v>
+        <v>201</v>
       </c>
     </row>
     <row r="173">
@@ -7316,7 +7319,7 @@
         <v>18</v>
       </c>
       <c r="D173" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E173">
         <v>179990</v>
@@ -7351,10 +7354,10 @@
         <v>18</v>
       </c>
       <c r="D174" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E174">
-        <v>130990</v>
+        <v>179990</v>
       </c>
       <c r="F174">
         <v>1</v>
@@ -7377,28 +7380,28 @@
     </row>
     <row r="175">
       <c r="A175" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B175" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C175" t="s">
         <v>18</v>
       </c>
       <c r="D175" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="E175">
-        <v>109990</v>
+        <v>130990</v>
       </c>
       <c r="F175">
         <v>1</v>
       </c>
       <c r="G175" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="H175" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="I175">
         <v>0</v>
@@ -7407,7 +7410,7 @@
         <v>0</v>
       </c>
       <c r="K175" t="s">
-        <v>21</v>
+        <v>71</v>
       </c>
     </row>
     <row r="176">
@@ -7421,7 +7424,7 @@
         <v>18</v>
       </c>
       <c r="D176" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E176">
         <v>109990</v>
@@ -7447,19 +7450,19 @@
     </row>
     <row r="177">
       <c r="A177" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B177" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C177" t="s">
         <v>18</v>
       </c>
       <c r="D177" t="s">
-        <v>208</v>
+        <v>19</v>
       </c>
       <c r="E177">
-        <v>82990</v>
+        <v>109990</v>
       </c>
       <c r="F177">
         <v>1</v>
@@ -7477,7 +7480,7 @@
         <v>0</v>
       </c>
       <c r="K177" t="s">
-        <v>87</v>
+        <v>21</v>
       </c>
     </row>
     <row r="178">
@@ -7512,33 +7515,33 @@
         <v>0</v>
       </c>
       <c r="K178" t="s">
-        <v>21</v>
+        <v>87</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B179" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C179" t="s">
         <v>18</v>
       </c>
       <c r="D179" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="E179">
-        <v>119990</v>
+        <v>82990</v>
       </c>
       <c r="F179">
         <v>1</v>
       </c>
       <c r="G179" t="s">
-        <v>25</v>
+        <v>82</v>
       </c>
       <c r="H179" t="s">
-        <v>25</v>
+        <v>82</v>
       </c>
       <c r="I179">
         <v>0</v>
@@ -7561,7 +7564,7 @@
         <v>18</v>
       </c>
       <c r="D180" t="s">
-        <v>32</v>
+        <v>211</v>
       </c>
       <c r="E180">
         <v>119990</v>
@@ -7596,7 +7599,7 @@
         <v>18</v>
       </c>
       <c r="D181" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E181">
         <v>119990</v>
@@ -7631,7 +7634,7 @@
         <v>18</v>
       </c>
       <c r="D182" t="s">
-        <v>211</v>
+        <v>19</v>
       </c>
       <c r="E182">
         <v>119990</v>
@@ -7652,7 +7655,7 @@
         <v>0</v>
       </c>
       <c r="K182" t="s">
-        <v>50</v>
+        <v>21</v>
       </c>
     </row>
     <row r="183">
@@ -7666,7 +7669,7 @@
         <v>18</v>
       </c>
       <c r="D183" t="s">
-        <v>32</v>
+        <v>211</v>
       </c>
       <c r="E183">
         <v>119990</v>
@@ -7701,7 +7704,7 @@
         <v>18</v>
       </c>
       <c r="D184" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E184">
         <v>119990</v>
@@ -7727,19 +7730,19 @@
     </row>
     <row r="185">
       <c r="A185" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B185" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C185" t="s">
         <v>18</v>
       </c>
       <c r="D185" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="E185">
-        <v>129990</v>
+        <v>119990</v>
       </c>
       <c r="F185">
         <v>1</v>
@@ -7757,7 +7760,7 @@
         <v>0</v>
       </c>
       <c r="K185" t="s">
-        <v>214</v>
+        <v>50</v>
       </c>
     </row>
     <row r="186">
@@ -7771,10 +7774,10 @@
         <v>18</v>
       </c>
       <c r="D186" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="E186">
-        <v>119990</v>
+        <v>129990</v>
       </c>
       <c r="F186">
         <v>1</v>
@@ -7806,7 +7809,7 @@
         <v>18</v>
       </c>
       <c r="D187" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E187">
         <v>119990</v>
@@ -7841,7 +7844,7 @@
         <v>18</v>
       </c>
       <c r="D188" t="s">
-        <v>132</v>
+        <v>32</v>
       </c>
       <c r="E188">
         <v>119990</v>
@@ -7876,10 +7879,10 @@
         <v>18</v>
       </c>
       <c r="D189" t="s">
-        <v>55</v>
+        <v>132</v>
       </c>
       <c r="E189">
-        <v>129990</v>
+        <v>119990</v>
       </c>
       <c r="F189">
         <v>1</v>
@@ -7897,7 +7900,7 @@
         <v>0</v>
       </c>
       <c r="K189" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="190">
@@ -7911,10 +7914,10 @@
         <v>18</v>
       </c>
       <c r="D190" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="E190">
-        <v>119990</v>
+        <v>129990</v>
       </c>
       <c r="F190">
         <v>1</v>
@@ -7946,7 +7949,7 @@
         <v>18</v>
       </c>
       <c r="D191" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E191">
         <v>119990</v>
@@ -7981,7 +7984,7 @@
         <v>18</v>
       </c>
       <c r="D192" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E192">
         <v>119990</v>
@@ -8016,7 +8019,7 @@
         <v>18</v>
       </c>
       <c r="D193" t="s">
-        <v>132</v>
+        <v>19</v>
       </c>
       <c r="E193">
         <v>119990</v>
@@ -8042,19 +8045,19 @@
     </row>
     <row r="194">
       <c r="A194" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="B194" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="C194" t="s">
         <v>18</v>
       </c>
       <c r="D194" t="s">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="E194">
-        <v>165990</v>
+        <v>119990</v>
       </c>
       <c r="F194">
         <v>1</v>
@@ -8072,7 +8075,7 @@
         <v>0</v>
       </c>
       <c r="K194" t="s">
-        <v>63</v>
+        <v>215</v>
       </c>
     </row>
     <row r="195">
@@ -8086,10 +8089,10 @@
         <v>18</v>
       </c>
       <c r="D195" t="s">
-        <v>36</v>
+        <v>107</v>
       </c>
       <c r="E195">
-        <v>149990</v>
+        <v>165990</v>
       </c>
       <c r="F195">
         <v>1</v>
@@ -8121,7 +8124,7 @@
         <v>18</v>
       </c>
       <c r="D196" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E196">
         <v>149990</v>
@@ -8156,7 +8159,7 @@
         <v>18</v>
       </c>
       <c r="D197" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E197">
         <v>149990</v>
@@ -8191,7 +8194,7 @@
         <v>18</v>
       </c>
       <c r="D198" t="s">
-        <v>132</v>
+        <v>19</v>
       </c>
       <c r="E198">
         <v>149990</v>
@@ -8217,28 +8220,28 @@
     </row>
     <row r="199">
       <c r="A199" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B199" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C199" t="s">
         <v>18</v>
       </c>
       <c r="D199" t="s">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="E199">
-        <v>189990</v>
+        <v>149990</v>
       </c>
       <c r="F199">
         <v>1</v>
       </c>
       <c r="G199" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H199" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I199">
         <v>0</v>
@@ -8247,7 +8250,7 @@
         <v>0</v>
       </c>
       <c r="K199" t="s">
-        <v>40</v>
+        <v>63</v>
       </c>
     </row>
     <row r="200">
@@ -8261,7 +8264,7 @@
         <v>18</v>
       </c>
       <c r="D200" t="s">
-        <v>36</v>
+        <v>107</v>
       </c>
       <c r="E200">
         <v>189990</v>
@@ -8296,7 +8299,7 @@
         <v>18</v>
       </c>
       <c r="D201" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E201">
         <v>189990</v>
@@ -8322,19 +8325,19 @@
     </row>
     <row r="202">
       <c r="A202" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B202" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C202" t="s">
         <v>18</v>
       </c>
       <c r="D202" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="E202">
-        <v>185990</v>
+        <v>189990</v>
       </c>
       <c r="F202">
         <v>1</v>
@@ -8352,7 +8355,7 @@
         <v>0</v>
       </c>
       <c r="K202" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
     </row>
     <row r="203">
@@ -8366,7 +8369,7 @@
         <v>18</v>
       </c>
       <c r="D203" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="E203">
         <v>185990</v>
@@ -8401,7 +8404,7 @@
         <v>18</v>
       </c>
       <c r="D204" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E204">
         <v>185990</v>
@@ -8427,28 +8430,28 @@
     </row>
     <row r="205">
       <c r="A205" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B205" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C205" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="D205" t="s">
-        <v>224</v>
+        <v>19</v>
       </c>
       <c r="E205">
-        <v>125990</v>
+        <v>185990</v>
       </c>
       <c r="F205">
         <v>1</v>
       </c>
       <c r="G205" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="H205" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="I205">
         <v>0</v>
@@ -8457,7 +8460,7 @@
         <v>0</v>
       </c>
       <c r="K205" t="s">
-        <v>87</v>
+        <v>21</v>
       </c>
     </row>
     <row r="206">
@@ -8471,7 +8474,7 @@
         <v>35</v>
       </c>
       <c r="D206" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E206">
         <v>125990</v>
@@ -8506,7 +8509,7 @@
         <v>35</v>
       </c>
       <c r="D207" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E207">
         <v>125990</v>
@@ -8541,7 +8544,7 @@
         <v>35</v>
       </c>
       <c r="D208" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E208">
         <v>125990</v>
@@ -8567,19 +8570,19 @@
     </row>
     <row r="209">
       <c r="A209" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="B209" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="C209" t="s">
         <v>35</v>
       </c>
       <c r="D209" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E209">
-        <v>129990</v>
+        <v>125990</v>
       </c>
       <c r="F209">
         <v>1</v>
@@ -8597,7 +8600,7 @@
         <v>0</v>
       </c>
       <c r="K209" t="s">
-        <v>21</v>
+        <v>87</v>
       </c>
     </row>
     <row r="210">
@@ -8611,7 +8614,7 @@
         <v>35</v>
       </c>
       <c r="D210" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E210">
         <v>129990</v>
@@ -8646,7 +8649,7 @@
         <v>35</v>
       </c>
       <c r="D211" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E211">
         <v>129990</v>
@@ -8672,28 +8675,28 @@
     </row>
     <row r="212">
       <c r="A212" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="B212" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="C212" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D212" t="s">
-        <v>36</v>
+        <v>232</v>
       </c>
       <c r="E212">
-        <v>125990</v>
+        <v>129990</v>
       </c>
       <c r="F212">
         <v>1</v>
       </c>
       <c r="G212" t="s">
-        <v>25</v>
+        <v>82</v>
       </c>
       <c r="H212" t="s">
-        <v>25</v>
+        <v>82</v>
       </c>
       <c r="I212">
         <v>0</v>
@@ -8716,7 +8719,7 @@
         <v>18</v>
       </c>
       <c r="D213" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E213">
         <v>125990</v>
@@ -8751,7 +8754,7 @@
         <v>18</v>
       </c>
       <c r="D214" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E214">
         <v>125990</v>
@@ -8777,19 +8780,19 @@
     </row>
     <row r="215">
       <c r="A215" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B215" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C215" t="s">
         <v>18</v>
       </c>
       <c r="D215" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="E215">
-        <v>140990</v>
+        <v>125990</v>
       </c>
       <c r="F215">
         <v>1</v>
@@ -8807,7 +8810,7 @@
         <v>0</v>
       </c>
       <c r="K215" t="s">
-        <v>214</v>
+        <v>21</v>
       </c>
     </row>
     <row r="216">
@@ -8821,7 +8824,7 @@
         <v>18</v>
       </c>
       <c r="D216" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="E216">
         <v>140990</v>
@@ -8856,7 +8859,7 @@
         <v>18</v>
       </c>
       <c r="D217" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="E217">
         <v>140990</v>
@@ -8891,7 +8894,7 @@
         <v>18</v>
       </c>
       <c r="D218" t="s">
-        <v>132</v>
+        <v>19</v>
       </c>
       <c r="E218">
         <v>140990</v>
@@ -8917,19 +8920,19 @@
     </row>
     <row r="219">
       <c r="A219" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B219" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C219" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="D219" t="s">
-        <v>36</v>
+        <v>132</v>
       </c>
       <c r="E219">
-        <v>195990</v>
+        <v>140990</v>
       </c>
       <c r="F219">
         <v>1</v>
@@ -8947,7 +8950,7 @@
         <v>0</v>
       </c>
       <c r="K219" t="s">
-        <v>116</v>
+        <v>214</v>
       </c>
     </row>
     <row r="220">
@@ -8961,7 +8964,7 @@
         <v>35</v>
       </c>
       <c r="D220" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E220">
         <v>195990</v>
@@ -8987,19 +8990,19 @@
     </row>
     <row r="221">
       <c r="A221" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B221" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C221" t="s">
         <v>35</v>
       </c>
       <c r="D221" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="E221">
-        <v>140900</v>
+        <v>195990</v>
       </c>
       <c r="F221">
         <v>1</v>
@@ -9031,10 +9034,10 @@
         <v>35</v>
       </c>
       <c r="D222" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="E222">
-        <v>130990</v>
+        <v>140900</v>
       </c>
       <c r="F222">
         <v>1</v>
@@ -9066,7 +9069,7 @@
         <v>35</v>
       </c>
       <c r="D223" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E223">
         <v>130990</v>
@@ -9101,7 +9104,7 @@
         <v>35</v>
       </c>
       <c r="D224" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E224">
         <v>130990</v>
@@ -9136,7 +9139,7 @@
         <v>35</v>
       </c>
       <c r="D225" t="s">
-        <v>132</v>
+        <v>19</v>
       </c>
       <c r="E225">
         <v>130990</v>
@@ -9162,28 +9165,28 @@
     </row>
     <row r="226">
       <c r="A226" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B226" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C226" t="s">
-        <v>122</v>
+        <v>35</v>
       </c>
       <c r="D226" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="E226">
-        <v>149990</v>
+        <v>130990</v>
       </c>
       <c r="F226">
         <v>1</v>
       </c>
       <c r="G226" t="s">
-        <v>119</v>
+        <v>25</v>
       </c>
       <c r="H226" t="s">
-        <v>78</v>
+        <v>25</v>
       </c>
       <c r="I226">
         <v>0</v>
@@ -9192,24 +9195,24 @@
         <v>0</v>
       </c>
       <c r="K226" t="s">
-        <v>21</v>
+        <v>116</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B227" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C227" t="s">
         <v>122</v>
       </c>
       <c r="D227" t="s">
-        <v>55</v>
+        <v>123</v>
       </c>
       <c r="E227">
-        <v>145990</v>
+        <v>149990</v>
       </c>
       <c r="F227">
         <v>1</v>
@@ -9227,24 +9230,24 @@
         <v>0</v>
       </c>
       <c r="K227" t="s">
-        <v>63</v>
+        <v>21</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B228" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C228" t="s">
         <v>122</v>
       </c>
       <c r="D228" t="s">
-        <v>123</v>
+        <v>55</v>
       </c>
       <c r="E228">
-        <v>279000</v>
+        <v>145990</v>
       </c>
       <c r="F228">
         <v>1</v>
@@ -9262,33 +9265,33 @@
         <v>0</v>
       </c>
       <c r="K228" t="s">
-        <v>40</v>
+        <v>63</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B229" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C229" t="s">
         <v>122</v>
       </c>
       <c r="D229" t="s">
-        <v>55</v>
+        <v>123</v>
       </c>
       <c r="E229">
-        <v>169990</v>
+        <v>279000</v>
       </c>
       <c r="F229">
         <v>1</v>
       </c>
       <c r="G229" t="s">
-        <v>25</v>
+        <v>119</v>
       </c>
       <c r="H229" t="s">
-        <v>25</v>
+        <v>78</v>
       </c>
       <c r="I229">
         <v>0</v>
@@ -9311,7 +9314,7 @@
         <v>122</v>
       </c>
       <c r="D230" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="E230">
         <v>169990</v>
@@ -9332,6 +9335,41 @@
         <v>0</v>
       </c>
       <c r="K230" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="s">
+        <v>247</v>
+      </c>
+      <c r="B231" t="s">
+        <v>248</v>
+      </c>
+      <c r="C231" t="s">
+        <v>122</v>
+      </c>
+      <c r="D231" t="s">
+        <v>36</v>
+      </c>
+      <c r="E231">
+        <v>169990</v>
+      </c>
+      <c r="F231">
+        <v>1</v>
+      </c>
+      <c r="G231" t="s">
+        <v>25</v>
+      </c>
+      <c r="H231" t="s">
+        <v>25</v>
+      </c>
+      <c r="I231">
+        <v>0</v>
+      </c>
+      <c r="J231">
+        <v>0</v>
+      </c>
+      <c r="K231" t="s">
         <v>40</v>
       </c>
     </row>

--- a/data/catalogo_jusp.xlsx
+++ b/data/catalogo_jusp.xlsx
@@ -1263,7 +1263,9 @@
       <c r="K3" t="s">
         <v>21</v>
       </c>
-      <c r="L3"/>
+      <c r="L3">
+        <v>10</v>
+      </c>
       <c r="N3" s="3"/>
       <c r="O3" s="3"/>
     </row>

--- a/data/catalogo_jusp.xlsx
+++ b/data/catalogo_jusp.xlsx
@@ -1264,7 +1264,7 @@
         <v>21</v>
       </c>
       <c r="L3">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="N3" s="3"/>
       <c r="O3" s="3"/>

--- a/data/catalogo_jusp.xlsx
+++ b/data/catalogo_jusp.xlsx
@@ -84,9 +84,6 @@
   </si>
   <si>
     <t>Black</t>
-  </si>
-  <si>
-    <t>TRUE</t>
   </si>
   <si>
     <t>nike-ir1526-500</t>
@@ -1216,18 +1213,11 @@
       <c r="K2" t="s">
         <v>21</v>
       </c>
-      <c r="M2" t="s">
-        <v>22</v>
-      </c>
-      <c r="N2" s="3">
-        <v>46143</v>
-      </c>
-      <c r="O2" s="3">
-        <v>46144</v>
-      </c>
-      <c r="P2" t="s">
-        <v>22</v>
-      </c>
+      <c r="L2">
+        <v>11</v>
+      </c>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
@@ -1264,17 +1254,17 @@
         <v>21</v>
       </c>
       <c r="L3">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="N3" s="3"/>
       <c r="O3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
         <v>23</v>
-      </c>
-      <c r="B4" t="s">
-        <v>24</v>
       </c>
       <c r="C4" t="s">
         <v>18</v>
@@ -1289,19 +1279,19 @@
         <v>1</v>
       </c>
       <c r="G4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4" t="s">
         <v>25</v>
-      </c>
-      <c r="H4" t="s">
-        <v>25</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4" t="s">
-        <v>26</v>
       </c>
       <c r="L4">
         <v>10</v>
@@ -1309,16 +1299,16 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" t="s">
         <v>23</v>
       </c>
-      <c r="B5" t="s">
-        <v>24</v>
-      </c>
       <c r="C5" t="s">
         <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E5">
         <v>599990</v>
@@ -1327,19 +1317,19 @@
         <v>1</v>
       </c>
       <c r="G5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5" t="s">
         <v>25</v>
-      </c>
-      <c r="H5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5" t="s">
-        <v>26</v>
       </c>
       <c r="L5">
         <v>10</v>
@@ -1347,10 +1337,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" t="s">
         <v>23</v>
-      </c>
-      <c r="B6" t="s">
-        <v>24</v>
       </c>
       <c r="C6" t="s">
         <v>18</v>
@@ -1365,19 +1355,19 @@
         <v>1</v>
       </c>
       <c r="G6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6" t="s">
         <v>25</v>
-      </c>
-      <c r="H6" t="s">
-        <v>28</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6" t="s">
-        <v>26</v>
       </c>
       <c r="L6">
         <v>10</v>
@@ -1385,10 +1375,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" t="s">
         <v>23</v>
-      </c>
-      <c r="B7" t="s">
-        <v>24</v>
       </c>
       <c r="C7" t="s">
         <v>18</v>
@@ -1403,19 +1393,19 @@
         <v>1</v>
       </c>
       <c r="G7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H7" t="s">
+        <v>27</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7" t="s">
         <v>25</v>
-      </c>
-      <c r="H7" t="s">
-        <v>28</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7" t="s">
-        <v>26</v>
       </c>
       <c r="L7">
         <v>10</v>
@@ -1423,16 +1413,16 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" t="s">
         <v>23</v>
       </c>
-      <c r="B8" t="s">
-        <v>24</v>
-      </c>
       <c r="C8" t="s">
         <v>18</v>
       </c>
       <c r="D8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E8">
         <v>599990</v>
@@ -1441,19 +1431,19 @@
         <v>1</v>
       </c>
       <c r="G8" t="s">
+        <v>24</v>
+      </c>
+      <c r="H8" t="s">
+        <v>27</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8" t="s">
         <v>25</v>
-      </c>
-      <c r="H8" t="s">
-        <v>28</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8" t="s">
-        <v>26</v>
       </c>
       <c r="L8">
         <v>10</v>
@@ -1461,10 +1451,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" t="s">
         <v>23</v>
-      </c>
-      <c r="B9" t="s">
-        <v>24</v>
       </c>
       <c r="C9" t="s">
         <v>18</v>
@@ -1479,19 +1469,19 @@
         <v>1</v>
       </c>
       <c r="G9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H9" t="s">
+        <v>27</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9" t="s">
         <v>25</v>
-      </c>
-      <c r="H9" t="s">
-        <v>28</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9" t="s">
-        <v>26</v>
       </c>
       <c r="L9">
         <v>10</v>
@@ -1499,10 +1489,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" t="s">
         <v>23</v>
-      </c>
-      <c r="B10" t="s">
-        <v>24</v>
       </c>
       <c r="C10" t="s">
         <v>18</v>
@@ -1517,19 +1507,19 @@
         <v>1</v>
       </c>
       <c r="G10" t="s">
+        <v>24</v>
+      </c>
+      <c r="H10" t="s">
+        <v>27</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10" t="s">
         <v>25</v>
-      </c>
-      <c r="H10" t="s">
-        <v>28</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10" t="s">
-        <v>26</v>
       </c>
       <c r="L10">
         <v>10</v>
@@ -1537,10 +1527,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" t="s">
         <v>23</v>
-      </c>
-      <c r="B11" t="s">
-        <v>24</v>
       </c>
       <c r="C11" t="s">
         <v>18</v>
@@ -1555,19 +1545,19 @@
         <v>1</v>
       </c>
       <c r="G11" t="s">
+        <v>24</v>
+      </c>
+      <c r="H11" t="s">
+        <v>27</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11" t="s">
         <v>25</v>
-      </c>
-      <c r="H11" t="s">
-        <v>28</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11" t="s">
-        <v>26</v>
       </c>
       <c r="L11">
         <v>10</v>
@@ -1575,16 +1565,16 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" t="s">
         <v>30</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" t="s">
         <v>31</v>
-      </c>
-      <c r="C12" t="s">
-        <v>18</v>
-      </c>
-      <c r="D12" t="s">
-        <v>32</v>
       </c>
       <c r="E12">
         <v>99990</v>
@@ -1615,16 +1605,16 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" t="s">
         <v>33</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>34</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>35</v>
-      </c>
-      <c r="D13" t="s">
-        <v>36</v>
       </c>
       <c r="E13">
         <v>119990</v>
@@ -1655,16 +1645,16 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" t="s">
         <v>37</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" t="s">
         <v>38</v>
-      </c>
-      <c r="C14" t="s">
-        <v>18</v>
-      </c>
-      <c r="D14" t="s">
-        <v>39</v>
       </c>
       <c r="E14">
         <v>95990</v>
@@ -1685,7 +1675,7 @@
         <v>1</v>
       </c>
       <c r="K14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L14">
         <v>45</v>
@@ -1695,10 +1685,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" t="s">
         <v>41</v>
-      </c>
-      <c r="B15" t="s">
-        <v>42</v>
       </c>
       <c r="C15" t="s">
         <v>18</v>
@@ -1725,7 +1715,7 @@
         <v>1</v>
       </c>
       <c r="K15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L15">
         <v>20</v>
@@ -1735,16 +1725,16 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" t="s">
         <v>43</v>
       </c>
-      <c r="B16" t="s">
-        <v>44</v>
-      </c>
       <c r="C16" t="s">
         <v>18</v>
       </c>
       <c r="D16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E16">
         <v>195990</v>
@@ -1765,17 +1755,17 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
     </row>
     <row r="17">
       <c r="A17" t="s">
+        <v>42</v>
+      </c>
+      <c r="B17" t="s">
         <v>43</v>
-      </c>
-      <c r="B17" t="s">
-        <v>44</v>
       </c>
       <c r="C17" t="s">
         <v>18</v>
@@ -1802,17 +1792,17 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
     </row>
     <row r="18">
       <c r="A18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" t="s">
         <v>46</v>
-      </c>
-      <c r="B18" t="s">
-        <v>47</v>
       </c>
       <c r="C18" t="s">
         <v>18</v>
@@ -1839,7 +1829,7 @@
         <v>1</v>
       </c>
       <c r="K18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L18">
         <v>20</v>
@@ -1849,16 +1839,16 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
+        <v>47</v>
+      </c>
+      <c r="B19" t="s">
         <v>48</v>
       </c>
-      <c r="B19" t="s">
-        <v>49</v>
-      </c>
       <c r="C19" t="s">
+        <v>34</v>
+      </c>
+      <c r="D19" t="s">
         <v>35</v>
-      </c>
-      <c r="D19" t="s">
-        <v>36</v>
       </c>
       <c r="E19">
         <v>125990</v>
@@ -1879,7 +1869,7 @@
         <v>1</v>
       </c>
       <c r="K19" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L19">
         <v>35</v>
@@ -1889,16 +1879,16 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
+        <v>50</v>
+      </c>
+      <c r="B20" t="s">
         <v>51</v>
       </c>
-      <c r="B20" t="s">
-        <v>52</v>
-      </c>
       <c r="C20" t="s">
         <v>18</v>
       </c>
       <c r="D20" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E20">
         <v>99990</v>
@@ -1929,16 +1919,16 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
+        <v>50</v>
+      </c>
+      <c r="B21" t="s">
         <v>51</v>
       </c>
-      <c r="B21" t="s">
-        <v>52</v>
-      </c>
       <c r="C21" t="s">
         <v>18</v>
       </c>
       <c r="D21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E21">
         <v>99990</v>
@@ -1969,16 +1959,16 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
+        <v>52</v>
+      </c>
+      <c r="B22" t="s">
         <v>53</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
+        <v>18</v>
+      </c>
+      <c r="D22" t="s">
         <v>54</v>
-      </c>
-      <c r="C22" t="s">
-        <v>18</v>
-      </c>
-      <c r="D22" t="s">
-        <v>55</v>
       </c>
       <c r="E22">
         <v>109990</v>
@@ -1999,7 +1989,7 @@
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L22">
         <v>30</v>
@@ -2009,16 +1999,16 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
+        <v>55</v>
+      </c>
+      <c r="B23" t="s">
         <v>56</v>
       </c>
-      <c r="B23" t="s">
-        <v>57</v>
-      </c>
       <c r="C23" t="s">
         <v>18</v>
       </c>
       <c r="D23" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E23">
         <v>119990</v>
@@ -2039,7 +2029,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L23">
         <v>30</v>
@@ -2049,16 +2039,16 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
+        <v>55</v>
+      </c>
+      <c r="B24" t="s">
         <v>56</v>
       </c>
-      <c r="B24" t="s">
-        <v>57</v>
-      </c>
       <c r="C24" t="s">
         <v>18</v>
       </c>
       <c r="D24" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E24">
         <v>119990</v>
@@ -2079,7 +2069,7 @@
         <v>0</v>
       </c>
       <c r="K24" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L24">
         <v>30</v>
@@ -2089,16 +2079,16 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B25" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C25" t="s">
         <v>18</v>
       </c>
       <c r="D25" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E25">
         <v>119990</v>
@@ -2119,7 +2109,7 @@
         <v>1</v>
       </c>
       <c r="K25" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L25">
         <v>30</v>
@@ -2129,16 +2119,16 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
+        <v>60</v>
+      </c>
+      <c r="B26" t="s">
         <v>61</v>
       </c>
-      <c r="B26" t="s">
-        <v>62</v>
-      </c>
       <c r="C26" t="s">
+        <v>34</v>
+      </c>
+      <c r="D26" t="s">
         <v>35</v>
-      </c>
-      <c r="D26" t="s">
-        <v>36</v>
       </c>
       <c r="E26">
         <v>119990</v>
@@ -2159,7 +2149,7 @@
         <v>1</v>
       </c>
       <c r="K26" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="L26">
         <v>35</v>
@@ -2169,16 +2159,16 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
+        <v>63</v>
+      </c>
+      <c r="B27" t="s">
         <v>64</v>
       </c>
-      <c r="B27" t="s">
-        <v>65</v>
-      </c>
       <c r="C27" t="s">
         <v>18</v>
       </c>
       <c r="D27" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E27">
         <v>99990</v>
@@ -2209,16 +2199,16 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
+        <v>65</v>
+      </c>
+      <c r="B28" t="s">
         <v>66</v>
       </c>
-      <c r="B28" t="s">
-        <v>67</v>
-      </c>
       <c r="C28" t="s">
         <v>18</v>
       </c>
       <c r="D28" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E28">
         <v>86990</v>
@@ -2249,10 +2239,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
+        <v>65</v>
+      </c>
+      <c r="B29" t="s">
         <v>66</v>
-      </c>
-      <c r="B29" t="s">
-        <v>67</v>
       </c>
       <c r="C29" t="s">
         <v>18</v>
@@ -2289,16 +2279,16 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
+        <v>67</v>
+      </c>
+      <c r="B30" t="s">
         <v>68</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
         <v>69</v>
       </c>
-      <c r="C30" t="s">
-        <v>70</v>
-      </c>
       <c r="D30" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E30">
         <v>96990</v>
@@ -2319,7 +2309,7 @@
         <v>1</v>
       </c>
       <c r="K30" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L30">
         <v>25</v>
@@ -2329,16 +2319,16 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
+        <v>71</v>
+      </c>
+      <c r="B31" t="s">
         <v>72</v>
       </c>
-      <c r="B31" t="s">
-        <v>73</v>
-      </c>
       <c r="C31" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D31" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E31">
         <v>95990</v>
@@ -2369,16 +2359,16 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
+        <v>73</v>
+      </c>
+      <c r="B32" t="s">
         <v>74</v>
       </c>
-      <c r="B32" t="s">
+      <c r="C32" t="s">
+        <v>18</v>
+      </c>
+      <c r="D32" t="s">
         <v>75</v>
-      </c>
-      <c r="C32" t="s">
-        <v>18</v>
-      </c>
-      <c r="D32" t="s">
-        <v>76</v>
       </c>
       <c r="E32">
         <v>129990</v>
@@ -2387,10 +2377,10 @@
         <v>1</v>
       </c>
       <c r="G32" t="s">
+        <v>76</v>
+      </c>
+      <c r="H32" t="s">
         <v>77</v>
-      </c>
-      <c r="H32" t="s">
-        <v>78</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -2406,16 +2396,16 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
+        <v>78</v>
+      </c>
+      <c r="B33" t="s">
         <v>79</v>
       </c>
-      <c r="B33" t="s">
+      <c r="C33" t="s">
+        <v>18</v>
+      </c>
+      <c r="D33" t="s">
         <v>80</v>
-      </c>
-      <c r="C33" t="s">
-        <v>18</v>
-      </c>
-      <c r="D33" t="s">
-        <v>81</v>
       </c>
       <c r="E33">
         <v>88990</v>
@@ -2424,10 +2414,10 @@
         <v>1</v>
       </c>
       <c r="G33" t="s">
+        <v>81</v>
+      </c>
+      <c r="H33" t="s">
         <v>82</v>
-      </c>
-      <c r="H33" t="s">
-        <v>83</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -2444,16 +2434,16 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
+        <v>78</v>
+      </c>
+      <c r="B34" t="s">
         <v>79</v>
       </c>
-      <c r="B34" t="s">
-        <v>80</v>
-      </c>
       <c r="C34" t="s">
         <v>18</v>
       </c>
       <c r="D34" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E34">
         <v>88990</v>
@@ -2462,10 +2452,10 @@
         <v>1</v>
       </c>
       <c r="G34" t="s">
+        <v>81</v>
+      </c>
+      <c r="H34" t="s">
         <v>82</v>
-      </c>
-      <c r="H34" t="s">
-        <v>83</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -2482,16 +2472,16 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
+        <v>84</v>
+      </c>
+      <c r="B35" t="s">
         <v>85</v>
       </c>
-      <c r="B35" t="s">
-        <v>86</v>
-      </c>
       <c r="C35" t="s">
         <v>18</v>
       </c>
       <c r="D35" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E35">
         <v>89990</v>
@@ -2512,21 +2502,21 @@
         <v>0</v>
       </c>
       <c r="K35" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
+        <v>84</v>
+      </c>
+      <c r="B36" t="s">
         <v>85</v>
       </c>
-      <c r="B36" t="s">
-        <v>86</v>
-      </c>
       <c r="C36" t="s">
         <v>18</v>
       </c>
       <c r="D36" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E36">
         <v>89990</v>
@@ -2547,21 +2537,21 @@
         <v>0</v>
       </c>
       <c r="K36" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
+        <v>87</v>
+      </c>
+      <c r="B37" t="s">
         <v>88</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C37" t="s">
+        <v>34</v>
+      </c>
+      <c r="D37" t="s">
         <v>89</v>
-      </c>
-      <c r="C37" t="s">
-        <v>35</v>
-      </c>
-      <c r="D37" t="s">
-        <v>90</v>
       </c>
       <c r="E37">
         <v>75990</v>
@@ -2570,10 +2560,10 @@
         <v>1</v>
       </c>
       <c r="G37" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H37" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -2582,21 +2572,21 @@
         <v>0</v>
       </c>
       <c r="K37" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
+        <v>87</v>
+      </c>
+      <c r="B38" t="s">
         <v>88</v>
       </c>
-      <c r="B38" t="s">
-        <v>89</v>
-      </c>
       <c r="C38" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D38" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E38">
         <v>79990</v>
@@ -2605,10 +2595,10 @@
         <v>1</v>
       </c>
       <c r="G38" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H38" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -2617,21 +2607,21 @@
         <v>0</v>
       </c>
       <c r="K38" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
+        <v>87</v>
+      </c>
+      <c r="B39" t="s">
         <v>88</v>
       </c>
-      <c r="B39" t="s">
-        <v>89</v>
-      </c>
       <c r="C39" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D39" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E39">
         <v>78990</v>
@@ -2640,10 +2630,10 @@
         <v>1</v>
       </c>
       <c r="G39" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H39" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I39">
         <v>0</v>
@@ -2652,21 +2642,21 @@
         <v>0</v>
       </c>
       <c r="K39" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
+        <v>93</v>
+      </c>
+      <c r="B40" t="s">
         <v>94</v>
       </c>
-      <c r="B40" t="s">
-        <v>95</v>
-      </c>
       <c r="C40" t="s">
         <v>18</v>
       </c>
       <c r="D40" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E40">
         <v>69990</v>
@@ -2687,15 +2677,15 @@
         <v>0</v>
       </c>
       <c r="K40" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
+        <v>95</v>
+      </c>
+      <c r="B41" t="s">
         <v>96</v>
-      </c>
-      <c r="B41" t="s">
-        <v>97</v>
       </c>
       <c r="C41" t="s">
         <v>18</v>
@@ -2722,15 +2712,15 @@
         <v>0</v>
       </c>
       <c r="K41" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
+        <v>97</v>
+      </c>
+      <c r="B42" t="s">
         <v>98</v>
-      </c>
-      <c r="B42" t="s">
-        <v>99</v>
       </c>
       <c r="C42" t="s">
         <v>18</v>
@@ -2745,10 +2735,10 @@
         <v>0</v>
       </c>
       <c r="G42" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H42" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -2757,21 +2747,21 @@
         <v>0</v>
       </c>
       <c r="K42" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
+        <v>99</v>
+      </c>
+      <c r="B43" t="s">
         <v>100</v>
       </c>
-      <c r="B43" t="s">
-        <v>101</v>
-      </c>
       <c r="C43" t="s">
         <v>18</v>
       </c>
       <c r="D43" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E43" s="4">
         <v>119990</v>
@@ -2792,21 +2782,21 @@
         <v>0</v>
       </c>
       <c r="K43" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
+        <v>101</v>
+      </c>
+      <c r="B44" t="s">
         <v>102</v>
       </c>
-      <c r="B44" t="s">
-        <v>103</v>
-      </c>
       <c r="C44" t="s">
         <v>18</v>
       </c>
       <c r="D44" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E44">
         <v>65990</v>
@@ -2815,10 +2805,10 @@
         <v>1</v>
       </c>
       <c r="G44" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H44" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I44">
         <v>0</v>
@@ -2827,21 +2817,21 @@
         <v>0</v>
       </c>
       <c r="K44" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
+        <v>101</v>
+      </c>
+      <c r="B45" t="s">
         <v>102</v>
       </c>
-      <c r="B45" t="s">
-        <v>103</v>
-      </c>
       <c r="C45" t="s">
         <v>18</v>
       </c>
       <c r="D45" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E45">
         <v>75990</v>
@@ -2850,10 +2840,10 @@
         <v>1</v>
       </c>
       <c r="G45" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H45" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I45">
         <v>0</v>
@@ -2862,21 +2852,21 @@
         <v>0</v>
       </c>
       <c r="K45" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
+        <v>101</v>
+      </c>
+      <c r="B46" t="s">
         <v>102</v>
       </c>
-      <c r="B46" t="s">
-        <v>103</v>
-      </c>
       <c r="C46" t="s">
         <v>18</v>
       </c>
       <c r="D46" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E46">
         <v>85990</v>
@@ -2885,10 +2875,10 @@
         <v>1</v>
       </c>
       <c r="G46" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H46" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I46">
         <v>0</v>
@@ -2897,21 +2887,21 @@
         <v>0</v>
       </c>
       <c r="K46" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
+        <v>104</v>
+      </c>
+      <c r="B47" t="s">
         <v>105</v>
       </c>
-      <c r="B47" t="s">
+      <c r="C47" t="s">
+        <v>18</v>
+      </c>
+      <c r="D47" t="s">
         <v>106</v>
-      </c>
-      <c r="C47" t="s">
-        <v>18</v>
-      </c>
-      <c r="D47" t="s">
-        <v>107</v>
       </c>
       <c r="E47">
         <v>79990</v>
@@ -2932,21 +2922,21 @@
         <v>0</v>
       </c>
       <c r="K47" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
+        <v>104</v>
+      </c>
+      <c r="B48" t="s">
         <v>105</v>
       </c>
-      <c r="B48" t="s">
-        <v>106</v>
-      </c>
       <c r="C48" t="s">
         <v>18</v>
       </c>
       <c r="D48" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E48">
         <v>79990</v>
@@ -2967,21 +2957,21 @@
         <v>0</v>
       </c>
       <c r="K48" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
+        <v>104</v>
+      </c>
+      <c r="B49" t="s">
         <v>105</v>
       </c>
-      <c r="B49" t="s">
-        <v>106</v>
-      </c>
       <c r="C49" t="s">
         <v>18</v>
       </c>
       <c r="D49" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E49">
         <v>79990</v>
@@ -3002,21 +2992,21 @@
         <v>0</v>
       </c>
       <c r="K49" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
+        <v>104</v>
+      </c>
+      <c r="B50" t="s">
         <v>105</v>
       </c>
-      <c r="B50" t="s">
-        <v>106</v>
-      </c>
       <c r="C50" t="s">
         <v>18</v>
       </c>
       <c r="D50" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E50">
         <v>79990</v>
@@ -3037,15 +3027,15 @@
         <v>0</v>
       </c>
       <c r="K50" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
+        <v>104</v>
+      </c>
+      <c r="B51" t="s">
         <v>105</v>
-      </c>
-      <c r="B51" t="s">
-        <v>106</v>
       </c>
       <c r="C51" t="s">
         <v>18</v>
@@ -3072,21 +3062,21 @@
         <v>0</v>
       </c>
       <c r="K51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
+        <v>107</v>
+      </c>
+      <c r="B52" t="s">
         <v>108</v>
       </c>
-      <c r="B52" t="s">
-        <v>109</v>
-      </c>
       <c r="C52" t="s">
         <v>18</v>
       </c>
       <c r="D52" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E52">
         <v>155990</v>
@@ -3107,21 +3097,21 @@
         <v>0</v>
       </c>
       <c r="K52" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
+        <v>107</v>
+      </c>
+      <c r="B53" t="s">
         <v>108</v>
       </c>
-      <c r="B53" t="s">
-        <v>109</v>
-      </c>
       <c r="C53" t="s">
         <v>18</v>
       </c>
       <c r="D53" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E53">
         <v>155990</v>
@@ -3142,21 +3132,21 @@
         <v>0</v>
       </c>
       <c r="K53" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
+        <v>107</v>
+      </c>
+      <c r="B54" t="s">
         <v>108</v>
       </c>
-      <c r="B54" t="s">
-        <v>109</v>
-      </c>
       <c r="C54" t="s">
         <v>18</v>
       </c>
       <c r="D54" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E54">
         <v>155990</v>
@@ -3177,15 +3167,15 @@
         <v>0</v>
       </c>
       <c r="K54" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
+        <v>107</v>
+      </c>
+      <c r="B55" t="s">
         <v>108</v>
-      </c>
-      <c r="B55" t="s">
-        <v>109</v>
       </c>
       <c r="C55" t="s">
         <v>18</v>
@@ -3212,21 +3202,21 @@
         <v>0</v>
       </c>
       <c r="K55" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
+        <v>109</v>
+      </c>
+      <c r="B56" t="s">
         <v>110</v>
       </c>
-      <c r="B56" t="s">
-        <v>111</v>
-      </c>
       <c r="C56" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D56" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E56">
         <v>49990</v>
@@ -3252,16 +3242,16 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
+        <v>109</v>
+      </c>
+      <c r="B57" t="s">
         <v>110</v>
       </c>
-      <c r="B57" t="s">
-        <v>111</v>
-      </c>
       <c r="C57" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D57" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E57">
         <v>49990</v>
@@ -3287,16 +3277,16 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
+        <v>111</v>
+      </c>
+      <c r="B58" t="s">
         <v>112</v>
       </c>
-      <c r="B58" t="s">
-        <v>113</v>
-      </c>
       <c r="C58" t="s">
+        <v>34</v>
+      </c>
+      <c r="D58" t="s">
         <v>35</v>
-      </c>
-      <c r="D58" t="s">
-        <v>36</v>
       </c>
       <c r="E58">
         <v>135990</v>
@@ -3317,21 +3307,21 @@
         <v>0</v>
       </c>
       <c r="K58" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
+        <v>113</v>
+      </c>
+      <c r="B59" t="s">
         <v>114</v>
       </c>
-      <c r="B59" t="s">
-        <v>115</v>
-      </c>
       <c r="C59" t="s">
         <v>18</v>
       </c>
       <c r="D59" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E59">
         <v>155990</v>
@@ -3352,21 +3342,21 @@
         <v>0</v>
       </c>
       <c r="K59" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
+        <v>113</v>
+      </c>
+      <c r="B60" t="s">
         <v>114</v>
       </c>
-      <c r="B60" t="s">
-        <v>115</v>
-      </c>
       <c r="C60" t="s">
         <v>18</v>
       </c>
       <c r="D60" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E60">
         <v>155990</v>
@@ -3387,15 +3377,15 @@
         <v>0</v>
       </c>
       <c r="K60" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
+        <v>113</v>
+      </c>
+      <c r="B61" t="s">
         <v>114</v>
-      </c>
-      <c r="B61" t="s">
-        <v>115</v>
       </c>
       <c r="C61" t="s">
         <v>18</v>
@@ -3422,21 +3412,21 @@
         <v>0</v>
       </c>
       <c r="K61" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
+        <v>116</v>
+      </c>
+      <c r="B62" t="s">
         <v>117</v>
       </c>
-      <c r="B62" t="s">
-        <v>118</v>
-      </c>
       <c r="C62" t="s">
         <v>18</v>
       </c>
       <c r="D62" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E62">
         <v>129990</v>
@@ -3445,10 +3435,10 @@
         <v>1</v>
       </c>
       <c r="G62" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H62" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I62">
         <v>0</v>
@@ -3462,16 +3452,16 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
+        <v>116</v>
+      </c>
+      <c r="B63" t="s">
         <v>117</v>
       </c>
-      <c r="B63" t="s">
-        <v>118</v>
-      </c>
       <c r="C63" t="s">
         <v>18</v>
       </c>
       <c r="D63" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E63">
         <v>129990</v>
@@ -3480,10 +3470,10 @@
         <v>1</v>
       </c>
       <c r="G63" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H63" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I63">
         <v>0</v>
@@ -3497,16 +3487,16 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
+        <v>119</v>
+      </c>
+      <c r="B64" t="s">
         <v>120</v>
       </c>
-      <c r="B64" t="s">
+      <c r="C64" t="s">
         <v>121</v>
       </c>
-      <c r="C64" t="s">
+      <c r="D64" t="s">
         <v>122</v>
-      </c>
-      <c r="D64" t="s">
-        <v>123</v>
       </c>
       <c r="E64">
         <v>179990</v>
@@ -3515,10 +3505,10 @@
         <v>1</v>
       </c>
       <c r="G64" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H64" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I64">
         <v>0</v>
@@ -3532,16 +3522,16 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
+        <v>123</v>
+      </c>
+      <c r="B65" t="s">
         <v>124</v>
       </c>
-      <c r="B65" t="s">
-        <v>125</v>
-      </c>
       <c r="C65" t="s">
         <v>18</v>
       </c>
       <c r="D65" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E65">
         <v>159990</v>
@@ -3550,10 +3540,10 @@
         <v>1</v>
       </c>
       <c r="G65" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H65" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I65">
         <v>0</v>
@@ -3567,16 +3557,16 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
+        <v>125</v>
+      </c>
+      <c r="B66" t="s">
         <v>126</v>
       </c>
-      <c r="B66" t="s">
-        <v>127</v>
-      </c>
       <c r="C66" t="s">
         <v>18</v>
       </c>
       <c r="D66" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E66">
         <v>134990</v>
@@ -3585,10 +3575,10 @@
         <v>1</v>
       </c>
       <c r="G66" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H66" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I66">
         <v>0</v>
@@ -3602,16 +3592,16 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
+        <v>125</v>
+      </c>
+      <c r="B67" t="s">
         <v>126</v>
       </c>
-      <c r="B67" t="s">
-        <v>127</v>
-      </c>
       <c r="C67" t="s">
         <v>18</v>
       </c>
       <c r="D67" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E67">
         <v>134990</v>
@@ -3620,10 +3610,10 @@
         <v>1</v>
       </c>
       <c r="G67" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H67" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I67">
         <v>0</v>
@@ -3637,16 +3627,16 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
+        <v>125</v>
+      </c>
+      <c r="B68" t="s">
         <v>126</v>
       </c>
-      <c r="B68" t="s">
-        <v>127</v>
-      </c>
       <c r="C68" t="s">
         <v>18</v>
       </c>
       <c r="D68" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E68">
         <v>134990</v>
@@ -3655,10 +3645,10 @@
         <v>1</v>
       </c>
       <c r="G68" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H68" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I68">
         <v>0</v>
@@ -3672,16 +3662,16 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
+        <v>127</v>
+      </c>
+      <c r="B69" t="s">
         <v>128</v>
       </c>
-      <c r="B69" t="s">
-        <v>129</v>
-      </c>
       <c r="C69" t="s">
         <v>18</v>
       </c>
       <c r="D69" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E69">
         <v>79990</v>
@@ -3690,10 +3680,10 @@
         <v>1</v>
       </c>
       <c r="G69" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H69" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I69">
         <v>0</v>
@@ -3707,16 +3697,16 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
+        <v>129</v>
+      </c>
+      <c r="B70" t="s">
         <v>130</v>
       </c>
-      <c r="B70" t="s">
-        <v>131</v>
-      </c>
       <c r="C70" t="s">
         <v>18</v>
       </c>
       <c r="D70" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E70">
         <v>134990</v>
@@ -3725,10 +3715,10 @@
         <v>1</v>
       </c>
       <c r="G70" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H70" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I70">
         <v>0</v>
@@ -3742,16 +3732,16 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
+        <v>129</v>
+      </c>
+      <c r="B71" t="s">
         <v>130</v>
       </c>
-      <c r="B71" t="s">
-        <v>131</v>
-      </c>
       <c r="C71" t="s">
+        <v>34</v>
+      </c>
+      <c r="D71" t="s">
         <v>35</v>
-      </c>
-      <c r="D71" t="s">
-        <v>36</v>
       </c>
       <c r="E71">
         <v>134990</v>
@@ -3760,10 +3750,10 @@
         <v>1</v>
       </c>
       <c r="G71" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H71" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I71">
         <v>0</v>
@@ -3777,16 +3767,16 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
+        <v>129</v>
+      </c>
+      <c r="B72" t="s">
         <v>130</v>
       </c>
-      <c r="B72" t="s">
-        <v>131</v>
-      </c>
       <c r="C72" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D72" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E72">
         <v>134990</v>
@@ -3795,10 +3785,10 @@
         <v>1</v>
       </c>
       <c r="G72" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H72" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I72">
         <v>0</v>
@@ -3812,13 +3802,13 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
+        <v>129</v>
+      </c>
+      <c r="B73" t="s">
         <v>130</v>
       </c>
-      <c r="B73" t="s">
-        <v>131</v>
-      </c>
       <c r="C73" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D73" t="s">
         <v>19</v>
@@ -3830,10 +3820,10 @@
         <v>1</v>
       </c>
       <c r="G73" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H73" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I73">
         <v>0</v>
@@ -3847,16 +3837,16 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
+        <v>129</v>
+      </c>
+      <c r="B74" t="s">
         <v>130</v>
       </c>
-      <c r="B74" t="s">
+      <c r="C74" t="s">
+        <v>34</v>
+      </c>
+      <c r="D74" t="s">
         <v>131</v>
-      </c>
-      <c r="C74" t="s">
-        <v>35</v>
-      </c>
-      <c r="D74" t="s">
-        <v>132</v>
       </c>
       <c r="E74">
         <v>134990</v>
@@ -3865,10 +3855,10 @@
         <v>1</v>
       </c>
       <c r="G74" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H74" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I74">
         <v>0</v>
@@ -3882,16 +3872,16 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
+        <v>132</v>
+      </c>
+      <c r="B75" t="s">
         <v>133</v>
       </c>
-      <c r="B75" t="s">
-        <v>134</v>
-      </c>
       <c r="C75" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D75" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E75">
         <v>119990</v>
@@ -3900,10 +3890,10 @@
         <v>1</v>
       </c>
       <c r="G75" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H75" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I75">
         <v>0</v>
@@ -3917,16 +3907,16 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
+        <v>132</v>
+      </c>
+      <c r="B76" t="s">
         <v>133</v>
       </c>
-      <c r="B76" t="s">
-        <v>134</v>
-      </c>
       <c r="C76" t="s">
+        <v>34</v>
+      </c>
+      <c r="D76" t="s">
         <v>35</v>
-      </c>
-      <c r="D76" t="s">
-        <v>36</v>
       </c>
       <c r="E76">
         <v>119990</v>
@@ -3935,10 +3925,10 @@
         <v>1</v>
       </c>
       <c r="G76" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H76" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I76">
         <v>0</v>
@@ -3952,16 +3942,16 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
+        <v>132</v>
+      </c>
+      <c r="B77" t="s">
         <v>133</v>
       </c>
-      <c r="B77" t="s">
-        <v>134</v>
-      </c>
       <c r="C77" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D77" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E77">
         <v>119990</v>
@@ -3970,10 +3960,10 @@
         <v>1</v>
       </c>
       <c r="G77" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H77" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I77">
         <v>0</v>
@@ -3987,16 +3977,16 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
+        <v>134</v>
+      </c>
+      <c r="B78" t="s">
         <v>135</v>
       </c>
-      <c r="B78" t="s">
-        <v>136</v>
-      </c>
       <c r="C78" t="s">
+        <v>34</v>
+      </c>
+      <c r="D78" t="s">
         <v>35</v>
-      </c>
-      <c r="D78" t="s">
-        <v>36</v>
       </c>
       <c r="E78">
         <v>119990</v>
@@ -4005,10 +3995,10 @@
         <v>1</v>
       </c>
       <c r="G78" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H78" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I78">
         <v>0</v>
@@ -4017,21 +4007,21 @@
         <v>0</v>
       </c>
       <c r="K78" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
+        <v>134</v>
+      </c>
+      <c r="B79" t="s">
         <v>135</v>
       </c>
-      <c r="B79" t="s">
-        <v>136</v>
-      </c>
       <c r="C79" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D79" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E79">
         <v>119990</v>
@@ -4040,10 +4030,10 @@
         <v>1</v>
       </c>
       <c r="G79" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H79" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I79">
         <v>0</v>
@@ -4052,21 +4042,21 @@
         <v>0</v>
       </c>
       <c r="K79" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
+        <v>137</v>
+      </c>
+      <c r="B80" t="s">
         <v>138</v>
       </c>
-      <c r="B80" t="s">
-        <v>139</v>
-      </c>
       <c r="C80" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D80" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E80">
         <v>39990</v>
@@ -4075,10 +4065,10 @@
         <v>1</v>
       </c>
       <c r="G80" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H80" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I80">
         <v>0</v>
@@ -4092,16 +4082,16 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
+        <v>137</v>
+      </c>
+      <c r="B81" t="s">
         <v>138</v>
       </c>
-      <c r="B81" t="s">
-        <v>139</v>
-      </c>
       <c r="C81" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D81" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E81">
         <v>39990</v>
@@ -4110,10 +4100,10 @@
         <v>1</v>
       </c>
       <c r="G81" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H81" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I81">
         <v>0</v>
@@ -4127,16 +4117,16 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
+        <v>139</v>
+      </c>
+      <c r="B82" t="s">
         <v>140</v>
       </c>
-      <c r="B82" t="s">
-        <v>141</v>
-      </c>
       <c r="C82" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D82" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E82">
         <v>39990</v>
@@ -4145,10 +4135,10 @@
         <v>1</v>
       </c>
       <c r="G82" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H82" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I82">
         <v>0</v>
@@ -4157,21 +4147,21 @@
         <v>0</v>
       </c>
       <c r="K82" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
+        <v>141</v>
+      </c>
+      <c r="B83" t="s">
         <v>142</v>
       </c>
-      <c r="B83" t="s">
+      <c r="C83" t="s">
+        <v>121</v>
+      </c>
+      <c r="D83" t="s">
         <v>143</v>
-      </c>
-      <c r="C83" t="s">
-        <v>122</v>
-      </c>
-      <c r="D83" t="s">
-        <v>144</v>
       </c>
       <c r="E83">
         <v>140990</v>
@@ -4180,10 +4170,10 @@
         <v>1</v>
       </c>
       <c r="G83" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H83" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I83">
         <v>0</v>
@@ -4192,21 +4182,21 @@
         <v>0</v>
       </c>
       <c r="K83" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
+        <v>141</v>
+      </c>
+      <c r="B84" t="s">
         <v>142</v>
       </c>
-      <c r="B84" t="s">
-        <v>143</v>
-      </c>
       <c r="C84" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D84" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E84">
         <v>145990</v>
@@ -4215,10 +4205,10 @@
         <v>1</v>
       </c>
       <c r="G84" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H84" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I84">
         <v>0</v>
@@ -4227,21 +4217,21 @@
         <v>0</v>
       </c>
       <c r="K84" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
+        <v>145</v>
+      </c>
+      <c r="B85" t="s">
         <v>146</v>
       </c>
-      <c r="B85" t="s">
-        <v>147</v>
-      </c>
       <c r="C85" t="s">
         <v>18</v>
       </c>
       <c r="D85" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E85" s="4">
         <v>199990</v>
@@ -4250,10 +4240,10 @@
         <v>1</v>
       </c>
       <c r="G85" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H85" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I85">
         <v>0</v>
@@ -4262,21 +4252,21 @@
         <v>0</v>
       </c>
       <c r="K85" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
+        <v>145</v>
+      </c>
+      <c r="B86" t="s">
         <v>146</v>
       </c>
-      <c r="B86" t="s">
-        <v>147</v>
-      </c>
       <c r="C86" t="s">
         <v>18</v>
       </c>
       <c r="D86" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E86" s="4">
         <v>199990</v>
@@ -4285,10 +4275,10 @@
         <v>1</v>
       </c>
       <c r="G86" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H86" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I86">
         <v>0</v>
@@ -4297,21 +4287,21 @@
         <v>0</v>
       </c>
       <c r="K86" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
+        <v>145</v>
+      </c>
+      <c r="B87" t="s">
         <v>146</v>
       </c>
-      <c r="B87" t="s">
-        <v>147</v>
-      </c>
       <c r="C87" t="s">
         <v>18</v>
       </c>
       <c r="D87" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E87" s="4">
         <v>199990</v>
@@ -4320,10 +4310,10 @@
         <v>1</v>
       </c>
       <c r="G87" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H87" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I87">
         <v>0</v>
@@ -4332,15 +4322,15 @@
         <v>0</v>
       </c>
       <c r="K87" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
+        <v>145</v>
+      </c>
+      <c r="B88" t="s">
         <v>146</v>
-      </c>
-      <c r="B88" t="s">
-        <v>147</v>
       </c>
       <c r="C88" t="s">
         <v>18</v>
@@ -4355,10 +4345,10 @@
         <v>1</v>
       </c>
       <c r="G88" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H88" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I88">
         <v>0</v>
@@ -4367,21 +4357,21 @@
         <v>0</v>
       </c>
       <c r="K88" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
+        <v>145</v>
+      </c>
+      <c r="B89" t="s">
         <v>146</v>
       </c>
-      <c r="B89" t="s">
-        <v>147</v>
-      </c>
       <c r="C89" t="s">
         <v>18</v>
       </c>
       <c r="D89" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E89" s="4">
         <v>199990</v>
@@ -4390,10 +4380,10 @@
         <v>1</v>
       </c>
       <c r="G89" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H89" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I89">
         <v>0</v>
@@ -4402,21 +4392,21 @@
         <v>0</v>
       </c>
       <c r="K89" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
+        <v>147</v>
+      </c>
+      <c r="B90" t="s">
         <v>148</v>
       </c>
-      <c r="B90" t="s">
-        <v>149</v>
-      </c>
       <c r="C90" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D90" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E90">
         <v>155990</v>
@@ -4425,10 +4415,10 @@
         <v>1</v>
       </c>
       <c r="G90" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H90" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I90">
         <v>0</v>
@@ -4442,16 +4432,16 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
+        <v>147</v>
+      </c>
+      <c r="B91" t="s">
         <v>148</v>
       </c>
-      <c r="B91" t="s">
-        <v>149</v>
-      </c>
       <c r="C91" t="s">
+        <v>34</v>
+      </c>
+      <c r="D91" t="s">
         <v>35</v>
-      </c>
-      <c r="D91" t="s">
-        <v>36</v>
       </c>
       <c r="E91">
         <v>155990</v>
@@ -4460,10 +4450,10 @@
         <v>1</v>
       </c>
       <c r="G91" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H91" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I91">
         <v>0</v>
@@ -4477,16 +4467,16 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
+        <v>147</v>
+      </c>
+      <c r="B92" t="s">
         <v>148</v>
       </c>
-      <c r="B92" t="s">
-        <v>149</v>
-      </c>
       <c r="C92" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D92" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E92">
         <v>155990</v>
@@ -4495,10 +4485,10 @@
         <v>1</v>
       </c>
       <c r="G92" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H92" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I92">
         <v>0</v>
@@ -4512,13 +4502,13 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
+        <v>147</v>
+      </c>
+      <c r="B93" t="s">
         <v>148</v>
       </c>
-      <c r="B93" t="s">
-        <v>149</v>
-      </c>
       <c r="C93" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D93" t="s">
         <v>19</v>
@@ -4530,10 +4520,10 @@
         <v>1</v>
       </c>
       <c r="G93" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H93" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I93">
         <v>0</v>
@@ -4547,16 +4537,16 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
+        <v>149</v>
+      </c>
+      <c r="B94" t="s">
         <v>150</v>
       </c>
-      <c r="B94" t="s">
-        <v>151</v>
-      </c>
       <c r="C94" t="s">
         <v>18</v>
       </c>
       <c r="D94" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E94">
         <v>269990</v>
@@ -4565,10 +4555,10 @@
         <v>1</v>
       </c>
       <c r="G94" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H94" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I94">
         <v>0</v>
@@ -4577,21 +4567,21 @@
         <v>0</v>
       </c>
       <c r="K94" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
+        <v>149</v>
+      </c>
+      <c r="B95" t="s">
         <v>150</v>
       </c>
-      <c r="B95" t="s">
-        <v>151</v>
-      </c>
       <c r="C95" t="s">
         <v>18</v>
       </c>
       <c r="D95" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E95">
         <v>269990</v>
@@ -4600,10 +4590,10 @@
         <v>1</v>
       </c>
       <c r="G95" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H95" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I95">
         <v>0</v>
@@ -4612,21 +4602,21 @@
         <v>0</v>
       </c>
       <c r="K95" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
+        <v>149</v>
+      </c>
+      <c r="B96" t="s">
         <v>150</v>
       </c>
-      <c r="B96" t="s">
-        <v>151</v>
-      </c>
       <c r="C96" t="s">
         <v>18</v>
       </c>
       <c r="D96" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E96">
         <v>269990</v>
@@ -4635,10 +4625,10 @@
         <v>1</v>
       </c>
       <c r="G96" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H96" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I96">
         <v>0</v>
@@ -4647,15 +4637,15 @@
         <v>0</v>
       </c>
       <c r="K96" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
+        <v>149</v>
+      </c>
+      <c r="B97" t="s">
         <v>150</v>
-      </c>
-      <c r="B97" t="s">
-        <v>151</v>
       </c>
       <c r="C97" t="s">
         <v>18</v>
@@ -4670,10 +4660,10 @@
         <v>1</v>
       </c>
       <c r="G97" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H97" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I97">
         <v>0</v>
@@ -4682,21 +4672,21 @@
         <v>0</v>
       </c>
       <c r="K97" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
+        <v>149</v>
+      </c>
+      <c r="B98" t="s">
         <v>150</v>
       </c>
-      <c r="B98" t="s">
-        <v>151</v>
-      </c>
       <c r="C98" t="s">
         <v>18</v>
       </c>
       <c r="D98" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E98">
         <v>269990</v>
@@ -4705,10 +4695,10 @@
         <v>1</v>
       </c>
       <c r="G98" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H98" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I98">
         <v>0</v>
@@ -4717,21 +4707,21 @@
         <v>0</v>
       </c>
       <c r="K98" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
+        <v>152</v>
+      </c>
+      <c r="B99" t="s">
         <v>153</v>
       </c>
-      <c r="B99" t="s">
-        <v>154</v>
-      </c>
       <c r="C99" t="s">
         <v>18</v>
       </c>
       <c r="D99" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E99">
         <v>199990</v>
@@ -4740,10 +4730,10 @@
         <v>1</v>
       </c>
       <c r="G99" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H99" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I99">
         <v>0</v>
@@ -4752,21 +4742,21 @@
         <v>0</v>
       </c>
       <c r="K99" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
+        <v>152</v>
+      </c>
+      <c r="B100" t="s">
         <v>153</v>
       </c>
-      <c r="B100" t="s">
-        <v>154</v>
-      </c>
       <c r="C100" t="s">
         <v>18</v>
       </c>
       <c r="D100" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E100">
         <v>199990</v>
@@ -4775,10 +4765,10 @@
         <v>1</v>
       </c>
       <c r="G100" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H100" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I100">
         <v>0</v>
@@ -4787,15 +4777,15 @@
         <v>0</v>
       </c>
       <c r="K100" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
+        <v>152</v>
+      </c>
+      <c r="B101" t="s">
         <v>153</v>
-      </c>
-      <c r="B101" t="s">
-        <v>154</v>
       </c>
       <c r="C101" t="s">
         <v>18</v>
@@ -4810,10 +4800,10 @@
         <v>1</v>
       </c>
       <c r="G101" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H101" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I101">
         <v>0</v>
@@ -4822,21 +4812,21 @@
         <v>0</v>
       </c>
       <c r="K101" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
+        <v>152</v>
+      </c>
+      <c r="B102" t="s">
         <v>153</v>
       </c>
-      <c r="B102" t="s">
-        <v>154</v>
-      </c>
       <c r="C102" t="s">
         <v>18</v>
       </c>
       <c r="D102" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E102">
         <v>199990</v>
@@ -4845,10 +4835,10 @@
         <v>1</v>
       </c>
       <c r="G102" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H102" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I102">
         <v>0</v>
@@ -4857,21 +4847,21 @@
         <v>0</v>
       </c>
       <c r="K102" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
+        <v>154</v>
+      </c>
+      <c r="B103" t="s">
         <v>155</v>
       </c>
-      <c r="B103" t="s">
-        <v>156</v>
-      </c>
       <c r="C103" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D103" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E103">
         <v>194990</v>
@@ -4880,10 +4870,10 @@
         <v>1</v>
       </c>
       <c r="G103" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H103" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I103">
         <v>0</v>
@@ -4897,16 +4887,16 @@
     </row>
     <row r="104">
       <c r="A104" t="s">
+        <v>154</v>
+      </c>
+      <c r="B104" t="s">
         <v>155</v>
       </c>
-      <c r="B104" t="s">
-        <v>156</v>
-      </c>
       <c r="C104" t="s">
+        <v>34</v>
+      </c>
+      <c r="D104" t="s">
         <v>35</v>
-      </c>
-      <c r="D104" t="s">
-        <v>36</v>
       </c>
       <c r="E104">
         <v>194990</v>
@@ -4915,10 +4905,10 @@
         <v>1</v>
       </c>
       <c r="G104" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H104" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I104">
         <v>0</v>
@@ -4932,16 +4922,16 @@
     </row>
     <row r="105">
       <c r="A105" t="s">
+        <v>154</v>
+      </c>
+      <c r="B105" t="s">
         <v>155</v>
       </c>
-      <c r="B105" t="s">
-        <v>156</v>
-      </c>
       <c r="C105" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D105" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E105">
         <v>194990</v>
@@ -4950,10 +4940,10 @@
         <v>1</v>
       </c>
       <c r="G105" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H105" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I105">
         <v>0</v>
@@ -4967,13 +4957,13 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
+        <v>154</v>
+      </c>
+      <c r="B106" t="s">
         <v>155</v>
       </c>
-      <c r="B106" t="s">
-        <v>156</v>
-      </c>
       <c r="C106" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D106" t="s">
         <v>19</v>
@@ -4985,10 +4975,10 @@
         <v>1</v>
       </c>
       <c r="G106" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H106" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I106">
         <v>0</v>
@@ -5002,16 +4992,16 @@
     </row>
     <row r="107">
       <c r="A107" t="s">
+        <v>156</v>
+      </c>
+      <c r="B107" t="s">
         <v>157</v>
       </c>
-      <c r="B107" t="s">
-        <v>158</v>
-      </c>
       <c r="C107" t="s">
         <v>18</v>
       </c>
       <c r="D107" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E107">
         <v>202990</v>
@@ -5032,21 +5022,21 @@
         <v>0</v>
       </c>
       <c r="K107" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
+        <v>158</v>
+      </c>
+      <c r="B108" t="s">
         <v>159</v>
       </c>
-      <c r="B108" t="s">
-        <v>160</v>
-      </c>
       <c r="C108" t="s">
         <v>18</v>
       </c>
       <c r="D108" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E108">
         <v>151990</v>
@@ -5055,10 +5045,10 @@
         <v>1</v>
       </c>
       <c r="G108" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H108" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I108">
         <v>0</v>
@@ -5067,21 +5057,21 @@
         <v>0</v>
       </c>
       <c r="K108" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
+        <v>158</v>
+      </c>
+      <c r="B109" t="s">
         <v>159</v>
       </c>
-      <c r="B109" t="s">
-        <v>160</v>
-      </c>
       <c r="C109" t="s">
         <v>18</v>
       </c>
       <c r="D109" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E109">
         <v>151990</v>
@@ -5090,10 +5080,10 @@
         <v>1</v>
       </c>
       <c r="G109" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H109" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I109">
         <v>0</v>
@@ -5102,21 +5092,21 @@
         <v>0</v>
       </c>
       <c r="K109" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
+        <v>158</v>
+      </c>
+      <c r="B110" t="s">
         <v>159</v>
       </c>
-      <c r="B110" t="s">
-        <v>160</v>
-      </c>
       <c r="C110" t="s">
         <v>18</v>
       </c>
       <c r="D110" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E110">
         <v>151990</v>
@@ -5125,10 +5115,10 @@
         <v>1</v>
       </c>
       <c r="G110" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H110" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I110">
         <v>0</v>
@@ -5137,15 +5127,15 @@
         <v>0</v>
       </c>
       <c r="K110" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
+        <v>158</v>
+      </c>
+      <c r="B111" t="s">
         <v>159</v>
-      </c>
-      <c r="B111" t="s">
-        <v>160</v>
       </c>
       <c r="C111" t="s">
         <v>18</v>
@@ -5160,10 +5150,10 @@
         <v>1</v>
       </c>
       <c r="G111" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H111" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I111">
         <v>0</v>
@@ -5172,21 +5162,21 @@
         <v>0</v>
       </c>
       <c r="K111" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
+        <v>158</v>
+      </c>
+      <c r="B112" t="s">
         <v>159</v>
       </c>
-      <c r="B112" t="s">
-        <v>160</v>
-      </c>
       <c r="C112" t="s">
         <v>18</v>
       </c>
       <c r="D112" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E112">
         <v>151990</v>
@@ -5195,10 +5185,10 @@
         <v>1</v>
       </c>
       <c r="G112" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H112" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I112">
         <v>0</v>
@@ -5207,21 +5197,21 @@
         <v>0</v>
       </c>
       <c r="K112" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
+        <v>160</v>
+      </c>
+      <c r="B113" t="s">
         <v>161</v>
       </c>
-      <c r="B113" t="s">
-        <v>162</v>
-      </c>
       <c r="C113" t="s">
         <v>18</v>
       </c>
       <c r="D113" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E113">
         <v>151990</v>
@@ -5230,10 +5220,10 @@
         <v>1</v>
       </c>
       <c r="G113" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H113" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I113">
         <v>0</v>
@@ -5242,21 +5232,21 @@
         <v>0</v>
       </c>
       <c r="K113" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
+        <v>160</v>
+      </c>
+      <c r="B114" t="s">
         <v>161</v>
       </c>
-      <c r="B114" t="s">
-        <v>162</v>
-      </c>
       <c r="C114" t="s">
         <v>18</v>
       </c>
       <c r="D114" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E114">
         <v>151990</v>
@@ -5265,10 +5255,10 @@
         <v>1</v>
       </c>
       <c r="G114" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H114" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I114">
         <v>0</v>
@@ -5277,21 +5267,21 @@
         <v>0</v>
       </c>
       <c r="K114" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
+        <v>160</v>
+      </c>
+      <c r="B115" t="s">
         <v>161</v>
       </c>
-      <c r="B115" t="s">
-        <v>162</v>
-      </c>
       <c r="C115" t="s">
         <v>18</v>
       </c>
       <c r="D115" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E115">
         <v>151990</v>
@@ -5300,10 +5290,10 @@
         <v>1</v>
       </c>
       <c r="G115" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H115" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I115">
         <v>0</v>
@@ -5312,15 +5302,15 @@
         <v>0</v>
       </c>
       <c r="K115" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
+        <v>160</v>
+      </c>
+      <c r="B116" t="s">
         <v>161</v>
-      </c>
-      <c r="B116" t="s">
-        <v>162</v>
       </c>
       <c r="C116" t="s">
         <v>18</v>
@@ -5335,10 +5325,10 @@
         <v>1</v>
       </c>
       <c r="G116" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H116" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I116">
         <v>0</v>
@@ -5347,21 +5337,21 @@
         <v>0</v>
       </c>
       <c r="K116" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
+        <v>160</v>
+      </c>
+      <c r="B117" t="s">
         <v>161</v>
       </c>
-      <c r="B117" t="s">
-        <v>162</v>
-      </c>
       <c r="C117" t="s">
         <v>18</v>
       </c>
       <c r="D117" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E117">
         <v>151990</v>
@@ -5370,10 +5360,10 @@
         <v>1</v>
       </c>
       <c r="G117" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H117" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I117">
         <v>0</v>
@@ -5382,21 +5372,21 @@
         <v>0</v>
       </c>
       <c r="K117" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
+        <v>162</v>
+      </c>
+      <c r="B118" t="s">
         <v>163</v>
       </c>
-      <c r="B118" t="s">
-        <v>164</v>
-      </c>
       <c r="C118" t="s">
         <v>18</v>
       </c>
       <c r="D118" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E118">
         <v>119990</v>
@@ -5422,16 +5412,16 @@
     </row>
     <row r="119">
       <c r="A119" t="s">
+        <v>162</v>
+      </c>
+      <c r="B119" t="s">
         <v>163</v>
       </c>
-      <c r="B119" t="s">
-        <v>164</v>
-      </c>
       <c r="C119" t="s">
         <v>18</v>
       </c>
       <c r="D119" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E119">
         <v>210990</v>
@@ -5457,16 +5447,16 @@
     </row>
     <row r="120">
       <c r="A120" t="s">
+        <v>162</v>
+      </c>
+      <c r="B120" t="s">
         <v>163</v>
       </c>
-      <c r="B120" t="s">
-        <v>164</v>
-      </c>
       <c r="C120" t="s">
         <v>18</v>
       </c>
       <c r="D120" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E120">
         <v>210990</v>
@@ -5492,10 +5482,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s">
+        <v>162</v>
+      </c>
+      <c r="B121" t="s">
         <v>163</v>
-      </c>
-      <c r="B121" t="s">
-        <v>164</v>
       </c>
       <c r="C121" t="s">
         <v>18</v>
@@ -5527,16 +5517,16 @@
     </row>
     <row r="122">
       <c r="A122" t="s">
+        <v>164</v>
+      </c>
+      <c r="B122" t="s">
         <v>165</v>
       </c>
-      <c r="B122" t="s">
-        <v>166</v>
-      </c>
       <c r="C122" t="s">
         <v>18</v>
       </c>
       <c r="D122" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E122">
         <v>108990</v>
@@ -5557,21 +5547,21 @@
         <v>0</v>
       </c>
       <c r="K122" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
+        <v>164</v>
+      </c>
+      <c r="B123" t="s">
         <v>165</v>
       </c>
-      <c r="B123" t="s">
-        <v>166</v>
-      </c>
       <c r="C123" t="s">
         <v>18</v>
       </c>
       <c r="D123" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E123">
         <v>114990</v>
@@ -5592,21 +5582,21 @@
         <v>0</v>
       </c>
       <c r="K123" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
+        <v>164</v>
+      </c>
+      <c r="B124" t="s">
         <v>165</v>
       </c>
-      <c r="B124" t="s">
-        <v>166</v>
-      </c>
       <c r="C124" t="s">
         <v>18</v>
       </c>
       <c r="D124" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E124">
         <v>124990</v>
@@ -5627,15 +5617,15 @@
         <v>0</v>
       </c>
       <c r="K124" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
+        <v>164</v>
+      </c>
+      <c r="B125" t="s">
         <v>165</v>
-      </c>
-      <c r="B125" t="s">
-        <v>166</v>
       </c>
       <c r="C125" t="s">
         <v>18</v>
@@ -5662,21 +5652,21 @@
         <v>0</v>
       </c>
       <c r="K125" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
+        <v>164</v>
+      </c>
+      <c r="B126" t="s">
         <v>165</v>
       </c>
-      <c r="B126" t="s">
-        <v>166</v>
-      </c>
       <c r="C126" t="s">
         <v>18</v>
       </c>
       <c r="D126" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E126">
         <v>140990</v>
@@ -5697,21 +5687,21 @@
         <v>0</v>
       </c>
       <c r="K126" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s">
+        <v>167</v>
+      </c>
+      <c r="B127" t="s">
         <v>168</v>
       </c>
-      <c r="B127" t="s">
-        <v>169</v>
-      </c>
       <c r="C127" t="s">
         <v>18</v>
       </c>
       <c r="D127" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E127">
         <v>140990</v>
@@ -5732,21 +5722,21 @@
         <v>0</v>
       </c>
       <c r="K127" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
+        <v>167</v>
+      </c>
+      <c r="B128" t="s">
         <v>168</v>
       </c>
-      <c r="B128" t="s">
-        <v>169</v>
-      </c>
       <c r="C128" t="s">
         <v>18</v>
       </c>
       <c r="D128" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E128">
         <v>140990</v>
@@ -5767,21 +5757,21 @@
         <v>0</v>
       </c>
       <c r="K128" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
+        <v>167</v>
+      </c>
+      <c r="B129" t="s">
         <v>168</v>
       </c>
-      <c r="B129" t="s">
-        <v>169</v>
-      </c>
       <c r="C129" t="s">
         <v>18</v>
       </c>
       <c r="D129" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E129">
         <v>140990</v>
@@ -5802,21 +5792,21 @@
         <v>0</v>
       </c>
       <c r="K129" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
+        <v>167</v>
+      </c>
+      <c r="B130" t="s">
         <v>168</v>
       </c>
-      <c r="B130" t="s">
-        <v>169</v>
-      </c>
       <c r="C130" t="s">
         <v>18</v>
       </c>
       <c r="D130" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E130">
         <v>140990</v>
@@ -5837,15 +5827,15 @@
         <v>0</v>
       </c>
       <c r="K130" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
+        <v>167</v>
+      </c>
+      <c r="B131" t="s">
         <v>168</v>
-      </c>
-      <c r="B131" t="s">
-        <v>169</v>
       </c>
       <c r="C131" t="s">
         <v>18</v>
@@ -5872,21 +5862,21 @@
         <v>0</v>
       </c>
       <c r="K131" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
+        <v>167</v>
+      </c>
+      <c r="B132" t="s">
         <v>168</v>
       </c>
-      <c r="B132" t="s">
-        <v>169</v>
-      </c>
       <c r="C132" t="s">
         <v>18</v>
       </c>
       <c r="D132" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E132">
         <v>140990</v>
@@ -5907,21 +5897,21 @@
         <v>0</v>
       </c>
       <c r="K132" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s">
+        <v>169</v>
+      </c>
+      <c r="B133" t="s">
         <v>170</v>
       </c>
-      <c r="B133" t="s">
-        <v>171</v>
-      </c>
       <c r="C133" t="s">
         <v>18</v>
       </c>
       <c r="D133" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E133">
         <v>92990</v>
@@ -5942,21 +5932,21 @@
         <v>0</v>
       </c>
       <c r="K133" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
+        <v>169</v>
+      </c>
+      <c r="B134" t="s">
         <v>170</v>
       </c>
-      <c r="B134" t="s">
-        <v>171</v>
-      </c>
       <c r="C134" t="s">
         <v>18</v>
       </c>
       <c r="D134" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E134">
         <v>92990</v>
@@ -5977,21 +5967,21 @@
         <v>0</v>
       </c>
       <c r="K134" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
+        <v>169</v>
+      </c>
+      <c r="B135" t="s">
         <v>170</v>
       </c>
-      <c r="B135" t="s">
-        <v>171</v>
-      </c>
       <c r="C135" t="s">
         <v>18</v>
       </c>
       <c r="D135" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E135">
         <v>92990</v>
@@ -6012,15 +6002,15 @@
         <v>0</v>
       </c>
       <c r="K135" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
+        <v>169</v>
+      </c>
+      <c r="B136" t="s">
         <v>170</v>
-      </c>
-      <c r="B136" t="s">
-        <v>171</v>
       </c>
       <c r="C136" t="s">
         <v>18</v>
@@ -6047,21 +6037,21 @@
         <v>0</v>
       </c>
       <c r="K136" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s">
+        <v>169</v>
+      </c>
+      <c r="B137" t="s">
         <v>170</v>
       </c>
-      <c r="B137" t="s">
-        <v>171</v>
-      </c>
       <c r="C137" t="s">
         <v>18</v>
       </c>
       <c r="D137" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E137">
         <v>92990</v>
@@ -6082,21 +6072,21 @@
         <v>0</v>
       </c>
       <c r="K137" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s">
+        <v>171</v>
+      </c>
+      <c r="B138" t="s">
         <v>172</v>
       </c>
-      <c r="B138" t="s">
-        <v>173</v>
-      </c>
       <c r="C138" t="s">
         <v>18</v>
       </c>
       <c r="D138" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E138">
         <v>108990</v>
@@ -6117,21 +6107,21 @@
         <v>0</v>
       </c>
       <c r="K138" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s">
+        <v>171</v>
+      </c>
+      <c r="B139" t="s">
         <v>172</v>
       </c>
-      <c r="B139" t="s">
-        <v>173</v>
-      </c>
       <c r="C139" t="s">
         <v>18</v>
       </c>
       <c r="D139" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E139">
         <v>108990</v>
@@ -6152,15 +6142,15 @@
         <v>0</v>
       </c>
       <c r="K139" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s">
+        <v>171</v>
+      </c>
+      <c r="B140" t="s">
         <v>172</v>
-      </c>
-      <c r="B140" t="s">
-        <v>173</v>
       </c>
       <c r="C140" t="s">
         <v>18</v>
@@ -6187,21 +6177,21 @@
         <v>0</v>
       </c>
       <c r="K140" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s">
+        <v>173</v>
+      </c>
+      <c r="B141" t="s">
         <v>174</v>
       </c>
-      <c r="B141" t="s">
+      <c r="C141" t="s">
+        <v>18</v>
+      </c>
+      <c r="D141" t="s">
         <v>175</v>
-      </c>
-      <c r="C141" t="s">
-        <v>18</v>
-      </c>
-      <c r="D141" t="s">
-        <v>176</v>
       </c>
       <c r="E141">
         <v>81990</v>
@@ -6210,10 +6200,10 @@
         <v>1</v>
       </c>
       <c r="G141" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H141" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I141">
         <v>0</v>
@@ -6222,21 +6212,21 @@
         <v>0</v>
       </c>
       <c r="K141" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s">
+        <v>173</v>
+      </c>
+      <c r="B142" t="s">
         <v>174</v>
       </c>
-      <c r="B142" t="s">
-        <v>175</v>
-      </c>
       <c r="C142" t="s">
         <v>18</v>
       </c>
       <c r="D142" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E142">
         <v>81990</v>
@@ -6245,10 +6235,10 @@
         <v>1</v>
       </c>
       <c r="G142" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H142" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I142">
         <v>0</v>
@@ -6257,21 +6247,21 @@
         <v>0</v>
       </c>
       <c r="K142" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s">
+        <v>177</v>
+      </c>
+      <c r="B143" t="s">
         <v>178</v>
       </c>
-      <c r="B143" t="s">
-        <v>179</v>
-      </c>
       <c r="C143" t="s">
         <v>18</v>
       </c>
       <c r="D143" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E143">
         <v>125990</v>
@@ -6280,10 +6270,10 @@
         <v>1</v>
       </c>
       <c r="G143" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H143" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I143">
         <v>0</v>
@@ -6297,16 +6287,16 @@
     </row>
     <row r="144">
       <c r="A144" t="s">
+        <v>177</v>
+      </c>
+      <c r="B144" t="s">
         <v>178</v>
       </c>
-      <c r="B144" t="s">
-        <v>179</v>
-      </c>
       <c r="C144" t="s">
         <v>18</v>
       </c>
       <c r="D144" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E144">
         <v>125990</v>
@@ -6315,10 +6305,10 @@
         <v>1</v>
       </c>
       <c r="G144" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H144" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I144">
         <v>0</v>
@@ -6332,16 +6322,16 @@
     </row>
     <row r="145">
       <c r="A145" t="s">
+        <v>179</v>
+      </c>
+      <c r="B145" t="s">
         <v>180</v>
       </c>
-      <c r="B145" t="s">
+      <c r="C145" t="s">
+        <v>18</v>
+      </c>
+      <c r="D145" t="s">
         <v>181</v>
-      </c>
-      <c r="C145" t="s">
-        <v>18</v>
-      </c>
-      <c r="D145" t="s">
-        <v>182</v>
       </c>
       <c r="E145">
         <v>125990</v>
@@ -6353,7 +6343,7 @@
         <v>20</v>
       </c>
       <c r="H145" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I145">
         <v>0</v>
@@ -6362,15 +6352,15 @@
         <v>0</v>
       </c>
       <c r="K145" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s">
+        <v>179</v>
+      </c>
+      <c r="B146" t="s">
         <v>180</v>
-      </c>
-      <c r="B146" t="s">
-        <v>181</v>
       </c>
       <c r="C146" t="s">
         <v>18</v>
@@ -6388,7 +6378,7 @@
         <v>20</v>
       </c>
       <c r="H146" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I146">
         <v>0</v>
@@ -6397,15 +6387,15 @@
         <v>0</v>
       </c>
       <c r="K146" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s">
+        <v>179</v>
+      </c>
+      <c r="B147" t="s">
         <v>180</v>
-      </c>
-      <c r="B147" t="s">
-        <v>181</v>
       </c>
       <c r="C147" t="s">
         <v>18</v>
@@ -6423,7 +6413,7 @@
         <v>20</v>
       </c>
       <c r="H147" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I147">
         <v>0</v>
@@ -6432,15 +6422,15 @@
         <v>0</v>
       </c>
       <c r="K147" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s">
+        <v>179</v>
+      </c>
+      <c r="B148" t="s">
         <v>180</v>
-      </c>
-      <c r="B148" t="s">
-        <v>181</v>
       </c>
       <c r="C148" t="s">
         <v>18</v>
@@ -6458,7 +6448,7 @@
         <v>20</v>
       </c>
       <c r="H148" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I148">
         <v>0</v>
@@ -6467,21 +6457,21 @@
         <v>0</v>
       </c>
       <c r="K148" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s">
+        <v>182</v>
+      </c>
+      <c r="B149" t="s">
         <v>183</v>
       </c>
-      <c r="B149" t="s">
-        <v>184</v>
-      </c>
       <c r="C149" t="s">
         <v>18</v>
       </c>
       <c r="D149" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E149">
         <v>145990</v>
@@ -6490,10 +6480,10 @@
         <v>1</v>
       </c>
       <c r="G149" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H149" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I149">
         <v>0</v>
@@ -6507,16 +6497,16 @@
     </row>
     <row r="150">
       <c r="A150" t="s">
+        <v>182</v>
+      </c>
+      <c r="B150" t="s">
         <v>183</v>
       </c>
-      <c r="B150" t="s">
-        <v>184</v>
-      </c>
       <c r="C150" t="s">
         <v>18</v>
       </c>
       <c r="D150" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E150">
         <v>145990</v>
@@ -6525,10 +6515,10 @@
         <v>1</v>
       </c>
       <c r="G150" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H150" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I150">
         <v>0</v>
@@ -6542,10 +6532,10 @@
     </row>
     <row r="151">
       <c r="A151" t="s">
+        <v>182</v>
+      </c>
+      <c r="B151" t="s">
         <v>183</v>
-      </c>
-      <c r="B151" t="s">
-        <v>184</v>
       </c>
       <c r="C151" t="s">
         <v>18</v>
@@ -6560,10 +6550,10 @@
         <v>1</v>
       </c>
       <c r="G151" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H151" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I151">
         <v>0</v>
@@ -6577,16 +6567,16 @@
     </row>
     <row r="152">
       <c r="A152" t="s">
+        <v>182</v>
+      </c>
+      <c r="B152" t="s">
         <v>183</v>
       </c>
-      <c r="B152" t="s">
-        <v>184</v>
-      </c>
       <c r="C152" t="s">
         <v>18</v>
       </c>
       <c r="D152" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E152">
         <v>145990</v>
@@ -6595,10 +6585,10 @@
         <v>1</v>
       </c>
       <c r="G152" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H152" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I152">
         <v>0</v>
@@ -6612,16 +6602,16 @@
     </row>
     <row r="153">
       <c r="A153" t="s">
+        <v>184</v>
+      </c>
+      <c r="B153" t="s">
         <v>185</v>
       </c>
-      <c r="B153" t="s">
-        <v>186</v>
-      </c>
       <c r="C153" t="s">
         <v>18</v>
       </c>
       <c r="D153" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E153">
         <v>199990</v>
@@ -6630,10 +6620,10 @@
         <v>1</v>
       </c>
       <c r="G153" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H153" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I153">
         <v>0</v>
@@ -6647,16 +6637,16 @@
     </row>
     <row r="154">
       <c r="A154" t="s">
+        <v>184</v>
+      </c>
+      <c r="B154" t="s">
         <v>185</v>
       </c>
-      <c r="B154" t="s">
-        <v>186</v>
-      </c>
       <c r="C154" t="s">
         <v>18</v>
       </c>
       <c r="D154" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E154">
         <v>199990</v>
@@ -6665,10 +6655,10 @@
         <v>1</v>
       </c>
       <c r="G154" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H154" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I154">
         <v>0</v>
@@ -6682,16 +6672,16 @@
     </row>
     <row r="155">
       <c r="A155" t="s">
+        <v>184</v>
+      </c>
+      <c r="B155" t="s">
         <v>185</v>
       </c>
-      <c r="B155" t="s">
-        <v>186</v>
-      </c>
       <c r="C155" t="s">
         <v>18</v>
       </c>
       <c r="D155" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E155">
         <v>199990</v>
@@ -6700,10 +6690,10 @@
         <v>1</v>
       </c>
       <c r="G155" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H155" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I155">
         <v>0</v>
@@ -6717,10 +6707,10 @@
     </row>
     <row r="156">
       <c r="A156" t="s">
+        <v>184</v>
+      </c>
+      <c r="B156" t="s">
         <v>185</v>
-      </c>
-      <c r="B156" t="s">
-        <v>186</v>
       </c>
       <c r="C156" t="s">
         <v>18</v>
@@ -6735,10 +6725,10 @@
         <v>1</v>
       </c>
       <c r="G156" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H156" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I156">
         <v>0</v>
@@ -6752,16 +6742,16 @@
     </row>
     <row r="157">
       <c r="A157" t="s">
+        <v>184</v>
+      </c>
+      <c r="B157" t="s">
         <v>185</v>
       </c>
-      <c r="B157" t="s">
-        <v>186</v>
-      </c>
       <c r="C157" t="s">
         <v>18</v>
       </c>
       <c r="D157" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E157">
         <v>199990</v>
@@ -6770,10 +6760,10 @@
         <v>1</v>
       </c>
       <c r="G157" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H157" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I157">
         <v>0</v>
@@ -6787,16 +6777,16 @@
     </row>
     <row r="158">
       <c r="A158" t="s">
+        <v>186</v>
+      </c>
+      <c r="B158" t="s">
         <v>187</v>
       </c>
-      <c r="B158" t="s">
-        <v>188</v>
-      </c>
       <c r="C158" t="s">
         <v>18</v>
       </c>
       <c r="D158" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E158">
         <v>159990</v>
@@ -6805,10 +6795,10 @@
         <v>1</v>
       </c>
       <c r="G158" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H158" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I158">
         <v>0</v>
@@ -6817,21 +6807,21 @@
         <v>0</v>
       </c>
       <c r="K158" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s">
+        <v>186</v>
+      </c>
+      <c r="B159" t="s">
         <v>187</v>
       </c>
-      <c r="B159" t="s">
-        <v>188</v>
-      </c>
       <c r="C159" t="s">
         <v>18</v>
       </c>
       <c r="D159" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E159">
         <v>199990</v>
@@ -6840,10 +6830,10 @@
         <v>1</v>
       </c>
       <c r="G159" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H159" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I159">
         <v>0</v>
@@ -6852,15 +6842,15 @@
         <v>0</v>
       </c>
       <c r="K159" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s">
+        <v>186</v>
+      </c>
+      <c r="B160" t="s">
         <v>187</v>
-      </c>
-      <c r="B160" t="s">
-        <v>188</v>
       </c>
       <c r="C160" t="s">
         <v>18</v>
@@ -6875,10 +6865,10 @@
         <v>1</v>
       </c>
       <c r="G160" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H160" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I160">
         <v>0</v>
@@ -6887,21 +6877,21 @@
         <v>0</v>
       </c>
       <c r="K160" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s">
+        <v>189</v>
+      </c>
+      <c r="B161" t="s">
         <v>190</v>
       </c>
-      <c r="B161" t="s">
-        <v>191</v>
-      </c>
       <c r="C161" t="s">
         <v>18</v>
       </c>
       <c r="D161" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E161">
         <v>109990</v>
@@ -6922,21 +6912,21 @@
         <v>0</v>
       </c>
       <c r="K161" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s">
+        <v>189</v>
+      </c>
+      <c r="B162" t="s">
         <v>190</v>
       </c>
-      <c r="B162" t="s">
-        <v>191</v>
-      </c>
       <c r="C162" t="s">
         <v>18</v>
       </c>
       <c r="D162" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E162">
         <v>109990</v>
@@ -6957,15 +6947,15 @@
         <v>0</v>
       </c>
       <c r="K162" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s">
+        <v>189</v>
+      </c>
+      <c r="B163" t="s">
         <v>190</v>
-      </c>
-      <c r="B163" t="s">
-        <v>191</v>
       </c>
       <c r="C163" t="s">
         <v>18</v>
@@ -6992,15 +6982,15 @@
         <v>0</v>
       </c>
       <c r="K163" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s">
+        <v>191</v>
+      </c>
+      <c r="B164" t="s">
         <v>192</v>
-      </c>
-      <c r="B164" t="s">
-        <v>193</v>
       </c>
       <c r="C164" t="s">
         <v>18</v>
@@ -7027,21 +7017,21 @@
         <v>0</v>
       </c>
       <c r="K164" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="s">
+        <v>191</v>
+      </c>
+      <c r="B165" t="s">
         <v>192</v>
       </c>
-      <c r="B165" t="s">
-        <v>193</v>
-      </c>
       <c r="C165" t="s">
         <v>18</v>
       </c>
       <c r="D165" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E165">
         <v>119990</v>
@@ -7062,21 +7052,21 @@
         <v>0</v>
       </c>
       <c r="K165" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s">
+        <v>193</v>
+      </c>
+      <c r="B166" t="s">
         <v>194</v>
       </c>
-      <c r="B166" t="s">
+      <c r="C166" t="s">
         <v>195</v>
       </c>
-      <c r="C166" t="s">
-        <v>196</v>
-      </c>
       <c r="D166" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E166">
         <v>85990</v>
@@ -7085,10 +7075,10 @@
         <v>1</v>
       </c>
       <c r="G166" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H166" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I166">
         <v>0</v>
@@ -7102,16 +7092,16 @@
     </row>
     <row r="167">
       <c r="A167" t="s">
+        <v>196</v>
+      </c>
+      <c r="B167" t="s">
         <v>197</v>
       </c>
-      <c r="B167" t="s">
-        <v>198</v>
-      </c>
       <c r="C167" t="s">
         <v>18</v>
       </c>
       <c r="D167" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E167">
         <v>105990</v>
@@ -7132,21 +7122,21 @@
         <v>0</v>
       </c>
       <c r="K167" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s">
+        <v>196</v>
+      </c>
+      <c r="B168" t="s">
         <v>197</v>
       </c>
-      <c r="B168" t="s">
-        <v>198</v>
-      </c>
       <c r="C168" t="s">
         <v>18</v>
       </c>
       <c r="D168" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E168">
         <v>105990</v>
@@ -7167,21 +7157,21 @@
         <v>0</v>
       </c>
       <c r="K168" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s">
+        <v>196</v>
+      </c>
+      <c r="B169" t="s">
         <v>197</v>
       </c>
-      <c r="B169" t="s">
-        <v>198</v>
-      </c>
       <c r="C169" t="s">
         <v>18</v>
       </c>
       <c r="D169" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E169">
         <v>105990</v>
@@ -7202,15 +7192,15 @@
         <v>0</v>
       </c>
       <c r="K169" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s">
+        <v>196</v>
+      </c>
+      <c r="B170" t="s">
         <v>197</v>
-      </c>
-      <c r="B170" t="s">
-        <v>198</v>
       </c>
       <c r="C170" t="s">
         <v>18</v>
@@ -7237,21 +7227,21 @@
         <v>0</v>
       </c>
       <c r="K170" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s">
+        <v>198</v>
+      </c>
+      <c r="B171" t="s">
         <v>199</v>
       </c>
-      <c r="B171" t="s">
-        <v>200</v>
-      </c>
       <c r="C171" t="s">
         <v>18</v>
       </c>
       <c r="D171" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E171">
         <v>119990</v>
@@ -7272,21 +7262,21 @@
         <v>0</v>
       </c>
       <c r="K171" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s">
+        <v>198</v>
+      </c>
+      <c r="B172" t="s">
         <v>199</v>
       </c>
-      <c r="B172" t="s">
-        <v>200</v>
-      </c>
       <c r="C172" t="s">
         <v>18</v>
       </c>
       <c r="D172" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E172">
         <v>189990</v>
@@ -7307,21 +7297,21 @@
         <v>0</v>
       </c>
       <c r="K172" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="s">
+        <v>201</v>
+      </c>
+      <c r="B173" t="s">
         <v>202</v>
       </c>
-      <c r="B173" t="s">
-        <v>203</v>
-      </c>
       <c r="C173" t="s">
         <v>18</v>
       </c>
       <c r="D173" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E173">
         <v>179990</v>
@@ -7342,21 +7332,21 @@
         <v>0</v>
       </c>
       <c r="K173" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="s">
+        <v>201</v>
+      </c>
+      <c r="B174" t="s">
         <v>202</v>
       </c>
-      <c r="B174" t="s">
-        <v>203</v>
-      </c>
       <c r="C174" t="s">
         <v>18</v>
       </c>
       <c r="D174" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E174">
         <v>179990</v>
@@ -7377,15 +7367,15 @@
         <v>0</v>
       </c>
       <c r="K174" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="s">
+        <v>201</v>
+      </c>
+      <c r="B175" t="s">
         <v>202</v>
-      </c>
-      <c r="B175" t="s">
-        <v>203</v>
       </c>
       <c r="C175" t="s">
         <v>18</v>
@@ -7412,21 +7402,21 @@
         <v>0</v>
       </c>
       <c r="K175" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="s">
+        <v>203</v>
+      </c>
+      <c r="B176" t="s">
         <v>204</v>
       </c>
-      <c r="B176" t="s">
-        <v>205</v>
-      </c>
       <c r="C176" t="s">
         <v>18</v>
       </c>
       <c r="D176" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E176">
         <v>109990</v>
@@ -7435,10 +7425,10 @@
         <v>1</v>
       </c>
       <c r="G176" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H176" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I176">
         <v>0</v>
@@ -7452,10 +7442,10 @@
     </row>
     <row r="177">
       <c r="A177" t="s">
+        <v>203</v>
+      </c>
+      <c r="B177" t="s">
         <v>204</v>
-      </c>
-      <c r="B177" t="s">
-        <v>205</v>
       </c>
       <c r="C177" t="s">
         <v>18</v>
@@ -7470,10 +7460,10 @@
         <v>1</v>
       </c>
       <c r="G177" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H177" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I177">
         <v>0</v>
@@ -7487,16 +7477,16 @@
     </row>
     <row r="178">
       <c r="A178" t="s">
+        <v>205</v>
+      </c>
+      <c r="B178" t="s">
         <v>206</v>
       </c>
-      <c r="B178" t="s">
+      <c r="C178" t="s">
+        <v>18</v>
+      </c>
+      <c r="D178" t="s">
         <v>207</v>
-      </c>
-      <c r="C178" t="s">
-        <v>18</v>
-      </c>
-      <c r="D178" t="s">
-        <v>208</v>
       </c>
       <c r="E178">
         <v>82990</v>
@@ -7505,10 +7495,10 @@
         <v>1</v>
       </c>
       <c r="G178" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H178" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I178">
         <v>0</v>
@@ -7517,21 +7507,21 @@
         <v>0</v>
       </c>
       <c r="K178" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="s">
+        <v>205</v>
+      </c>
+      <c r="B179" t="s">
         <v>206</v>
       </c>
-      <c r="B179" t="s">
+      <c r="C179" t="s">
+        <v>18</v>
+      </c>
+      <c r="D179" t="s">
         <v>207</v>
-      </c>
-      <c r="C179" t="s">
-        <v>18</v>
-      </c>
-      <c r="D179" t="s">
-        <v>208</v>
       </c>
       <c r="E179">
         <v>82990</v>
@@ -7540,10 +7530,10 @@
         <v>1</v>
       </c>
       <c r="G179" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H179" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I179">
         <v>0</v>
@@ -7557,16 +7547,16 @@
     </row>
     <row r="180">
       <c r="A180" t="s">
+        <v>208</v>
+      </c>
+      <c r="B180" t="s">
         <v>209</v>
       </c>
-      <c r="B180" t="s">
+      <c r="C180" t="s">
+        <v>18</v>
+      </c>
+      <c r="D180" t="s">
         <v>210</v>
-      </c>
-      <c r="C180" t="s">
-        <v>18</v>
-      </c>
-      <c r="D180" t="s">
-        <v>211</v>
       </c>
       <c r="E180">
         <v>119990</v>
@@ -7575,10 +7565,10 @@
         <v>1</v>
       </c>
       <c r="G180" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H180" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I180">
         <v>0</v>
@@ -7592,16 +7582,16 @@
     </row>
     <row r="181">
       <c r="A181" t="s">
+        <v>208</v>
+      </c>
+      <c r="B181" t="s">
         <v>209</v>
       </c>
-      <c r="B181" t="s">
-        <v>210</v>
-      </c>
       <c r="C181" t="s">
         <v>18</v>
       </c>
       <c r="D181" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E181">
         <v>119990</v>
@@ -7610,10 +7600,10 @@
         <v>1</v>
       </c>
       <c r="G181" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H181" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I181">
         <v>0</v>
@@ -7627,10 +7617,10 @@
     </row>
     <row r="182">
       <c r="A182" t="s">
+        <v>208</v>
+      </c>
+      <c r="B182" t="s">
         <v>209</v>
-      </c>
-      <c r="B182" t="s">
-        <v>210</v>
       </c>
       <c r="C182" t="s">
         <v>18</v>
@@ -7645,10 +7635,10 @@
         <v>1</v>
       </c>
       <c r="G182" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H182" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I182">
         <v>0</v>
@@ -7662,16 +7652,16 @@
     </row>
     <row r="183">
       <c r="A183" t="s">
+        <v>208</v>
+      </c>
+      <c r="B183" t="s">
         <v>209</v>
       </c>
-      <c r="B183" t="s">
+      <c r="C183" t="s">
+        <v>18</v>
+      </c>
+      <c r="D183" t="s">
         <v>210</v>
-      </c>
-      <c r="C183" t="s">
-        <v>18</v>
-      </c>
-      <c r="D183" t="s">
-        <v>211</v>
       </c>
       <c r="E183">
         <v>119990</v>
@@ -7680,10 +7670,10 @@
         <v>1</v>
       </c>
       <c r="G183" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H183" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I183">
         <v>0</v>
@@ -7692,21 +7682,21 @@
         <v>0</v>
       </c>
       <c r="K183" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="s">
+        <v>208</v>
+      </c>
+      <c r="B184" t="s">
         <v>209</v>
       </c>
-      <c r="B184" t="s">
-        <v>210</v>
-      </c>
       <c r="C184" t="s">
         <v>18</v>
       </c>
       <c r="D184" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E184">
         <v>119990</v>
@@ -7715,10 +7705,10 @@
         <v>1</v>
       </c>
       <c r="G184" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H184" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I184">
         <v>0</v>
@@ -7727,15 +7717,15 @@
         <v>0</v>
       </c>
       <c r="K184" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="s">
+        <v>208</v>
+      </c>
+      <c r="B185" t="s">
         <v>209</v>
-      </c>
-      <c r="B185" t="s">
-        <v>210</v>
       </c>
       <c r="C185" t="s">
         <v>18</v>
@@ -7750,10 +7740,10 @@
         <v>1</v>
       </c>
       <c r="G185" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H185" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I185">
         <v>0</v>
@@ -7762,21 +7752,21 @@
         <v>0</v>
       </c>
       <c r="K185" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="s">
+        <v>211</v>
+      </c>
+      <c r="B186" t="s">
         <v>212</v>
       </c>
-      <c r="B186" t="s">
-        <v>213</v>
-      </c>
       <c r="C186" t="s">
         <v>18</v>
       </c>
       <c r="D186" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E186">
         <v>129990</v>
@@ -7785,10 +7775,10 @@
         <v>1</v>
       </c>
       <c r="G186" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H186" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I186">
         <v>0</v>
@@ -7797,21 +7787,21 @@
         <v>0</v>
       </c>
       <c r="K186" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="s">
+        <v>211</v>
+      </c>
+      <c r="B187" t="s">
         <v>212</v>
       </c>
-      <c r="B187" t="s">
-        <v>213</v>
-      </c>
       <c r="C187" t="s">
         <v>18</v>
       </c>
       <c r="D187" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E187">
         <v>119990</v>
@@ -7820,10 +7810,10 @@
         <v>1</v>
       </c>
       <c r="G187" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H187" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I187">
         <v>0</v>
@@ -7832,21 +7822,21 @@
         <v>0</v>
       </c>
       <c r="K187" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="s">
+        <v>211</v>
+      </c>
+      <c r="B188" t="s">
         <v>212</v>
       </c>
-      <c r="B188" t="s">
-        <v>213</v>
-      </c>
       <c r="C188" t="s">
         <v>18</v>
       </c>
       <c r="D188" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E188">
         <v>119990</v>
@@ -7855,10 +7845,10 @@
         <v>1</v>
       </c>
       <c r="G188" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H188" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I188">
         <v>0</v>
@@ -7867,21 +7857,21 @@
         <v>0</v>
       </c>
       <c r="K188" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="s">
+        <v>211</v>
+      </c>
+      <c r="B189" t="s">
         <v>212</v>
       </c>
-      <c r="B189" t="s">
-        <v>213</v>
-      </c>
       <c r="C189" t="s">
         <v>18</v>
       </c>
       <c r="D189" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E189">
         <v>119990</v>
@@ -7890,10 +7880,10 @@
         <v>1</v>
       </c>
       <c r="G189" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H189" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I189">
         <v>0</v>
@@ -7902,21 +7892,21 @@
         <v>0</v>
       </c>
       <c r="K189" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="s">
+        <v>211</v>
+      </c>
+      <c r="B190" t="s">
         <v>212</v>
       </c>
-      <c r="B190" t="s">
-        <v>213</v>
-      </c>
       <c r="C190" t="s">
         <v>18</v>
       </c>
       <c r="D190" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E190">
         <v>129990</v>
@@ -7925,10 +7915,10 @@
         <v>1</v>
       </c>
       <c r="G190" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H190" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I190">
         <v>0</v>
@@ -7937,21 +7927,21 @@
         <v>0</v>
       </c>
       <c r="K190" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="s">
+        <v>211</v>
+      </c>
+      <c r="B191" t="s">
         <v>212</v>
       </c>
-      <c r="B191" t="s">
-        <v>213</v>
-      </c>
       <c r="C191" t="s">
         <v>18</v>
       </c>
       <c r="D191" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E191">
         <v>119990</v>
@@ -7960,10 +7950,10 @@
         <v>1</v>
       </c>
       <c r="G191" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H191" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I191">
         <v>0</v>
@@ -7972,21 +7962,21 @@
         <v>0</v>
       </c>
       <c r="K191" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="s">
+        <v>211</v>
+      </c>
+      <c r="B192" t="s">
         <v>212</v>
       </c>
-      <c r="B192" t="s">
-        <v>213</v>
-      </c>
       <c r="C192" t="s">
         <v>18</v>
       </c>
       <c r="D192" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E192">
         <v>119990</v>
@@ -7995,10 +7985,10 @@
         <v>1</v>
       </c>
       <c r="G192" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H192" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I192">
         <v>0</v>
@@ -8007,15 +7997,15 @@
         <v>0</v>
       </c>
       <c r="K192" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="s">
+        <v>211</v>
+      </c>
+      <c r="B193" t="s">
         <v>212</v>
-      </c>
-      <c r="B193" t="s">
-        <v>213</v>
       </c>
       <c r="C193" t="s">
         <v>18</v>
@@ -8030,10 +8020,10 @@
         <v>1</v>
       </c>
       <c r="G193" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H193" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I193">
         <v>0</v>
@@ -8042,21 +8032,21 @@
         <v>0</v>
       </c>
       <c r="K193" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="s">
+        <v>211</v>
+      </c>
+      <c r="B194" t="s">
         <v>212</v>
       </c>
-      <c r="B194" t="s">
-        <v>213</v>
-      </c>
       <c r="C194" t="s">
         <v>18</v>
       </c>
       <c r="D194" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E194">
         <v>119990</v>
@@ -8065,10 +8055,10 @@
         <v>1</v>
       </c>
       <c r="G194" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H194" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I194">
         <v>0</v>
@@ -8077,21 +8067,21 @@
         <v>0</v>
       </c>
       <c r="K194" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="s">
+        <v>215</v>
+      </c>
+      <c r="B195" t="s">
         <v>216</v>
       </c>
-      <c r="B195" t="s">
-        <v>217</v>
-      </c>
       <c r="C195" t="s">
         <v>18</v>
       </c>
       <c r="D195" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E195">
         <v>165990</v>
@@ -8100,10 +8090,10 @@
         <v>1</v>
       </c>
       <c r="G195" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H195" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I195">
         <v>0</v>
@@ -8112,21 +8102,21 @@
         <v>0</v>
       </c>
       <c r="K195" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="s">
+        <v>215</v>
+      </c>
+      <c r="B196" t="s">
         <v>216</v>
       </c>
-      <c r="B196" t="s">
-        <v>217</v>
-      </c>
       <c r="C196" t="s">
         <v>18</v>
       </c>
       <c r="D196" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E196">
         <v>149990</v>
@@ -8135,10 +8125,10 @@
         <v>1</v>
       </c>
       <c r="G196" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H196" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I196">
         <v>0</v>
@@ -8147,21 +8137,21 @@
         <v>0</v>
       </c>
       <c r="K196" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="s">
+        <v>215</v>
+      </c>
+      <c r="B197" t="s">
         <v>216</v>
       </c>
-      <c r="B197" t="s">
-        <v>217</v>
-      </c>
       <c r="C197" t="s">
         <v>18</v>
       </c>
       <c r="D197" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E197">
         <v>149990</v>
@@ -8170,10 +8160,10 @@
         <v>1</v>
       </c>
       <c r="G197" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H197" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I197">
         <v>0</v>
@@ -8182,15 +8172,15 @@
         <v>0</v>
       </c>
       <c r="K197" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="s">
+        <v>215</v>
+      </c>
+      <c r="B198" t="s">
         <v>216</v>
-      </c>
-      <c r="B198" t="s">
-        <v>217</v>
       </c>
       <c r="C198" t="s">
         <v>18</v>
@@ -8205,10 +8195,10 @@
         <v>1</v>
       </c>
       <c r="G198" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H198" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I198">
         <v>0</v>
@@ -8217,21 +8207,21 @@
         <v>0</v>
       </c>
       <c r="K198" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="s">
+        <v>215</v>
+      </c>
+      <c r="B199" t="s">
         <v>216</v>
       </c>
-      <c r="B199" t="s">
-        <v>217</v>
-      </c>
       <c r="C199" t="s">
         <v>18</v>
       </c>
       <c r="D199" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E199">
         <v>149990</v>
@@ -8240,10 +8230,10 @@
         <v>1</v>
       </c>
       <c r="G199" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H199" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I199">
         <v>0</v>
@@ -8252,21 +8242,21 @@
         <v>0</v>
       </c>
       <c r="K199" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="s">
+        <v>217</v>
+      </c>
+      <c r="B200" t="s">
         <v>218</v>
       </c>
-      <c r="B200" t="s">
-        <v>219</v>
-      </c>
       <c r="C200" t="s">
         <v>18</v>
       </c>
       <c r="D200" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E200">
         <v>189990</v>
@@ -8287,21 +8277,21 @@
         <v>0</v>
       </c>
       <c r="K200" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="s">
+        <v>217</v>
+      </c>
+      <c r="B201" t="s">
         <v>218</v>
       </c>
-      <c r="B201" t="s">
-        <v>219</v>
-      </c>
       <c r="C201" t="s">
         <v>18</v>
       </c>
       <c r="D201" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E201">
         <v>189990</v>
@@ -8322,21 +8312,21 @@
         <v>0</v>
       </c>
       <c r="K201" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="s">
+        <v>217</v>
+      </c>
+      <c r="B202" t="s">
         <v>218</v>
       </c>
-      <c r="B202" t="s">
-        <v>219</v>
-      </c>
       <c r="C202" t="s">
         <v>18</v>
       </c>
       <c r="D202" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E202">
         <v>189990</v>
@@ -8357,21 +8347,21 @@
         <v>0</v>
       </c>
       <c r="K202" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="s">
+        <v>219</v>
+      </c>
+      <c r="B203" t="s">
         <v>220</v>
       </c>
-      <c r="B203" t="s">
-        <v>221</v>
-      </c>
       <c r="C203" t="s">
         <v>18</v>
       </c>
       <c r="D203" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E203">
         <v>185990</v>
@@ -8397,16 +8387,16 @@
     </row>
     <row r="204">
       <c r="A204" t="s">
+        <v>219</v>
+      </c>
+      <c r="B204" t="s">
         <v>220</v>
       </c>
-      <c r="B204" t="s">
-        <v>221</v>
-      </c>
       <c r="C204" t="s">
         <v>18</v>
       </c>
       <c r="D204" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E204">
         <v>185990</v>
@@ -8432,10 +8422,10 @@
     </row>
     <row r="205">
       <c r="A205" t="s">
+        <v>219</v>
+      </c>
+      <c r="B205" t="s">
         <v>220</v>
-      </c>
-      <c r="B205" t="s">
-        <v>221</v>
       </c>
       <c r="C205" t="s">
         <v>18</v>
@@ -8467,16 +8457,16 @@
     </row>
     <row r="206">
       <c r="A206" t="s">
+        <v>221</v>
+      </c>
+      <c r="B206" t="s">
         <v>222</v>
       </c>
-      <c r="B206" t="s">
+      <c r="C206" t="s">
+        <v>34</v>
+      </c>
+      <c r="D206" t="s">
         <v>223</v>
-      </c>
-      <c r="C206" t="s">
-        <v>35</v>
-      </c>
-      <c r="D206" t="s">
-        <v>224</v>
       </c>
       <c r="E206">
         <v>125990</v>
@@ -8485,10 +8475,10 @@
         <v>1</v>
       </c>
       <c r="G206" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H206" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I206">
         <v>0</v>
@@ -8497,21 +8487,21 @@
         <v>0</v>
       </c>
       <c r="K206" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="s">
+        <v>221</v>
+      </c>
+      <c r="B207" t="s">
         <v>222</v>
       </c>
-      <c r="B207" t="s">
-        <v>223</v>
-      </c>
       <c r="C207" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D207" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E207">
         <v>125990</v>
@@ -8520,10 +8510,10 @@
         <v>1</v>
       </c>
       <c r="G207" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H207" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I207">
         <v>0</v>
@@ -8532,21 +8522,21 @@
         <v>0</v>
       </c>
       <c r="K207" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="s">
+        <v>221</v>
+      </c>
+      <c r="B208" t="s">
         <v>222</v>
       </c>
-      <c r="B208" t="s">
-        <v>223</v>
-      </c>
       <c r="C208" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D208" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E208">
         <v>125990</v>
@@ -8555,10 +8545,10 @@
         <v>1</v>
       </c>
       <c r="G208" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H208" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I208">
         <v>0</v>
@@ -8567,21 +8557,21 @@
         <v>0</v>
       </c>
       <c r="K208" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="s">
+        <v>221</v>
+      </c>
+      <c r="B209" t="s">
         <v>222</v>
       </c>
-      <c r="B209" t="s">
-        <v>223</v>
-      </c>
       <c r="C209" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D209" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E209">
         <v>125990</v>
@@ -8590,10 +8580,10 @@
         <v>1</v>
       </c>
       <c r="G209" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H209" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I209">
         <v>0</v>
@@ -8602,21 +8592,21 @@
         <v>0</v>
       </c>
       <c r="K209" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="s">
+        <v>227</v>
+      </c>
+      <c r="B210" t="s">
         <v>228</v>
       </c>
-      <c r="B210" t="s">
+      <c r="C210" t="s">
+        <v>34</v>
+      </c>
+      <c r="D210" t="s">
         <v>229</v>
-      </c>
-      <c r="C210" t="s">
-        <v>35</v>
-      </c>
-      <c r="D210" t="s">
-        <v>230</v>
       </c>
       <c r="E210">
         <v>129990</v>
@@ -8625,10 +8615,10 @@
         <v>1</v>
       </c>
       <c r="G210" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H210" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I210">
         <v>0</v>
@@ -8642,16 +8632,16 @@
     </row>
     <row r="211">
       <c r="A211" t="s">
+        <v>227</v>
+      </c>
+      <c r="B211" t="s">
         <v>228</v>
       </c>
-      <c r="B211" t="s">
-        <v>229</v>
-      </c>
       <c r="C211" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D211" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E211">
         <v>129990</v>
@@ -8660,10 +8650,10 @@
         <v>1</v>
       </c>
       <c r="G211" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H211" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I211">
         <v>0</v>
@@ -8677,16 +8667,16 @@
     </row>
     <row r="212">
       <c r="A212" t="s">
+        <v>227</v>
+      </c>
+      <c r="B212" t="s">
         <v>228</v>
       </c>
-      <c r="B212" t="s">
-        <v>229</v>
-      </c>
       <c r="C212" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D212" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E212">
         <v>129990</v>
@@ -8695,10 +8685,10 @@
         <v>1</v>
       </c>
       <c r="G212" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H212" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I212">
         <v>0</v>
@@ -8712,16 +8702,16 @@
     </row>
     <row r="213">
       <c r="A213" t="s">
+        <v>232</v>
+      </c>
+      <c r="B213" t="s">
         <v>233</v>
       </c>
-      <c r="B213" t="s">
-        <v>234</v>
-      </c>
       <c r="C213" t="s">
         <v>18</v>
       </c>
       <c r="D213" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E213">
         <v>125990</v>
@@ -8730,10 +8720,10 @@
         <v>1</v>
       </c>
       <c r="G213" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H213" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I213">
         <v>0</v>
@@ -8747,16 +8737,16 @@
     </row>
     <row r="214">
       <c r="A214" t="s">
+        <v>232</v>
+      </c>
+      <c r="B214" t="s">
         <v>233</v>
       </c>
-      <c r="B214" t="s">
-        <v>234</v>
-      </c>
       <c r="C214" t="s">
         <v>18</v>
       </c>
       <c r="D214" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E214">
         <v>125990</v>
@@ -8765,10 +8755,10 @@
         <v>1</v>
       </c>
       <c r="G214" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H214" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I214">
         <v>0</v>
@@ -8782,10 +8772,10 @@
     </row>
     <row r="215">
       <c r="A215" t="s">
+        <v>232</v>
+      </c>
+      <c r="B215" t="s">
         <v>233</v>
-      </c>
-      <c r="B215" t="s">
-        <v>234</v>
       </c>
       <c r="C215" t="s">
         <v>18</v>
@@ -8800,10 +8790,10 @@
         <v>1</v>
       </c>
       <c r="G215" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H215" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I215">
         <v>0</v>
@@ -8817,16 +8807,16 @@
     </row>
     <row r="216">
       <c r="A216" t="s">
+        <v>234</v>
+      </c>
+      <c r="B216" t="s">
         <v>235</v>
       </c>
-      <c r="B216" t="s">
-        <v>236</v>
-      </c>
       <c r="C216" t="s">
         <v>18</v>
       </c>
       <c r="D216" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E216">
         <v>140990</v>
@@ -8835,10 +8825,10 @@
         <v>1</v>
       </c>
       <c r="G216" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H216" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I216">
         <v>0</v>
@@ -8847,21 +8837,21 @@
         <v>0</v>
       </c>
       <c r="K216" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="s">
+        <v>234</v>
+      </c>
+      <c r="B217" t="s">
         <v>235</v>
       </c>
-      <c r="B217" t="s">
-        <v>236</v>
-      </c>
       <c r="C217" t="s">
         <v>18</v>
       </c>
       <c r="D217" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E217">
         <v>140990</v>
@@ -8870,10 +8860,10 @@
         <v>1</v>
       </c>
       <c r="G217" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H217" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I217">
         <v>0</v>
@@ -8882,15 +8872,15 @@
         <v>0</v>
       </c>
       <c r="K217" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="s">
+        <v>234</v>
+      </c>
+      <c r="B218" t="s">
         <v>235</v>
-      </c>
-      <c r="B218" t="s">
-        <v>236</v>
       </c>
       <c r="C218" t="s">
         <v>18</v>
@@ -8905,10 +8895,10 @@
         <v>1</v>
       </c>
       <c r="G218" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H218" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I218">
         <v>0</v>
@@ -8917,21 +8907,21 @@
         <v>0</v>
       </c>
       <c r="K218" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="s">
+        <v>234</v>
+      </c>
+      <c r="B219" t="s">
         <v>235</v>
       </c>
-      <c r="B219" t="s">
-        <v>236</v>
-      </c>
       <c r="C219" t="s">
         <v>18</v>
       </c>
       <c r="D219" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E219">
         <v>140990</v>
@@ -8940,10 +8930,10 @@
         <v>1</v>
       </c>
       <c r="G219" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H219" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I219">
         <v>0</v>
@@ -8952,21 +8942,21 @@
         <v>0</v>
       </c>
       <c r="K219" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="s">
+        <v>236</v>
+      </c>
+      <c r="B220" t="s">
         <v>237</v>
       </c>
-      <c r="B220" t="s">
-        <v>238</v>
-      </c>
       <c r="C220" t="s">
+        <v>34</v>
+      </c>
+      <c r="D220" t="s">
         <v>35</v>
-      </c>
-      <c r="D220" t="s">
-        <v>36</v>
       </c>
       <c r="E220">
         <v>195990</v>
@@ -8975,10 +8965,10 @@
         <v>1</v>
       </c>
       <c r="G220" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H220" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I220">
         <v>0</v>
@@ -8987,21 +8977,21 @@
         <v>0</v>
       </c>
       <c r="K220" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="s">
+        <v>236</v>
+      </c>
+      <c r="B221" t="s">
         <v>237</v>
       </c>
-      <c r="B221" t="s">
-        <v>238</v>
-      </c>
       <c r="C221" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D221" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E221">
         <v>195990</v>
@@ -9010,10 +9000,10 @@
         <v>1</v>
       </c>
       <c r="G221" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H221" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I221">
         <v>0</v>
@@ -9022,21 +9012,21 @@
         <v>0</v>
       </c>
       <c r="K221" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="s">
+        <v>238</v>
+      </c>
+      <c r="B222" t="s">
         <v>239</v>
       </c>
-      <c r="B222" t="s">
-        <v>240</v>
-      </c>
       <c r="C222" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D222" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E222">
         <v>140900</v>
@@ -9045,10 +9035,10 @@
         <v>1</v>
       </c>
       <c r="G222" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H222" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I222">
         <v>0</v>
@@ -9057,21 +9047,21 @@
         <v>0</v>
       </c>
       <c r="K222" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="s">
+        <v>238</v>
+      </c>
+      <c r="B223" t="s">
         <v>239</v>
       </c>
-      <c r="B223" t="s">
-        <v>240</v>
-      </c>
       <c r="C223" t="s">
+        <v>34</v>
+      </c>
+      <c r="D223" t="s">
         <v>35</v>
-      </c>
-      <c r="D223" t="s">
-        <v>36</v>
       </c>
       <c r="E223">
         <v>130990</v>
@@ -9080,10 +9070,10 @@
         <v>1</v>
       </c>
       <c r="G223" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H223" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I223">
         <v>0</v>
@@ -9092,21 +9082,21 @@
         <v>0</v>
       </c>
       <c r="K223" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="s">
+        <v>238</v>
+      </c>
+      <c r="B224" t="s">
         <v>239</v>
       </c>
-      <c r="B224" t="s">
-        <v>240</v>
-      </c>
       <c r="C224" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D224" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E224">
         <v>130990</v>
@@ -9115,10 +9105,10 @@
         <v>1</v>
       </c>
       <c r="G224" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H224" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I224">
         <v>0</v>
@@ -9127,18 +9117,18 @@
         <v>0</v>
       </c>
       <c r="K224" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="s">
+        <v>238</v>
+      </c>
+      <c r="B225" t="s">
         <v>239</v>
       </c>
-      <c r="B225" t="s">
-        <v>240</v>
-      </c>
       <c r="C225" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D225" t="s">
         <v>19</v>
@@ -9150,10 +9140,10 @@
         <v>1</v>
       </c>
       <c r="G225" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H225" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I225">
         <v>0</v>
@@ -9162,21 +9152,21 @@
         <v>0</v>
       </c>
       <c r="K225" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="s">
+        <v>238</v>
+      </c>
+      <c r="B226" t="s">
         <v>239</v>
       </c>
-      <c r="B226" t="s">
-        <v>240</v>
-      </c>
       <c r="C226" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D226" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E226">
         <v>130990</v>
@@ -9185,10 +9175,10 @@
         <v>1</v>
       </c>
       <c r="G226" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H226" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I226">
         <v>0</v>
@@ -9197,21 +9187,21 @@
         <v>0</v>
       </c>
       <c r="K226" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="s">
+        <v>240</v>
+      </c>
+      <c r="B227" t="s">
         <v>241</v>
       </c>
-      <c r="B227" t="s">
-        <v>242</v>
-      </c>
       <c r="C227" t="s">
+        <v>121</v>
+      </c>
+      <c r="D227" t="s">
         <v>122</v>
-      </c>
-      <c r="D227" t="s">
-        <v>123</v>
       </c>
       <c r="E227">
         <v>149990</v>
@@ -9220,10 +9210,10 @@
         <v>1</v>
       </c>
       <c r="G227" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H227" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I227">
         <v>0</v>
@@ -9237,16 +9227,16 @@
     </row>
     <row r="228">
       <c r="A228" t="s">
+        <v>242</v>
+      </c>
+      <c r="B228" t="s">
         <v>243</v>
       </c>
-      <c r="B228" t="s">
-        <v>244</v>
-      </c>
       <c r="C228" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D228" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E228">
         <v>145990</v>
@@ -9255,10 +9245,10 @@
         <v>1</v>
       </c>
       <c r="G228" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H228" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I228">
         <v>0</v>
@@ -9267,21 +9257,21 @@
         <v>0</v>
       </c>
       <c r="K228" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="s">
+        <v>244</v>
+      </c>
+      <c r="B229" t="s">
         <v>245</v>
       </c>
-      <c r="B229" t="s">
-        <v>246</v>
-      </c>
       <c r="C229" t="s">
+        <v>121</v>
+      </c>
+      <c r="D229" t="s">
         <v>122</v>
-      </c>
-      <c r="D229" t="s">
-        <v>123</v>
       </c>
       <c r="E229">
         <v>279000</v>
@@ -9290,10 +9280,10 @@
         <v>1</v>
       </c>
       <c r="G229" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H229" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I229">
         <v>0</v>
@@ -9302,21 +9292,21 @@
         <v>0</v>
       </c>
       <c r="K229" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="s">
+        <v>246</v>
+      </c>
+      <c r="B230" t="s">
         <v>247</v>
       </c>
-      <c r="B230" t="s">
-        <v>248</v>
-      </c>
       <c r="C230" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D230" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E230">
         <v>169990</v>
@@ -9325,10 +9315,10 @@
         <v>1</v>
       </c>
       <c r="G230" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H230" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I230">
         <v>0</v>
@@ -9337,21 +9327,21 @@
         <v>0</v>
       </c>
       <c r="K230" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="s">
+        <v>246</v>
+      </c>
+      <c r="B231" t="s">
         <v>247</v>
       </c>
-      <c r="B231" t="s">
-        <v>248</v>
-      </c>
       <c r="C231" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D231" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E231">
         <v>169990</v>
@@ -9360,10 +9350,10 @@
         <v>1</v>
       </c>
       <c r="G231" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H231" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I231">
         <v>0</v>
@@ -9372,7 +9362,7 @@
         <v>0</v>
       </c>
       <c r="K231" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/data/catalogo_jusp.xlsx
+++ b/data/catalogo_jusp.xlsx
@@ -1214,7 +1214,7 @@
         <v>21</v>
       </c>
       <c r="L2">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="N2" s="3"/>
       <c r="O2" s="3"/>
@@ -1254,7 +1254,7 @@
         <v>21</v>
       </c>
       <c r="L3">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="N3" s="3"/>
       <c r="O3" s="3"/>

--- a/data/catalogo_jusp.xlsx
+++ b/data/catalogo_jusp.xlsx
@@ -1214,7 +1214,7 @@
         <v>21</v>
       </c>
       <c r="L2">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="N2" s="3"/>
       <c r="O2" s="3"/>
@@ -1254,7 +1254,7 @@
         <v>21</v>
       </c>
       <c r="L3">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="N3" s="3"/>
       <c r="O3" s="3"/>

--- a/data/catalogo_jusp.xlsx
+++ b/data/catalogo_jusp.xlsx
@@ -1214,7 +1214,7 @@
         <v>21</v>
       </c>
       <c r="L2">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="N2" s="3"/>
       <c r="O2" s="3"/>
@@ -1254,7 +1254,7 @@
         <v>21</v>
       </c>
       <c r="L3">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="N3" s="3"/>
       <c r="O3" s="3"/>

--- a/data/catalogo_jusp.xlsx
+++ b/data/catalogo_jusp.xlsx
@@ -1214,7 +1214,7 @@
         <v>21</v>
       </c>
       <c r="L2">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="N2" s="3"/>
       <c r="O2" s="3"/>
@@ -1254,7 +1254,7 @@
         <v>21</v>
       </c>
       <c r="L3">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="N3" s="3"/>
       <c r="O3" s="3"/>
